--- a/artfynd/A 51086-2025 artfynd.xlsx
+++ b/artfynd/A 51086-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129319307</v>
+        <v>129319384</v>
       </c>
       <c r="B2" t="n">
-        <v>91536</v>
+        <v>79041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540962</v>
+        <v>540775</v>
       </c>
       <c r="R2" t="n">
-        <v>7193400</v>
+        <v>7193467</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129319384</v>
+        <v>129319323</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>80182</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540775</v>
+        <v>540719</v>
       </c>
       <c r="R3" t="n">
-        <v>7193467</v>
+        <v>7193483</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129319285</v>
+        <v>129319302</v>
       </c>
       <c r="B4" t="n">
-        <v>91536</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540886</v>
+        <v>540960</v>
       </c>
       <c r="R4" t="n">
-        <v>7193172</v>
+        <v>7193375</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,32 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129319323</v>
+        <v>129319420</v>
       </c>
       <c r="B5" t="n">
-        <v>80180</v>
+        <v>80146</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540719</v>
+        <v>540982</v>
       </c>
       <c r="R5" t="n">
-        <v>7193483</v>
+        <v>7193144</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,32 +1103,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129319302</v>
+        <v>129319386</v>
       </c>
       <c r="B6" t="n">
-        <v>79039</v>
+        <v>95904</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540960</v>
+        <v>540774</v>
       </c>
       <c r="R6" t="n">
-        <v>7193375</v>
+        <v>7193457</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,45 +1210,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129319386</v>
+        <v>129319300</v>
       </c>
       <c r="B7" t="n">
-        <v>95902</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2809</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540774</v>
+        <v>540961</v>
       </c>
       <c r="R7" t="n">
-        <v>7193457</v>
+        <v>7193376</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1280,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1295,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1320,7 +1325,7 @@
         <v>129319414</v>
       </c>
       <c r="B8" t="n">
-        <v>58358</v>
+        <v>58360</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,10 +1438,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129319420</v>
+        <v>129319307</v>
       </c>
       <c r="B9" t="n">
-        <v>80144</v>
+        <v>91538</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1444,21 +1449,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1468,10 +1473,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540982</v>
+        <v>540962</v>
       </c>
       <c r="R9" t="n">
-        <v>7193144</v>
+        <v>7193400</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1503,7 +1508,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1513,7 +1518,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1540,10 +1545,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129319300</v>
+        <v>129319285</v>
       </c>
       <c r="B10" t="n">
-        <v>57725</v>
+        <v>91538</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,39 +1556,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540961</v>
+        <v>540886</v>
       </c>
       <c r="R10" t="n">
-        <v>7193376</v>
+        <v>7193172</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1615,7 +1615,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1652,10 +1652,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129319424</v>
+        <v>129319352</v>
       </c>
       <c r="B11" t="n">
-        <v>80145</v>
+        <v>78054</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1663,21 +1663,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>228579</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540975</v>
+        <v>540715</v>
       </c>
       <c r="R11" t="n">
-        <v>7193139</v>
+        <v>7193537</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1759,10 +1759,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129319430</v>
+        <v>129319419</v>
       </c>
       <c r="B12" t="n">
-        <v>80179</v>
+        <v>80181</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1794,10 +1794,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540971</v>
+        <v>540986</v>
       </c>
       <c r="R12" t="n">
-        <v>7193066</v>
+        <v>7193130</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1829,7 +1829,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1866,10 +1866,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129319438</v>
+        <v>129319328</v>
       </c>
       <c r="B13" t="n">
-        <v>57885</v>
+        <v>80146</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1877,43 +1877,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540982</v>
+        <v>540693</v>
       </c>
       <c r="R13" t="n">
-        <v>7193110</v>
+        <v>7193540</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1945,7 +1936,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1955,7 +1946,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1982,10 +1973,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129319419</v>
+        <v>129319313</v>
       </c>
       <c r="B14" t="n">
-        <v>80179</v>
+        <v>80182</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1993,21 +1984,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2017,10 +2008,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540986</v>
+        <v>540789</v>
       </c>
       <c r="R14" t="n">
-        <v>7193130</v>
+        <v>7193372</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2052,7 +2043,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2062,7 +2053,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2089,10 +2080,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129319328</v>
+        <v>129319296</v>
       </c>
       <c r="B15" t="n">
-        <v>80144</v>
+        <v>79041</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2100,21 +2091,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2124,10 +2115,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540693</v>
+        <v>540970</v>
       </c>
       <c r="R15" t="n">
-        <v>7193540</v>
+        <v>7193365</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2159,7 +2150,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2169,7 +2160,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2196,10 +2187,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129319296</v>
+        <v>129319324</v>
       </c>
       <c r="B16" t="n">
-        <v>79039</v>
+        <v>80146</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2207,21 +2198,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2231,10 +2222,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540970</v>
+        <v>540719</v>
       </c>
       <c r="R16" t="n">
-        <v>7193365</v>
+        <v>7193483</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2266,7 +2257,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2276,7 +2267,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2303,32 +2294,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129319352</v>
+        <v>129319430</v>
       </c>
       <c r="B17" t="n">
-        <v>78052</v>
+        <v>80181</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228579</v>
+        <v>6463</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2338,10 +2329,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540715</v>
+        <v>540971</v>
       </c>
       <c r="R17" t="n">
-        <v>7193537</v>
+        <v>7193066</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2373,7 +2364,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2383,7 +2374,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2410,10 +2401,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129319361</v>
+        <v>129319438</v>
       </c>
       <c r="B18" t="n">
-        <v>91540</v>
+        <v>57887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2421,34 +2412,43 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540726</v>
+        <v>540982</v>
       </c>
       <c r="R18" t="n">
-        <v>7193531</v>
+        <v>7193110</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2480,7 +2480,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2517,32 +2517,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129319313</v>
+        <v>129319361</v>
       </c>
       <c r="B19" t="n">
-        <v>80180</v>
+        <v>91542</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2552,10 +2552,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540789</v>
+        <v>540726</v>
       </c>
       <c r="R19" t="n">
-        <v>7193372</v>
+        <v>7193531</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2624,32 +2624,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129319295</v>
+        <v>129319381</v>
       </c>
       <c r="B20" t="n">
-        <v>95902</v>
+        <v>82873</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2809</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540972</v>
+        <v>540758</v>
       </c>
       <c r="R20" t="n">
-        <v>7193357</v>
+        <v>7193475</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2731,32 +2731,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129319381</v>
+        <v>129319295</v>
       </c>
       <c r="B21" t="n">
-        <v>82871</v>
+        <v>95904</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>2809</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2766,10 +2766,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540758</v>
+        <v>540972</v>
       </c>
       <c r="R21" t="n">
-        <v>7193475</v>
+        <v>7193357</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2838,10 +2838,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129319324</v>
+        <v>129319424</v>
       </c>
       <c r="B22" t="n">
-        <v>80144</v>
+        <v>80147</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2849,21 +2849,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540719</v>
+        <v>540975</v>
       </c>
       <c r="R22" t="n">
-        <v>7193483</v>
+        <v>7193139</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2948,7 +2948,7 @@
         <v>129319390</v>
       </c>
       <c r="B23" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3052,10 +3052,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129319281</v>
+        <v>129319383</v>
       </c>
       <c r="B24" t="n">
-        <v>80145</v>
+        <v>79041</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3063,21 +3063,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3087,10 +3087,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540902</v>
+        <v>540764</v>
       </c>
       <c r="R24" t="n">
-        <v>7193083</v>
+        <v>7193475</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3159,10 +3159,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129319383</v>
+        <v>129319349</v>
       </c>
       <c r="B25" t="n">
-        <v>79039</v>
+        <v>91560</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3170,21 +3170,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3194,10 +3194,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540764</v>
+        <v>540670</v>
       </c>
       <c r="R25" t="n">
-        <v>7193475</v>
+        <v>7193521</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3229,7 +3229,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3239,7 +3239,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3266,10 +3266,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129319316</v>
+        <v>129319354</v>
       </c>
       <c r="B26" t="n">
-        <v>80145</v>
+        <v>79041</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3277,21 +3277,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3301,10 +3301,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540763</v>
+        <v>540722</v>
       </c>
       <c r="R26" t="n">
-        <v>7193372</v>
+        <v>7193542</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3373,10 +3373,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129319291</v>
+        <v>129319281</v>
       </c>
       <c r="B27" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3408,10 +3408,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>540996</v>
+        <v>540902</v>
       </c>
       <c r="R27" t="n">
-        <v>7193327</v>
+        <v>7193083</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3480,10 +3480,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129319340</v>
+        <v>129319316</v>
       </c>
       <c r="B28" t="n">
-        <v>91540</v>
+        <v>80147</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3491,21 +3491,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3515,10 +3515,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>540666</v>
+        <v>540763</v>
       </c>
       <c r="R28" t="n">
-        <v>7193537</v>
+        <v>7193372</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3550,7 +3550,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3587,10 +3587,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129319349</v>
+        <v>129319291</v>
       </c>
       <c r="B29" t="n">
-        <v>91558</v>
+        <v>80147</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3598,21 +3598,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3622,10 +3622,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>540670</v>
+        <v>540996</v>
       </c>
       <c r="R29" t="n">
-        <v>7193521</v>
+        <v>7193327</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3657,7 +3657,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3667,7 +3667,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3694,10 +3694,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129319354</v>
+        <v>129319340</v>
       </c>
       <c r="B30" t="n">
-        <v>79039</v>
+        <v>91542</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3705,21 +3705,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3729,10 +3729,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>540722</v>
+        <v>540666</v>
       </c>
       <c r="R30" t="n">
-        <v>7193542</v>
+        <v>7193537</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3764,7 +3764,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3801,32 +3801,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129319422</v>
+        <v>129319337</v>
       </c>
       <c r="B31" t="n">
-        <v>80179</v>
+        <v>80146</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3836,10 +3836,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>540980</v>
+        <v>540676</v>
       </c>
       <c r="R31" t="n">
-        <v>7193139</v>
+        <v>7193539</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3871,7 +3871,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3908,27 +3908,27 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129319427</v>
+        <v>129319422</v>
       </c>
       <c r="B32" t="n">
-        <v>79039</v>
+        <v>80181</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3943,10 +3943,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>540969</v>
+        <v>540980</v>
       </c>
       <c r="R32" t="n">
-        <v>7193117</v>
+        <v>7193139</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4015,10 +4015,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129319337</v>
+        <v>129319396</v>
       </c>
       <c r="B33" t="n">
-        <v>80144</v>
+        <v>79041</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4026,21 +4026,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4050,10 +4050,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>540676</v>
+        <v>540928</v>
       </c>
       <c r="R33" t="n">
-        <v>7193539</v>
+        <v>7193263</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4085,7 +4085,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4122,10 +4122,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129319396</v>
+        <v>129319427</v>
       </c>
       <c r="B34" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4157,10 +4157,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>540928</v>
+        <v>540969</v>
       </c>
       <c r="R34" t="n">
-        <v>7193263</v>
+        <v>7193117</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4232,7 +4232,7 @@
         <v>129319282</v>
       </c>
       <c r="B35" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4336,10 +4336,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129319404</v>
+        <v>129319405</v>
       </c>
       <c r="B36" t="n">
-        <v>78052</v>
+        <v>83007</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4347,21 +4347,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4443,10 +4443,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129319374</v>
+        <v>129319404</v>
       </c>
       <c r="B37" t="n">
-        <v>80145</v>
+        <v>78054</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4454,21 +4454,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2081</v>
+        <v>228579</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4478,10 +4478,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>540734</v>
+        <v>540931</v>
       </c>
       <c r="R37" t="n">
-        <v>7193499</v>
+        <v>7193220</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4513,7 +4513,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4523,7 +4523,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4550,10 +4550,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129319405</v>
+        <v>129319374</v>
       </c>
       <c r="B38" t="n">
-        <v>83005</v>
+        <v>80147</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4561,21 +4561,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4585,10 +4585,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>540931</v>
+        <v>540734</v>
       </c>
       <c r="R38" t="n">
-        <v>7193220</v>
+        <v>7193499</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4620,7 +4620,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4630,7 +4630,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4660,7 +4660,7 @@
         <v>129319377</v>
       </c>
       <c r="B39" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4764,10 +4764,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129319403</v>
+        <v>129319303</v>
       </c>
       <c r="B40" t="n">
-        <v>80144</v>
+        <v>79041</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4775,21 +4775,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4799,10 +4799,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>540930</v>
+        <v>540934</v>
       </c>
       <c r="R40" t="n">
-        <v>7193219</v>
+        <v>7193385</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4871,10 +4871,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129319294</v>
+        <v>129319348</v>
       </c>
       <c r="B41" t="n">
-        <v>83010</v>
+        <v>80146</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4882,21 +4882,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1467</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4906,10 +4906,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>540974</v>
+        <v>540653</v>
       </c>
       <c r="R41" t="n">
-        <v>7193351</v>
+        <v>7193521</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4941,7 +4941,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4951,7 +4951,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4978,10 +4978,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129319303</v>
+        <v>129319288</v>
       </c>
       <c r="B42" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5013,10 +5013,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>540934</v>
+        <v>540915</v>
       </c>
       <c r="R42" t="n">
-        <v>7193385</v>
+        <v>7193185</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5048,7 +5048,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5085,32 +5085,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129319348</v>
+        <v>129319401</v>
       </c>
       <c r="B43" t="n">
-        <v>80144</v>
+        <v>80175</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5120,10 +5120,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540653</v>
+        <v>540942</v>
       </c>
       <c r="R43" t="n">
-        <v>7193521</v>
+        <v>7193229</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5155,7 +5155,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5192,10 +5192,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129319288</v>
+        <v>129319403</v>
       </c>
       <c r="B44" t="n">
-        <v>79039</v>
+        <v>80146</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5203,21 +5203,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5227,10 +5227,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540915</v>
+        <v>540930</v>
       </c>
       <c r="R44" t="n">
-        <v>7193185</v>
+        <v>7193219</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5262,7 +5262,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5272,7 +5272,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5299,32 +5299,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129319278</v>
+        <v>129319320</v>
       </c>
       <c r="B45" t="n">
-        <v>80145</v>
+        <v>80181</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5334,10 +5334,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>540864</v>
+        <v>540719</v>
       </c>
       <c r="R45" t="n">
-        <v>7193066</v>
+        <v>7193463</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5369,7 +5369,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5379,7 +5379,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5406,32 +5406,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129319401</v>
+        <v>129319278</v>
       </c>
       <c r="B46" t="n">
-        <v>80173</v>
+        <v>80147</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5441,10 +5441,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>540942</v>
+        <v>540864</v>
       </c>
       <c r="R46" t="n">
-        <v>7193229</v>
+        <v>7193066</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5476,7 +5476,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5516,7 +5516,7 @@
         <v>129319365</v>
       </c>
       <c r="B47" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5620,32 +5620,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129319320</v>
+        <v>129319294</v>
       </c>
       <c r="B48" t="n">
-        <v>80179</v>
+        <v>83012</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6463</v>
+        <v>1467</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5655,10 +5655,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>540719</v>
+        <v>540974</v>
       </c>
       <c r="R48" t="n">
-        <v>7193463</v>
+        <v>7193351</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5690,7 +5690,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5700,7 +5700,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5730,7 +5730,7 @@
         <v>129319395</v>
       </c>
       <c r="B49" t="n">
-        <v>82990</v>
+        <v>82992</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>129319366</v>
       </c>
       <c r="B50" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5941,32 +5941,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129319280</v>
+        <v>129319356</v>
       </c>
       <c r="B51" t="n">
-        <v>95902</v>
+        <v>80146</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2809</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5976,10 +5976,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>540900</v>
+        <v>540726</v>
       </c>
       <c r="R51" t="n">
-        <v>7193073</v>
+        <v>7193540</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6011,7 +6011,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6021,7 +6021,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6048,32 +6048,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129319356</v>
+        <v>129319280</v>
       </c>
       <c r="B52" t="n">
-        <v>80144</v>
+        <v>95904</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>2809</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6083,10 +6083,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>540726</v>
+        <v>540900</v>
       </c>
       <c r="R52" t="n">
-        <v>7193540</v>
+        <v>7193073</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6118,7 +6118,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6158,7 +6158,7 @@
         <v>129319335</v>
       </c>
       <c r="B53" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6262,10 +6262,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129319388</v>
+        <v>129319429</v>
       </c>
       <c r="B54" t="n">
-        <v>57725</v>
+        <v>80147</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6273,48 +6273,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>540828</v>
+        <v>540972</v>
       </c>
       <c r="R54" t="n">
-        <v>7193425</v>
+        <v>7193067</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6346,7 +6332,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6356,7 +6342,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6386,7 +6372,7 @@
         <v>129319417</v>
       </c>
       <c r="B55" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6490,10 +6476,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129319304</v>
+        <v>129319388</v>
       </c>
       <c r="B56" t="n">
-        <v>79039</v>
+        <v>57727</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6501,34 +6487,48 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>540962</v>
+        <v>540828</v>
       </c>
       <c r="R56" t="n">
-        <v>7193388</v>
+        <v>7193425</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6560,7 +6560,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6597,10 +6597,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129319429</v>
+        <v>129319304</v>
       </c>
       <c r="B57" t="n">
-        <v>80145</v>
+        <v>79041</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6608,21 +6608,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6632,10 +6632,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>540972</v>
+        <v>540962</v>
       </c>
       <c r="R57" t="n">
-        <v>7193067</v>
+        <v>7193388</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6667,7 +6667,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6707,7 +6707,7 @@
         <v>129319330</v>
       </c>
       <c r="B58" t="n">
-        <v>82988</v>
+        <v>82990</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6811,10 +6811,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129319311</v>
+        <v>129319372</v>
       </c>
       <c r="B59" t="n">
-        <v>91536</v>
+        <v>80146</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6822,21 +6822,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6846,10 +6846,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>540830</v>
+        <v>540736</v>
       </c>
       <c r="R59" t="n">
-        <v>7193366</v>
+        <v>7193500</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6881,7 +6881,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6918,54 +6918,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129319423</v>
+        <v>129319292</v>
       </c>
       <c r="B60" t="n">
-        <v>57829</v>
+        <v>79041</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>540976</v>
+        <v>540996</v>
       </c>
       <c r="R60" t="n">
-        <v>7193139</v>
+        <v>7193327</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6997,7 +6988,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7007,7 +6998,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7034,10 +7025,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129319353</v>
+        <v>129319392</v>
       </c>
       <c r="B61" t="n">
-        <v>82871</v>
+        <v>79041</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7045,21 +7036,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7069,10 +7060,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>540721</v>
+        <v>540826</v>
       </c>
       <c r="R61" t="n">
-        <v>7193542</v>
+        <v>7193294</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7104,7 +7095,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7114,7 +7105,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7141,45 +7132,54 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129319279</v>
+        <v>129319423</v>
       </c>
       <c r="B62" t="n">
-        <v>80145</v>
+        <v>57831</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2081</v>
+        <v>103031</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>540872</v>
+        <v>540976</v>
       </c>
       <c r="R62" t="n">
-        <v>7193070</v>
+        <v>7193139</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7211,7 +7211,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7248,10 +7248,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129319372</v>
+        <v>129319353</v>
       </c>
       <c r="B63" t="n">
-        <v>80144</v>
+        <v>82873</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7259,21 +7259,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7283,10 +7283,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>540736</v>
+        <v>540721</v>
       </c>
       <c r="R63" t="n">
-        <v>7193500</v>
+        <v>7193542</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7318,7 +7318,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7328,7 +7328,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7355,10 +7355,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129319292</v>
+        <v>129319311</v>
       </c>
       <c r="B64" t="n">
-        <v>79039</v>
+        <v>91538</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7366,21 +7366,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7390,10 +7390,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>540996</v>
+        <v>540830</v>
       </c>
       <c r="R64" t="n">
-        <v>7193327</v>
+        <v>7193366</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7425,7 +7425,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7435,7 +7435,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7462,10 +7462,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129319392</v>
+        <v>129319279</v>
       </c>
       <c r="B65" t="n">
-        <v>79039</v>
+        <v>80147</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7473,21 +7473,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7497,10 +7497,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>540826</v>
+        <v>540872</v>
       </c>
       <c r="R65" t="n">
-        <v>7193294</v>
+        <v>7193070</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7532,7 +7532,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7572,7 +7572,7 @@
         <v>129319339</v>
       </c>
       <c r="B66" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7676,10 +7676,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129319334</v>
+        <v>129319397</v>
       </c>
       <c r="B67" t="n">
-        <v>80144</v>
+        <v>79041</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7687,21 +7687,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7711,10 +7711,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>540674</v>
+        <v>540946</v>
       </c>
       <c r="R67" t="n">
-        <v>7193550</v>
+        <v>7193256</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7746,7 +7746,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7756,7 +7756,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7783,32 +7783,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129319400</v>
+        <v>129319421</v>
       </c>
       <c r="B68" t="n">
-        <v>79039</v>
+        <v>80175</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7818,10 +7818,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>540943</v>
+        <v>540981</v>
       </c>
       <c r="R68" t="n">
-        <v>7193233</v>
+        <v>7193140</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7890,32 +7890,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129319370</v>
+        <v>129319334</v>
       </c>
       <c r="B69" t="n">
-        <v>80173</v>
+        <v>80146</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7925,10 +7925,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>540737</v>
+        <v>540674</v>
       </c>
       <c r="R69" t="n">
-        <v>7193504</v>
+        <v>7193550</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7960,7 +7960,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7997,10 +7997,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129319293</v>
+        <v>129319400</v>
       </c>
       <c r="B70" t="n">
-        <v>57885</v>
+        <v>79041</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8008,43 +8008,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>540980</v>
+        <v>540943</v>
       </c>
       <c r="R70" t="n">
-        <v>7193345</v>
+        <v>7193233</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8076,7 +8067,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8086,7 +8077,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8113,32 +8104,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129319397</v>
+        <v>129319370</v>
       </c>
       <c r="B71" t="n">
-        <v>79039</v>
+        <v>80175</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8148,10 +8139,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>540946</v>
+        <v>540737</v>
       </c>
       <c r="R71" t="n">
-        <v>7193256</v>
+        <v>7193504</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8183,7 +8174,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8193,7 +8184,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8220,45 +8211,54 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129319421</v>
+        <v>129319293</v>
       </c>
       <c r="B72" t="n">
-        <v>80173</v>
+        <v>57887</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>540981</v>
+        <v>540980</v>
       </c>
       <c r="R72" t="n">
-        <v>7193140</v>
+        <v>7193345</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8290,7 +8290,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8300,7 +8300,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8327,10 +8327,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129319412</v>
+        <v>129319402</v>
       </c>
       <c r="B73" t="n">
-        <v>91558</v>
+        <v>79041</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8338,21 +8338,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8362,10 +8362,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>540952</v>
+        <v>540936</v>
       </c>
       <c r="R73" t="n">
-        <v>7193187</v>
+        <v>7193225</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8397,7 +8397,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8407,7 +8407,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8434,32 +8434,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129319367</v>
+        <v>129319412</v>
       </c>
       <c r="B74" t="n">
-        <v>80173</v>
+        <v>91560</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8469,10 +8469,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>540734</v>
+        <v>540952</v>
       </c>
       <c r="R74" t="n">
-        <v>7193503</v>
+        <v>7193187</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8504,7 +8504,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8514,7 +8514,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8541,54 +8541,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129319432</v>
+        <v>129319413</v>
       </c>
       <c r="B75" t="n">
-        <v>58358</v>
+        <v>79041</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>102125</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>540978</v>
+        <v>540965</v>
       </c>
       <c r="R75" t="n">
-        <v>7193078</v>
+        <v>7193181</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8620,7 +8611,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8630,7 +8621,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8657,32 +8648,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129319402</v>
+        <v>129319367</v>
       </c>
       <c r="B76" t="n">
-        <v>79039</v>
+        <v>80175</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8692,10 +8683,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>540936</v>
+        <v>540734</v>
       </c>
       <c r="R76" t="n">
-        <v>7193225</v>
+        <v>7193503</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8727,7 +8718,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8737,7 +8728,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8764,45 +8755,54 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129319413</v>
+        <v>129319432</v>
       </c>
       <c r="B77" t="n">
-        <v>79039</v>
+        <v>58360</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>102125</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>540965</v>
+        <v>540978</v>
       </c>
       <c r="R77" t="n">
-        <v>7193181</v>
+        <v>7193078</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8844,7 +8844,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8871,10 +8871,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129319342</v>
+        <v>129319371</v>
       </c>
       <c r="B78" t="n">
-        <v>57722</v>
+        <v>80146</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8882,39 +8882,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>540667</v>
+        <v>540737</v>
       </c>
       <c r="R78" t="n">
-        <v>7193539</v>
+        <v>7193504</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8946,7 +8941,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8956,7 +8951,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8983,10 +8978,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129319371</v>
+        <v>129319342</v>
       </c>
       <c r="B79" t="n">
-        <v>80144</v>
+        <v>57724</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8994,34 +8989,39 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>540737</v>
+        <v>540667</v>
       </c>
       <c r="R79" t="n">
-        <v>7193504</v>
+        <v>7193539</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9053,7 +9053,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9063,7 +9063,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9090,32 +9090,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129319431</v>
+        <v>129319336</v>
       </c>
       <c r="B80" t="n">
-        <v>80173</v>
+        <v>79041</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9125,10 +9125,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>540979</v>
+        <v>540668</v>
       </c>
       <c r="R80" t="n">
-        <v>7193075</v>
+        <v>7193543</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9160,7 +9160,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9170,7 +9170,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9197,10 +9197,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129319338</v>
+        <v>129319382</v>
       </c>
       <c r="B81" t="n">
-        <v>80145</v>
+        <v>79041</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9208,21 +9208,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9232,10 +9232,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>540676</v>
+        <v>540761</v>
       </c>
       <c r="R81" t="n">
-        <v>7193539</v>
+        <v>7193473</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9267,7 +9267,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9304,10 +9304,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129319336</v>
+        <v>129319408</v>
       </c>
       <c r="B82" t="n">
-        <v>79039</v>
+        <v>80146</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9315,21 +9315,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9339,10 +9339,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>540668</v>
+        <v>540939</v>
       </c>
       <c r="R82" t="n">
-        <v>7193543</v>
+        <v>7193177</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9374,7 +9374,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9384,7 +9384,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9411,32 +9411,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129319382</v>
+        <v>129319431</v>
       </c>
       <c r="B83" t="n">
-        <v>79039</v>
+        <v>80175</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9446,10 +9446,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>540761</v>
+        <v>540979</v>
       </c>
       <c r="R83" t="n">
-        <v>7193473</v>
+        <v>7193075</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9481,7 +9481,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9518,10 +9518,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129319408</v>
+        <v>129319394</v>
       </c>
       <c r="B84" t="n">
-        <v>80144</v>
+        <v>79041</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9529,21 +9529,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9553,10 +9553,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>540939</v>
+        <v>540877</v>
       </c>
       <c r="R84" t="n">
-        <v>7193177</v>
+        <v>7193291</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9588,7 +9588,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9625,10 +9625,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129319394</v>
+        <v>129319338</v>
       </c>
       <c r="B85" t="n">
-        <v>79039</v>
+        <v>80147</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9636,21 +9636,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9660,10 +9660,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>540877</v>
+        <v>540676</v>
       </c>
       <c r="R85" t="n">
-        <v>7193291</v>
+        <v>7193539</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9695,7 +9695,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9705,7 +9705,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9735,7 +9735,7 @@
         <v>129319284</v>
       </c>
       <c r="B86" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9839,32 +9839,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129319389</v>
+        <v>129319409</v>
       </c>
       <c r="B87" t="n">
-        <v>95902</v>
+        <v>80146</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2809</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9874,10 +9874,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>540818</v>
+        <v>540942</v>
       </c>
       <c r="R87" t="n">
-        <v>7193358</v>
+        <v>7193182</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -9909,7 +9909,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9919,7 +9919,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9946,10 +9946,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129319333</v>
+        <v>129319298</v>
       </c>
       <c r="B88" t="n">
-        <v>80145</v>
+        <v>91560</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9957,21 +9957,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9981,10 +9981,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>540674</v>
+        <v>540964</v>
       </c>
       <c r="R88" t="n">
-        <v>7193551</v>
+        <v>7193371</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -10016,7 +10016,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10026,7 +10026,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10053,32 +10053,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129319376</v>
+        <v>129319393</v>
       </c>
       <c r="B89" t="n">
-        <v>80145</v>
+        <v>82990</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2081</v>
+        <v>6439</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10088,10 +10088,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>540738</v>
+        <v>540824</v>
       </c>
       <c r="R89" t="n">
-        <v>7193476</v>
+        <v>7193288</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -10123,7 +10123,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10133,7 +10133,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10160,10 +10160,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129319409</v>
+        <v>129319299</v>
       </c>
       <c r="B90" t="n">
-        <v>80144</v>
+        <v>79041</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10171,21 +10171,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10195,10 +10195,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>540942</v>
+        <v>540964</v>
       </c>
       <c r="R90" t="n">
-        <v>7193182</v>
+        <v>7193371</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -10230,7 +10230,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10240,7 +10240,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10267,10 +10267,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129319375</v>
+        <v>129319344</v>
       </c>
       <c r="B91" t="n">
-        <v>80145</v>
+        <v>79041</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10278,21 +10278,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10302,10 +10302,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>540730</v>
+        <v>540650</v>
       </c>
       <c r="R91" t="n">
-        <v>7193493</v>
+        <v>7193540</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -10337,7 +10337,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10347,7 +10347,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10374,32 +10374,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129319298</v>
+        <v>129319389</v>
       </c>
       <c r="B92" t="n">
-        <v>91558</v>
+        <v>95904</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5432</v>
+        <v>2809</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10409,10 +10409,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>540964</v>
+        <v>540818</v>
       </c>
       <c r="R92" t="n">
-        <v>7193371</v>
+        <v>7193358</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -10444,7 +10444,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10454,7 +10454,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10481,32 +10481,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129319393</v>
+        <v>129319333</v>
       </c>
       <c r="B93" t="n">
-        <v>82988</v>
+        <v>80147</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6439</v>
+        <v>2081</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10516,10 +10516,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>540824</v>
+        <v>540674</v>
       </c>
       <c r="R93" t="n">
-        <v>7193288</v>
+        <v>7193551</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -10551,7 +10551,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10561,7 +10561,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10588,10 +10588,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129319299</v>
+        <v>129319376</v>
       </c>
       <c r="B94" t="n">
-        <v>79039</v>
+        <v>80147</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10599,21 +10599,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10623,10 +10623,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>540964</v>
+        <v>540738</v>
       </c>
       <c r="R94" t="n">
-        <v>7193371</v>
+        <v>7193476</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -10658,7 +10658,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10668,7 +10668,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10695,10 +10695,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129319344</v>
+        <v>129319375</v>
       </c>
       <c r="B95" t="n">
-        <v>79039</v>
+        <v>80147</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10706,21 +10706,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10730,10 +10730,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>540650</v>
+        <v>540730</v>
       </c>
       <c r="R95" t="n">
-        <v>7193540</v>
+        <v>7193493</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -10765,7 +10765,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10775,7 +10775,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10802,10 +10802,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129319357</v>
+        <v>129319433</v>
       </c>
       <c r="B96" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10837,10 +10837,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>540726</v>
+        <v>540979</v>
       </c>
       <c r="R96" t="n">
-        <v>7193539</v>
+        <v>7193075</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -10872,7 +10872,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10882,7 +10882,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10909,10 +10909,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129319433</v>
+        <v>129319357</v>
       </c>
       <c r="B97" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10944,10 +10944,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>540979</v>
+        <v>540726</v>
       </c>
       <c r="R97" t="n">
-        <v>7193075</v>
+        <v>7193539</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -10979,7 +10979,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10989,7 +10989,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11016,10 +11016,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129319445</v>
+        <v>129319399</v>
       </c>
       <c r="B98" t="n">
-        <v>57722</v>
+        <v>79041</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11027,43 +11027,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>541052</v>
+        <v>540945</v>
       </c>
       <c r="R98" t="n">
-        <v>7193255</v>
+        <v>7193248</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -11095,7 +11086,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11105,7 +11096,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11135,7 +11126,7 @@
         <v>129319308</v>
       </c>
       <c r="B99" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11242,7 +11233,7 @@
         <v>129319362</v>
       </c>
       <c r="B100" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11349,7 +11340,7 @@
         <v>129319306</v>
       </c>
       <c r="B101" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11456,7 +11447,7 @@
         <v>129319286</v>
       </c>
       <c r="B102" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11563,7 +11554,7 @@
         <v>129319359</v>
       </c>
       <c r="B103" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11667,10 +11658,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129319399</v>
+        <v>129319445</v>
       </c>
       <c r="B104" t="n">
-        <v>79039</v>
+        <v>57724</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11678,34 +11669,43 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>540945</v>
+        <v>541052</v>
       </c>
       <c r="R104" t="n">
-        <v>7193248</v>
+        <v>7193255</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -11737,7 +11737,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11747,7 +11747,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11777,7 +11777,7 @@
         <v>129319368</v>
       </c>
       <c r="B105" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11884,7 +11884,7 @@
         <v>129319411</v>
       </c>
       <c r="B106" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11991,7 +11991,7 @@
         <v>129319418</v>
       </c>
       <c r="B107" t="n">
-        <v>80180</v>
+        <v>80182</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12095,10 +12095,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129319355</v>
+        <v>129319407</v>
       </c>
       <c r="B108" t="n">
-        <v>80145</v>
+        <v>79041</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12106,21 +12106,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12130,10 +12130,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>540726</v>
+        <v>540924</v>
       </c>
       <c r="R108" t="n">
-        <v>7193541</v>
+        <v>7193211</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -12165,7 +12165,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12175,7 +12175,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12202,10 +12202,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129319360</v>
+        <v>129319355</v>
       </c>
       <c r="B109" t="n">
-        <v>91536</v>
+        <v>80147</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12213,21 +12213,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12237,10 +12237,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>540725</v>
+        <v>540726</v>
       </c>
       <c r="R109" t="n">
-        <v>7193532</v>
+        <v>7193541</v>
       </c>
       <c r="S109" t="n">
         <v>25</v>
@@ -12272,7 +12272,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12282,7 +12282,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12312,7 +12312,7 @@
         <v>129319369</v>
       </c>
       <c r="B110" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12419,7 +12419,7 @@
         <v>129319391</v>
       </c>
       <c r="B111" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12523,10 +12523,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129319407</v>
+        <v>129319360</v>
       </c>
       <c r="B112" t="n">
-        <v>79039</v>
+        <v>91538</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12534,21 +12534,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12558,10 +12558,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>540924</v>
+        <v>540725</v>
       </c>
       <c r="R112" t="n">
-        <v>7193211</v>
+        <v>7193532</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>
@@ -12593,7 +12593,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12603,7 +12603,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12630,32 +12630,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129319425</v>
+        <v>129319426</v>
       </c>
       <c r="B113" t="n">
-        <v>80179</v>
+        <v>80147</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12665,10 +12665,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>540980</v>
+        <v>540979</v>
       </c>
       <c r="R113" t="n">
-        <v>7193116</v>
+        <v>7193115</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -12737,32 +12737,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129319426</v>
+        <v>129319425</v>
       </c>
       <c r="B114" t="n">
-        <v>80145</v>
+        <v>80181</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12772,10 +12772,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>540979</v>
+        <v>540980</v>
       </c>
       <c r="R114" t="n">
-        <v>7193115</v>
+        <v>7193116</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -12844,10 +12844,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129319332</v>
+        <v>129319305</v>
       </c>
       <c r="B115" t="n">
-        <v>57885</v>
+        <v>91560</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12855,43 +12855,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>540675</v>
+        <v>540959</v>
       </c>
       <c r="R115" t="n">
-        <v>7193538</v>
+        <v>7193395</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -12923,7 +12914,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12933,7 +12924,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12960,10 +12951,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129319305</v>
+        <v>129319309</v>
       </c>
       <c r="B116" t="n">
-        <v>91558</v>
+        <v>79041</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12971,21 +12962,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12995,10 +12986,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>540959</v>
+        <v>540894</v>
       </c>
       <c r="R116" t="n">
-        <v>7193395</v>
+        <v>7193411</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -13030,7 +13021,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13040,7 +13031,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13067,10 +13058,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129319341</v>
+        <v>129319332</v>
       </c>
       <c r="B117" t="n">
-        <v>91536</v>
+        <v>57887</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13078,34 +13069,43 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>540670</v>
+        <v>540675</v>
       </c>
       <c r="R117" t="n">
-        <v>7193533</v>
+        <v>7193538</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -13137,7 +13137,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13147,7 +13147,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13174,10 +13174,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129319309</v>
+        <v>129319341</v>
       </c>
       <c r="B118" t="n">
-        <v>79039</v>
+        <v>91538</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13185,21 +13185,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13209,10 +13209,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>540894</v>
+        <v>540670</v>
       </c>
       <c r="R118" t="n">
-        <v>7193411</v>
+        <v>7193533</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -13244,7 +13244,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13254,7 +13254,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13281,54 +13281,45 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129319363</v>
+        <v>129319416</v>
       </c>
       <c r="B119" t="n">
-        <v>58358</v>
+        <v>80182</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>102125</v>
+        <v>6464</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>540731</v>
+        <v>540970</v>
       </c>
       <c r="R119" t="n">
-        <v>7193512</v>
+        <v>7193154</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -13360,7 +13351,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13370,7 +13361,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13397,10 +13388,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129319416</v>
+        <v>129319373</v>
       </c>
       <c r="B120" t="n">
-        <v>80180</v>
+        <v>80182</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13432,10 +13423,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>540970</v>
+        <v>540734</v>
       </c>
       <c r="R120" t="n">
-        <v>7193154</v>
+        <v>7193499</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -13467,7 +13458,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13477,7 +13468,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13504,10 +13495,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129319373</v>
+        <v>129319321</v>
       </c>
       <c r="B121" t="n">
-        <v>80180</v>
+        <v>80175</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13515,21 +13506,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13539,10 +13530,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>540734</v>
+        <v>540719</v>
       </c>
       <c r="R121" t="n">
-        <v>7193499</v>
+        <v>7193463</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -13574,7 +13565,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13584,7 +13575,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13614,7 +13605,7 @@
         <v>129319277</v>
       </c>
       <c r="B122" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13718,10 +13709,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129319410</v>
+        <v>129319325</v>
       </c>
       <c r="B123" t="n">
-        <v>56906</v>
+        <v>80147</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13729,43 +13720,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>102612</v>
+        <v>2081</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>540946</v>
+        <v>540714</v>
       </c>
       <c r="R123" t="n">
-        <v>7193171</v>
+        <v>7193488</v>
       </c>
       <c r="S123" t="n">
         <v>25</v>
@@ -13797,7 +13779,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13807,7 +13789,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13834,10 +13816,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129319325</v>
+        <v>129319319</v>
       </c>
       <c r="B124" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13869,10 +13851,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>540714</v>
+        <v>540719</v>
       </c>
       <c r="R124" t="n">
-        <v>7193488</v>
+        <v>7193463</v>
       </c>
       <c r="S124" t="n">
         <v>25</v>
@@ -13904,7 +13886,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13914,7 +13896,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13941,45 +13923,54 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129319321</v>
+        <v>129319363</v>
       </c>
       <c r="B125" t="n">
-        <v>80173</v>
+        <v>58360</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6462</v>
+        <v>102125</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>540719</v>
+        <v>540731</v>
       </c>
       <c r="R125" t="n">
-        <v>7193463</v>
+        <v>7193512</v>
       </c>
       <c r="S125" t="n">
         <v>25</v>
@@ -14011,7 +14002,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14021,7 +14012,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14048,10 +14039,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129319329</v>
+        <v>129319410</v>
       </c>
       <c r="B126" t="n">
-        <v>88937</v>
+        <v>56908</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14059,34 +14050,43 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>510</v>
+        <v>102612</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>540692</v>
+        <v>540946</v>
       </c>
       <c r="R126" t="n">
-        <v>7193539</v>
+        <v>7193171</v>
       </c>
       <c r="S126" t="n">
         <v>25</v>
@@ -14118,7 +14118,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14128,7 +14128,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14155,10 +14155,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129319319</v>
+        <v>129319350</v>
       </c>
       <c r="B127" t="n">
-        <v>80145</v>
+        <v>80146</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14166,21 +14166,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14190,10 +14190,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>540719</v>
+        <v>540681</v>
       </c>
       <c r="R127" t="n">
-        <v>7193463</v>
+        <v>7193521</v>
       </c>
       <c r="S127" t="n">
         <v>25</v>
@@ -14225,7 +14225,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14235,7 +14235,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14262,10 +14262,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129319350</v>
+        <v>129319329</v>
       </c>
       <c r="B128" t="n">
-        <v>80144</v>
+        <v>88939</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14273,21 +14273,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14297,10 +14297,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>540681</v>
+        <v>540692</v>
       </c>
       <c r="R128" t="n">
-        <v>7193521</v>
+        <v>7193539</v>
       </c>
       <c r="S128" t="n">
         <v>25</v>
@@ -14332,7 +14332,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14342,7 +14342,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14369,10 +14369,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129319434</v>
+        <v>129319326</v>
       </c>
       <c r="B129" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14404,10 +14404,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>540979</v>
+        <v>540701</v>
       </c>
       <c r="R129" t="n">
-        <v>7193075</v>
+        <v>7193533</v>
       </c>
       <c r="S129" t="n">
         <v>25</v>
@@ -14439,7 +14439,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14449,7 +14449,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14476,10 +14476,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129319326</v>
+        <v>129319379</v>
       </c>
       <c r="B130" t="n">
-        <v>80144</v>
+        <v>79041</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14487,21 +14487,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14511,10 +14511,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>540701</v>
+        <v>540761</v>
       </c>
       <c r="R130" t="n">
-        <v>7193533</v>
+        <v>7193485</v>
       </c>
       <c r="S130" t="n">
         <v>25</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14556,7 +14556,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14583,10 +14583,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129319379</v>
+        <v>129319434</v>
       </c>
       <c r="B131" t="n">
-        <v>79039</v>
+        <v>80146</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14594,21 +14594,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14618,10 +14618,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>540761</v>
+        <v>540979</v>
       </c>
       <c r="R131" t="n">
-        <v>7193485</v>
+        <v>7193075</v>
       </c>
       <c r="S131" t="n">
         <v>25</v>
@@ -14653,7 +14653,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14663,7 +14663,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14690,10 +14690,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129319343</v>
+        <v>129319310</v>
       </c>
       <c r="B132" t="n">
-        <v>57725</v>
+        <v>79041</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14701,39 +14701,34 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>540661</v>
+        <v>540830</v>
       </c>
       <c r="R132" t="n">
-        <v>7193538</v>
+        <v>7193366</v>
       </c>
       <c r="S132" t="n">
         <v>25</v>
@@ -14765,7 +14760,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14775,12 +14770,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>11:27</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>Färska och äldre spår på samma träd.</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14807,45 +14797,50 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129319380</v>
+        <v>129319343</v>
       </c>
       <c r="B133" t="n">
-        <v>92240</v>
+        <v>57727</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>540761</v>
+        <v>540661</v>
       </c>
       <c r="R133" t="n">
-        <v>7193490</v>
+        <v>7193538</v>
       </c>
       <c r="S133" t="n">
         <v>25</v>
@@ -14877,7 +14872,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14887,7 +14882,12 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Färska och äldre spår på samma träd.</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14914,32 +14914,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129319322</v>
+        <v>129319378</v>
       </c>
       <c r="B134" t="n">
-        <v>80145</v>
+        <v>82992</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>2081</v>
+        <v>306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14949,10 +14949,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>540719</v>
+        <v>540757</v>
       </c>
       <c r="R134" t="n">
-        <v>7193483</v>
+        <v>7193474</v>
       </c>
       <c r="S134" t="n">
         <v>25</v>
@@ -14984,7 +14984,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15021,32 +15021,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129319312</v>
+        <v>129319380</v>
       </c>
       <c r="B135" t="n">
-        <v>80145</v>
+        <v>92242</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>2081</v>
+        <v>3298</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15056,10 +15056,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>540789</v>
+        <v>540761</v>
       </c>
       <c r="R135" t="n">
-        <v>7193373</v>
+        <v>7193490</v>
       </c>
       <c r="S135" t="n">
         <v>25</v>
@@ -15091,7 +15091,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15101,7 +15101,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15128,10 +15128,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129319310</v>
+        <v>129319322</v>
       </c>
       <c r="B136" t="n">
-        <v>79039</v>
+        <v>80147</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15139,21 +15139,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15163,10 +15163,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>540830</v>
+        <v>540719</v>
       </c>
       <c r="R136" t="n">
-        <v>7193366</v>
+        <v>7193483</v>
       </c>
       <c r="S136" t="n">
         <v>25</v>
@@ -15198,7 +15198,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15208,7 +15208,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15235,32 +15235,32 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129319378</v>
+        <v>129319312</v>
       </c>
       <c r="B137" t="n">
-        <v>82990</v>
+        <v>80147</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>306</v>
+        <v>2081</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15270,10 +15270,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>540757</v>
+        <v>540789</v>
       </c>
       <c r="R137" t="n">
-        <v>7193474</v>
+        <v>7193373</v>
       </c>
       <c r="S137" t="n">
         <v>25</v>
@@ -15305,7 +15305,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15315,7 +15315,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15342,10 +15342,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129319428</v>
+        <v>129319387</v>
       </c>
       <c r="B138" t="n">
-        <v>80144</v>
+        <v>82999</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15353,21 +15353,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15377,10 +15377,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>540971</v>
+        <v>540772</v>
       </c>
       <c r="R138" t="n">
-        <v>7193081</v>
+        <v>7193446</v>
       </c>
       <c r="S138" t="n">
         <v>25</v>
@@ -15412,7 +15412,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15422,7 +15422,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15449,32 +15449,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129319347</v>
+        <v>129319406</v>
       </c>
       <c r="B139" t="n">
-        <v>80180</v>
+        <v>79120</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6464</v>
+        <v>864</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15484,10 +15484,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>540653</v>
+        <v>540938</v>
       </c>
       <c r="R139" t="n">
-        <v>7193521</v>
+        <v>7193168</v>
       </c>
       <c r="S139" t="n">
         <v>25</v>
@@ -15519,7 +15519,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15529,7 +15529,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15556,32 +15556,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129319315</v>
+        <v>129319428</v>
       </c>
       <c r="B140" t="n">
-        <v>82988</v>
+        <v>80146</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6439</v>
+        <v>6458</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15591,10 +15591,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>540765</v>
+        <v>540971</v>
       </c>
       <c r="R140" t="n">
-        <v>7193370</v>
+        <v>7193081</v>
       </c>
       <c r="S140" t="n">
         <v>25</v>
@@ -15626,7 +15626,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15636,7 +15636,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15663,32 +15663,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129319387</v>
+        <v>129319347</v>
       </c>
       <c r="B141" t="n">
-        <v>82997</v>
+        <v>80182</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>308</v>
+        <v>6464</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15698,10 +15698,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>540772</v>
+        <v>540653</v>
       </c>
       <c r="R141" t="n">
-        <v>7193446</v>
+        <v>7193521</v>
       </c>
       <c r="S141" t="n">
         <v>25</v>
@@ -15733,7 +15733,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15743,7 +15743,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15770,32 +15770,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129319406</v>
+        <v>129319315</v>
       </c>
       <c r="B142" t="n">
-        <v>79118</v>
+        <v>82990</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>864</v>
+        <v>6439</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15805,10 +15805,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>540938</v>
+        <v>540765</v>
       </c>
       <c r="R142" t="n">
-        <v>7193168</v>
+        <v>7193370</v>
       </c>
       <c r="S142" t="n">
         <v>25</v>
@@ -15840,7 +15840,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15850,7 +15850,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15877,32 +15877,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129319287</v>
+        <v>129319327</v>
       </c>
       <c r="B143" t="n">
-        <v>92240</v>
+        <v>79041</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15912,10 +15912,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>540913</v>
+        <v>540693</v>
       </c>
       <c r="R143" t="n">
-        <v>7193185</v>
+        <v>7193540</v>
       </c>
       <c r="S143" t="n">
         <v>25</v>
@@ -15947,7 +15947,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15957,7 +15957,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15984,32 +15984,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129319327</v>
+        <v>129319287</v>
       </c>
       <c r="B144" t="n">
-        <v>79039</v>
+        <v>92242</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -16019,10 +16019,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>540693</v>
+        <v>540913</v>
       </c>
       <c r="R144" t="n">
-        <v>7193540</v>
+        <v>7193185</v>
       </c>
       <c r="S144" t="n">
         <v>25</v>
@@ -16054,7 +16054,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16064,7 +16064,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD144" t="b">

--- a/artfynd/A 51086-2025 artfynd.xlsx
+++ b/artfynd/A 51086-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129319384</v>
+        <v>129319323</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>80182</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540775</v>
+        <v>540719</v>
       </c>
       <c r="R2" t="n">
-        <v>7193467</v>
+        <v>7193483</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,45 +782,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129319323</v>
+        <v>129319300</v>
       </c>
       <c r="B3" t="n">
-        <v>80182</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540719</v>
+        <v>540961</v>
       </c>
       <c r="R3" t="n">
-        <v>7193483</v>
+        <v>7193376</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -852,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129319302</v>
+        <v>129319307</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>91538</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540960</v>
+        <v>540962</v>
       </c>
       <c r="R4" t="n">
-        <v>7193375</v>
+        <v>7193400</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -959,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129319420</v>
+        <v>129319285</v>
       </c>
       <c r="B5" t="n">
-        <v>80146</v>
+        <v>91538</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540982</v>
+        <v>540886</v>
       </c>
       <c r="R5" t="n">
-        <v>7193144</v>
+        <v>7193172</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1066,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1210,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129319300</v>
+        <v>129319384</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,39 +1226,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540961</v>
+        <v>540775</v>
       </c>
       <c r="R7" t="n">
-        <v>7193376</v>
+        <v>7193467</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1322,54 +1322,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129319414</v>
+        <v>129319302</v>
       </c>
       <c r="B8" t="n">
-        <v>58360</v>
+        <v>79041</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102125</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540963</v>
+        <v>540960</v>
       </c>
       <c r="R8" t="n">
-        <v>7193203</v>
+        <v>7193375</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1401,7 +1392,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1411,7 +1402,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1438,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129319307</v>
+        <v>129319420</v>
       </c>
       <c r="B9" t="n">
-        <v>91538</v>
+        <v>80146</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1449,21 +1440,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1473,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540962</v>
+        <v>540982</v>
       </c>
       <c r="R9" t="n">
-        <v>7193400</v>
+        <v>7193144</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1508,7 +1499,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1518,7 +1509,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1545,45 +1536,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129319285</v>
+        <v>129319414</v>
       </c>
       <c r="B10" t="n">
-        <v>91538</v>
+        <v>58360</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>102125</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540886</v>
+        <v>540963</v>
       </c>
       <c r="R10" t="n">
-        <v>7193172</v>
+        <v>7193203</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1615,7 +1615,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1652,32 +1652,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129319352</v>
+        <v>129319295</v>
       </c>
       <c r="B11" t="n">
-        <v>78054</v>
+        <v>95904</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228579</v>
+        <v>2809</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540715</v>
+        <v>540972</v>
       </c>
       <c r="R11" t="n">
-        <v>7193537</v>
+        <v>7193357</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1759,32 +1759,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129319419</v>
+        <v>129319361</v>
       </c>
       <c r="B12" t="n">
-        <v>80181</v>
+        <v>91542</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1794,10 +1794,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540986</v>
+        <v>540726</v>
       </c>
       <c r="R12" t="n">
-        <v>7193130</v>
+        <v>7193531</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1829,7 +1829,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1866,10 +1866,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129319328</v>
+        <v>129319424</v>
       </c>
       <c r="B13" t="n">
-        <v>80146</v>
+        <v>80147</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1877,21 +1877,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1901,10 +1901,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540693</v>
+        <v>540975</v>
       </c>
       <c r="R13" t="n">
-        <v>7193540</v>
+        <v>7193139</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1973,32 +1973,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129319313</v>
+        <v>129319381</v>
       </c>
       <c r="B14" t="n">
-        <v>80182</v>
+        <v>82873</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2008,10 +2008,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540789</v>
+        <v>540758</v>
       </c>
       <c r="R14" t="n">
-        <v>7193372</v>
+        <v>7193475</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2080,10 +2080,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129319296</v>
+        <v>129319438</v>
       </c>
       <c r="B15" t="n">
-        <v>79041</v>
+        <v>57887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2091,34 +2091,43 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540970</v>
+        <v>540982</v>
       </c>
       <c r="R15" t="n">
-        <v>7193365</v>
+        <v>7193110</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2150,7 +2159,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2160,7 +2169,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2187,10 +2196,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129319324</v>
+        <v>129319352</v>
       </c>
       <c r="B16" t="n">
-        <v>80146</v>
+        <v>78054</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2198,21 +2207,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2222,10 +2231,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540719</v>
+        <v>540715</v>
       </c>
       <c r="R16" t="n">
-        <v>7193483</v>
+        <v>7193537</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2257,7 +2266,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2267,7 +2276,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2294,32 +2303,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129319430</v>
+        <v>129319328</v>
       </c>
       <c r="B17" t="n">
-        <v>80181</v>
+        <v>80146</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2329,10 +2338,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540971</v>
+        <v>540693</v>
       </c>
       <c r="R17" t="n">
-        <v>7193066</v>
+        <v>7193540</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2364,7 +2373,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2374,7 +2383,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2401,10 +2410,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129319438</v>
+        <v>129319296</v>
       </c>
       <c r="B18" t="n">
-        <v>57887</v>
+        <v>79041</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2412,43 +2421,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540982</v>
+        <v>540970</v>
       </c>
       <c r="R18" t="n">
-        <v>7193110</v>
+        <v>7193365</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2480,7 +2480,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2517,10 +2517,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129319361</v>
+        <v>129319324</v>
       </c>
       <c r="B19" t="n">
-        <v>91542</v>
+        <v>80146</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2528,21 +2528,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2552,10 +2552,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540726</v>
+        <v>540719</v>
       </c>
       <c r="R19" t="n">
-        <v>7193531</v>
+        <v>7193483</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2624,32 +2624,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129319381</v>
+        <v>129319419</v>
       </c>
       <c r="B20" t="n">
-        <v>82873</v>
+        <v>80181</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>6463</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540758</v>
+        <v>540986</v>
       </c>
       <c r="R20" t="n">
-        <v>7193475</v>
+        <v>7193130</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2731,10 +2731,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129319295</v>
+        <v>129319313</v>
       </c>
       <c r="B21" t="n">
-        <v>95904</v>
+        <v>80182</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2742,21 +2742,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2809</v>
+        <v>6464</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2766,10 +2766,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540972</v>
+        <v>540789</v>
       </c>
       <c r="R21" t="n">
-        <v>7193357</v>
+        <v>7193372</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2838,32 +2838,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129319424</v>
+        <v>129319430</v>
       </c>
       <c r="B22" t="n">
-        <v>80147</v>
+        <v>80181</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540975</v>
+        <v>540971</v>
       </c>
       <c r="R22" t="n">
-        <v>7193139</v>
+        <v>7193066</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2945,10 +2945,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129319390</v>
+        <v>129319281</v>
       </c>
       <c r="B23" t="n">
-        <v>79041</v>
+        <v>80147</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2956,21 +2956,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2980,10 +2980,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540818</v>
+        <v>540902</v>
       </c>
       <c r="R23" t="n">
-        <v>7193358</v>
+        <v>7193083</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3015,7 +3015,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3052,10 +3052,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129319383</v>
+        <v>129319316</v>
       </c>
       <c r="B24" t="n">
-        <v>79041</v>
+        <v>80147</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3063,21 +3063,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3087,10 +3087,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540764</v>
+        <v>540763</v>
       </c>
       <c r="R24" t="n">
-        <v>7193475</v>
+        <v>7193372</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3159,10 +3159,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129319349</v>
+        <v>129319291</v>
       </c>
       <c r="B25" t="n">
-        <v>91560</v>
+        <v>80147</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3170,21 +3170,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3194,10 +3194,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540670</v>
+        <v>540996</v>
       </c>
       <c r="R25" t="n">
-        <v>7193521</v>
+        <v>7193327</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3229,7 +3229,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3239,7 +3239,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3266,10 +3266,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129319354</v>
+        <v>129319340</v>
       </c>
       <c r="B26" t="n">
-        <v>79041</v>
+        <v>91542</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3277,21 +3277,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3301,10 +3301,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540722</v>
+        <v>540666</v>
       </c>
       <c r="R26" t="n">
-        <v>7193542</v>
+        <v>7193537</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3373,10 +3373,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129319281</v>
+        <v>129319390</v>
       </c>
       <c r="B27" t="n">
-        <v>80147</v>
+        <v>79041</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3384,21 +3384,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3408,10 +3408,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>540902</v>
+        <v>540818</v>
       </c>
       <c r="R27" t="n">
-        <v>7193083</v>
+        <v>7193358</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3480,10 +3480,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129319316</v>
+        <v>129319383</v>
       </c>
       <c r="B28" t="n">
-        <v>80147</v>
+        <v>79041</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3491,21 +3491,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3515,10 +3515,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>540763</v>
+        <v>540764</v>
       </c>
       <c r="R28" t="n">
-        <v>7193372</v>
+        <v>7193475</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3550,7 +3550,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3587,10 +3587,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129319291</v>
+        <v>129319349</v>
       </c>
       <c r="B29" t="n">
-        <v>80147</v>
+        <v>91560</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3598,21 +3598,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3622,10 +3622,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>540996</v>
+        <v>540670</v>
       </c>
       <c r="R29" t="n">
-        <v>7193327</v>
+        <v>7193521</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3657,7 +3657,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3667,7 +3667,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3694,10 +3694,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129319340</v>
+        <v>129319354</v>
       </c>
       <c r="B30" t="n">
-        <v>91542</v>
+        <v>79041</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3705,21 +3705,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3729,10 +3729,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>540666</v>
+        <v>540722</v>
       </c>
       <c r="R30" t="n">
-        <v>7193537</v>
+        <v>7193542</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3764,7 +3764,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3801,10 +3801,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129319337</v>
+        <v>129319374</v>
       </c>
       <c r="B31" t="n">
-        <v>80146</v>
+        <v>80147</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3812,21 +3812,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3836,10 +3836,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>540676</v>
+        <v>540734</v>
       </c>
       <c r="R31" t="n">
-        <v>7193539</v>
+        <v>7193499</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3871,7 +3871,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3908,32 +3908,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129319422</v>
+        <v>129319377</v>
       </c>
       <c r="B32" t="n">
-        <v>80181</v>
+        <v>80147</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3943,10 +3943,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>540980</v>
+        <v>540745</v>
       </c>
       <c r="R32" t="n">
-        <v>7193139</v>
+        <v>7193494</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4015,27 +4015,27 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129319396</v>
+        <v>129319422</v>
       </c>
       <c r="B33" t="n">
-        <v>79041</v>
+        <v>80181</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4050,10 +4050,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>540928</v>
+        <v>540980</v>
       </c>
       <c r="R33" t="n">
-        <v>7193263</v>
+        <v>7193139</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4085,7 +4085,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4122,10 +4122,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129319427</v>
+        <v>129319337</v>
       </c>
       <c r="B34" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4133,21 +4133,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4157,10 +4157,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>540969</v>
+        <v>540676</v>
       </c>
       <c r="R34" t="n">
-        <v>7193117</v>
+        <v>7193539</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4229,7 +4229,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129319282</v>
+        <v>129319396</v>
       </c>
       <c r="B35" t="n">
         <v>79041</v>
@@ -4264,10 +4264,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>540901</v>
+        <v>540928</v>
       </c>
       <c r="R35" t="n">
-        <v>7193084</v>
+        <v>7193263</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4336,10 +4336,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129319405</v>
+        <v>129319427</v>
       </c>
       <c r="B36" t="n">
-        <v>83007</v>
+        <v>79041</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4347,21 +4347,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4371,10 +4371,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>540931</v>
+        <v>540969</v>
       </c>
       <c r="R36" t="n">
-        <v>7193220</v>
+        <v>7193117</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4406,7 +4406,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4443,10 +4443,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129319404</v>
+        <v>129319282</v>
       </c>
       <c r="B37" t="n">
-        <v>78054</v>
+        <v>79041</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4454,21 +4454,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4478,10 +4478,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>540931</v>
+        <v>540901</v>
       </c>
       <c r="R37" t="n">
-        <v>7193220</v>
+        <v>7193084</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4513,7 +4513,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4523,7 +4523,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4550,10 +4550,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129319374</v>
+        <v>129319405</v>
       </c>
       <c r="B38" t="n">
-        <v>80147</v>
+        <v>83007</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4561,21 +4561,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4585,10 +4585,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>540734</v>
+        <v>540931</v>
       </c>
       <c r="R38" t="n">
-        <v>7193499</v>
+        <v>7193220</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4620,7 +4620,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4630,7 +4630,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4657,10 +4657,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129319377</v>
+        <v>129319404</v>
       </c>
       <c r="B39" t="n">
-        <v>80147</v>
+        <v>78054</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4668,21 +4668,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>228579</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4692,10 +4692,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>540745</v>
+        <v>540931</v>
       </c>
       <c r="R39" t="n">
-        <v>7193494</v>
+        <v>7193220</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4727,7 +4727,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4764,10 +4764,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129319303</v>
+        <v>129319278</v>
       </c>
       <c r="B40" t="n">
-        <v>79041</v>
+        <v>80147</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4775,21 +4775,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4799,10 +4799,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>540934</v>
+        <v>540864</v>
       </c>
       <c r="R40" t="n">
-        <v>7193385</v>
+        <v>7193066</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4871,10 +4871,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129319348</v>
+        <v>129319365</v>
       </c>
       <c r="B41" t="n">
-        <v>80146</v>
+        <v>80147</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4882,21 +4882,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4906,10 +4906,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>540653</v>
+        <v>540738</v>
       </c>
       <c r="R41" t="n">
-        <v>7193521</v>
+        <v>7193503</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4941,7 +4941,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4951,7 +4951,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4978,32 +4978,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129319288</v>
+        <v>129319395</v>
       </c>
       <c r="B42" t="n">
-        <v>79041</v>
+        <v>82992</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5013,10 +5013,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>540915</v>
+        <v>540878</v>
       </c>
       <c r="R42" t="n">
-        <v>7193185</v>
+        <v>7193291</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5048,7 +5048,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5085,32 +5085,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129319401</v>
+        <v>129319294</v>
       </c>
       <c r="B43" t="n">
-        <v>80175</v>
+        <v>83012</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>1467</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5120,10 +5120,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540942</v>
+        <v>540974</v>
       </c>
       <c r="R43" t="n">
-        <v>7193229</v>
+        <v>7193351</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5155,7 +5155,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5192,10 +5192,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129319403</v>
+        <v>129319303</v>
       </c>
       <c r="B44" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5203,21 +5203,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5227,10 +5227,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540930</v>
+        <v>540934</v>
       </c>
       <c r="R44" t="n">
-        <v>7193219</v>
+        <v>7193385</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5262,7 +5262,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5272,7 +5272,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5299,32 +5299,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129319320</v>
+        <v>129319348</v>
       </c>
       <c r="B45" t="n">
-        <v>80181</v>
+        <v>80146</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5334,10 +5334,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>540719</v>
+        <v>540653</v>
       </c>
       <c r="R45" t="n">
-        <v>7193463</v>
+        <v>7193521</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5369,7 +5369,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5379,7 +5379,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5406,10 +5406,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129319278</v>
+        <v>129319288</v>
       </c>
       <c r="B46" t="n">
-        <v>80147</v>
+        <v>79041</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5417,21 +5417,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5441,10 +5441,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>540864</v>
+        <v>540915</v>
       </c>
       <c r="R46" t="n">
-        <v>7193066</v>
+        <v>7193185</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5476,7 +5476,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5513,10 +5513,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129319365</v>
+        <v>129319403</v>
       </c>
       <c r="B47" t="n">
-        <v>80147</v>
+        <v>80146</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5524,21 +5524,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5548,10 +5548,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>540738</v>
+        <v>540930</v>
       </c>
       <c r="R47" t="n">
-        <v>7193503</v>
+        <v>7193219</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5593,7 +5593,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5620,32 +5620,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129319294</v>
+        <v>129319401</v>
       </c>
       <c r="B48" t="n">
-        <v>83012</v>
+        <v>80175</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1467</v>
+        <v>6462</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5655,10 +5655,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>540974</v>
+        <v>540942</v>
       </c>
       <c r="R48" t="n">
-        <v>7193351</v>
+        <v>7193229</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5690,7 +5690,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5700,7 +5700,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5727,10 +5727,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129319395</v>
+        <v>129319320</v>
       </c>
       <c r="B49" t="n">
-        <v>82992</v>
+        <v>80181</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5738,21 +5738,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>306</v>
+        <v>6463</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5762,10 +5762,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>540878</v>
+        <v>540719</v>
       </c>
       <c r="R49" t="n">
-        <v>7193291</v>
+        <v>7193463</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5797,7 +5797,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5807,7 +5807,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6262,10 +6262,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129319429</v>
+        <v>129319388</v>
       </c>
       <c r="B54" t="n">
-        <v>80147</v>
+        <v>57727</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6273,34 +6273,48 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>540972</v>
+        <v>540828</v>
       </c>
       <c r="R54" t="n">
-        <v>7193067</v>
+        <v>7193425</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6332,7 +6346,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6342,7 +6356,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6369,7 +6383,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129319417</v>
+        <v>129319429</v>
       </c>
       <c r="B55" t="n">
         <v>80147</v>
@@ -6404,10 +6418,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>540989</v>
+        <v>540972</v>
       </c>
       <c r="R55" t="n">
-        <v>7193132</v>
+        <v>7193067</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6439,7 +6453,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6449,7 +6463,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6476,10 +6490,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129319388</v>
+        <v>129319417</v>
       </c>
       <c r="B56" t="n">
-        <v>57727</v>
+        <v>80147</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6487,48 +6501,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>540828</v>
+        <v>540989</v>
       </c>
       <c r="R56" t="n">
-        <v>7193425</v>
+        <v>7193132</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6560,7 +6560,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6704,32 +6704,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129319330</v>
+        <v>129319353</v>
       </c>
       <c r="B58" t="n">
-        <v>82990</v>
+        <v>82873</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6439</v>
+        <v>1312</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6739,10 +6739,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>540683</v>
+        <v>540721</v>
       </c>
       <c r="R58" t="n">
-        <v>7193545</v>
+        <v>7193542</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6774,7 +6774,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6784,7 +6784,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6811,10 +6811,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129319372</v>
+        <v>129319279</v>
       </c>
       <c r="B59" t="n">
-        <v>80146</v>
+        <v>80147</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6822,21 +6822,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6846,10 +6846,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>540736</v>
+        <v>540872</v>
       </c>
       <c r="R59" t="n">
-        <v>7193500</v>
+        <v>7193070</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6881,7 +6881,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6918,10 +6918,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129319292</v>
+        <v>129319339</v>
       </c>
       <c r="B60" t="n">
-        <v>79041</v>
+        <v>80147</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6929,21 +6929,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6953,10 +6953,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>540996</v>
+        <v>540669</v>
       </c>
       <c r="R60" t="n">
-        <v>7193327</v>
+        <v>7193542</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6988,7 +6988,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6998,7 +6998,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7025,10 +7025,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129319392</v>
+        <v>129319311</v>
       </c>
       <c r="B61" t="n">
-        <v>79041</v>
+        <v>91538</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7036,21 +7036,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7060,10 +7060,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>540826</v>
+        <v>540830</v>
       </c>
       <c r="R61" t="n">
-        <v>7193294</v>
+        <v>7193366</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7095,7 +7095,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7105,7 +7105,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7132,10 +7132,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129319423</v>
+        <v>129319330</v>
       </c>
       <c r="B62" t="n">
-        <v>57831</v>
+        <v>82990</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7143,43 +7143,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103031</v>
+        <v>6439</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>540976</v>
+        <v>540683</v>
       </c>
       <c r="R62" t="n">
-        <v>7193139</v>
+        <v>7193545</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7211,7 +7202,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7221,7 +7212,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7248,10 +7239,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129319353</v>
+        <v>129319372</v>
       </c>
       <c r="B63" t="n">
-        <v>82873</v>
+        <v>80146</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7259,21 +7250,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7283,10 +7274,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>540721</v>
+        <v>540736</v>
       </c>
       <c r="R63" t="n">
-        <v>7193542</v>
+        <v>7193500</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7318,7 +7309,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7328,7 +7319,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7355,10 +7346,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129319311</v>
+        <v>129319292</v>
       </c>
       <c r="B64" t="n">
-        <v>91538</v>
+        <v>79041</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7366,21 +7357,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7390,10 +7381,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>540830</v>
+        <v>540996</v>
       </c>
       <c r="R64" t="n">
-        <v>7193366</v>
+        <v>7193327</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7425,7 +7416,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7435,7 +7426,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7462,10 +7453,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129319279</v>
+        <v>129319392</v>
       </c>
       <c r="B65" t="n">
-        <v>80147</v>
+        <v>79041</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7473,21 +7464,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7497,10 +7488,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>540872</v>
+        <v>540826</v>
       </c>
       <c r="R65" t="n">
-        <v>7193070</v>
+        <v>7193294</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7532,7 +7523,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7542,7 +7533,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7569,45 +7560,54 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129319339</v>
+        <v>129319423</v>
       </c>
       <c r="B66" t="n">
-        <v>80147</v>
+        <v>57831</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2081</v>
+        <v>103031</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>540669</v>
+        <v>540976</v>
       </c>
       <c r="R66" t="n">
-        <v>7193542</v>
+        <v>7193139</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7639,7 +7639,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7649,7 +7649,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7783,32 +7783,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129319421</v>
+        <v>129319334</v>
       </c>
       <c r="B68" t="n">
-        <v>80175</v>
+        <v>80146</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7818,10 +7818,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>540981</v>
+        <v>540674</v>
       </c>
       <c r="R68" t="n">
-        <v>7193140</v>
+        <v>7193550</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7890,10 +7890,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129319334</v>
+        <v>129319400</v>
       </c>
       <c r="B69" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7901,21 +7901,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7925,10 +7925,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>540674</v>
+        <v>540943</v>
       </c>
       <c r="R69" t="n">
-        <v>7193550</v>
+        <v>7193233</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7960,7 +7960,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7997,10 +7997,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129319400</v>
+        <v>129319293</v>
       </c>
       <c r="B70" t="n">
-        <v>79041</v>
+        <v>57887</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8008,34 +8008,43 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>540943</v>
+        <v>540980</v>
       </c>
       <c r="R70" t="n">
-        <v>7193233</v>
+        <v>7193345</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8067,7 +8076,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8077,7 +8086,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8104,7 +8113,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129319370</v>
+        <v>129319421</v>
       </c>
       <c r="B71" t="n">
         <v>80175</v>
@@ -8139,10 +8148,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>540737</v>
+        <v>540981</v>
       </c>
       <c r="R71" t="n">
-        <v>7193504</v>
+        <v>7193140</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8174,7 +8183,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8184,7 +8193,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8211,54 +8220,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129319293</v>
+        <v>129319370</v>
       </c>
       <c r="B72" t="n">
-        <v>57887</v>
+        <v>80175</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>540980</v>
+        <v>540737</v>
       </c>
       <c r="R72" t="n">
-        <v>7193345</v>
+        <v>7193504</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8290,7 +8290,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8300,7 +8300,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8327,45 +8327,54 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129319402</v>
+        <v>129319432</v>
       </c>
       <c r="B73" t="n">
-        <v>79041</v>
+        <v>58360</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>102125</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>540936</v>
+        <v>540978</v>
       </c>
       <c r="R73" t="n">
-        <v>7193225</v>
+        <v>7193078</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8397,7 +8406,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8407,7 +8416,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8434,32 +8443,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129319412</v>
+        <v>129319367</v>
       </c>
       <c r="B74" t="n">
-        <v>91560</v>
+        <v>80175</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8469,10 +8478,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>540952</v>
+        <v>540734</v>
       </c>
       <c r="R74" t="n">
-        <v>7193187</v>
+        <v>7193503</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8504,7 +8513,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8514,7 +8523,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8541,7 +8550,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129319413</v>
+        <v>129319402</v>
       </c>
       <c r="B75" t="n">
         <v>79041</v>
@@ -8576,10 +8585,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>540965</v>
+        <v>540936</v>
       </c>
       <c r="R75" t="n">
-        <v>7193181</v>
+        <v>7193225</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8611,7 +8620,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8621,7 +8630,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8648,32 +8657,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129319367</v>
+        <v>129319412</v>
       </c>
       <c r="B76" t="n">
-        <v>80175</v>
+        <v>91560</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8683,10 +8692,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>540734</v>
+        <v>540952</v>
       </c>
       <c r="R76" t="n">
-        <v>7193503</v>
+        <v>7193187</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8718,7 +8727,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8728,7 +8737,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8755,54 +8764,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129319432</v>
+        <v>129319413</v>
       </c>
       <c r="B77" t="n">
-        <v>58360</v>
+        <v>79041</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>102125</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>540978</v>
+        <v>540965</v>
       </c>
       <c r="R77" t="n">
-        <v>7193078</v>
+        <v>7193181</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8844,7 +8844,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8871,10 +8871,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129319371</v>
+        <v>129319342</v>
       </c>
       <c r="B78" t="n">
-        <v>80146</v>
+        <v>57724</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8882,34 +8882,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>540737</v>
+        <v>540667</v>
       </c>
       <c r="R78" t="n">
-        <v>7193504</v>
+        <v>7193539</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8941,7 +8946,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8951,7 +8956,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8978,10 +8983,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129319342</v>
+        <v>129319371</v>
       </c>
       <c r="B79" t="n">
-        <v>57724</v>
+        <v>80146</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8989,39 +8994,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>540667</v>
+        <v>540737</v>
       </c>
       <c r="R79" t="n">
-        <v>7193539</v>
+        <v>7193504</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9053,7 +9053,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9063,7 +9063,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9090,10 +9090,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129319336</v>
+        <v>129319338</v>
       </c>
       <c r="B80" t="n">
-        <v>79041</v>
+        <v>80147</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9101,21 +9101,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9125,10 +9125,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>540668</v>
+        <v>540676</v>
       </c>
       <c r="R80" t="n">
-        <v>7193543</v>
+        <v>7193539</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9160,7 +9160,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9170,7 +9170,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9197,7 +9197,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129319382</v>
+        <v>129319336</v>
       </c>
       <c r="B81" t="n">
         <v>79041</v>
@@ -9232,10 +9232,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>540761</v>
+        <v>540668</v>
       </c>
       <c r="R81" t="n">
-        <v>7193473</v>
+        <v>7193543</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9267,7 +9267,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9304,10 +9304,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129319408</v>
+        <v>129319382</v>
       </c>
       <c r="B82" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9315,21 +9315,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9339,10 +9339,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>540939</v>
+        <v>540761</v>
       </c>
       <c r="R82" t="n">
-        <v>7193177</v>
+        <v>7193473</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9374,7 +9374,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9384,7 +9384,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9411,32 +9411,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129319431</v>
+        <v>129319394</v>
       </c>
       <c r="B83" t="n">
-        <v>80175</v>
+        <v>79041</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9446,10 +9446,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>540979</v>
+        <v>540877</v>
       </c>
       <c r="R83" t="n">
-        <v>7193075</v>
+        <v>7193291</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9481,7 +9481,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9518,10 +9518,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129319394</v>
+        <v>129319408</v>
       </c>
       <c r="B84" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9529,21 +9529,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9553,10 +9553,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>540877</v>
+        <v>540939</v>
       </c>
       <c r="R84" t="n">
-        <v>7193291</v>
+        <v>7193177</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9588,7 +9588,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9625,32 +9625,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129319338</v>
+        <v>129319431</v>
       </c>
       <c r="B85" t="n">
-        <v>80147</v>
+        <v>80175</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9660,10 +9660,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>540676</v>
+        <v>540979</v>
       </c>
       <c r="R85" t="n">
-        <v>7193539</v>
+        <v>7193075</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9695,7 +9695,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9705,7 +9705,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9732,10 +9732,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129319284</v>
+        <v>129319298</v>
       </c>
       <c r="B86" t="n">
-        <v>79041</v>
+        <v>91560</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9743,21 +9743,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9767,10 +9767,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>540867</v>
+        <v>540964</v>
       </c>
       <c r="R86" t="n">
-        <v>7193169</v>
+        <v>7193371</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9802,7 +9802,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9812,7 +9812,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9839,10 +9839,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129319409</v>
+        <v>129319284</v>
       </c>
       <c r="B87" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9850,21 +9850,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9874,10 +9874,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>540942</v>
+        <v>540867</v>
       </c>
       <c r="R87" t="n">
-        <v>7193182</v>
+        <v>7193169</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -9909,7 +9909,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9919,7 +9919,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9946,10 +9946,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129319298</v>
+        <v>129319409</v>
       </c>
       <c r="B88" t="n">
-        <v>91560</v>
+        <v>80146</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9957,21 +9957,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9981,10 +9981,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>540964</v>
+        <v>540942</v>
       </c>
       <c r="R88" t="n">
-        <v>7193371</v>
+        <v>7193182</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -10016,7 +10016,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10026,7 +10026,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11016,10 +11016,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129319399</v>
+        <v>129319445</v>
       </c>
       <c r="B98" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11027,34 +11027,43 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>540945</v>
+        <v>541052</v>
       </c>
       <c r="R98" t="n">
-        <v>7193248</v>
+        <v>7193255</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -11086,7 +11095,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11096,7 +11105,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11123,7 +11132,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129319308</v>
+        <v>129319399</v>
       </c>
       <c r="B99" t="n">
         <v>79041</v>
@@ -11158,10 +11167,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>540907</v>
+        <v>540945</v>
       </c>
       <c r="R99" t="n">
-        <v>7193409</v>
+        <v>7193248</v>
       </c>
       <c r="S99" t="n">
         <v>25</v>
@@ -11193,7 +11202,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11203,7 +11212,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11230,7 +11239,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129319362</v>
+        <v>129319308</v>
       </c>
       <c r="B100" t="n">
         <v>79041</v>
@@ -11265,10 +11274,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>540721</v>
+        <v>540907</v>
       </c>
       <c r="R100" t="n">
-        <v>7193527</v>
+        <v>7193409</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -11300,7 +11309,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11310,7 +11319,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11337,7 +11346,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129319306</v>
+        <v>129319362</v>
       </c>
       <c r="B101" t="n">
         <v>79041</v>
@@ -11372,10 +11381,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>540961</v>
+        <v>540721</v>
       </c>
       <c r="R101" t="n">
-        <v>7193398</v>
+        <v>7193527</v>
       </c>
       <c r="S101" t="n">
         <v>25</v>
@@ -11407,7 +11416,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11417,7 +11426,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11444,7 +11453,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129319286</v>
+        <v>129319306</v>
       </c>
       <c r="B102" t="n">
         <v>79041</v>
@@ -11479,10 +11488,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>540891</v>
+        <v>540961</v>
       </c>
       <c r="R102" t="n">
-        <v>7193174</v>
+        <v>7193398</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -11514,7 +11523,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11524,7 +11533,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11551,10 +11560,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129319359</v>
+        <v>129319286</v>
       </c>
       <c r="B103" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11562,21 +11571,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11586,10 +11595,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>540725</v>
+        <v>540891</v>
       </c>
       <c r="R103" t="n">
-        <v>7193537</v>
+        <v>7193174</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -11621,7 +11630,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11631,7 +11640,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11658,10 +11667,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129319445</v>
+        <v>129319359</v>
       </c>
       <c r="B104" t="n">
-        <v>57724</v>
+        <v>80146</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11669,43 +11678,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>541052</v>
+        <v>540725</v>
       </c>
       <c r="R104" t="n">
-        <v>7193255</v>
+        <v>7193537</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -11737,7 +11737,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11747,7 +11747,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11774,10 +11774,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129319368</v>
+        <v>129319355</v>
       </c>
       <c r="B105" t="n">
-        <v>80146</v>
+        <v>80147</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11785,21 +11785,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11809,10 +11809,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>540734</v>
+        <v>540726</v>
       </c>
       <c r="R105" t="n">
-        <v>7193503</v>
+        <v>7193541</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -11844,7 +11844,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11854,7 +11854,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11881,10 +11881,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129319411</v>
+        <v>129319360</v>
       </c>
       <c r="B106" t="n">
-        <v>79041</v>
+        <v>91538</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11892,21 +11892,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11916,10 +11916,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>540955</v>
+        <v>540725</v>
       </c>
       <c r="R106" t="n">
-        <v>7193186</v>
+        <v>7193532</v>
       </c>
       <c r="S106" t="n">
         <v>25</v>
@@ -11951,7 +11951,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11961,7 +11961,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11988,32 +11988,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129319418</v>
+        <v>129319369</v>
       </c>
       <c r="B107" t="n">
-        <v>80182</v>
+        <v>80147</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12023,10 +12023,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>540986</v>
+        <v>540734</v>
       </c>
       <c r="R107" t="n">
-        <v>7193130</v>
+        <v>7193503</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -12058,7 +12058,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12068,7 +12068,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12095,10 +12095,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129319407</v>
+        <v>129319391</v>
       </c>
       <c r="B108" t="n">
-        <v>79041</v>
+        <v>80147</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12106,21 +12106,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12130,10 +12130,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>540924</v>
+        <v>540818</v>
       </c>
       <c r="R108" t="n">
-        <v>7193211</v>
+        <v>7193333</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -12165,7 +12165,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12175,7 +12175,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12202,10 +12202,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129319355</v>
+        <v>129319368</v>
       </c>
       <c r="B109" t="n">
-        <v>80147</v>
+        <v>80146</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12213,21 +12213,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12237,10 +12237,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>540726</v>
+        <v>540734</v>
       </c>
       <c r="R109" t="n">
-        <v>7193541</v>
+        <v>7193503</v>
       </c>
       <c r="S109" t="n">
         <v>25</v>
@@ -12272,7 +12272,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12282,7 +12282,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12309,10 +12309,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129319369</v>
+        <v>129319411</v>
       </c>
       <c r="B110" t="n">
-        <v>80147</v>
+        <v>79041</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12320,21 +12320,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12344,10 +12344,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>540734</v>
+        <v>540955</v>
       </c>
       <c r="R110" t="n">
-        <v>7193503</v>
+        <v>7193186</v>
       </c>
       <c r="S110" t="n">
         <v>25</v>
@@ -12379,7 +12379,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12389,7 +12389,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12416,10 +12416,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129319391</v>
+        <v>129319407</v>
       </c>
       <c r="B111" t="n">
-        <v>80147</v>
+        <v>79041</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12427,21 +12427,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12451,10 +12451,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>540818</v>
+        <v>540924</v>
       </c>
       <c r="R111" t="n">
-        <v>7193333</v>
+        <v>7193211</v>
       </c>
       <c r="S111" t="n">
         <v>25</v>
@@ -12486,7 +12486,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12496,7 +12496,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12523,32 +12523,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129319360</v>
+        <v>129319418</v>
       </c>
       <c r="B112" t="n">
-        <v>91538</v>
+        <v>80182</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1108</v>
+        <v>6464</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12558,10 +12558,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>540725</v>
+        <v>540986</v>
       </c>
       <c r="R112" t="n">
-        <v>7193532</v>
+        <v>7193130</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>
@@ -12593,7 +12593,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12603,7 +12603,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12737,32 +12737,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129319425</v>
+        <v>129319341</v>
       </c>
       <c r="B114" t="n">
-        <v>80181</v>
+        <v>91538</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6463</v>
+        <v>1108</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12772,10 +12772,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>540980</v>
+        <v>540670</v>
       </c>
       <c r="R114" t="n">
-        <v>7193116</v>
+        <v>7193533</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -12807,7 +12807,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12817,7 +12817,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13174,32 +13174,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129319341</v>
+        <v>129319425</v>
       </c>
       <c r="B118" t="n">
-        <v>91538</v>
+        <v>80181</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1108</v>
+        <v>6463</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13209,10 +13209,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>540670</v>
+        <v>540980</v>
       </c>
       <c r="R118" t="n">
-        <v>7193533</v>
+        <v>7193116</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -13244,7 +13244,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13254,7 +13254,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13281,32 +13281,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129319416</v>
+        <v>129319277</v>
       </c>
       <c r="B119" t="n">
-        <v>80182</v>
+        <v>80147</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13316,10 +13316,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>540970</v>
+        <v>540837</v>
       </c>
       <c r="R119" t="n">
-        <v>7193154</v>
+        <v>7193042</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -13351,7 +13351,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13388,32 +13388,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129319373</v>
+        <v>129319325</v>
       </c>
       <c r="B120" t="n">
-        <v>80182</v>
+        <v>80147</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13423,10 +13423,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>540734</v>
+        <v>540714</v>
       </c>
       <c r="R120" t="n">
-        <v>7193499</v>
+        <v>7193488</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -13458,7 +13458,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13468,7 +13468,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13495,32 +13495,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129319321</v>
+        <v>129319329</v>
       </c>
       <c r="B121" t="n">
-        <v>80175</v>
+        <v>88939</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6462</v>
+        <v>510</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13530,10 +13530,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>540719</v>
+        <v>540692</v>
       </c>
       <c r="R121" t="n">
-        <v>7193463</v>
+        <v>7193539</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -13565,7 +13565,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13575,7 +13575,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13602,7 +13602,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129319277</v>
+        <v>129319319</v>
       </c>
       <c r="B122" t="n">
         <v>80147</v>
@@ -13637,10 +13637,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>540837</v>
+        <v>540719</v>
       </c>
       <c r="R122" t="n">
-        <v>7193042</v>
+        <v>7193463</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -13672,7 +13672,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13682,7 +13682,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13709,10 +13709,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129319325</v>
+        <v>129319410</v>
       </c>
       <c r="B123" t="n">
-        <v>80147</v>
+        <v>56908</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13720,34 +13720,43 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>2081</v>
+        <v>102612</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>540714</v>
+        <v>540946</v>
       </c>
       <c r="R123" t="n">
-        <v>7193488</v>
+        <v>7193171</v>
       </c>
       <c r="S123" t="n">
         <v>25</v>
@@ -13779,7 +13788,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13789,7 +13798,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13816,45 +13825,54 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129319319</v>
+        <v>129319363</v>
       </c>
       <c r="B124" t="n">
-        <v>80147</v>
+        <v>58360</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>2081</v>
+        <v>102125</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>540719</v>
+        <v>540731</v>
       </c>
       <c r="R124" t="n">
-        <v>7193463</v>
+        <v>7193512</v>
       </c>
       <c r="S124" t="n">
         <v>25</v>
@@ -13886,7 +13904,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13896,7 +13914,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13923,54 +13941,45 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129319363</v>
+        <v>129319350</v>
       </c>
       <c r="B125" t="n">
-        <v>58360</v>
+        <v>80146</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>102125</v>
+        <v>6458</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>540731</v>
+        <v>540681</v>
       </c>
       <c r="R125" t="n">
-        <v>7193512</v>
+        <v>7193521</v>
       </c>
       <c r="S125" t="n">
         <v>25</v>
@@ -14002,7 +14011,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14012,7 +14021,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14039,54 +14048,45 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129319410</v>
+        <v>129319416</v>
       </c>
       <c r="B126" t="n">
-        <v>56908</v>
+        <v>80182</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>102612</v>
+        <v>6464</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>540946</v>
+        <v>540970</v>
       </c>
       <c r="R126" t="n">
-        <v>7193171</v>
+        <v>7193154</v>
       </c>
       <c r="S126" t="n">
         <v>25</v>
@@ -14118,7 +14118,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14128,7 +14128,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14155,32 +14155,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129319350</v>
+        <v>129319373</v>
       </c>
       <c r="B127" t="n">
-        <v>80146</v>
+        <v>80182</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14190,10 +14190,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>540681</v>
+        <v>540734</v>
       </c>
       <c r="R127" t="n">
-        <v>7193521</v>
+        <v>7193499</v>
       </c>
       <c r="S127" t="n">
         <v>25</v>
@@ -14225,7 +14225,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14235,7 +14235,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14262,32 +14262,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129319329</v>
+        <v>129319321</v>
       </c>
       <c r="B128" t="n">
-        <v>88939</v>
+        <v>80175</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>510</v>
+        <v>6462</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14297,10 +14297,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>540692</v>
+        <v>540719</v>
       </c>
       <c r="R128" t="n">
-        <v>7193539</v>
+        <v>7193463</v>
       </c>
       <c r="S128" t="n">
         <v>25</v>
@@ -14332,7 +14332,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14342,7 +14342,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14476,10 +14476,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129319379</v>
+        <v>129319434</v>
       </c>
       <c r="B130" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14487,21 +14487,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14511,10 +14511,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>540761</v>
+        <v>540979</v>
       </c>
       <c r="R130" t="n">
-        <v>7193485</v>
+        <v>7193075</v>
       </c>
       <c r="S130" t="n">
         <v>25</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14556,7 +14556,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14583,10 +14583,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129319434</v>
+        <v>129319379</v>
       </c>
       <c r="B131" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14594,21 +14594,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14618,10 +14618,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>540979</v>
+        <v>540761</v>
       </c>
       <c r="R131" t="n">
-        <v>7193075</v>
+        <v>7193485</v>
       </c>
       <c r="S131" t="n">
         <v>25</v>
@@ -14653,7 +14653,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14663,7 +14663,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14690,32 +14690,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129319310</v>
+        <v>129319380</v>
       </c>
       <c r="B132" t="n">
-        <v>79041</v>
+        <v>92242</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14725,10 +14725,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>540830</v>
+        <v>540761</v>
       </c>
       <c r="R132" t="n">
-        <v>7193366</v>
+        <v>7193490</v>
       </c>
       <c r="S132" t="n">
         <v>25</v>
@@ -14760,7 +14760,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14770,7 +14770,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14797,10 +14797,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129319343</v>
+        <v>129319322</v>
       </c>
       <c r="B133" t="n">
-        <v>57727</v>
+        <v>80147</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14808,39 +14808,34 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>540661</v>
+        <v>540719</v>
       </c>
       <c r="R133" t="n">
-        <v>7193538</v>
+        <v>7193483</v>
       </c>
       <c r="S133" t="n">
         <v>25</v>
@@ -14872,7 +14867,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14882,12 +14877,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>11:27</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>Färska och äldre spår på samma träd.</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14914,32 +14904,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129319378</v>
+        <v>129319312</v>
       </c>
       <c r="B134" t="n">
-        <v>82992</v>
+        <v>80147</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>306</v>
+        <v>2081</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14949,10 +14939,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>540757</v>
+        <v>540789</v>
       </c>
       <c r="R134" t="n">
-        <v>7193474</v>
+        <v>7193373</v>
       </c>
       <c r="S134" t="n">
         <v>25</v>
@@ -14984,7 +14974,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14994,7 +14984,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15021,10 +15011,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129319380</v>
+        <v>129319378</v>
       </c>
       <c r="B135" t="n">
-        <v>92242</v>
+        <v>82992</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15032,21 +15022,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>3298</v>
+        <v>306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15056,10 +15046,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>540761</v>
+        <v>540757</v>
       </c>
       <c r="R135" t="n">
-        <v>7193490</v>
+        <v>7193474</v>
       </c>
       <c r="S135" t="n">
         <v>25</v>
@@ -15091,7 +15081,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15101,7 +15091,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15128,10 +15118,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129319322</v>
+        <v>129319310</v>
       </c>
       <c r="B136" t="n">
-        <v>80147</v>
+        <v>79041</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15139,21 +15129,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15163,10 +15153,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>540719</v>
+        <v>540830</v>
       </c>
       <c r="R136" t="n">
-        <v>7193483</v>
+        <v>7193366</v>
       </c>
       <c r="S136" t="n">
         <v>25</v>
@@ -15198,7 +15188,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15208,7 +15198,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15235,10 +15225,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129319312</v>
+        <v>129319343</v>
       </c>
       <c r="B137" t="n">
-        <v>80147</v>
+        <v>57727</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15246,34 +15236,39 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>540789</v>
+        <v>540661</v>
       </c>
       <c r="R137" t="n">
-        <v>7193373</v>
+        <v>7193538</v>
       </c>
       <c r="S137" t="n">
         <v>25</v>
@@ -15305,7 +15300,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15315,7 +15310,12 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>Färska och äldre spår på samma träd.</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15342,32 +15342,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129319387</v>
+        <v>129319287</v>
       </c>
       <c r="B138" t="n">
-        <v>82999</v>
+        <v>92242</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>308</v>
+        <v>3298</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15377,10 +15377,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>540772</v>
+        <v>540913</v>
       </c>
       <c r="R138" t="n">
-        <v>7193446</v>
+        <v>7193185</v>
       </c>
       <c r="S138" t="n">
         <v>25</v>
@@ -15412,7 +15412,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15422,7 +15422,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15449,10 +15449,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129319406</v>
+        <v>129319428</v>
       </c>
       <c r="B139" t="n">
-        <v>79120</v>
+        <v>80146</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15460,21 +15460,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>864</v>
+        <v>6458</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15484,10 +15484,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>540938</v>
+        <v>540971</v>
       </c>
       <c r="R139" t="n">
-        <v>7193168</v>
+        <v>7193081</v>
       </c>
       <c r="S139" t="n">
         <v>25</v>
@@ -15519,7 +15519,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15529,7 +15529,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15556,32 +15556,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129319428</v>
+        <v>129319315</v>
       </c>
       <c r="B140" t="n">
-        <v>80146</v>
+        <v>82990</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6458</v>
+        <v>6439</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15591,10 +15591,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>540971</v>
+        <v>540765</v>
       </c>
       <c r="R140" t="n">
-        <v>7193081</v>
+        <v>7193370</v>
       </c>
       <c r="S140" t="n">
         <v>25</v>
@@ -15626,7 +15626,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15636,7 +15636,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15663,32 +15663,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129319347</v>
+        <v>129319327</v>
       </c>
       <c r="B141" t="n">
-        <v>80182</v>
+        <v>79041</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15698,10 +15698,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>540653</v>
+        <v>540693</v>
       </c>
       <c r="R141" t="n">
-        <v>7193521</v>
+        <v>7193540</v>
       </c>
       <c r="S141" t="n">
         <v>25</v>
@@ -15733,7 +15733,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15743,7 +15743,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15770,32 +15770,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129319315</v>
+        <v>129319387</v>
       </c>
       <c r="B142" t="n">
-        <v>82990</v>
+        <v>82999</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6439</v>
+        <v>308</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15805,10 +15805,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>540765</v>
+        <v>540772</v>
       </c>
       <c r="R142" t="n">
-        <v>7193370</v>
+        <v>7193446</v>
       </c>
       <c r="S142" t="n">
         <v>25</v>
@@ -15840,7 +15840,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15850,7 +15850,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15877,10 +15877,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129319327</v>
+        <v>129319406</v>
       </c>
       <c r="B143" t="n">
-        <v>79041</v>
+        <v>79120</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15888,21 +15888,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15912,10 +15912,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>540693</v>
+        <v>540938</v>
       </c>
       <c r="R143" t="n">
-        <v>7193540</v>
+        <v>7193168</v>
       </c>
       <c r="S143" t="n">
         <v>25</v>
@@ -15947,7 +15947,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15957,7 +15957,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15984,10 +15984,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129319287</v>
+        <v>129319347</v>
       </c>
       <c r="B144" t="n">
-        <v>92242</v>
+        <v>80182</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15995,21 +15995,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>3298</v>
+        <v>6464</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -16019,10 +16019,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>540913</v>
+        <v>540653</v>
       </c>
       <c r="R144" t="n">
-        <v>7193185</v>
+        <v>7193521</v>
       </c>
       <c r="S144" t="n">
         <v>25</v>
@@ -16054,7 +16054,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16064,7 +16064,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD144" t="b">

--- a/artfynd/A 51086-2025 artfynd.xlsx
+++ b/artfynd/A 51086-2025 artfynd.xlsx
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129319307</v>
+        <v>129319384</v>
       </c>
       <c r="B4" t="n">
-        <v>91538</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540962</v>
+        <v>540775</v>
       </c>
       <c r="R4" t="n">
-        <v>7193400</v>
+        <v>7193467</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129319285</v>
+        <v>129319302</v>
       </c>
       <c r="B5" t="n">
-        <v>91538</v>
+        <v>79041</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540886</v>
+        <v>540960</v>
       </c>
       <c r="R5" t="n">
-        <v>7193172</v>
+        <v>7193375</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,32 +1108,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129319386</v>
+        <v>129319420</v>
       </c>
       <c r="B6" t="n">
-        <v>95904</v>
+        <v>80146</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2809</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540774</v>
+        <v>540982</v>
       </c>
       <c r="R6" t="n">
-        <v>7193457</v>
+        <v>7193144</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,45 +1215,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129319384</v>
+        <v>129319414</v>
       </c>
       <c r="B7" t="n">
-        <v>79041</v>
+        <v>58360</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>102125</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540775</v>
+        <v>540963</v>
       </c>
       <c r="R7" t="n">
-        <v>7193467</v>
+        <v>7193203</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1285,7 +1294,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1295,7 +1304,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1322,10 +1331,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129319302</v>
+        <v>129319307</v>
       </c>
       <c r="B8" t="n">
-        <v>79041</v>
+        <v>91538</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1333,21 +1342,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1357,10 +1366,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540960</v>
+        <v>540962</v>
       </c>
       <c r="R8" t="n">
-        <v>7193375</v>
+        <v>7193400</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1392,7 +1401,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1402,7 +1411,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1429,10 +1438,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129319420</v>
+        <v>129319285</v>
       </c>
       <c r="B9" t="n">
-        <v>80146</v>
+        <v>91538</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1440,21 +1449,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1473,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540982</v>
+        <v>540886</v>
       </c>
       <c r="R9" t="n">
-        <v>7193144</v>
+        <v>7193172</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1499,7 +1508,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1509,7 +1518,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,54 +1545,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129319414</v>
+        <v>129319386</v>
       </c>
       <c r="B10" t="n">
-        <v>58360</v>
+        <v>95904</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102125</v>
+        <v>2809</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540963</v>
+        <v>540774</v>
       </c>
       <c r="R10" t="n">
-        <v>7193203</v>
+        <v>7193457</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1615,7 +1615,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -5834,32 +5834,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129319366</v>
+        <v>129319280</v>
       </c>
       <c r="B50" t="n">
-        <v>80146</v>
+        <v>95904</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>2809</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5869,10 +5869,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>540738</v>
+        <v>540900</v>
       </c>
       <c r="R50" t="n">
-        <v>7193503</v>
+        <v>7193073</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5904,7 +5904,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5941,10 +5941,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129319356</v>
+        <v>129319335</v>
       </c>
       <c r="B51" t="n">
-        <v>80146</v>
+        <v>80147</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5952,21 +5952,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5976,10 +5976,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>540726</v>
+        <v>540655</v>
       </c>
       <c r="R51" t="n">
-        <v>7193540</v>
+        <v>7193534</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6011,7 +6011,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6021,7 +6021,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6048,32 +6048,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129319280</v>
+        <v>129319366</v>
       </c>
       <c r="B52" t="n">
-        <v>95904</v>
+        <v>80146</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2809</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6083,10 +6083,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>540900</v>
+        <v>540738</v>
       </c>
       <c r="R52" t="n">
-        <v>7193073</v>
+        <v>7193503</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6118,7 +6118,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6155,10 +6155,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129319335</v>
+        <v>129319356</v>
       </c>
       <c r="B53" t="n">
-        <v>80147</v>
+        <v>80146</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6166,21 +6166,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6190,10 +6190,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>540655</v>
+        <v>540726</v>
       </c>
       <c r="R53" t="n">
-        <v>7193534</v>
+        <v>7193540</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6225,7 +6225,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6235,7 +6235,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6262,10 +6262,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129319388</v>
+        <v>129319429</v>
       </c>
       <c r="B54" t="n">
-        <v>57727</v>
+        <v>80147</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6273,48 +6273,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>540828</v>
+        <v>540972</v>
       </c>
       <c r="R54" t="n">
-        <v>7193425</v>
+        <v>7193067</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6346,7 +6332,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6356,7 +6342,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6383,7 +6369,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129319429</v>
+        <v>129319417</v>
       </c>
       <c r="B55" t="n">
         <v>80147</v>
@@ -6418,10 +6404,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>540972</v>
+        <v>540989</v>
       </c>
       <c r="R55" t="n">
-        <v>7193067</v>
+        <v>7193132</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6453,7 +6439,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6463,7 +6449,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6490,10 +6476,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129319417</v>
+        <v>129319304</v>
       </c>
       <c r="B56" t="n">
-        <v>80147</v>
+        <v>79041</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6501,21 +6487,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6525,10 +6511,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>540989</v>
+        <v>540962</v>
       </c>
       <c r="R56" t="n">
-        <v>7193132</v>
+        <v>7193388</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6560,7 +6546,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6570,7 +6556,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6597,10 +6583,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129319304</v>
+        <v>129319388</v>
       </c>
       <c r="B57" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6608,34 +6594,48 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>540962</v>
+        <v>540828</v>
       </c>
       <c r="R57" t="n">
-        <v>7193388</v>
+        <v>7193425</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6667,7 +6667,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8327,54 +8327,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129319432</v>
+        <v>129319402</v>
       </c>
       <c r="B73" t="n">
-        <v>58360</v>
+        <v>79041</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>102125</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>540978</v>
+        <v>540936</v>
       </c>
       <c r="R73" t="n">
-        <v>7193078</v>
+        <v>7193225</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8406,7 +8397,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8416,7 +8407,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8443,32 +8434,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129319367</v>
+        <v>129319412</v>
       </c>
       <c r="B74" t="n">
-        <v>80175</v>
+        <v>91560</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8478,10 +8469,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>540734</v>
+        <v>540952</v>
       </c>
       <c r="R74" t="n">
-        <v>7193503</v>
+        <v>7193187</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8513,7 +8504,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8523,7 +8514,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8550,7 +8541,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129319402</v>
+        <v>129319413</v>
       </c>
       <c r="B75" t="n">
         <v>79041</v>
@@ -8585,10 +8576,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>540936</v>
+        <v>540965</v>
       </c>
       <c r="R75" t="n">
-        <v>7193225</v>
+        <v>7193181</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8620,7 +8611,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8630,7 +8621,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8657,45 +8648,54 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129319412</v>
+        <v>129319432</v>
       </c>
       <c r="B76" t="n">
-        <v>91560</v>
+        <v>58360</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5432</v>
+        <v>102125</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>540952</v>
+        <v>540978</v>
       </c>
       <c r="R76" t="n">
-        <v>7193187</v>
+        <v>7193078</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8727,7 +8727,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8737,7 +8737,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8764,32 +8764,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129319413</v>
+        <v>129319367</v>
       </c>
       <c r="B77" t="n">
-        <v>79041</v>
+        <v>80175</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8799,10 +8799,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>540965</v>
+        <v>540734</v>
       </c>
       <c r="R77" t="n">
-        <v>7193181</v>
+        <v>7193503</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8844,7 +8844,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -12630,32 +12630,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129319426</v>
+        <v>129319425</v>
       </c>
       <c r="B113" t="n">
-        <v>80147</v>
+        <v>80181</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12665,10 +12665,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>540979</v>
+        <v>540980</v>
       </c>
       <c r="R113" t="n">
-        <v>7193115</v>
+        <v>7193116</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -12737,10 +12737,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129319341</v>
+        <v>129319426</v>
       </c>
       <c r="B114" t="n">
-        <v>91538</v>
+        <v>80147</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12748,21 +12748,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12772,10 +12772,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>540670</v>
+        <v>540979</v>
       </c>
       <c r="R114" t="n">
-        <v>7193533</v>
+        <v>7193115</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -12807,7 +12807,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12817,7 +12817,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12844,10 +12844,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129319305</v>
+        <v>129319341</v>
       </c>
       <c r="B115" t="n">
-        <v>91560</v>
+        <v>91538</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12855,21 +12855,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12879,10 +12879,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>540959</v>
+        <v>540670</v>
       </c>
       <c r="R115" t="n">
-        <v>7193395</v>
+        <v>7193533</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12924,7 +12924,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12951,10 +12951,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129319309</v>
+        <v>129319305</v>
       </c>
       <c r="B116" t="n">
-        <v>79041</v>
+        <v>91560</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12962,21 +12962,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12986,10 +12986,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>540894</v>
+        <v>540959</v>
       </c>
       <c r="R116" t="n">
-        <v>7193411</v>
+        <v>7193395</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -13021,7 +13021,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13031,7 +13031,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13058,10 +13058,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129319332</v>
+        <v>129319309</v>
       </c>
       <c r="B117" t="n">
-        <v>57887</v>
+        <v>79041</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13069,43 +13069,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>540675</v>
+        <v>540894</v>
       </c>
       <c r="R117" t="n">
-        <v>7193538</v>
+        <v>7193411</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -13137,7 +13128,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13147,7 +13138,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13174,45 +13165,54 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129319425</v>
+        <v>129319332</v>
       </c>
       <c r="B118" t="n">
-        <v>80181</v>
+        <v>57887</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6463</v>
+        <v>103021</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>540980</v>
+        <v>540675</v>
       </c>
       <c r="R118" t="n">
-        <v>7193116</v>
+        <v>7193538</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -13244,7 +13244,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13254,7 +13254,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -14369,10 +14369,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129319326</v>
+        <v>129319379</v>
       </c>
       <c r="B129" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14380,21 +14380,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14404,10 +14404,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>540701</v>
+        <v>540761</v>
       </c>
       <c r="R129" t="n">
-        <v>7193533</v>
+        <v>7193485</v>
       </c>
       <c r="S129" t="n">
         <v>25</v>
@@ -14439,7 +14439,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14449,7 +14449,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14476,7 +14476,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129319434</v>
+        <v>129319326</v>
       </c>
       <c r="B130" t="n">
         <v>80146</v>
@@ -14511,10 +14511,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>540979</v>
+        <v>540701</v>
       </c>
       <c r="R130" t="n">
-        <v>7193075</v>
+        <v>7193533</v>
       </c>
       <c r="S130" t="n">
         <v>25</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14556,7 +14556,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14583,10 +14583,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129319379</v>
+        <v>129319434</v>
       </c>
       <c r="B131" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14594,21 +14594,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14618,10 +14618,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>540761</v>
+        <v>540979</v>
       </c>
       <c r="R131" t="n">
-        <v>7193485</v>
+        <v>7193075</v>
       </c>
       <c r="S131" t="n">
         <v>25</v>
@@ -14653,7 +14653,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14663,7 +14663,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD131" t="b">

--- a/artfynd/A 51086-2025 artfynd.xlsx
+++ b/artfynd/A 51086-2025 artfynd.xlsx
@@ -675,45 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129319323</v>
+        <v>129319414</v>
       </c>
       <c r="B2" t="n">
-        <v>80182</v>
+        <v>58360</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6464</v>
+        <v>102125</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540719</v>
+        <v>540963</v>
       </c>
       <c r="R2" t="n">
-        <v>7193483</v>
+        <v>7193203</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,50 +791,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129319300</v>
+        <v>129319386</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>95930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>2809</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540961</v>
+        <v>540774</v>
       </c>
       <c r="R3" t="n">
-        <v>7193376</v>
+        <v>7193457</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -857,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129319384</v>
+        <v>129319307</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>91536</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540775</v>
+        <v>540962</v>
       </c>
       <c r="R4" t="n">
-        <v>7193467</v>
+        <v>7193400</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -964,7 +968,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +978,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129319302</v>
+        <v>129319285</v>
       </c>
       <c r="B5" t="n">
-        <v>79041</v>
+        <v>91536</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,21 +1016,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540960</v>
+        <v>540886</v>
       </c>
       <c r="R5" t="n">
-        <v>7193375</v>
+        <v>7193172</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1071,7 +1075,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1085,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,10 +1112,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129319420</v>
+        <v>129319384</v>
       </c>
       <c r="B6" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,21 +1123,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1147,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540982</v>
+        <v>540775</v>
       </c>
       <c r="R6" t="n">
-        <v>7193144</v>
+        <v>7193467</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1178,7 +1182,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1192,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,54 +1219,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129319414</v>
+        <v>129319323</v>
       </c>
       <c r="B7" t="n">
-        <v>58360</v>
+        <v>80182</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102125</v>
+        <v>6464</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540963</v>
+        <v>540719</v>
       </c>
       <c r="R7" t="n">
-        <v>7193203</v>
+        <v>7193483</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1294,7 +1289,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1304,7 +1299,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1331,10 +1326,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129319307</v>
+        <v>129319302</v>
       </c>
       <c r="B8" t="n">
-        <v>91538</v>
+        <v>79041</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1342,21 +1337,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1366,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540962</v>
+        <v>540960</v>
       </c>
       <c r="R8" t="n">
-        <v>7193400</v>
+        <v>7193375</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1401,7 +1396,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1411,7 +1406,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1438,10 +1433,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129319285</v>
+        <v>129319420</v>
       </c>
       <c r="B9" t="n">
-        <v>91538</v>
+        <v>80146</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1449,21 +1444,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1473,10 +1468,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540886</v>
+        <v>540982</v>
       </c>
       <c r="R9" t="n">
-        <v>7193172</v>
+        <v>7193144</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1508,7 +1503,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1518,7 +1513,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1545,45 +1540,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129319386</v>
+        <v>129319300</v>
       </c>
       <c r="B10" t="n">
-        <v>95904</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2809</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540774</v>
+        <v>540961</v>
       </c>
       <c r="R10" t="n">
-        <v>7193457</v>
+        <v>7193376</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1615,7 +1615,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1652,45 +1652,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129319295</v>
+        <v>129319438</v>
       </c>
       <c r="B11" t="n">
-        <v>95904</v>
+        <v>57887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2809</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540972</v>
+        <v>540982</v>
       </c>
       <c r="R11" t="n">
-        <v>7193357</v>
+        <v>7193110</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1722,7 +1731,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1732,7 +1741,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1759,32 +1768,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129319361</v>
+        <v>129319295</v>
       </c>
       <c r="B12" t="n">
-        <v>91542</v>
+        <v>95930</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>2809</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1794,10 +1803,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540726</v>
+        <v>540972</v>
       </c>
       <c r="R12" t="n">
-        <v>7193531</v>
+        <v>7193357</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1829,7 +1838,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1839,7 +1848,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2080,10 +2089,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129319438</v>
+        <v>129319361</v>
       </c>
       <c r="B15" t="n">
-        <v>57887</v>
+        <v>91540</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2091,43 +2100,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540982</v>
+        <v>540726</v>
       </c>
       <c r="R15" t="n">
-        <v>7193110</v>
+        <v>7193531</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2159,7 +2159,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2196,32 +2196,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129319352</v>
+        <v>129319419</v>
       </c>
       <c r="B16" t="n">
-        <v>78054</v>
+        <v>80181</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228579</v>
+        <v>6463</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540715</v>
+        <v>540986</v>
       </c>
       <c r="R16" t="n">
-        <v>7193537</v>
+        <v>7193130</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2410,32 +2410,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129319296</v>
+        <v>129319313</v>
       </c>
       <c r="B18" t="n">
-        <v>79041</v>
+        <v>80182</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2445,10 +2445,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540970</v>
+        <v>540789</v>
       </c>
       <c r="R18" t="n">
-        <v>7193365</v>
+        <v>7193372</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2480,7 +2480,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2517,10 +2517,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129319324</v>
+        <v>129319296</v>
       </c>
       <c r="B19" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2528,21 +2528,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2552,10 +2552,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540719</v>
+        <v>540970</v>
       </c>
       <c r="R19" t="n">
-        <v>7193483</v>
+        <v>7193365</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2624,32 +2624,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129319419</v>
+        <v>129319324</v>
       </c>
       <c r="B20" t="n">
-        <v>80181</v>
+        <v>80146</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540986</v>
+        <v>540719</v>
       </c>
       <c r="R20" t="n">
-        <v>7193130</v>
+        <v>7193483</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2731,10 +2731,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129319313</v>
+        <v>129319430</v>
       </c>
       <c r="B21" t="n">
-        <v>80182</v>
+        <v>80181</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2742,21 +2742,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2766,10 +2766,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540789</v>
+        <v>540971</v>
       </c>
       <c r="R21" t="n">
-        <v>7193372</v>
+        <v>7193066</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2838,32 +2838,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129319430</v>
+        <v>129319352</v>
       </c>
       <c r="B22" t="n">
-        <v>80181</v>
+        <v>78054</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6463</v>
+        <v>228579</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540971</v>
+        <v>540715</v>
       </c>
       <c r="R22" t="n">
-        <v>7193066</v>
+        <v>7193537</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3269,7 +3269,7 @@
         <v>129319340</v>
       </c>
       <c r="B26" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3587,10 +3587,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129319349</v>
+        <v>129319354</v>
       </c>
       <c r="B29" t="n">
-        <v>91560</v>
+        <v>79041</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3598,21 +3598,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3622,10 +3622,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>540670</v>
+        <v>540722</v>
       </c>
       <c r="R29" t="n">
-        <v>7193521</v>
+        <v>7193542</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3657,7 +3657,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3667,7 +3667,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3694,10 +3694,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129319354</v>
+        <v>129319349</v>
       </c>
       <c r="B30" t="n">
-        <v>79041</v>
+        <v>91558</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3705,21 +3705,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3729,10 +3729,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>540722</v>
+        <v>540670</v>
       </c>
       <c r="R30" t="n">
-        <v>7193542</v>
+        <v>7193521</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3764,7 +3764,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4015,32 +4015,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129319422</v>
+        <v>129319337</v>
       </c>
       <c r="B33" t="n">
-        <v>80181</v>
+        <v>80146</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4050,10 +4050,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>540980</v>
+        <v>540676</v>
       </c>
       <c r="R33" t="n">
-        <v>7193139</v>
+        <v>7193539</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4085,7 +4085,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4122,32 +4122,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129319337</v>
+        <v>129319422</v>
       </c>
       <c r="B34" t="n">
-        <v>80146</v>
+        <v>80181</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4157,10 +4157,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>540676</v>
+        <v>540980</v>
       </c>
       <c r="R34" t="n">
-        <v>7193539</v>
+        <v>7193139</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4764,7 +4764,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129319278</v>
+        <v>129319365</v>
       </c>
       <c r="B40" t="n">
         <v>80147</v>
@@ -4799,10 +4799,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>540864</v>
+        <v>540738</v>
       </c>
       <c r="R40" t="n">
-        <v>7193066</v>
+        <v>7193503</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4871,10 +4871,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129319365</v>
+        <v>129319294</v>
       </c>
       <c r="B41" t="n">
-        <v>80147</v>
+        <v>83012</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4882,21 +4882,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>1467</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4906,10 +4906,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>540738</v>
+        <v>540974</v>
       </c>
       <c r="R41" t="n">
-        <v>7193503</v>
+        <v>7193351</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4941,7 +4941,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4951,7 +4951,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5085,10 +5085,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129319294</v>
+        <v>129319303</v>
       </c>
       <c r="B43" t="n">
-        <v>83012</v>
+        <v>79041</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5096,21 +5096,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5120,10 +5120,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540974</v>
+        <v>540934</v>
       </c>
       <c r="R43" t="n">
-        <v>7193351</v>
+        <v>7193385</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5155,7 +5155,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5192,10 +5192,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129319303</v>
+        <v>129319348</v>
       </c>
       <c r="B44" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5203,21 +5203,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5227,10 +5227,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540934</v>
+        <v>540653</v>
       </c>
       <c r="R44" t="n">
-        <v>7193385</v>
+        <v>7193521</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5262,7 +5262,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5272,7 +5272,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5299,10 +5299,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129319348</v>
+        <v>129319288</v>
       </c>
       <c r="B45" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5310,21 +5310,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5334,10 +5334,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>540653</v>
+        <v>540915</v>
       </c>
       <c r="R45" t="n">
-        <v>7193521</v>
+        <v>7193185</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5369,7 +5369,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5379,7 +5379,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5406,32 +5406,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129319288</v>
+        <v>129319401</v>
       </c>
       <c r="B46" t="n">
-        <v>79041</v>
+        <v>80175</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5441,10 +5441,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>540915</v>
+        <v>540942</v>
       </c>
       <c r="R46" t="n">
-        <v>7193185</v>
+        <v>7193229</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5476,7 +5476,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5620,10 +5620,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129319401</v>
+        <v>129319320</v>
       </c>
       <c r="B48" t="n">
-        <v>80175</v>
+        <v>80181</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5631,21 +5631,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5655,10 +5655,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>540942</v>
+        <v>540719</v>
       </c>
       <c r="R48" t="n">
-        <v>7193229</v>
+        <v>7193463</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5690,7 +5690,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5700,7 +5700,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5727,32 +5727,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129319320</v>
+        <v>129319278</v>
       </c>
       <c r="B49" t="n">
-        <v>80181</v>
+        <v>80147</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5762,10 +5762,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>540719</v>
+        <v>540864</v>
       </c>
       <c r="R49" t="n">
-        <v>7193463</v>
+        <v>7193066</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5797,7 +5797,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5807,7 +5807,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5837,7 +5837,7 @@
         <v>129319280</v>
       </c>
       <c r="B50" t="n">
-        <v>95904</v>
+        <v>95930</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6476,10 +6476,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129319304</v>
+        <v>129319388</v>
       </c>
       <c r="B56" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6487,34 +6487,48 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>540962</v>
+        <v>540828</v>
       </c>
       <c r="R56" t="n">
-        <v>7193388</v>
+        <v>7193425</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6546,7 +6560,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6556,7 +6570,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6583,10 +6597,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129319388</v>
+        <v>129319304</v>
       </c>
       <c r="B57" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6594,48 +6608,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>540828</v>
+        <v>540962</v>
       </c>
       <c r="R57" t="n">
-        <v>7193425</v>
+        <v>7193388</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6667,7 +6667,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7028,7 +7028,7 @@
         <v>129319311</v>
       </c>
       <c r="B61" t="n">
-        <v>91538</v>
+        <v>91536</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7783,32 +7783,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129319334</v>
+        <v>129319421</v>
       </c>
       <c r="B68" t="n">
-        <v>80146</v>
+        <v>80175</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7818,10 +7818,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>540674</v>
+        <v>540981</v>
       </c>
       <c r="R68" t="n">
-        <v>7193550</v>
+        <v>7193140</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7890,10 +7890,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129319400</v>
+        <v>129319334</v>
       </c>
       <c r="B69" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7901,21 +7901,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7925,10 +7925,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>540943</v>
+        <v>540674</v>
       </c>
       <c r="R69" t="n">
-        <v>7193233</v>
+        <v>7193550</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7960,7 +7960,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7997,10 +7997,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129319293</v>
+        <v>129319400</v>
       </c>
       <c r="B70" t="n">
-        <v>57887</v>
+        <v>79041</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8008,43 +8008,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>540980</v>
+        <v>540943</v>
       </c>
       <c r="R70" t="n">
-        <v>7193345</v>
+        <v>7193233</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8076,7 +8067,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8086,7 +8077,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8113,7 +8104,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129319421</v>
+        <v>129319370</v>
       </c>
       <c r="B71" t="n">
         <v>80175</v>
@@ -8148,10 +8139,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>540981</v>
+        <v>540737</v>
       </c>
       <c r="R71" t="n">
-        <v>7193140</v>
+        <v>7193504</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8183,7 +8174,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8193,7 +8184,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8220,45 +8211,54 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129319370</v>
+        <v>129319293</v>
       </c>
       <c r="B72" t="n">
-        <v>80175</v>
+        <v>57887</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>540737</v>
+        <v>540980</v>
       </c>
       <c r="R72" t="n">
-        <v>7193504</v>
+        <v>7193345</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8290,7 +8290,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8300,7 +8300,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8327,10 +8327,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129319402</v>
+        <v>129319412</v>
       </c>
       <c r="B73" t="n">
-        <v>79041</v>
+        <v>91558</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8338,21 +8338,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8362,10 +8362,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>540936</v>
+        <v>540952</v>
       </c>
       <c r="R73" t="n">
-        <v>7193225</v>
+        <v>7193187</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8397,7 +8397,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8407,7 +8407,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8434,10 +8434,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129319412</v>
+        <v>129319402</v>
       </c>
       <c r="B74" t="n">
-        <v>91560</v>
+        <v>79041</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8445,21 +8445,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8469,10 +8469,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>540952</v>
+        <v>540936</v>
       </c>
       <c r="R74" t="n">
-        <v>7193187</v>
+        <v>7193225</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8504,7 +8504,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8514,7 +8514,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8648,54 +8648,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129319432</v>
+        <v>129319367</v>
       </c>
       <c r="B76" t="n">
-        <v>58360</v>
+        <v>80175</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>102125</v>
+        <v>6462</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>540978</v>
+        <v>540734</v>
       </c>
       <c r="R76" t="n">
-        <v>7193078</v>
+        <v>7193503</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8727,7 +8718,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8737,7 +8728,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8764,45 +8755,54 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129319367</v>
+        <v>129319432</v>
       </c>
       <c r="B77" t="n">
-        <v>80175</v>
+        <v>58360</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6462</v>
+        <v>102125</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>540734</v>
+        <v>540978</v>
       </c>
       <c r="R77" t="n">
-        <v>7193503</v>
+        <v>7193078</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8844,7 +8844,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9090,10 +9090,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129319338</v>
+        <v>129319336</v>
       </c>
       <c r="B80" t="n">
-        <v>80147</v>
+        <v>79041</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9101,21 +9101,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9125,10 +9125,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>540676</v>
+        <v>540668</v>
       </c>
       <c r="R80" t="n">
-        <v>7193539</v>
+        <v>7193543</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9160,7 +9160,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9170,7 +9170,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9197,7 +9197,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129319336</v>
+        <v>129319382</v>
       </c>
       <c r="B81" t="n">
         <v>79041</v>
@@ -9232,10 +9232,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>540668</v>
+        <v>540761</v>
       </c>
       <c r="R81" t="n">
-        <v>7193543</v>
+        <v>7193473</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9267,7 +9267,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9304,10 +9304,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129319382</v>
+        <v>129319408</v>
       </c>
       <c r="B82" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9315,21 +9315,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9339,10 +9339,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>540761</v>
+        <v>540939</v>
       </c>
       <c r="R82" t="n">
-        <v>7193473</v>
+        <v>7193177</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9374,7 +9374,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9384,7 +9384,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9411,32 +9411,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129319394</v>
+        <v>129319431</v>
       </c>
       <c r="B83" t="n">
-        <v>79041</v>
+        <v>80175</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9446,10 +9446,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>540877</v>
+        <v>540979</v>
       </c>
       <c r="R83" t="n">
-        <v>7193291</v>
+        <v>7193075</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9481,7 +9481,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9518,10 +9518,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129319408</v>
+        <v>129319394</v>
       </c>
       <c r="B84" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9529,21 +9529,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9553,10 +9553,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>540939</v>
+        <v>540877</v>
       </c>
       <c r="R84" t="n">
-        <v>7193177</v>
+        <v>7193291</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9588,7 +9588,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9625,32 +9625,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129319431</v>
+        <v>129319338</v>
       </c>
       <c r="B85" t="n">
-        <v>80175</v>
+        <v>80147</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9660,10 +9660,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>540979</v>
+        <v>540676</v>
       </c>
       <c r="R85" t="n">
-        <v>7193075</v>
+        <v>7193539</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9695,7 +9695,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9705,7 +9705,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9732,32 +9732,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129319298</v>
+        <v>129319389</v>
       </c>
       <c r="B86" t="n">
-        <v>91560</v>
+        <v>95930</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5432</v>
+        <v>2809</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9767,10 +9767,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>540964</v>
+        <v>540818</v>
       </c>
       <c r="R86" t="n">
-        <v>7193371</v>
+        <v>7193358</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9802,7 +9802,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9812,7 +9812,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9839,10 +9839,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129319284</v>
+        <v>129319375</v>
       </c>
       <c r="B87" t="n">
-        <v>79041</v>
+        <v>80147</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9850,21 +9850,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9874,10 +9874,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>540867</v>
+        <v>540730</v>
       </c>
       <c r="R87" t="n">
-        <v>7193169</v>
+        <v>7193493</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -9909,7 +9909,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9919,7 +9919,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9946,10 +9946,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129319409</v>
+        <v>129319357</v>
       </c>
       <c r="B88" t="n">
-        <v>80146</v>
+        <v>80147</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9957,21 +9957,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9981,10 +9981,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>540942</v>
+        <v>540726</v>
       </c>
       <c r="R88" t="n">
-        <v>7193182</v>
+        <v>7193539</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -10016,7 +10016,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10026,7 +10026,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10053,32 +10053,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129319393</v>
+        <v>129319298</v>
       </c>
       <c r="B89" t="n">
-        <v>82990</v>
+        <v>91558</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6439</v>
+        <v>5432</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10088,10 +10088,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>540824</v>
+        <v>540964</v>
       </c>
       <c r="R89" t="n">
-        <v>7193288</v>
+        <v>7193371</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -10123,7 +10123,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10133,7 +10133,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10160,7 +10160,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129319299</v>
+        <v>129319284</v>
       </c>
       <c r="B90" t="n">
         <v>79041</v>
@@ -10195,10 +10195,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>540964</v>
+        <v>540867</v>
       </c>
       <c r="R90" t="n">
-        <v>7193371</v>
+        <v>7193169</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -10230,7 +10230,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10240,7 +10240,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10267,10 +10267,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129319344</v>
+        <v>129319409</v>
       </c>
       <c r="B91" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10278,21 +10278,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10302,10 +10302,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>540650</v>
+        <v>540942</v>
       </c>
       <c r="R91" t="n">
-        <v>7193540</v>
+        <v>7193182</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -10337,7 +10337,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10347,7 +10347,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10374,10 +10374,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129319389</v>
+        <v>129319393</v>
       </c>
       <c r="B92" t="n">
-        <v>95904</v>
+        <v>82990</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10385,21 +10385,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2809</v>
+        <v>6439</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10409,10 +10409,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>540818</v>
+        <v>540824</v>
       </c>
       <c r="R92" t="n">
-        <v>7193358</v>
+        <v>7193288</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -10444,7 +10444,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10454,7 +10454,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10481,10 +10481,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129319333</v>
+        <v>129319299</v>
       </c>
       <c r="B93" t="n">
-        <v>80147</v>
+        <v>79041</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10492,21 +10492,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10516,10 +10516,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>540674</v>
+        <v>540964</v>
       </c>
       <c r="R93" t="n">
-        <v>7193551</v>
+        <v>7193371</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -10551,7 +10551,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10561,7 +10561,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10588,10 +10588,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129319376</v>
+        <v>129319344</v>
       </c>
       <c r="B94" t="n">
-        <v>80147</v>
+        <v>79041</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10599,21 +10599,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10623,10 +10623,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>540738</v>
+        <v>540650</v>
       </c>
       <c r="R94" t="n">
-        <v>7193476</v>
+        <v>7193540</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -10658,7 +10658,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10668,7 +10668,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10695,7 +10695,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129319375</v>
+        <v>129319333</v>
       </c>
       <c r="B95" t="n">
         <v>80147</v>
@@ -10730,10 +10730,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>540730</v>
+        <v>540674</v>
       </c>
       <c r="R95" t="n">
-        <v>7193493</v>
+        <v>7193551</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -10765,7 +10765,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10775,7 +10775,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10802,7 +10802,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129319433</v>
+        <v>129319376</v>
       </c>
       <c r="B96" t="n">
         <v>80147</v>
@@ -10837,10 +10837,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>540979</v>
+        <v>540738</v>
       </c>
       <c r="R96" t="n">
-        <v>7193075</v>
+        <v>7193476</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -10872,7 +10872,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10882,7 +10882,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10909,7 +10909,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129319357</v>
+        <v>129319433</v>
       </c>
       <c r="B97" t="n">
         <v>80147</v>
@@ -10944,10 +10944,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>540726</v>
+        <v>540979</v>
       </c>
       <c r="R97" t="n">
-        <v>7193539</v>
+        <v>7193075</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -10979,7 +10979,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10989,7 +10989,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11881,10 +11881,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129319360</v>
+        <v>129319369</v>
       </c>
       <c r="B106" t="n">
-        <v>91538</v>
+        <v>80147</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11892,21 +11892,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11916,10 +11916,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>540725</v>
+        <v>540734</v>
       </c>
       <c r="R106" t="n">
-        <v>7193532</v>
+        <v>7193503</v>
       </c>
       <c r="S106" t="n">
         <v>25</v>
@@ -11951,7 +11951,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11961,7 +11961,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11988,7 +11988,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129319369</v>
+        <v>129319391</v>
       </c>
       <c r="B107" t="n">
         <v>80147</v>
@@ -12023,10 +12023,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>540734</v>
+        <v>540818</v>
       </c>
       <c r="R107" t="n">
-        <v>7193503</v>
+        <v>7193333</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -12058,7 +12058,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12068,7 +12068,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12095,10 +12095,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129319391</v>
+        <v>129319360</v>
       </c>
       <c r="B108" t="n">
-        <v>80147</v>
+        <v>91536</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12106,21 +12106,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12130,10 +12130,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>540818</v>
+        <v>540725</v>
       </c>
       <c r="R108" t="n">
-        <v>7193333</v>
+        <v>7193532</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -12165,7 +12165,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12175,7 +12175,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12416,32 +12416,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129319407</v>
+        <v>129319418</v>
       </c>
       <c r="B111" t="n">
-        <v>79041</v>
+        <v>80182</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12451,10 +12451,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>540924</v>
+        <v>540986</v>
       </c>
       <c r="R111" t="n">
-        <v>7193211</v>
+        <v>7193130</v>
       </c>
       <c r="S111" t="n">
         <v>25</v>
@@ -12486,7 +12486,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12496,7 +12496,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12523,32 +12523,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129319418</v>
+        <v>129319407</v>
       </c>
       <c r="B112" t="n">
-        <v>80182</v>
+        <v>79041</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12558,10 +12558,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>540986</v>
+        <v>540924</v>
       </c>
       <c r="R112" t="n">
-        <v>7193130</v>
+        <v>7193211</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>
@@ -12593,7 +12593,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12603,7 +12603,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12630,32 +12630,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129319425</v>
+        <v>129319341</v>
       </c>
       <c r="B113" t="n">
-        <v>80181</v>
+        <v>91536</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6463</v>
+        <v>1108</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12665,10 +12665,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>540980</v>
+        <v>540670</v>
       </c>
       <c r="R113" t="n">
-        <v>7193116</v>
+        <v>7193533</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -12700,7 +12700,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12710,7 +12710,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12844,32 +12844,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129319341</v>
+        <v>129319425</v>
       </c>
       <c r="B115" t="n">
-        <v>91538</v>
+        <v>80181</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1108</v>
+        <v>6463</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12879,10 +12879,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>540670</v>
+        <v>540980</v>
       </c>
       <c r="R115" t="n">
-        <v>7193533</v>
+        <v>7193116</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12924,7 +12924,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12951,10 +12951,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129319305</v>
+        <v>129319309</v>
       </c>
       <c r="B116" t="n">
-        <v>91560</v>
+        <v>79041</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12962,21 +12962,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12986,10 +12986,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>540959</v>
+        <v>540894</v>
       </c>
       <c r="R116" t="n">
-        <v>7193395</v>
+        <v>7193411</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -13021,7 +13021,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13031,7 +13031,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13058,10 +13058,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129319309</v>
+        <v>129319305</v>
       </c>
       <c r="B117" t="n">
-        <v>79041</v>
+        <v>91558</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13069,21 +13069,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>540894</v>
+        <v>540959</v>
       </c>
       <c r="R117" t="n">
-        <v>7193411</v>
+        <v>7193395</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -13128,7 +13128,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13138,7 +13138,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13495,10 +13495,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129319329</v>
+        <v>129319319</v>
       </c>
       <c r="B121" t="n">
-        <v>88939</v>
+        <v>80147</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13506,21 +13506,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>510</v>
+        <v>2081</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13530,10 +13530,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>540692</v>
+        <v>540719</v>
       </c>
       <c r="R121" t="n">
-        <v>7193539</v>
+        <v>7193463</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -13565,7 +13565,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13575,7 +13575,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13602,10 +13602,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129319319</v>
+        <v>129319329</v>
       </c>
       <c r="B122" t="n">
-        <v>80147</v>
+        <v>88940</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13613,21 +13613,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>2081</v>
+        <v>510</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13637,10 +13637,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>540719</v>
+        <v>540692</v>
       </c>
       <c r="R122" t="n">
-        <v>7193463</v>
+        <v>7193539</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -13672,7 +13672,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13682,7 +13682,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13709,54 +13709,45 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129319410</v>
+        <v>129319416</v>
       </c>
       <c r="B123" t="n">
-        <v>56908</v>
+        <v>80182</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>102612</v>
+        <v>6464</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>540946</v>
+        <v>540970</v>
       </c>
       <c r="R123" t="n">
-        <v>7193171</v>
+        <v>7193154</v>
       </c>
       <c r="S123" t="n">
         <v>25</v>
@@ -13788,7 +13779,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13798,7 +13789,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13825,54 +13816,45 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129319363</v>
+        <v>129319373</v>
       </c>
       <c r="B124" t="n">
-        <v>58360</v>
+        <v>80182</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>102125</v>
+        <v>6464</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>540731</v>
+        <v>540734</v>
       </c>
       <c r="R124" t="n">
-        <v>7193512</v>
+        <v>7193499</v>
       </c>
       <c r="S124" t="n">
         <v>25</v>
@@ -13904,7 +13886,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13914,7 +13896,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13941,32 +13923,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129319350</v>
+        <v>129319321</v>
       </c>
       <c r="B125" t="n">
-        <v>80146</v>
+        <v>80175</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13976,10 +13958,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>540681</v>
+        <v>540719</v>
       </c>
       <c r="R125" t="n">
-        <v>7193521</v>
+        <v>7193463</v>
       </c>
       <c r="S125" t="n">
         <v>25</v>
@@ -14011,7 +13993,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14021,7 +14003,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14048,32 +14030,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129319416</v>
+        <v>129319350</v>
       </c>
       <c r="B126" t="n">
-        <v>80182</v>
+        <v>80146</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14083,10 +14065,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>540970</v>
+        <v>540681</v>
       </c>
       <c r="R126" t="n">
-        <v>7193154</v>
+        <v>7193521</v>
       </c>
       <c r="S126" t="n">
         <v>25</v>
@@ -14118,7 +14100,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14128,7 +14110,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14155,45 +14137,54 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129319373</v>
+        <v>129319363</v>
       </c>
       <c r="B127" t="n">
-        <v>80182</v>
+        <v>58360</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6464</v>
+        <v>102125</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>540734</v>
+        <v>540731</v>
       </c>
       <c r="R127" t="n">
-        <v>7193499</v>
+        <v>7193512</v>
       </c>
       <c r="S127" t="n">
         <v>25</v>
@@ -14225,7 +14216,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14235,7 +14226,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14262,45 +14253,54 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129319321</v>
+        <v>129319410</v>
       </c>
       <c r="B128" t="n">
-        <v>80175</v>
+        <v>56908</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6462</v>
+        <v>102612</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>540719</v>
+        <v>540946</v>
       </c>
       <c r="R128" t="n">
-        <v>7193463</v>
+        <v>7193171</v>
       </c>
       <c r="S128" t="n">
         <v>25</v>
@@ -14332,7 +14332,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14342,7 +14342,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14369,10 +14369,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129319379</v>
+        <v>129319326</v>
       </c>
       <c r="B129" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14380,21 +14380,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14404,10 +14404,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>540761</v>
+        <v>540701</v>
       </c>
       <c r="R129" t="n">
-        <v>7193485</v>
+        <v>7193533</v>
       </c>
       <c r="S129" t="n">
         <v>25</v>
@@ -14439,7 +14439,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14449,7 +14449,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14476,10 +14476,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129319326</v>
+        <v>129319379</v>
       </c>
       <c r="B130" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14487,21 +14487,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14511,10 +14511,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>540701</v>
+        <v>540761</v>
       </c>
       <c r="R130" t="n">
-        <v>7193533</v>
+        <v>7193485</v>
       </c>
       <c r="S130" t="n">
         <v>25</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14556,7 +14556,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14690,10 +14690,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129319380</v>
+        <v>129319378</v>
       </c>
       <c r="B132" t="n">
-        <v>92242</v>
+        <v>82992</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14701,21 +14701,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>3298</v>
+        <v>306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14725,10 +14725,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>540761</v>
+        <v>540757</v>
       </c>
       <c r="R132" t="n">
-        <v>7193490</v>
+        <v>7193474</v>
       </c>
       <c r="S132" t="n">
         <v>25</v>
@@ -14760,7 +14760,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14770,7 +14770,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14797,10 +14797,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129319322</v>
+        <v>129319310</v>
       </c>
       <c r="B133" t="n">
-        <v>80147</v>
+        <v>79041</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14808,21 +14808,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14832,10 +14832,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>540719</v>
+        <v>540830</v>
       </c>
       <c r="R133" t="n">
-        <v>7193483</v>
+        <v>7193366</v>
       </c>
       <c r="S133" t="n">
         <v>25</v>
@@ -14867,7 +14867,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14877,7 +14877,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14904,10 +14904,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129319312</v>
+        <v>129319343</v>
       </c>
       <c r="B134" t="n">
-        <v>80147</v>
+        <v>57727</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14915,34 +14915,39 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>540789</v>
+        <v>540661</v>
       </c>
       <c r="R134" t="n">
-        <v>7193373</v>
+        <v>7193538</v>
       </c>
       <c r="S134" t="n">
         <v>25</v>
@@ -14974,7 +14979,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14984,7 +14989,12 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>Färska och äldre spår på samma träd.</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15011,32 +15021,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129319378</v>
+        <v>129319322</v>
       </c>
       <c r="B135" t="n">
-        <v>82992</v>
+        <v>80147</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>306</v>
+        <v>2081</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15046,10 +15056,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>540757</v>
+        <v>540719</v>
       </c>
       <c r="R135" t="n">
-        <v>7193474</v>
+        <v>7193483</v>
       </c>
       <c r="S135" t="n">
         <v>25</v>
@@ -15081,7 +15091,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15091,7 +15101,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15118,10 +15128,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129319310</v>
+        <v>129319312</v>
       </c>
       <c r="B136" t="n">
-        <v>79041</v>
+        <v>80147</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15129,21 +15139,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15153,10 +15163,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>540830</v>
+        <v>540789</v>
       </c>
       <c r="R136" t="n">
-        <v>7193366</v>
+        <v>7193373</v>
       </c>
       <c r="S136" t="n">
         <v>25</v>
@@ -15188,7 +15198,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15198,7 +15208,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15225,50 +15235,45 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129319343</v>
+        <v>129319380</v>
       </c>
       <c r="B137" t="n">
-        <v>57727</v>
+        <v>92257</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P137" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>540661</v>
+        <v>540761</v>
       </c>
       <c r="R137" t="n">
-        <v>7193538</v>
+        <v>7193490</v>
       </c>
       <c r="S137" t="n">
         <v>25</v>
@@ -15300,7 +15305,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15310,12 +15315,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>11:27</t>
-        </is>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>Färska och äldre spår på samma träd.</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15345,7 +15345,7 @@
         <v>129319287</v>
       </c>
       <c r="B138" t="n">
-        <v>92242</v>
+        <v>92257</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15449,10 +15449,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129319428</v>
+        <v>129319387</v>
       </c>
       <c r="B139" t="n">
-        <v>80146</v>
+        <v>82999</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15460,21 +15460,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15484,10 +15484,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>540971</v>
+        <v>540772</v>
       </c>
       <c r="R139" t="n">
-        <v>7193081</v>
+        <v>7193446</v>
       </c>
       <c r="S139" t="n">
         <v>25</v>
@@ -15519,7 +15519,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15529,7 +15529,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15556,32 +15556,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129319315</v>
+        <v>129319406</v>
       </c>
       <c r="B140" t="n">
-        <v>82990</v>
+        <v>79120</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6439</v>
+        <v>864</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15591,10 +15591,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>540765</v>
+        <v>540938</v>
       </c>
       <c r="R140" t="n">
-        <v>7193370</v>
+        <v>7193168</v>
       </c>
       <c r="S140" t="n">
         <v>25</v>
@@ -15626,7 +15626,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15636,7 +15636,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15663,10 +15663,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129319327</v>
+        <v>129319428</v>
       </c>
       <c r="B141" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15674,21 +15674,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15698,10 +15698,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>540693</v>
+        <v>540971</v>
       </c>
       <c r="R141" t="n">
-        <v>7193540</v>
+        <v>7193081</v>
       </c>
       <c r="S141" t="n">
         <v>25</v>
@@ -15733,7 +15733,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15743,7 +15743,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15770,32 +15770,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129319387</v>
+        <v>129319347</v>
       </c>
       <c r="B142" t="n">
-        <v>82999</v>
+        <v>80182</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>308</v>
+        <v>6464</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15805,10 +15805,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>540772</v>
+        <v>540653</v>
       </c>
       <c r="R142" t="n">
-        <v>7193446</v>
+        <v>7193521</v>
       </c>
       <c r="S142" t="n">
         <v>25</v>
@@ -15840,7 +15840,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15850,7 +15850,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15877,32 +15877,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129319406</v>
+        <v>129319315</v>
       </c>
       <c r="B143" t="n">
-        <v>79120</v>
+        <v>82990</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>864</v>
+        <v>6439</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15912,10 +15912,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>540938</v>
+        <v>540765</v>
       </c>
       <c r="R143" t="n">
-        <v>7193168</v>
+        <v>7193370</v>
       </c>
       <c r="S143" t="n">
         <v>25</v>
@@ -15947,7 +15947,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15957,7 +15957,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15984,32 +15984,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129319347</v>
+        <v>129319327</v>
       </c>
       <c r="B144" t="n">
-        <v>80182</v>
+        <v>79041</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -16019,10 +16019,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>540653</v>
+        <v>540693</v>
       </c>
       <c r="R144" t="n">
-        <v>7193521</v>
+        <v>7193540</v>
       </c>
       <c r="S144" t="n">
         <v>25</v>
@@ -16054,7 +16054,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16064,7 +16064,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD144" t="b">

--- a/artfynd/A 51086-2025 artfynd.xlsx
+++ b/artfynd/A 51086-2025 artfynd.xlsx
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129319414</v>
+        <v>129319307</v>
       </c>
       <c r="B2" t="n">
-        <v>58360</v>
+        <v>91536</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102125</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540963</v>
+        <v>540962</v>
       </c>
       <c r="R2" t="n">
-        <v>7193203</v>
+        <v>7193400</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -754,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129319386</v>
+        <v>129319285</v>
       </c>
       <c r="B3" t="n">
-        <v>95930</v>
+        <v>91536</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2809</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540774</v>
+        <v>540886</v>
       </c>
       <c r="R3" t="n">
-        <v>7193457</v>
+        <v>7193172</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -861,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -871,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129319307</v>
+        <v>129319300</v>
       </c>
       <c r="B4" t="n">
-        <v>91536</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -909,34 +900,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540962</v>
+        <v>540961</v>
       </c>
       <c r="R4" t="n">
-        <v>7193400</v>
+        <v>7193376</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -968,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -978,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,45 +1001,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129319285</v>
+        <v>129319414</v>
       </c>
       <c r="B5" t="n">
-        <v>91536</v>
+        <v>58360</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>102125</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540886</v>
+        <v>540963</v>
       </c>
       <c r="R5" t="n">
-        <v>7193172</v>
+        <v>7193203</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1075,7 +1080,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1085,7 +1090,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,32 +1117,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129319384</v>
+        <v>129319386</v>
       </c>
       <c r="B6" t="n">
-        <v>79041</v>
+        <v>95931</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1147,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540775</v>
+        <v>540774</v>
       </c>
       <c r="R6" t="n">
-        <v>7193467</v>
+        <v>7193457</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1182,7 +1187,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1192,7 +1197,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1219,32 +1224,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129319323</v>
+        <v>129319420</v>
       </c>
       <c r="B7" t="n">
-        <v>80182</v>
+        <v>80146</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1254,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540719</v>
+        <v>540982</v>
       </c>
       <c r="R7" t="n">
-        <v>7193483</v>
+        <v>7193144</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1289,7 +1294,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1299,7 +1304,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1326,7 +1331,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129319302</v>
+        <v>129319384</v>
       </c>
       <c r="B8" t="n">
         <v>79041</v>
@@ -1361,10 +1366,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540960</v>
+        <v>540775</v>
       </c>
       <c r="R8" t="n">
-        <v>7193375</v>
+        <v>7193467</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1396,7 +1401,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1406,7 +1411,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1433,32 +1438,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129319420</v>
+        <v>129319323</v>
       </c>
       <c r="B9" t="n">
-        <v>80146</v>
+        <v>80182</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1468,10 +1473,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540982</v>
+        <v>540719</v>
       </c>
       <c r="R9" t="n">
-        <v>7193144</v>
+        <v>7193483</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1503,7 +1508,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1513,7 +1518,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1540,10 +1545,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129319300</v>
+        <v>129319302</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,39 +1556,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540961</v>
+        <v>540960</v>
       </c>
       <c r="R10" t="n">
-        <v>7193376</v>
+        <v>7193375</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1615,7 +1615,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1652,54 +1652,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129319438</v>
+        <v>129319295</v>
       </c>
       <c r="B11" t="n">
-        <v>57887</v>
+        <v>95931</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>2809</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540982</v>
+        <v>540972</v>
       </c>
       <c r="R11" t="n">
-        <v>7193110</v>
+        <v>7193357</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1731,7 +1722,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1741,7 +1732,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1768,32 +1759,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129319295</v>
+        <v>129319361</v>
       </c>
       <c r="B12" t="n">
-        <v>95930</v>
+        <v>91540</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2809</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1803,10 +1794,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540972</v>
+        <v>540726</v>
       </c>
       <c r="R12" t="n">
-        <v>7193357</v>
+        <v>7193531</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1838,7 +1829,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1848,7 +1839,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2089,10 +2080,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129319361</v>
+        <v>129319296</v>
       </c>
       <c r="B15" t="n">
-        <v>91540</v>
+        <v>79041</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2100,21 +2091,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2124,10 +2115,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540726</v>
+        <v>540970</v>
       </c>
       <c r="R15" t="n">
-        <v>7193531</v>
+        <v>7193365</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2159,7 +2150,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2169,7 +2160,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2196,7 +2187,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129319419</v>
+        <v>129319430</v>
       </c>
       <c r="B16" t="n">
         <v>80181</v>
@@ -2231,10 +2222,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540986</v>
+        <v>540971</v>
       </c>
       <c r="R16" t="n">
-        <v>7193130</v>
+        <v>7193066</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2266,7 +2257,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2276,7 +2267,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2303,7 +2294,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129319328</v>
+        <v>129319324</v>
       </c>
       <c r="B17" t="n">
         <v>80146</v>
@@ -2338,10 +2329,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540693</v>
+        <v>540719</v>
       </c>
       <c r="R17" t="n">
-        <v>7193540</v>
+        <v>7193483</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2373,7 +2364,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2383,7 +2374,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2410,10 +2401,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129319313</v>
+        <v>129319419</v>
       </c>
       <c r="B18" t="n">
-        <v>80182</v>
+        <v>80181</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2421,21 +2412,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2445,10 +2436,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540789</v>
+        <v>540986</v>
       </c>
       <c r="R18" t="n">
-        <v>7193372</v>
+        <v>7193130</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2480,7 +2471,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2490,7 +2481,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2517,32 +2508,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129319296</v>
+        <v>129319313</v>
       </c>
       <c r="B19" t="n">
-        <v>79041</v>
+        <v>80182</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2552,10 +2543,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540970</v>
+        <v>540789</v>
       </c>
       <c r="R19" t="n">
-        <v>7193365</v>
+        <v>7193372</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2587,7 +2578,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2597,7 +2588,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2624,7 +2615,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129319324</v>
+        <v>129319328</v>
       </c>
       <c r="B20" t="n">
         <v>80146</v>
@@ -2659,10 +2650,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540719</v>
+        <v>540693</v>
       </c>
       <c r="R20" t="n">
-        <v>7193483</v>
+        <v>7193540</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2694,7 +2685,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2704,7 +2695,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2731,32 +2722,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129319430</v>
+        <v>129319352</v>
       </c>
       <c r="B21" t="n">
-        <v>80181</v>
+        <v>78054</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6463</v>
+        <v>228579</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2766,10 +2757,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540971</v>
+        <v>540715</v>
       </c>
       <c r="R21" t="n">
-        <v>7193066</v>
+        <v>7193537</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2801,7 +2792,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2811,7 +2802,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2838,10 +2829,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129319352</v>
+        <v>129319438</v>
       </c>
       <c r="B22" t="n">
-        <v>78054</v>
+        <v>57887</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2849,34 +2840,43 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228579</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540715</v>
+        <v>540982</v>
       </c>
       <c r="R22" t="n">
-        <v>7193537</v>
+        <v>7193110</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2945,7 +2945,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129319281</v>
+        <v>129319316</v>
       </c>
       <c r="B23" t="n">
         <v>80147</v>
@@ -2980,10 +2980,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540902</v>
+        <v>540763</v>
       </c>
       <c r="R23" t="n">
-        <v>7193083</v>
+        <v>7193372</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3015,7 +3015,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3052,7 +3052,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129319316</v>
+        <v>129319281</v>
       </c>
       <c r="B24" t="n">
         <v>80147</v>
@@ -3087,10 +3087,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540763</v>
+        <v>540902</v>
       </c>
       <c r="R24" t="n">
-        <v>7193372</v>
+        <v>7193083</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3373,10 +3373,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129319390</v>
+        <v>129319349</v>
       </c>
       <c r="B27" t="n">
-        <v>79041</v>
+        <v>91560</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3384,23 +3384,19 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3408,10 +3404,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>540818</v>
+        <v>540670</v>
       </c>
       <c r="R27" t="n">
-        <v>7193358</v>
+        <v>7193521</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3443,7 +3439,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3453,7 +3449,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3587,7 +3583,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129319354</v>
+        <v>129319390</v>
       </c>
       <c r="B29" t="n">
         <v>79041</v>
@@ -3622,10 +3618,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>540722</v>
+        <v>540818</v>
       </c>
       <c r="R29" t="n">
-        <v>7193542</v>
+        <v>7193358</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3657,7 +3653,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3667,7 +3663,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3694,10 +3690,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129319349</v>
+        <v>129319354</v>
       </c>
       <c r="B30" t="n">
-        <v>91558</v>
+        <v>79041</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3705,21 +3701,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3729,10 +3725,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>540670</v>
+        <v>540722</v>
       </c>
       <c r="R30" t="n">
-        <v>7193521</v>
+        <v>7193542</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3764,7 +3760,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3774,7 +3770,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3801,10 +3797,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129319374</v>
+        <v>129319404</v>
       </c>
       <c r="B31" t="n">
-        <v>80147</v>
+        <v>78054</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3812,21 +3808,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>228579</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3836,10 +3832,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>540734</v>
+        <v>540931</v>
       </c>
       <c r="R31" t="n">
-        <v>7193499</v>
+        <v>7193220</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3871,7 +3867,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3881,7 +3877,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3908,7 +3904,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129319377</v>
+        <v>129319374</v>
       </c>
       <c r="B32" t="n">
         <v>80147</v>
@@ -3943,10 +3939,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>540745</v>
+        <v>540734</v>
       </c>
       <c r="R32" t="n">
-        <v>7193494</v>
+        <v>7193499</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3978,7 +3974,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3988,7 +3984,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4015,10 +4011,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129319337</v>
+        <v>129319377</v>
       </c>
       <c r="B33" t="n">
-        <v>80146</v>
+        <v>80147</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4026,21 +4022,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4050,10 +4046,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>540676</v>
+        <v>540745</v>
       </c>
       <c r="R33" t="n">
-        <v>7193539</v>
+        <v>7193494</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4085,7 +4081,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4095,7 +4091,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4122,32 +4118,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129319422</v>
+        <v>129319405</v>
       </c>
       <c r="B34" t="n">
-        <v>80181</v>
+        <v>83007</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6463</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4157,10 +4153,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>540980</v>
+        <v>540931</v>
       </c>
       <c r="R34" t="n">
-        <v>7193139</v>
+        <v>7193220</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4192,7 +4188,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4202,7 +4198,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4229,7 +4225,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129319396</v>
+        <v>129319427</v>
       </c>
       <c r="B35" t="n">
         <v>79041</v>
@@ -4264,10 +4260,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>540928</v>
+        <v>540969</v>
       </c>
       <c r="R35" t="n">
-        <v>7193263</v>
+        <v>7193117</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4299,7 +4295,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4309,7 +4305,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4336,7 +4332,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129319427</v>
+        <v>129319396</v>
       </c>
       <c r="B36" t="n">
         <v>79041</v>
@@ -4371,10 +4367,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>540969</v>
+        <v>540928</v>
       </c>
       <c r="R36" t="n">
-        <v>7193117</v>
+        <v>7193263</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4406,7 +4402,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4416,7 +4412,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4443,10 +4439,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129319282</v>
+        <v>129319337</v>
       </c>
       <c r="B37" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4454,21 +4450,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4478,10 +4474,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>540901</v>
+        <v>540676</v>
       </c>
       <c r="R37" t="n">
-        <v>7193084</v>
+        <v>7193539</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4513,7 +4509,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4523,7 +4519,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4550,32 +4546,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129319405</v>
+        <v>129319422</v>
       </c>
       <c r="B38" t="n">
-        <v>83007</v>
+        <v>80181</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6440</v>
+        <v>6463</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4585,10 +4581,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>540931</v>
+        <v>540980</v>
       </c>
       <c r="R38" t="n">
-        <v>7193220</v>
+        <v>7193139</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4620,7 +4616,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4630,7 +4626,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4657,10 +4653,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129319404</v>
+        <v>129319282</v>
       </c>
       <c r="B39" t="n">
-        <v>78054</v>
+        <v>79041</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4668,21 +4664,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4692,10 +4688,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>540931</v>
+        <v>540901</v>
       </c>
       <c r="R39" t="n">
-        <v>7193220</v>
+        <v>7193084</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4727,7 +4723,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4737,7 +4733,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4764,32 +4760,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129319365</v>
+        <v>129319401</v>
       </c>
       <c r="B40" t="n">
-        <v>80147</v>
+        <v>80175</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4799,10 +4795,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>540738</v>
+        <v>540942</v>
       </c>
       <c r="R40" t="n">
-        <v>7193503</v>
+        <v>7193229</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4834,7 +4830,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4844,7 +4840,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4871,32 +4867,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129319294</v>
+        <v>129319320</v>
       </c>
       <c r="B41" t="n">
-        <v>83012</v>
+        <v>80181</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1467</v>
+        <v>6463</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4906,10 +4902,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>540974</v>
+        <v>540719</v>
       </c>
       <c r="R41" t="n">
-        <v>7193351</v>
+        <v>7193463</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4941,7 +4937,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4951,7 +4947,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4978,32 +4974,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129319395</v>
+        <v>129319303</v>
       </c>
       <c r="B42" t="n">
-        <v>82992</v>
+        <v>79041</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>306</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5013,10 +5009,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>540878</v>
+        <v>540934</v>
       </c>
       <c r="R42" t="n">
-        <v>7193291</v>
+        <v>7193385</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5048,7 +5044,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5058,7 +5054,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5085,7 +5081,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129319303</v>
+        <v>129319288</v>
       </c>
       <c r="B43" t="n">
         <v>79041</v>
@@ -5120,10 +5116,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540934</v>
+        <v>540915</v>
       </c>
       <c r="R43" t="n">
-        <v>7193385</v>
+        <v>7193185</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5155,7 +5151,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5165,7 +5161,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5192,7 +5188,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129319348</v>
+        <v>129319403</v>
       </c>
       <c r="B44" t="n">
         <v>80146</v>
@@ -5227,10 +5223,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540653</v>
+        <v>540930</v>
       </c>
       <c r="R44" t="n">
-        <v>7193521</v>
+        <v>7193219</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5262,7 +5258,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5272,7 +5268,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5299,10 +5295,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129319288</v>
+        <v>129319348</v>
       </c>
       <c r="B45" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5310,21 +5306,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5334,10 +5330,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>540915</v>
+        <v>540653</v>
       </c>
       <c r="R45" t="n">
-        <v>7193185</v>
+        <v>7193521</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5369,7 +5365,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5379,7 +5375,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5406,32 +5402,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129319401</v>
+        <v>129319278</v>
       </c>
       <c r="B46" t="n">
-        <v>80175</v>
+        <v>80147</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5441,10 +5437,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>540942</v>
+        <v>540864</v>
       </c>
       <c r="R46" t="n">
-        <v>7193229</v>
+        <v>7193066</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5476,7 +5472,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5486,7 +5482,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5513,10 +5509,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129319403</v>
+        <v>129319365</v>
       </c>
       <c r="B47" t="n">
-        <v>80146</v>
+        <v>80147</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5524,21 +5520,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5548,10 +5544,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>540930</v>
+        <v>540738</v>
       </c>
       <c r="R47" t="n">
-        <v>7193219</v>
+        <v>7193503</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5583,7 +5579,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5593,7 +5589,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5620,10 +5616,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129319320</v>
+        <v>129319395</v>
       </c>
       <c r="B48" t="n">
-        <v>80181</v>
+        <v>82992</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5631,21 +5627,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6463</v>
+        <v>306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5655,10 +5651,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>540719</v>
+        <v>540878</v>
       </c>
       <c r="R48" t="n">
-        <v>7193463</v>
+        <v>7193291</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5690,7 +5686,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5700,7 +5696,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5727,10 +5723,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129319278</v>
+        <v>129319294</v>
       </c>
       <c r="B49" t="n">
-        <v>80147</v>
+        <v>83012</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5738,21 +5734,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2081</v>
+        <v>1467</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5762,10 +5758,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>540864</v>
+        <v>540974</v>
       </c>
       <c r="R49" t="n">
-        <v>7193066</v>
+        <v>7193351</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5797,7 +5793,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5807,7 +5803,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5837,7 +5833,7 @@
         <v>129319280</v>
       </c>
       <c r="B50" t="n">
-        <v>95930</v>
+        <v>95931</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5941,10 +5937,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129319335</v>
+        <v>129319366</v>
       </c>
       <c r="B51" t="n">
-        <v>80147</v>
+        <v>80146</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5952,21 +5948,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5976,10 +5972,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>540655</v>
+        <v>540738</v>
       </c>
       <c r="R51" t="n">
-        <v>7193534</v>
+        <v>7193503</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6011,7 +6007,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6021,7 +6017,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6048,7 +6044,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129319366</v>
+        <v>129319356</v>
       </c>
       <c r="B52" t="n">
         <v>80146</v>
@@ -6083,10 +6079,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>540738</v>
+        <v>540726</v>
       </c>
       <c r="R52" t="n">
-        <v>7193503</v>
+        <v>7193540</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6118,7 +6114,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6128,7 +6124,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6155,10 +6151,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129319356</v>
+        <v>129319335</v>
       </c>
       <c r="B53" t="n">
-        <v>80146</v>
+        <v>80147</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6166,21 +6162,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6190,10 +6186,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>540726</v>
+        <v>540655</v>
       </c>
       <c r="R53" t="n">
-        <v>7193540</v>
+        <v>7193534</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6225,7 +6221,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6235,7 +6231,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6262,10 +6258,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129319429</v>
+        <v>129319304</v>
       </c>
       <c r="B54" t="n">
-        <v>80147</v>
+        <v>79041</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6273,21 +6269,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6297,10 +6293,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>540972</v>
+        <v>540962</v>
       </c>
       <c r="R54" t="n">
-        <v>7193067</v>
+        <v>7193388</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6332,7 +6328,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6342,7 +6338,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6369,10 +6365,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129319417</v>
+        <v>129319388</v>
       </c>
       <c r="B55" t="n">
-        <v>80147</v>
+        <v>57727</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6380,34 +6376,48 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>540989</v>
+        <v>540828</v>
       </c>
       <c r="R55" t="n">
-        <v>7193132</v>
+        <v>7193425</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6439,7 +6449,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6449,7 +6459,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6476,10 +6486,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129319388</v>
+        <v>129319429</v>
       </c>
       <c r="B56" t="n">
-        <v>57727</v>
+        <v>80147</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6487,48 +6497,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>540828</v>
+        <v>540972</v>
       </c>
       <c r="R56" t="n">
-        <v>7193425</v>
+        <v>7193067</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6560,7 +6556,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6570,7 +6566,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6597,10 +6593,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129319304</v>
+        <v>129319417</v>
       </c>
       <c r="B57" t="n">
-        <v>79041</v>
+        <v>80147</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6608,21 +6604,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6632,10 +6628,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>540962</v>
+        <v>540989</v>
       </c>
       <c r="R57" t="n">
-        <v>7193388</v>
+        <v>7193132</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6667,7 +6663,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6677,7 +6673,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6704,45 +6700,54 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129319353</v>
+        <v>129319423</v>
       </c>
       <c r="B58" t="n">
-        <v>82873</v>
+        <v>57831</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1312</v>
+        <v>103031</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>540721</v>
+        <v>540976</v>
       </c>
       <c r="R58" t="n">
-        <v>7193542</v>
+        <v>7193139</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6774,7 +6779,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6784,7 +6789,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6918,10 +6923,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129319339</v>
+        <v>129319353</v>
       </c>
       <c r="B60" t="n">
-        <v>80147</v>
+        <v>82873</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6929,21 +6934,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6953,7 +6958,7 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>540669</v>
+        <v>540721</v>
       </c>
       <c r="R60" t="n">
         <v>7193542</v>
@@ -6988,7 +6993,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6998,7 +7003,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7025,10 +7030,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129319311</v>
+        <v>129319339</v>
       </c>
       <c r="B61" t="n">
-        <v>91536</v>
+        <v>80147</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7036,21 +7041,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7060,10 +7065,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>540830</v>
+        <v>540669</v>
       </c>
       <c r="R61" t="n">
-        <v>7193366</v>
+        <v>7193542</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7095,7 +7100,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7105,7 +7110,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7132,32 +7137,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129319330</v>
+        <v>129319311</v>
       </c>
       <c r="B62" t="n">
-        <v>82990</v>
+        <v>91536</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6439</v>
+        <v>1108</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7167,10 +7172,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>540683</v>
+        <v>540830</v>
       </c>
       <c r="R62" t="n">
-        <v>7193545</v>
+        <v>7193366</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7202,7 +7207,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7212,7 +7217,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7239,10 +7244,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129319372</v>
+        <v>129319292</v>
       </c>
       <c r="B63" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7250,21 +7255,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7274,10 +7279,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>540736</v>
+        <v>540996</v>
       </c>
       <c r="R63" t="n">
-        <v>7193500</v>
+        <v>7193327</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7309,7 +7314,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7319,7 +7324,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7346,10 +7351,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129319292</v>
+        <v>129319372</v>
       </c>
       <c r="B64" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7357,21 +7362,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7381,10 +7386,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>540996</v>
+        <v>540736</v>
       </c>
       <c r="R64" t="n">
-        <v>7193327</v>
+        <v>7193500</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7416,7 +7421,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7426,7 +7431,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7453,32 +7458,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129319392</v>
+        <v>129319330</v>
       </c>
       <c r="B65" t="n">
-        <v>79041</v>
+        <v>82990</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7488,10 +7493,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>540826</v>
+        <v>540683</v>
       </c>
       <c r="R65" t="n">
-        <v>7193294</v>
+        <v>7193545</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7523,7 +7528,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7533,7 +7538,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7560,54 +7565,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129319423</v>
+        <v>129319392</v>
       </c>
       <c r="B66" t="n">
-        <v>57831</v>
+        <v>79041</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>540976</v>
+        <v>540826</v>
       </c>
       <c r="R66" t="n">
-        <v>7193139</v>
+        <v>7193294</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7639,7 +7635,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7649,7 +7645,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7676,10 +7672,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129319397</v>
+        <v>129319293</v>
       </c>
       <c r="B67" t="n">
-        <v>79041</v>
+        <v>57887</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7687,34 +7683,43 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>540946</v>
+        <v>540980</v>
       </c>
       <c r="R67" t="n">
-        <v>7193256</v>
+        <v>7193345</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7746,7 +7751,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7756,7 +7761,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7783,32 +7788,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129319421</v>
+        <v>129319400</v>
       </c>
       <c r="B68" t="n">
-        <v>80175</v>
+        <v>79041</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7818,10 +7823,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>540981</v>
+        <v>540943</v>
       </c>
       <c r="R68" t="n">
-        <v>7193140</v>
+        <v>7193233</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7853,7 +7858,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7863,7 +7868,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7997,32 +8002,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129319400</v>
+        <v>129319370</v>
       </c>
       <c r="B70" t="n">
-        <v>79041</v>
+        <v>80175</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8032,10 +8037,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>540943</v>
+        <v>540737</v>
       </c>
       <c r="R70" t="n">
-        <v>7193233</v>
+        <v>7193504</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8067,7 +8072,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8077,7 +8082,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8104,7 +8109,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129319370</v>
+        <v>129319421</v>
       </c>
       <c r="B71" t="n">
         <v>80175</v>
@@ -8139,10 +8144,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>540737</v>
+        <v>540981</v>
       </c>
       <c r="R71" t="n">
-        <v>7193504</v>
+        <v>7193140</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8174,7 +8179,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8184,7 +8189,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8211,10 +8216,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129319293</v>
+        <v>129319397</v>
       </c>
       <c r="B72" t="n">
-        <v>57887</v>
+        <v>79041</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8222,43 +8227,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>540980</v>
+        <v>540946</v>
       </c>
       <c r="R72" t="n">
-        <v>7193345</v>
+        <v>7193256</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8290,7 +8286,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8300,7 +8296,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8327,32 +8323,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129319412</v>
+        <v>129319367</v>
       </c>
       <c r="B73" t="n">
-        <v>91558</v>
+        <v>80175</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8362,10 +8358,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>540952</v>
+        <v>540734</v>
       </c>
       <c r="R73" t="n">
-        <v>7193187</v>
+        <v>7193503</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8397,7 +8393,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8407,7 +8403,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8434,7 +8430,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129319402</v>
+        <v>129319413</v>
       </c>
       <c r="B74" t="n">
         <v>79041</v>
@@ -8469,10 +8465,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>540936</v>
+        <v>540965</v>
       </c>
       <c r="R74" t="n">
-        <v>7193225</v>
+        <v>7193181</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8504,7 +8500,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8514,7 +8510,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8541,7 +8537,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129319413</v>
+        <v>129319402</v>
       </c>
       <c r="B75" t="n">
         <v>79041</v>
@@ -8576,10 +8572,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>540965</v>
+        <v>540936</v>
       </c>
       <c r="R75" t="n">
-        <v>7193181</v>
+        <v>7193225</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8611,7 +8607,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8621,7 +8617,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8648,34 +8644,30 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129319367</v>
+        <v>129319412</v>
       </c>
       <c r="B76" t="n">
-        <v>80175</v>
+        <v>91560</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -8683,10 +8675,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>540734</v>
+        <v>540952</v>
       </c>
       <c r="R76" t="n">
-        <v>7193503</v>
+        <v>7193187</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8718,7 +8710,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8728,7 +8720,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8871,10 +8863,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129319342</v>
+        <v>129319371</v>
       </c>
       <c r="B78" t="n">
-        <v>57724</v>
+        <v>80146</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8882,39 +8874,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>540667</v>
+        <v>540737</v>
       </c>
       <c r="R78" t="n">
-        <v>7193539</v>
+        <v>7193504</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8946,7 +8933,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8956,7 +8943,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8983,10 +8970,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129319371</v>
+        <v>129319342</v>
       </c>
       <c r="B79" t="n">
-        <v>80146</v>
+        <v>57724</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8994,34 +8981,39 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>540737</v>
+        <v>540667</v>
       </c>
       <c r="R79" t="n">
-        <v>7193504</v>
+        <v>7193539</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9053,7 +9045,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9063,7 +9055,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9090,10 +9082,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129319336</v>
+        <v>129319338</v>
       </c>
       <c r="B80" t="n">
-        <v>79041</v>
+        <v>80147</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9101,21 +9093,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9125,10 +9117,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>540668</v>
+        <v>540676</v>
       </c>
       <c r="R80" t="n">
-        <v>7193543</v>
+        <v>7193539</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9160,7 +9152,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9170,7 +9162,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9197,32 +9189,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129319382</v>
+        <v>129319431</v>
       </c>
       <c r="B81" t="n">
-        <v>79041</v>
+        <v>80175</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9232,10 +9224,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>540761</v>
+        <v>540979</v>
       </c>
       <c r="R81" t="n">
-        <v>7193473</v>
+        <v>7193075</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9267,7 +9259,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9277,7 +9269,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9304,10 +9296,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129319408</v>
+        <v>129319382</v>
       </c>
       <c r="B82" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9315,21 +9307,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9339,10 +9331,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>540939</v>
+        <v>540761</v>
       </c>
       <c r="R82" t="n">
-        <v>7193177</v>
+        <v>7193473</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9374,7 +9366,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9384,7 +9376,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9411,32 +9403,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129319431</v>
+        <v>129319408</v>
       </c>
       <c r="B83" t="n">
-        <v>80175</v>
+        <v>80146</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9446,10 +9438,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>540979</v>
+        <v>540939</v>
       </c>
       <c r="R83" t="n">
-        <v>7193075</v>
+        <v>7193177</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9481,7 +9473,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9491,7 +9483,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9518,7 +9510,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129319394</v>
+        <v>129319336</v>
       </c>
       <c r="B84" t="n">
         <v>79041</v>
@@ -9553,10 +9545,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>540877</v>
+        <v>540668</v>
       </c>
       <c r="R84" t="n">
-        <v>7193291</v>
+        <v>7193543</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9588,7 +9580,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9598,7 +9590,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9625,10 +9617,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129319338</v>
+        <v>129319394</v>
       </c>
       <c r="B85" t="n">
-        <v>80147</v>
+        <v>79041</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9636,21 +9628,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9660,10 +9652,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>540676</v>
+        <v>540877</v>
       </c>
       <c r="R85" t="n">
-        <v>7193539</v>
+        <v>7193291</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9695,7 +9687,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9705,7 +9697,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9735,7 +9727,7 @@
         <v>129319389</v>
       </c>
       <c r="B86" t="n">
-        <v>95930</v>
+        <v>95931</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9839,7 +9831,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129319375</v>
+        <v>129319333</v>
       </c>
       <c r="B87" t="n">
         <v>80147</v>
@@ -9874,10 +9866,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>540730</v>
+        <v>540674</v>
       </c>
       <c r="R87" t="n">
-        <v>7193493</v>
+        <v>7193551</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -9909,7 +9901,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9919,7 +9911,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9946,7 +9938,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129319357</v>
+        <v>129319375</v>
       </c>
       <c r="B88" t="n">
         <v>80147</v>
@@ -9981,10 +9973,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>540726</v>
+        <v>540730</v>
       </c>
       <c r="R88" t="n">
-        <v>7193539</v>
+        <v>7193493</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -10016,7 +10008,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10026,7 +10018,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10053,10 +10045,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129319298</v>
+        <v>129319433</v>
       </c>
       <c r="B89" t="n">
-        <v>91558</v>
+        <v>80147</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10064,21 +10056,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10088,10 +10080,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>540964</v>
+        <v>540979</v>
       </c>
       <c r="R89" t="n">
-        <v>7193371</v>
+        <v>7193075</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -10123,7 +10115,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10133,7 +10125,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10160,10 +10152,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129319284</v>
+        <v>129319357</v>
       </c>
       <c r="B90" t="n">
-        <v>79041</v>
+        <v>80147</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10171,21 +10163,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10195,10 +10187,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>540867</v>
+        <v>540726</v>
       </c>
       <c r="R90" t="n">
-        <v>7193169</v>
+        <v>7193539</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -10230,7 +10222,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10240,7 +10232,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10267,10 +10259,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129319409</v>
+        <v>129319376</v>
       </c>
       <c r="B91" t="n">
-        <v>80146</v>
+        <v>80147</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10278,21 +10270,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10302,10 +10294,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>540942</v>
+        <v>540738</v>
       </c>
       <c r="R91" t="n">
-        <v>7193182</v>
+        <v>7193476</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -10337,7 +10329,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10347,7 +10339,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10374,34 +10366,30 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129319393</v>
+        <v>129319298</v>
       </c>
       <c r="B92" t="n">
-        <v>82990</v>
+        <v>91560</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6439</v>
+        <v>5432</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -10409,10 +10397,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>540824</v>
+        <v>540964</v>
       </c>
       <c r="R92" t="n">
-        <v>7193288</v>
+        <v>7193371</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -10444,7 +10432,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10454,7 +10442,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10481,10 +10469,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129319299</v>
+        <v>129319409</v>
       </c>
       <c r="B93" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10492,21 +10480,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10516,10 +10504,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>540964</v>
+        <v>540942</v>
       </c>
       <c r="R93" t="n">
-        <v>7193371</v>
+        <v>7193182</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -10551,7 +10539,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10561,7 +10549,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10588,7 +10576,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129319344</v>
+        <v>129319299</v>
       </c>
       <c r="B94" t="n">
         <v>79041</v>
@@ -10623,10 +10611,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>540650</v>
+        <v>540964</v>
       </c>
       <c r="R94" t="n">
-        <v>7193540</v>
+        <v>7193371</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -10658,7 +10646,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10668,7 +10656,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10695,10 +10683,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129319333</v>
+        <v>129319284</v>
       </c>
       <c r="B95" t="n">
-        <v>80147</v>
+        <v>79041</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10706,21 +10694,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10730,10 +10718,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>540674</v>
+        <v>540867</v>
       </c>
       <c r="R95" t="n">
-        <v>7193551</v>
+        <v>7193169</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -10765,7 +10753,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10775,7 +10763,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10802,32 +10790,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129319376</v>
+        <v>129319393</v>
       </c>
       <c r="B96" t="n">
-        <v>80147</v>
+        <v>82990</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2081</v>
+        <v>6439</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10837,10 +10825,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>540738</v>
+        <v>540824</v>
       </c>
       <c r="R96" t="n">
-        <v>7193476</v>
+        <v>7193288</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -10872,7 +10860,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10882,7 +10870,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10909,10 +10897,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129319433</v>
+        <v>129319344</v>
       </c>
       <c r="B97" t="n">
-        <v>80147</v>
+        <v>79041</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10920,21 +10908,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10944,10 +10932,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>540979</v>
+        <v>540650</v>
       </c>
       <c r="R97" t="n">
-        <v>7193075</v>
+        <v>7193540</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -10979,7 +10967,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10989,7 +10977,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11016,10 +11004,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129319445</v>
+        <v>129319359</v>
       </c>
       <c r="B98" t="n">
-        <v>57724</v>
+        <v>80146</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11027,43 +11015,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>541052</v>
+        <v>540725</v>
       </c>
       <c r="R98" t="n">
-        <v>7193255</v>
+        <v>7193537</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -11095,7 +11074,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11105,7 +11084,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11346,7 +11325,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129319362</v>
+        <v>129319286</v>
       </c>
       <c r="B101" t="n">
         <v>79041</v>
@@ -11381,10 +11360,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>540721</v>
+        <v>540891</v>
       </c>
       <c r="R101" t="n">
-        <v>7193527</v>
+        <v>7193174</v>
       </c>
       <c r="S101" t="n">
         <v>25</v>
@@ -11416,7 +11395,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11426,7 +11405,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11453,7 +11432,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129319306</v>
+        <v>129319362</v>
       </c>
       <c r="B102" t="n">
         <v>79041</v>
@@ -11488,10 +11467,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>540961</v>
+        <v>540721</v>
       </c>
       <c r="R102" t="n">
-        <v>7193398</v>
+        <v>7193527</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -11523,7 +11502,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11533,7 +11512,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11560,7 +11539,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129319286</v>
+        <v>129319306</v>
       </c>
       <c r="B103" t="n">
         <v>79041</v>
@@ -11595,10 +11574,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>540891</v>
+        <v>540961</v>
       </c>
       <c r="R103" t="n">
-        <v>7193174</v>
+        <v>7193398</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -11630,7 +11609,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11640,7 +11619,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11667,10 +11646,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129319359</v>
+        <v>129319445</v>
       </c>
       <c r="B104" t="n">
-        <v>80146</v>
+        <v>57724</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11678,34 +11657,43 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>540725</v>
+        <v>541052</v>
       </c>
       <c r="R104" t="n">
-        <v>7193537</v>
+        <v>7193255</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -11737,7 +11725,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11747,7 +11735,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11774,10 +11762,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129319355</v>
+        <v>129319411</v>
       </c>
       <c r="B105" t="n">
-        <v>80147</v>
+        <v>79041</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11785,21 +11773,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11809,10 +11797,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>540726</v>
+        <v>540955</v>
       </c>
       <c r="R105" t="n">
-        <v>7193541</v>
+        <v>7193186</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -11844,7 +11832,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11854,7 +11842,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11881,32 +11869,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129319369</v>
+        <v>129319418</v>
       </c>
       <c r="B106" t="n">
-        <v>80147</v>
+        <v>80182</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11916,10 +11904,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>540734</v>
+        <v>540986</v>
       </c>
       <c r="R106" t="n">
-        <v>7193503</v>
+        <v>7193130</v>
       </c>
       <c r="S106" t="n">
         <v>25</v>
@@ -11951,7 +11939,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11961,7 +11949,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11988,10 +11976,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129319391</v>
+        <v>129319368</v>
       </c>
       <c r="B107" t="n">
-        <v>80147</v>
+        <v>80146</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11999,21 +11987,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12023,10 +12011,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>540818</v>
+        <v>540734</v>
       </c>
       <c r="R107" t="n">
-        <v>7193333</v>
+        <v>7193503</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -12058,7 +12046,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12068,7 +12056,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12095,10 +12083,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129319360</v>
+        <v>129319407</v>
       </c>
       <c r="B108" t="n">
-        <v>91536</v>
+        <v>79041</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12106,21 +12094,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12130,10 +12118,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>540725</v>
+        <v>540924</v>
       </c>
       <c r="R108" t="n">
-        <v>7193532</v>
+        <v>7193211</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -12165,7 +12153,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12175,7 +12163,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12202,10 +12190,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129319368</v>
+        <v>129319391</v>
       </c>
       <c r="B109" t="n">
-        <v>80146</v>
+        <v>80147</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12213,21 +12201,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12237,10 +12225,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>540734</v>
+        <v>540818</v>
       </c>
       <c r="R109" t="n">
-        <v>7193503</v>
+        <v>7193333</v>
       </c>
       <c r="S109" t="n">
         <v>25</v>
@@ -12272,7 +12260,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12282,7 +12270,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12309,10 +12297,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129319411</v>
+        <v>129319355</v>
       </c>
       <c r="B110" t="n">
-        <v>79041</v>
+        <v>80147</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12320,21 +12308,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12344,10 +12332,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>540955</v>
+        <v>540726</v>
       </c>
       <c r="R110" t="n">
-        <v>7193186</v>
+        <v>7193541</v>
       </c>
       <c r="S110" t="n">
         <v>25</v>
@@ -12379,7 +12367,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12389,7 +12377,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12416,32 +12404,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129319418</v>
+        <v>129319360</v>
       </c>
       <c r="B111" t="n">
-        <v>80182</v>
+        <v>91536</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6464</v>
+        <v>1108</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12451,10 +12439,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>540986</v>
+        <v>540725</v>
       </c>
       <c r="R111" t="n">
-        <v>7193130</v>
+        <v>7193532</v>
       </c>
       <c r="S111" t="n">
         <v>25</v>
@@ -12486,7 +12474,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12496,7 +12484,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12523,10 +12511,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129319407</v>
+        <v>129319369</v>
       </c>
       <c r="B112" t="n">
-        <v>79041</v>
+        <v>80147</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12534,21 +12522,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12558,10 +12546,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>540924</v>
+        <v>540734</v>
       </c>
       <c r="R112" t="n">
-        <v>7193211</v>
+        <v>7193503</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>
@@ -12593,7 +12581,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12603,7 +12591,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12630,10 +12618,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129319341</v>
+        <v>129319426</v>
       </c>
       <c r="B113" t="n">
-        <v>91536</v>
+        <v>80147</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12641,21 +12629,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12665,10 +12653,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>540670</v>
+        <v>540979</v>
       </c>
       <c r="R113" t="n">
-        <v>7193533</v>
+        <v>7193115</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -12700,7 +12688,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12710,7 +12698,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12737,10 +12725,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129319426</v>
+        <v>129319341</v>
       </c>
       <c r="B114" t="n">
-        <v>80147</v>
+        <v>91536</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12748,21 +12736,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12772,10 +12760,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>540979</v>
+        <v>540670</v>
       </c>
       <c r="R114" t="n">
-        <v>7193115</v>
+        <v>7193533</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -12807,7 +12795,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12817,7 +12805,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12844,34 +12832,30 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129319425</v>
+        <v>129319305</v>
       </c>
       <c r="B115" t="n">
-        <v>80181</v>
+        <v>91560</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
@@ -12879,10 +12863,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>540980</v>
+        <v>540959</v>
       </c>
       <c r="R115" t="n">
-        <v>7193116</v>
+        <v>7193395</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -12914,7 +12898,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12924,7 +12908,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12951,10 +12935,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129319309</v>
+        <v>129319332</v>
       </c>
       <c r="B116" t="n">
-        <v>79041</v>
+        <v>57887</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12962,34 +12946,43 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>540894</v>
+        <v>540675</v>
       </c>
       <c r="R116" t="n">
-        <v>7193411</v>
+        <v>7193538</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -13021,7 +13014,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13031,7 +13024,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13058,10 +13051,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129319305</v>
+        <v>129319309</v>
       </c>
       <c r="B117" t="n">
-        <v>91558</v>
+        <v>79041</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13069,21 +13062,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13093,10 +13086,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>540959</v>
+        <v>540894</v>
       </c>
       <c r="R117" t="n">
-        <v>7193395</v>
+        <v>7193411</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -13128,7 +13121,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13138,7 +13131,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13165,54 +13158,45 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129319332</v>
+        <v>129319425</v>
       </c>
       <c r="B118" t="n">
-        <v>57887</v>
+        <v>80181</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>103021</v>
+        <v>6463</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>540675</v>
+        <v>540980</v>
       </c>
       <c r="R118" t="n">
-        <v>7193538</v>
+        <v>7193116</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -13244,7 +13228,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13254,7 +13238,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13388,7 +13372,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129319325</v>
+        <v>129319319</v>
       </c>
       <c r="B120" t="n">
         <v>80147</v>
@@ -13423,10 +13407,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>540714</v>
+        <v>540719</v>
       </c>
       <c r="R120" t="n">
-        <v>7193488</v>
+        <v>7193463</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -13458,7 +13442,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13468,7 +13452,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13495,7 +13479,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129319319</v>
+        <v>129319325</v>
       </c>
       <c r="B121" t="n">
         <v>80147</v>
@@ -13530,10 +13514,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>540719</v>
+        <v>540714</v>
       </c>
       <c r="R121" t="n">
-        <v>7193463</v>
+        <v>7193488</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -13565,7 +13549,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13575,7 +13559,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13816,10 +13800,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129319373</v>
+        <v>129319321</v>
       </c>
       <c r="B124" t="n">
-        <v>80182</v>
+        <v>80175</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13827,21 +13811,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13851,10 +13835,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>540734</v>
+        <v>540719</v>
       </c>
       <c r="R124" t="n">
-        <v>7193499</v>
+        <v>7193463</v>
       </c>
       <c r="S124" t="n">
         <v>25</v>
@@ -13886,7 +13870,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13896,7 +13880,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13923,10 +13907,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129319321</v>
+        <v>129319373</v>
       </c>
       <c r="B125" t="n">
-        <v>80175</v>
+        <v>80182</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13934,21 +13918,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13958,10 +13942,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>540719</v>
+        <v>540734</v>
       </c>
       <c r="R125" t="n">
-        <v>7193463</v>
+        <v>7193499</v>
       </c>
       <c r="S125" t="n">
         <v>25</v>
@@ -13993,7 +13977,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14003,7 +13987,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14369,7 +14353,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129319326</v>
+        <v>129319434</v>
       </c>
       <c r="B129" t="n">
         <v>80146</v>
@@ -14404,10 +14388,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>540701</v>
+        <v>540979</v>
       </c>
       <c r="R129" t="n">
-        <v>7193533</v>
+        <v>7193075</v>
       </c>
       <c r="S129" t="n">
         <v>25</v>
@@ -14439,7 +14423,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14449,7 +14433,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14476,10 +14460,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129319379</v>
+        <v>129319326</v>
       </c>
       <c r="B130" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14487,21 +14471,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14511,10 +14495,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>540761</v>
+        <v>540701</v>
       </c>
       <c r="R130" t="n">
-        <v>7193485</v>
+        <v>7193533</v>
       </c>
       <c r="S130" t="n">
         <v>25</v>
@@ -14546,7 +14530,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14556,7 +14540,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14583,10 +14567,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129319434</v>
+        <v>129319379</v>
       </c>
       <c r="B131" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14594,21 +14578,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14618,10 +14602,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>540979</v>
+        <v>540761</v>
       </c>
       <c r="R131" t="n">
-        <v>7193075</v>
+        <v>7193485</v>
       </c>
       <c r="S131" t="n">
         <v>25</v>
@@ -14653,7 +14637,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14663,7 +14647,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14690,10 +14674,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129319378</v>
+        <v>129319380</v>
       </c>
       <c r="B132" t="n">
-        <v>82992</v>
+        <v>92258</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14701,21 +14685,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>306</v>
+        <v>3298</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14725,10 +14709,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>540757</v>
+        <v>540761</v>
       </c>
       <c r="R132" t="n">
-        <v>7193474</v>
+        <v>7193490</v>
       </c>
       <c r="S132" t="n">
         <v>25</v>
@@ -14760,7 +14744,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14770,7 +14754,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15235,10 +15219,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129319380</v>
+        <v>129319378</v>
       </c>
       <c r="B137" t="n">
-        <v>92257</v>
+        <v>82992</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15246,21 +15230,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>3298</v>
+        <v>306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15270,10 +15254,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>540761</v>
+        <v>540757</v>
       </c>
       <c r="R137" t="n">
-        <v>7193490</v>
+        <v>7193474</v>
       </c>
       <c r="S137" t="n">
         <v>25</v>
@@ -15305,7 +15289,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15315,7 +15299,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15345,7 +15329,7 @@
         <v>129319287</v>
       </c>
       <c r="B138" t="n">
-        <v>92257</v>
+        <v>92258</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15663,10 +15647,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129319428</v>
+        <v>129319327</v>
       </c>
       <c r="B141" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15674,21 +15658,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15698,10 +15682,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>540971</v>
+        <v>540693</v>
       </c>
       <c r="R141" t="n">
-        <v>7193081</v>
+        <v>7193540</v>
       </c>
       <c r="S141" t="n">
         <v>25</v>
@@ -15733,7 +15717,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15743,7 +15727,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15984,10 +15968,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129319327</v>
+        <v>129319428</v>
       </c>
       <c r="B144" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15995,21 +15979,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -16019,10 +16003,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>540693</v>
+        <v>540971</v>
       </c>
       <c r="R144" t="n">
-        <v>7193540</v>
+        <v>7193081</v>
       </c>
       <c r="S144" t="n">
         <v>25</v>
@@ -16054,7 +16038,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16064,7 +16048,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD144" t="b">

--- a/artfynd/A 51086-2025 artfynd.xlsx
+++ b/artfynd/A 51086-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129319307</v>
+        <v>129319384</v>
       </c>
       <c r="B2" t="n">
-        <v>91536</v>
+        <v>79041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540962</v>
+        <v>540775</v>
       </c>
       <c r="R2" t="n">
-        <v>7193400</v>
+        <v>7193467</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129319285</v>
+        <v>129319386</v>
       </c>
       <c r="B3" t="n">
-        <v>91536</v>
+        <v>95932</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>2809</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540886</v>
+        <v>540774</v>
       </c>
       <c r="R3" t="n">
-        <v>7193172</v>
+        <v>7193457</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129319300</v>
+        <v>129319285</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>91536</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,39 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540961</v>
+        <v>540886</v>
       </c>
       <c r="R4" t="n">
-        <v>7193376</v>
+        <v>7193172</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -964,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,54 +996,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129319414</v>
+        <v>129319307</v>
       </c>
       <c r="B5" t="n">
-        <v>58360</v>
+        <v>91536</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102125</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540963</v>
+        <v>540962</v>
       </c>
       <c r="R5" t="n">
-        <v>7193203</v>
+        <v>7193400</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1080,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1090,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129319386</v>
+        <v>129319323</v>
       </c>
       <c r="B6" t="n">
-        <v>95931</v>
+        <v>80182</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1128,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2809</v>
+        <v>6464</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1152,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540774</v>
+        <v>540719</v>
       </c>
       <c r="R6" t="n">
-        <v>7193457</v>
+        <v>7193483</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1187,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1197,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1331,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129319384</v>
+        <v>129319300</v>
       </c>
       <c r="B8" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1342,34 +1328,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540775</v>
+        <v>540961</v>
       </c>
       <c r="R8" t="n">
-        <v>7193467</v>
+        <v>7193376</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1401,7 +1392,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1411,7 +1402,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1438,32 +1429,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129319323</v>
+        <v>129319302</v>
       </c>
       <c r="B9" t="n">
-        <v>80182</v>
+        <v>79041</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1473,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540719</v>
+        <v>540960</v>
       </c>
       <c r="R9" t="n">
-        <v>7193483</v>
+        <v>7193375</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1508,7 +1499,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1518,7 +1509,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1545,45 +1536,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129319302</v>
+        <v>129319414</v>
       </c>
       <c r="B10" t="n">
-        <v>79041</v>
+        <v>58360</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>102125</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540960</v>
+        <v>540963</v>
       </c>
       <c r="R10" t="n">
-        <v>7193375</v>
+        <v>7193203</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1615,7 +1615,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1652,32 +1652,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129319295</v>
+        <v>129319381</v>
       </c>
       <c r="B11" t="n">
-        <v>95931</v>
+        <v>82873</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2809</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540972</v>
+        <v>540758</v>
       </c>
       <c r="R11" t="n">
-        <v>7193357</v>
+        <v>7193475</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1759,10 +1759,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129319361</v>
+        <v>129319424</v>
       </c>
       <c r="B12" t="n">
-        <v>91540</v>
+        <v>80147</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1770,21 +1770,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1794,10 +1794,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540726</v>
+        <v>540975</v>
       </c>
       <c r="R12" t="n">
-        <v>7193531</v>
+        <v>7193139</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1829,7 +1829,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1866,32 +1866,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129319424</v>
+        <v>129319295</v>
       </c>
       <c r="B13" t="n">
-        <v>80147</v>
+        <v>95932</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>2809</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1901,10 +1901,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540975</v>
+        <v>540972</v>
       </c>
       <c r="R13" t="n">
-        <v>7193139</v>
+        <v>7193357</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1973,10 +1973,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129319381</v>
+        <v>129319361</v>
       </c>
       <c r="B14" t="n">
-        <v>82873</v>
+        <v>91540</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1984,21 +1984,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2008,10 +2008,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540758</v>
+        <v>540726</v>
       </c>
       <c r="R14" t="n">
-        <v>7193475</v>
+        <v>7193531</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2080,27 +2080,27 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129319296</v>
+        <v>129319419</v>
       </c>
       <c r="B15" t="n">
-        <v>79041</v>
+        <v>80181</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540970</v>
+        <v>540986</v>
       </c>
       <c r="R15" t="n">
-        <v>7193365</v>
+        <v>7193130</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2187,32 +2187,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129319430</v>
+        <v>129319328</v>
       </c>
       <c r="B16" t="n">
-        <v>80181</v>
+        <v>80146</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2222,10 +2222,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540971</v>
+        <v>540693</v>
       </c>
       <c r="R16" t="n">
-        <v>7193066</v>
+        <v>7193540</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2294,32 +2294,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129319324</v>
+        <v>129319313</v>
       </c>
       <c r="B17" t="n">
-        <v>80146</v>
+        <v>80182</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2329,10 +2329,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540719</v>
+        <v>540789</v>
       </c>
       <c r="R17" t="n">
-        <v>7193483</v>
+        <v>7193372</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2401,7 +2401,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129319419</v>
+        <v>129319430</v>
       </c>
       <c r="B18" t="n">
         <v>80181</v>
@@ -2436,10 +2436,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540986</v>
+        <v>540971</v>
       </c>
       <c r="R18" t="n">
-        <v>7193130</v>
+        <v>7193066</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2508,32 +2508,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129319313</v>
+        <v>129319296</v>
       </c>
       <c r="B19" t="n">
-        <v>80182</v>
+        <v>79041</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2543,10 +2543,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540789</v>
+        <v>540970</v>
       </c>
       <c r="R19" t="n">
-        <v>7193372</v>
+        <v>7193365</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2615,7 +2615,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129319328</v>
+        <v>129319324</v>
       </c>
       <c r="B20" t="n">
         <v>80146</v>
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540693</v>
+        <v>540719</v>
       </c>
       <c r="R20" t="n">
-        <v>7193540</v>
+        <v>7193483</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2722,10 +2722,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129319352</v>
+        <v>129319438</v>
       </c>
       <c r="B21" t="n">
-        <v>78054</v>
+        <v>57887</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2733,34 +2733,43 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228579</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540715</v>
+        <v>540982</v>
       </c>
       <c r="R21" t="n">
-        <v>7193537</v>
+        <v>7193110</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2792,7 +2801,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2802,7 +2811,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2829,10 +2838,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129319438</v>
+        <v>129319352</v>
       </c>
       <c r="B22" t="n">
-        <v>57887</v>
+        <v>78054</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2840,43 +2849,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>228579</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540982</v>
+        <v>540715</v>
       </c>
       <c r="R22" t="n">
-        <v>7193110</v>
+        <v>7193537</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3476,7 +3476,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129319383</v>
+        <v>129319390</v>
       </c>
       <c r="B28" t="n">
         <v>79041</v>
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>540764</v>
+        <v>540818</v>
       </c>
       <c r="R28" t="n">
-        <v>7193475</v>
+        <v>7193358</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3583,7 +3583,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129319390</v>
+        <v>129319383</v>
       </c>
       <c r="B29" t="n">
         <v>79041</v>
@@ -3618,10 +3618,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>540818</v>
+        <v>540764</v>
       </c>
       <c r="R29" t="n">
-        <v>7193358</v>
+        <v>7193475</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3653,7 +3653,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3797,10 +3797,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129319404</v>
+        <v>129319377</v>
       </c>
       <c r="B31" t="n">
-        <v>78054</v>
+        <v>80147</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3808,21 +3808,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228579</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>540931</v>
+        <v>540745</v>
       </c>
       <c r="R31" t="n">
-        <v>7193220</v>
+        <v>7193494</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3867,7 +3867,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4011,10 +4011,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129319377</v>
+        <v>129319337</v>
       </c>
       <c r="B33" t="n">
-        <v>80147</v>
+        <v>80146</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4022,21 +4022,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4046,10 +4046,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>540745</v>
+        <v>540676</v>
       </c>
       <c r="R33" t="n">
-        <v>7193494</v>
+        <v>7193539</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4081,7 +4081,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4118,32 +4118,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129319405</v>
+        <v>129319422</v>
       </c>
       <c r="B34" t="n">
-        <v>83007</v>
+        <v>80181</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6440</v>
+        <v>6463</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4153,10 +4153,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>540931</v>
+        <v>540980</v>
       </c>
       <c r="R34" t="n">
-        <v>7193220</v>
+        <v>7193139</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4225,7 +4225,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129319427</v>
+        <v>129319396</v>
       </c>
       <c r="B35" t="n">
         <v>79041</v>
@@ -4260,10 +4260,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>540969</v>
+        <v>540928</v>
       </c>
       <c r="R35" t="n">
-        <v>7193117</v>
+        <v>7193263</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4295,7 +4295,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4305,7 +4305,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4332,7 +4332,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129319396</v>
+        <v>129319427</v>
       </c>
       <c r="B36" t="n">
         <v>79041</v>
@@ -4367,10 +4367,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>540928</v>
+        <v>540969</v>
       </c>
       <c r="R36" t="n">
-        <v>7193263</v>
+        <v>7193117</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4402,7 +4402,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4439,10 +4439,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129319337</v>
+        <v>129319282</v>
       </c>
       <c r="B37" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4450,21 +4450,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4474,10 +4474,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>540676</v>
+        <v>540901</v>
       </c>
       <c r="R37" t="n">
-        <v>7193539</v>
+        <v>7193084</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4546,32 +4546,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129319422</v>
+        <v>129319405</v>
       </c>
       <c r="B38" t="n">
-        <v>80181</v>
+        <v>83007</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6463</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>540980</v>
+        <v>540931</v>
       </c>
       <c r="R38" t="n">
-        <v>7193139</v>
+        <v>7193220</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4653,10 +4653,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129319282</v>
+        <v>129319404</v>
       </c>
       <c r="B39" t="n">
-        <v>79041</v>
+        <v>78054</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4664,21 +4664,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4688,10 +4688,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>540901</v>
+        <v>540931</v>
       </c>
       <c r="R39" t="n">
-        <v>7193084</v>
+        <v>7193220</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4760,32 +4760,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129319401</v>
+        <v>129319278</v>
       </c>
       <c r="B40" t="n">
-        <v>80175</v>
+        <v>80147</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>540942</v>
+        <v>540864</v>
       </c>
       <c r="R40" t="n">
-        <v>7193229</v>
+        <v>7193066</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4840,7 +4840,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4867,32 +4867,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129319320</v>
+        <v>129319294</v>
       </c>
       <c r="B41" t="n">
-        <v>80181</v>
+        <v>83012</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6463</v>
+        <v>1467</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>540719</v>
+        <v>540974</v>
       </c>
       <c r="R41" t="n">
-        <v>7193463</v>
+        <v>7193351</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4947,7 +4947,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4974,10 +4974,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129319303</v>
+        <v>129319365</v>
       </c>
       <c r="B42" t="n">
-        <v>79041</v>
+        <v>80147</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4985,21 +4985,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>540934</v>
+        <v>540738</v>
       </c>
       <c r="R42" t="n">
-        <v>7193385</v>
+        <v>7193503</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5081,10 +5081,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129319288</v>
+        <v>129319348</v>
       </c>
       <c r="B43" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5092,21 +5092,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5116,10 +5116,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540915</v>
+        <v>540653</v>
       </c>
       <c r="R43" t="n">
-        <v>7193185</v>
+        <v>7193521</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5188,32 +5188,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129319403</v>
+        <v>129319401</v>
       </c>
       <c r="B44" t="n">
-        <v>80146</v>
+        <v>80175</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540930</v>
+        <v>540942</v>
       </c>
       <c r="R44" t="n">
-        <v>7193219</v>
+        <v>7193229</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5295,7 +5295,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129319348</v>
+        <v>129319403</v>
       </c>
       <c r="B45" t="n">
         <v>80146</v>
@@ -5330,10 +5330,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>540653</v>
+        <v>540930</v>
       </c>
       <c r="R45" t="n">
-        <v>7193521</v>
+        <v>7193219</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5365,7 +5365,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5375,7 +5375,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5402,32 +5402,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129319278</v>
+        <v>129319320</v>
       </c>
       <c r="B46" t="n">
-        <v>80147</v>
+        <v>80181</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5437,10 +5437,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>540864</v>
+        <v>540719</v>
       </c>
       <c r="R46" t="n">
-        <v>7193066</v>
+        <v>7193463</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5472,7 +5472,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5509,32 +5509,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129319365</v>
+        <v>129319395</v>
       </c>
       <c r="B47" t="n">
-        <v>80147</v>
+        <v>82992</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2081</v>
+        <v>306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5544,10 +5544,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>540738</v>
+        <v>540878</v>
       </c>
       <c r="R47" t="n">
-        <v>7193503</v>
+        <v>7193291</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5579,7 +5579,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5616,32 +5616,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129319395</v>
+        <v>129319303</v>
       </c>
       <c r="B48" t="n">
-        <v>82992</v>
+        <v>79041</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>306</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5651,10 +5651,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>540878</v>
+        <v>540934</v>
       </c>
       <c r="R48" t="n">
-        <v>7193291</v>
+        <v>7193385</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5686,7 +5686,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5723,10 +5723,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129319294</v>
+        <v>129319288</v>
       </c>
       <c r="B49" t="n">
-        <v>83012</v>
+        <v>79041</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5734,21 +5734,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>540974</v>
+        <v>540915</v>
       </c>
       <c r="R49" t="n">
-        <v>7193351</v>
+        <v>7193185</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5833,7 +5833,7 @@
         <v>129319280</v>
       </c>
       <c r="B50" t="n">
-        <v>95931</v>
+        <v>95932</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5937,10 +5937,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129319366</v>
+        <v>129319335</v>
       </c>
       <c r="B51" t="n">
-        <v>80146</v>
+        <v>80147</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5948,21 +5948,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5972,10 +5972,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>540738</v>
+        <v>540655</v>
       </c>
       <c r="R51" t="n">
-        <v>7193503</v>
+        <v>7193534</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6044,7 +6044,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129319356</v>
+        <v>129319366</v>
       </c>
       <c r="B52" t="n">
         <v>80146</v>
@@ -6079,10 +6079,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>540726</v>
+        <v>540738</v>
       </c>
       <c r="R52" t="n">
-        <v>7193540</v>
+        <v>7193503</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6124,7 +6124,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6151,10 +6151,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129319335</v>
+        <v>129319356</v>
       </c>
       <c r="B53" t="n">
-        <v>80147</v>
+        <v>80146</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6162,21 +6162,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6186,10 +6186,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>540655</v>
+        <v>540726</v>
       </c>
       <c r="R53" t="n">
-        <v>7193534</v>
+        <v>7193540</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6221,7 +6221,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6258,10 +6258,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129319304</v>
+        <v>129319429</v>
       </c>
       <c r="B54" t="n">
-        <v>79041</v>
+        <v>80147</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6269,21 +6269,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6293,10 +6293,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>540962</v>
+        <v>540972</v>
       </c>
       <c r="R54" t="n">
-        <v>7193388</v>
+        <v>7193067</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6328,7 +6328,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6338,7 +6338,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6365,10 +6365,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129319388</v>
+        <v>129319417</v>
       </c>
       <c r="B55" t="n">
-        <v>57727</v>
+        <v>80147</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6376,48 +6376,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>540828</v>
+        <v>540989</v>
       </c>
       <c r="R55" t="n">
-        <v>7193425</v>
+        <v>7193132</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6449,7 +6435,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6459,7 +6445,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6486,10 +6472,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129319429</v>
+        <v>129319388</v>
       </c>
       <c r="B56" t="n">
-        <v>80147</v>
+        <v>57727</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6497,34 +6483,48 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>540972</v>
+        <v>540828</v>
       </c>
       <c r="R56" t="n">
-        <v>7193067</v>
+        <v>7193425</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6556,7 +6556,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6593,10 +6593,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129319417</v>
+        <v>129319304</v>
       </c>
       <c r="B57" t="n">
-        <v>80147</v>
+        <v>79041</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6604,21 +6604,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6628,10 +6628,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>540989</v>
+        <v>540962</v>
       </c>
       <c r="R57" t="n">
-        <v>7193132</v>
+        <v>7193388</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6673,7 +6673,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6700,54 +6700,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129319423</v>
+        <v>129319339</v>
       </c>
       <c r="B58" t="n">
-        <v>57831</v>
+        <v>80147</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103031</v>
+        <v>2081</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>540976</v>
+        <v>540669</v>
       </c>
       <c r="R58" t="n">
-        <v>7193139</v>
+        <v>7193542</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6779,7 +6770,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6789,7 +6780,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6816,10 +6807,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129319279</v>
+        <v>129319353</v>
       </c>
       <c r="B59" t="n">
-        <v>80147</v>
+        <v>82873</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6827,21 +6818,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6851,10 +6842,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>540872</v>
+        <v>540721</v>
       </c>
       <c r="R59" t="n">
-        <v>7193070</v>
+        <v>7193542</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6886,7 +6877,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6896,7 +6887,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6923,10 +6914,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129319353</v>
+        <v>129319311</v>
       </c>
       <c r="B60" t="n">
-        <v>82873</v>
+        <v>91536</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6934,21 +6925,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6958,10 +6949,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>540721</v>
+        <v>540830</v>
       </c>
       <c r="R60" t="n">
-        <v>7193542</v>
+        <v>7193366</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6993,7 +6984,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7003,7 +6994,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7030,7 +7021,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129319339</v>
+        <v>129319279</v>
       </c>
       <c r="B61" t="n">
         <v>80147</v>
@@ -7065,10 +7056,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>540669</v>
+        <v>540872</v>
       </c>
       <c r="R61" t="n">
-        <v>7193542</v>
+        <v>7193070</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7100,7 +7091,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7110,7 +7101,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7137,10 +7128,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129319311</v>
+        <v>129319372</v>
       </c>
       <c r="B62" t="n">
-        <v>91536</v>
+        <v>80146</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7148,21 +7139,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7172,10 +7163,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>540830</v>
+        <v>540736</v>
       </c>
       <c r="R62" t="n">
-        <v>7193366</v>
+        <v>7193500</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7207,7 +7198,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7217,7 +7208,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7244,32 +7235,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129319292</v>
+        <v>129319330</v>
       </c>
       <c r="B63" t="n">
-        <v>79041</v>
+        <v>82990</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7279,10 +7270,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>540996</v>
+        <v>540683</v>
       </c>
       <c r="R63" t="n">
-        <v>7193327</v>
+        <v>7193545</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7314,7 +7305,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7324,7 +7315,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7351,10 +7342,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129319372</v>
+        <v>129319292</v>
       </c>
       <c r="B64" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7362,21 +7353,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7386,10 +7377,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>540736</v>
+        <v>540996</v>
       </c>
       <c r="R64" t="n">
-        <v>7193500</v>
+        <v>7193327</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7421,7 +7412,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7431,7 +7422,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7458,32 +7449,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129319330</v>
+        <v>129319392</v>
       </c>
       <c r="B65" t="n">
-        <v>82990</v>
+        <v>79041</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7493,10 +7484,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>540683</v>
+        <v>540826</v>
       </c>
       <c r="R65" t="n">
-        <v>7193545</v>
+        <v>7193294</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7528,7 +7519,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7538,7 +7529,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7565,45 +7556,54 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129319392</v>
+        <v>129319423</v>
       </c>
       <c r="B66" t="n">
-        <v>79041</v>
+        <v>57831</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>540826</v>
+        <v>540976</v>
       </c>
       <c r="R66" t="n">
-        <v>7193294</v>
+        <v>7193139</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7635,7 +7635,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7645,7 +7645,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7672,54 +7672,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129319293</v>
+        <v>129319421</v>
       </c>
       <c r="B67" t="n">
-        <v>57887</v>
+        <v>80175</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>540980</v>
+        <v>540981</v>
       </c>
       <c r="R67" t="n">
-        <v>7193345</v>
+        <v>7193140</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7751,7 +7742,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7761,7 +7752,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7788,10 +7779,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129319400</v>
+        <v>129319334</v>
       </c>
       <c r="B68" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7799,21 +7790,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7823,10 +7814,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>540943</v>
+        <v>540674</v>
       </c>
       <c r="R68" t="n">
-        <v>7193233</v>
+        <v>7193550</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7858,7 +7849,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7868,7 +7859,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7895,32 +7886,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129319334</v>
+        <v>129319370</v>
       </c>
       <c r="B69" t="n">
-        <v>80146</v>
+        <v>80175</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7930,10 +7921,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>540674</v>
+        <v>540737</v>
       </c>
       <c r="R69" t="n">
-        <v>7193550</v>
+        <v>7193504</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7965,7 +7956,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7975,7 +7966,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8002,32 +7993,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129319370</v>
+        <v>129319397</v>
       </c>
       <c r="B70" t="n">
-        <v>80175</v>
+        <v>79041</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8037,10 +8028,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>540737</v>
+        <v>540946</v>
       </c>
       <c r="R70" t="n">
-        <v>7193504</v>
+        <v>7193256</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8072,7 +8063,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8082,7 +8073,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8109,32 +8100,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129319421</v>
+        <v>129319400</v>
       </c>
       <c r="B71" t="n">
-        <v>80175</v>
+        <v>79041</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8144,10 +8135,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>540981</v>
+        <v>540943</v>
       </c>
       <c r="R71" t="n">
-        <v>7193140</v>
+        <v>7193233</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8179,7 +8170,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8189,7 +8180,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8216,10 +8207,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129319397</v>
+        <v>129319293</v>
       </c>
       <c r="B72" t="n">
-        <v>79041</v>
+        <v>57887</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8227,34 +8218,43 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>540946</v>
+        <v>540980</v>
       </c>
       <c r="R72" t="n">
-        <v>7193256</v>
+        <v>7193345</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8286,7 +8286,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8323,45 +8323,54 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129319367</v>
+        <v>129319432</v>
       </c>
       <c r="B73" t="n">
-        <v>80175</v>
+        <v>58360</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6462</v>
+        <v>102125</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>540734</v>
+        <v>540978</v>
       </c>
       <c r="R73" t="n">
-        <v>7193503</v>
+        <v>7193078</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8393,7 +8402,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8403,7 +8412,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8430,32 +8439,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129319413</v>
+        <v>129319367</v>
       </c>
       <c r="B74" t="n">
-        <v>79041</v>
+        <v>80175</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8465,10 +8474,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>540965</v>
+        <v>540734</v>
       </c>
       <c r="R74" t="n">
-        <v>7193181</v>
+        <v>7193503</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8500,7 +8509,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8510,7 +8519,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8644,10 +8653,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129319412</v>
+        <v>129319413</v>
       </c>
       <c r="B76" t="n">
-        <v>91560</v>
+        <v>79041</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8655,19 +8664,23 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -8675,10 +8688,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>540952</v>
+        <v>540965</v>
       </c>
       <c r="R76" t="n">
-        <v>7193187</v>
+        <v>7193181</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8710,7 +8723,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8720,7 +8733,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8747,54 +8760,41 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129319432</v>
+        <v>129319412</v>
       </c>
       <c r="B77" t="n">
-        <v>58360</v>
+        <v>91560</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>102125</v>
+        <v>5432</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>540978</v>
+        <v>540952</v>
       </c>
       <c r="R77" t="n">
-        <v>7193078</v>
+        <v>7193187</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8826,7 +8826,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8836,7 +8836,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9082,10 +9082,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129319338</v>
+        <v>129319336</v>
       </c>
       <c r="B80" t="n">
-        <v>80147</v>
+        <v>79041</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9093,21 +9093,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9117,10 +9117,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>540676</v>
+        <v>540668</v>
       </c>
       <c r="R80" t="n">
-        <v>7193539</v>
+        <v>7193543</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9152,7 +9152,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9162,7 +9162,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9189,32 +9189,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129319431</v>
+        <v>129319382</v>
       </c>
       <c r="B81" t="n">
-        <v>80175</v>
+        <v>79041</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9224,10 +9224,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>540979</v>
+        <v>540761</v>
       </c>
       <c r="R81" t="n">
-        <v>7193075</v>
+        <v>7193473</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9259,7 +9259,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9296,7 +9296,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129319382</v>
+        <v>129319394</v>
       </c>
       <c r="B82" t="n">
         <v>79041</v>
@@ -9331,10 +9331,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>540761</v>
+        <v>540877</v>
       </c>
       <c r="R82" t="n">
-        <v>7193473</v>
+        <v>7193291</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9366,7 +9366,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9376,7 +9376,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9403,10 +9403,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129319408</v>
+        <v>129319338</v>
       </c>
       <c r="B83" t="n">
-        <v>80146</v>
+        <v>80147</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9414,21 +9414,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9438,10 +9438,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>540939</v>
+        <v>540676</v>
       </c>
       <c r="R83" t="n">
-        <v>7193177</v>
+        <v>7193539</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9473,7 +9473,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9483,7 +9483,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9510,10 +9510,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129319336</v>
+        <v>129319408</v>
       </c>
       <c r="B84" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9521,21 +9521,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9545,10 +9545,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>540668</v>
+        <v>540939</v>
       </c>
       <c r="R84" t="n">
-        <v>7193543</v>
+        <v>7193177</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9580,7 +9580,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9590,7 +9590,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9617,32 +9617,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129319394</v>
+        <v>129319431</v>
       </c>
       <c r="B85" t="n">
-        <v>79041</v>
+        <v>80175</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9652,10 +9652,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>540877</v>
+        <v>540979</v>
       </c>
       <c r="R85" t="n">
-        <v>7193291</v>
+        <v>7193075</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9687,7 +9687,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9697,7 +9697,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9724,32 +9724,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129319389</v>
+        <v>129319375</v>
       </c>
       <c r="B86" t="n">
-        <v>95931</v>
+        <v>80147</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2809</v>
+        <v>2081</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9759,10 +9759,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>540818</v>
+        <v>540730</v>
       </c>
       <c r="R86" t="n">
-        <v>7193358</v>
+        <v>7193493</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9794,7 +9794,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9804,7 +9804,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9938,7 +9938,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129319375</v>
+        <v>129319376</v>
       </c>
       <c r="B88" t="n">
         <v>80147</v>
@@ -9973,10 +9973,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>540730</v>
+        <v>540738</v>
       </c>
       <c r="R88" t="n">
-        <v>7193493</v>
+        <v>7193476</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -10008,7 +10008,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10018,7 +10018,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10259,32 +10259,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129319376</v>
+        <v>129319389</v>
       </c>
       <c r="B91" t="n">
-        <v>80147</v>
+        <v>95932</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2081</v>
+        <v>2809</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10294,10 +10294,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>540738</v>
+        <v>540818</v>
       </c>
       <c r="R91" t="n">
-        <v>7193476</v>
+        <v>7193358</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -10329,7 +10329,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10339,7 +10339,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10366,10 +10366,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129319298</v>
+        <v>129319284</v>
       </c>
       <c r="B92" t="n">
-        <v>91560</v>
+        <v>79041</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10377,19 +10377,23 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -10397,10 +10401,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>540964</v>
+        <v>540867</v>
       </c>
       <c r="R92" t="n">
-        <v>7193371</v>
+        <v>7193169</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -10432,7 +10436,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10442,7 +10446,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10469,32 +10473,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129319409</v>
+        <v>129319393</v>
       </c>
       <c r="B93" t="n">
-        <v>80146</v>
+        <v>82990</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6458</v>
+        <v>6439</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10504,10 +10508,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>540942</v>
+        <v>540824</v>
       </c>
       <c r="R93" t="n">
-        <v>7193182</v>
+        <v>7193288</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -10539,7 +10543,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10549,7 +10553,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10683,7 +10687,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129319284</v>
+        <v>129319344</v>
       </c>
       <c r="B95" t="n">
         <v>79041</v>
@@ -10718,10 +10722,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>540867</v>
+        <v>540650</v>
       </c>
       <c r="R95" t="n">
-        <v>7193169</v>
+        <v>7193540</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -10753,7 +10757,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10763,7 +10767,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10790,34 +10794,30 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129319393</v>
+        <v>129319298</v>
       </c>
       <c r="B96" t="n">
-        <v>82990</v>
+        <v>91560</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6439</v>
+        <v>5432</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -10825,10 +10825,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>540824</v>
+        <v>540964</v>
       </c>
       <c r="R96" t="n">
-        <v>7193288</v>
+        <v>7193371</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -10860,7 +10860,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10870,7 +10870,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10897,10 +10897,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129319344</v>
+        <v>129319409</v>
       </c>
       <c r="B97" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10908,21 +10908,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10932,10 +10932,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>540650</v>
+        <v>540942</v>
       </c>
       <c r="R97" t="n">
-        <v>7193540</v>
+        <v>7193182</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -10967,7 +10967,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10977,7 +10977,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11325,7 +11325,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129319286</v>
+        <v>129319362</v>
       </c>
       <c r="B101" t="n">
         <v>79041</v>
@@ -11360,10 +11360,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>540891</v>
+        <v>540721</v>
       </c>
       <c r="R101" t="n">
-        <v>7193174</v>
+        <v>7193527</v>
       </c>
       <c r="S101" t="n">
         <v>25</v>
@@ -11395,7 +11395,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11405,7 +11405,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11432,7 +11432,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129319362</v>
+        <v>129319306</v>
       </c>
       <c r="B102" t="n">
         <v>79041</v>
@@ -11467,10 +11467,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>540721</v>
+        <v>540961</v>
       </c>
       <c r="R102" t="n">
-        <v>7193527</v>
+        <v>7193398</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -11502,7 +11502,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11512,7 +11512,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11539,7 +11539,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129319306</v>
+        <v>129319286</v>
       </c>
       <c r="B103" t="n">
         <v>79041</v>
@@ -11574,10 +11574,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>540961</v>
+        <v>540891</v>
       </c>
       <c r="R103" t="n">
-        <v>7193398</v>
+        <v>7193174</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -11609,7 +11609,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11619,7 +11619,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11762,10 +11762,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129319411</v>
+        <v>129319368</v>
       </c>
       <c r="B105" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11773,21 +11773,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11797,10 +11797,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>540955</v>
+        <v>540734</v>
       </c>
       <c r="R105" t="n">
-        <v>7193186</v>
+        <v>7193503</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -11832,7 +11832,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11842,7 +11842,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11976,10 +11976,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129319368</v>
+        <v>129319391</v>
       </c>
       <c r="B107" t="n">
-        <v>80146</v>
+        <v>80147</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11987,21 +11987,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12011,10 +12011,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>540734</v>
+        <v>540818</v>
       </c>
       <c r="R107" t="n">
-        <v>7193503</v>
+        <v>7193333</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -12046,7 +12046,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12056,7 +12056,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12083,10 +12083,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129319407</v>
+        <v>129319355</v>
       </c>
       <c r="B108" t="n">
-        <v>79041</v>
+        <v>80147</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12094,21 +12094,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12118,10 +12118,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>540924</v>
+        <v>540726</v>
       </c>
       <c r="R108" t="n">
-        <v>7193211</v>
+        <v>7193541</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -12153,7 +12153,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12163,7 +12163,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12190,10 +12190,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129319391</v>
+        <v>129319360</v>
       </c>
       <c r="B109" t="n">
-        <v>80147</v>
+        <v>91536</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12201,21 +12201,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12225,10 +12225,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>540818</v>
+        <v>540725</v>
       </c>
       <c r="R109" t="n">
-        <v>7193333</v>
+        <v>7193532</v>
       </c>
       <c r="S109" t="n">
         <v>25</v>
@@ -12260,7 +12260,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12270,7 +12270,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12297,7 +12297,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129319355</v>
+        <v>129319369</v>
       </c>
       <c r="B110" t="n">
         <v>80147</v>
@@ -12332,10 +12332,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>540726</v>
+        <v>540734</v>
       </c>
       <c r="R110" t="n">
-        <v>7193541</v>
+        <v>7193503</v>
       </c>
       <c r="S110" t="n">
         <v>25</v>
@@ -12367,7 +12367,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12377,7 +12377,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12404,10 +12404,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129319360</v>
+        <v>129319411</v>
       </c>
       <c r="B111" t="n">
-        <v>91536</v>
+        <v>79041</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12415,21 +12415,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12439,10 +12439,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>540725</v>
+        <v>540955</v>
       </c>
       <c r="R111" t="n">
-        <v>7193532</v>
+        <v>7193186</v>
       </c>
       <c r="S111" t="n">
         <v>25</v>
@@ -12474,7 +12474,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12484,7 +12484,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12511,10 +12511,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129319369</v>
+        <v>129319407</v>
       </c>
       <c r="B112" t="n">
-        <v>80147</v>
+        <v>79041</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12522,21 +12522,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12546,10 +12546,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>540734</v>
+        <v>540924</v>
       </c>
       <c r="R112" t="n">
-        <v>7193503</v>
+        <v>7193211</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>
@@ -12581,7 +12581,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12591,7 +12591,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12618,10 +12618,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129319426</v>
+        <v>129319309</v>
       </c>
       <c r="B113" t="n">
-        <v>80147</v>
+        <v>79041</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12629,21 +12629,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12653,10 +12653,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>540979</v>
+        <v>540894</v>
       </c>
       <c r="R113" t="n">
-        <v>7193115</v>
+        <v>7193411</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -12688,7 +12688,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12725,10 +12725,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129319341</v>
+        <v>129319332</v>
       </c>
       <c r="B114" t="n">
-        <v>91536</v>
+        <v>57887</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12736,34 +12736,43 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>540670</v>
+        <v>540675</v>
       </c>
       <c r="R114" t="n">
-        <v>7193533</v>
+        <v>7193538</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -12795,7 +12804,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12805,7 +12814,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12832,10 +12841,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129319305</v>
+        <v>129319341</v>
       </c>
       <c r="B115" t="n">
-        <v>91560</v>
+        <v>91536</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12843,19 +12852,23 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
@@ -12863,10 +12876,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>540959</v>
+        <v>540670</v>
       </c>
       <c r="R115" t="n">
-        <v>7193395</v>
+        <v>7193533</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -12898,7 +12911,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12908,7 +12921,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12935,10 +12948,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129319332</v>
+        <v>129319426</v>
       </c>
       <c r="B116" t="n">
-        <v>57887</v>
+        <v>80147</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12946,43 +12959,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>540675</v>
+        <v>540979</v>
       </c>
       <c r="R116" t="n">
-        <v>7193538</v>
+        <v>7193115</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -13014,7 +13018,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13024,7 +13028,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13051,27 +13055,27 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129319309</v>
+        <v>129319425</v>
       </c>
       <c r="B117" t="n">
-        <v>79041</v>
+        <v>80181</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -13086,10 +13090,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>540894</v>
+        <v>540980</v>
       </c>
       <c r="R117" t="n">
-        <v>7193411</v>
+        <v>7193116</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -13121,7 +13125,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13131,7 +13135,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13158,34 +13162,30 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129319425</v>
+        <v>129319305</v>
       </c>
       <c r="B118" t="n">
-        <v>80181</v>
+        <v>91560</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
@@ -13193,10 +13193,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>540980</v>
+        <v>540959</v>
       </c>
       <c r="R118" t="n">
-        <v>7193116</v>
+        <v>7193395</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -13228,7 +13228,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13238,7 +13238,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13265,45 +13265,54 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129319277</v>
+        <v>129319363</v>
       </c>
       <c r="B119" t="n">
-        <v>80147</v>
+        <v>58360</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>2081</v>
+        <v>102125</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>540837</v>
+        <v>540731</v>
       </c>
       <c r="R119" t="n">
-        <v>7193042</v>
+        <v>7193512</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -13335,7 +13344,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13345,7 +13354,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13372,10 +13381,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129319319</v>
+        <v>129319410</v>
       </c>
       <c r="B120" t="n">
-        <v>80147</v>
+        <v>56908</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13383,34 +13392,43 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>2081</v>
+        <v>102612</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>540719</v>
+        <v>540946</v>
       </c>
       <c r="R120" t="n">
-        <v>7193463</v>
+        <v>7193171</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -13442,7 +13460,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13452,7 +13470,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13479,10 +13497,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129319325</v>
+        <v>129319329</v>
       </c>
       <c r="B121" t="n">
-        <v>80147</v>
+        <v>88940</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13490,21 +13508,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>2081</v>
+        <v>510</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13514,10 +13532,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>540714</v>
+        <v>540692</v>
       </c>
       <c r="R121" t="n">
-        <v>7193488</v>
+        <v>7193539</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -13549,7 +13567,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13559,7 +13577,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13586,10 +13604,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129319329</v>
+        <v>129319325</v>
       </c>
       <c r="B122" t="n">
-        <v>88940</v>
+        <v>80147</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13597,21 +13615,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>510</v>
+        <v>2081</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13621,10 +13639,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>540692</v>
+        <v>540714</v>
       </c>
       <c r="R122" t="n">
-        <v>7193539</v>
+        <v>7193488</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -13656,7 +13674,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13666,7 +13684,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13693,32 +13711,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129319416</v>
+        <v>129319277</v>
       </c>
       <c r="B123" t="n">
-        <v>80182</v>
+        <v>80147</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13728,10 +13746,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>540970</v>
+        <v>540837</v>
       </c>
       <c r="R123" t="n">
-        <v>7193154</v>
+        <v>7193042</v>
       </c>
       <c r="S123" t="n">
         <v>25</v>
@@ -13763,7 +13781,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13773,7 +13791,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13800,32 +13818,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129319321</v>
+        <v>129319319</v>
       </c>
       <c r="B124" t="n">
-        <v>80175</v>
+        <v>80147</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13907,7 +13925,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129319373</v>
+        <v>129319416</v>
       </c>
       <c r="B125" t="n">
         <v>80182</v>
@@ -13942,10 +13960,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>540734</v>
+        <v>540970</v>
       </c>
       <c r="R125" t="n">
-        <v>7193499</v>
+        <v>7193154</v>
       </c>
       <c r="S125" t="n">
         <v>25</v>
@@ -13977,7 +13995,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13987,7 +14005,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14014,32 +14032,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129319350</v>
+        <v>129319373</v>
       </c>
       <c r="B126" t="n">
-        <v>80146</v>
+        <v>80182</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14049,10 +14067,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>540681</v>
+        <v>540734</v>
       </c>
       <c r="R126" t="n">
-        <v>7193521</v>
+        <v>7193499</v>
       </c>
       <c r="S126" t="n">
         <v>25</v>
@@ -14084,7 +14102,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14094,7 +14112,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14121,54 +14139,45 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129319363</v>
+        <v>129319321</v>
       </c>
       <c r="B127" t="n">
-        <v>58360</v>
+        <v>80175</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>102125</v>
+        <v>6462</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>540731</v>
+        <v>540719</v>
       </c>
       <c r="R127" t="n">
-        <v>7193512</v>
+        <v>7193463</v>
       </c>
       <c r="S127" t="n">
         <v>25</v>
@@ -14200,7 +14209,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14210,7 +14219,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14237,10 +14246,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129319410</v>
+        <v>129319350</v>
       </c>
       <c r="B128" t="n">
-        <v>56908</v>
+        <v>80146</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14248,43 +14257,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>540946</v>
+        <v>540681</v>
       </c>
       <c r="R128" t="n">
-        <v>7193171</v>
+        <v>7193521</v>
       </c>
       <c r="S128" t="n">
         <v>25</v>
@@ -14316,7 +14316,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14326,7 +14326,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14353,7 +14353,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129319434</v>
+        <v>129319326</v>
       </c>
       <c r="B129" t="n">
         <v>80146</v>
@@ -14388,10 +14388,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>540979</v>
+        <v>540701</v>
       </c>
       <c r="R129" t="n">
-        <v>7193075</v>
+        <v>7193533</v>
       </c>
       <c r="S129" t="n">
         <v>25</v>
@@ -14423,7 +14423,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14433,7 +14433,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14460,7 +14460,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129319326</v>
+        <v>129319434</v>
       </c>
       <c r="B130" t="n">
         <v>80146</v>
@@ -14495,10 +14495,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>540701</v>
+        <v>540979</v>
       </c>
       <c r="R130" t="n">
-        <v>7193533</v>
+        <v>7193075</v>
       </c>
       <c r="S130" t="n">
         <v>25</v>
@@ -14530,7 +14530,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14540,7 +14540,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14674,32 +14674,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129319380</v>
+        <v>129319312</v>
       </c>
       <c r="B132" t="n">
-        <v>92258</v>
+        <v>80147</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>3298</v>
+        <v>2081</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14709,10 +14709,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>540761</v>
+        <v>540789</v>
       </c>
       <c r="R132" t="n">
-        <v>7193490</v>
+        <v>7193373</v>
       </c>
       <c r="S132" t="n">
         <v>25</v>
@@ -14744,7 +14744,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14754,7 +14754,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14781,10 +14781,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129319310</v>
+        <v>129319322</v>
       </c>
       <c r="B133" t="n">
-        <v>79041</v>
+        <v>80147</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14792,21 +14792,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14816,10 +14816,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>540830</v>
+        <v>540719</v>
       </c>
       <c r="R133" t="n">
-        <v>7193366</v>
+        <v>7193483</v>
       </c>
       <c r="S133" t="n">
         <v>25</v>
@@ -14851,7 +14851,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14861,7 +14861,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14888,50 +14888,45 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129319343</v>
+        <v>129319378</v>
       </c>
       <c r="B134" t="n">
-        <v>57727</v>
+        <v>82992</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100109</v>
+        <v>306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>540661</v>
+        <v>540757</v>
       </c>
       <c r="R134" t="n">
-        <v>7193538</v>
+        <v>7193474</v>
       </c>
       <c r="S134" t="n">
         <v>25</v>
@@ -14963,7 +14958,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14973,12 +14968,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>11:27</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>Färska och äldre spår på samma träd.</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15005,10 +14995,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129319322</v>
+        <v>129319343</v>
       </c>
       <c r="B135" t="n">
-        <v>80147</v>
+        <v>57727</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15016,34 +15006,39 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>540719</v>
+        <v>540661</v>
       </c>
       <c r="R135" t="n">
-        <v>7193483</v>
+        <v>7193538</v>
       </c>
       <c r="S135" t="n">
         <v>25</v>
@@ -15075,7 +15070,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15085,7 +15080,12 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>Färska och äldre spår på samma träd.</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15112,32 +15112,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129319312</v>
+        <v>129319380</v>
       </c>
       <c r="B136" t="n">
-        <v>80147</v>
+        <v>92258</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>2081</v>
+        <v>3298</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15147,10 +15147,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>540789</v>
+        <v>540761</v>
       </c>
       <c r="R136" t="n">
-        <v>7193373</v>
+        <v>7193490</v>
       </c>
       <c r="S136" t="n">
         <v>25</v>
@@ -15182,7 +15182,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15192,7 +15192,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15219,32 +15219,32 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129319378</v>
+        <v>129319310</v>
       </c>
       <c r="B137" t="n">
-        <v>82992</v>
+        <v>79041</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>306</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15254,10 +15254,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>540757</v>
+        <v>540830</v>
       </c>
       <c r="R137" t="n">
-        <v>7193474</v>
+        <v>7193366</v>
       </c>
       <c r="S137" t="n">
         <v>25</v>
@@ -15289,7 +15289,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15299,7 +15299,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15326,10 +15326,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129319287</v>
+        <v>129319315</v>
       </c>
       <c r="B138" t="n">
-        <v>92258</v>
+        <v>82990</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15337,21 +15337,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>3298</v>
+        <v>6439</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15361,10 +15361,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>540913</v>
+        <v>540765</v>
       </c>
       <c r="R138" t="n">
-        <v>7193185</v>
+        <v>7193370</v>
       </c>
       <c r="S138" t="n">
         <v>25</v>
@@ -15396,7 +15396,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15406,7 +15406,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15433,10 +15433,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129319387</v>
+        <v>129319327</v>
       </c>
       <c r="B139" t="n">
-        <v>82999</v>
+        <v>79041</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15444,21 +15444,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15468,10 +15468,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>540772</v>
+        <v>540693</v>
       </c>
       <c r="R139" t="n">
-        <v>7193446</v>
+        <v>7193540</v>
       </c>
       <c r="S139" t="n">
         <v>25</v>
@@ -15503,7 +15503,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15513,7 +15513,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15540,32 +15540,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129319406</v>
+        <v>129319287</v>
       </c>
       <c r="B140" t="n">
-        <v>79120</v>
+        <v>92258</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>864</v>
+        <v>3298</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15575,10 +15575,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>540938</v>
+        <v>540913</v>
       </c>
       <c r="R140" t="n">
-        <v>7193168</v>
+        <v>7193185</v>
       </c>
       <c r="S140" t="n">
         <v>25</v>
@@ -15610,7 +15610,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15620,7 +15620,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15647,10 +15647,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129319327</v>
+        <v>129319387</v>
       </c>
       <c r="B141" t="n">
-        <v>79041</v>
+        <v>82999</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15658,21 +15658,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15682,10 +15682,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>540693</v>
+        <v>540772</v>
       </c>
       <c r="R141" t="n">
-        <v>7193540</v>
+        <v>7193446</v>
       </c>
       <c r="S141" t="n">
         <v>25</v>
@@ -15717,7 +15717,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15727,7 +15727,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15754,32 +15754,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129319347</v>
+        <v>129319406</v>
       </c>
       <c r="B142" t="n">
-        <v>80182</v>
+        <v>79120</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6464</v>
+        <v>864</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15789,10 +15789,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>540653</v>
+        <v>540938</v>
       </c>
       <c r="R142" t="n">
-        <v>7193521</v>
+        <v>7193168</v>
       </c>
       <c r="S142" t="n">
         <v>25</v>
@@ -15824,7 +15824,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15861,32 +15861,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129319315</v>
+        <v>129319428</v>
       </c>
       <c r="B143" t="n">
-        <v>82990</v>
+        <v>80146</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6439</v>
+        <v>6458</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15896,10 +15896,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>540765</v>
+        <v>540971</v>
       </c>
       <c r="R143" t="n">
-        <v>7193370</v>
+        <v>7193081</v>
       </c>
       <c r="S143" t="n">
         <v>25</v>
@@ -15931,7 +15931,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15941,7 +15941,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15968,32 +15968,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129319428</v>
+        <v>129319347</v>
       </c>
       <c r="B144" t="n">
-        <v>80146</v>
+        <v>80182</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -16003,10 +16003,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>540971</v>
+        <v>540653</v>
       </c>
       <c r="R144" t="n">
-        <v>7193081</v>
+        <v>7193521</v>
       </c>
       <c r="S144" t="n">
         <v>25</v>
@@ -16038,7 +16038,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16048,7 +16048,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD144" t="b">

--- a/artfynd/A 51086-2025 artfynd.xlsx
+++ b/artfynd/A 51086-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129319384</v>
+        <v>129319285</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>91539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540775</v>
+        <v>540886</v>
       </c>
       <c r="R2" t="n">
-        <v>7193467</v>
+        <v>7193172</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129319386</v>
+        <v>129319307</v>
       </c>
       <c r="B3" t="n">
-        <v>95932</v>
+        <v>91539</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2809</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540774</v>
+        <v>540962</v>
       </c>
       <c r="R3" t="n">
-        <v>7193457</v>
+        <v>7193400</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129319285</v>
+        <v>129319420</v>
       </c>
       <c r="B4" t="n">
-        <v>91536</v>
+        <v>80148</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540886</v>
+        <v>540982</v>
       </c>
       <c r="R4" t="n">
-        <v>7193172</v>
+        <v>7193144</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129319307</v>
+        <v>129319384</v>
       </c>
       <c r="B5" t="n">
-        <v>91536</v>
+        <v>79043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540962</v>
+        <v>540775</v>
       </c>
       <c r="R5" t="n">
-        <v>7193400</v>
+        <v>7193467</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,32 +1103,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129319323</v>
+        <v>129319302</v>
       </c>
       <c r="B6" t="n">
-        <v>80182</v>
+        <v>79043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540719</v>
+        <v>540960</v>
       </c>
       <c r="R6" t="n">
-        <v>7193483</v>
+        <v>7193375</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129319420</v>
+        <v>129319300</v>
       </c>
       <c r="B7" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,34 +1221,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540982</v>
+        <v>540961</v>
       </c>
       <c r="R7" t="n">
-        <v>7193144</v>
+        <v>7193376</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1280,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1295,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,27 +1322,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129319300</v>
+        <v>129319414</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>58360</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>102125</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1345,10 +1350,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1357,10 +1366,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540961</v>
+        <v>540963</v>
       </c>
       <c r="R8" t="n">
-        <v>7193376</v>
+        <v>7193203</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1392,7 +1401,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1402,7 +1411,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1429,32 +1438,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129319302</v>
+        <v>129319386</v>
       </c>
       <c r="B9" t="n">
-        <v>79041</v>
+        <v>95936</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1473,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540960</v>
+        <v>540774</v>
       </c>
       <c r="R9" t="n">
-        <v>7193375</v>
+        <v>7193457</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1499,7 +1508,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1509,7 +1518,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,54 +1545,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129319414</v>
+        <v>129319323</v>
       </c>
       <c r="B10" t="n">
-        <v>58360</v>
+        <v>80184</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102125</v>
+        <v>6464</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540963</v>
+        <v>540719</v>
       </c>
       <c r="R10" t="n">
-        <v>7193203</v>
+        <v>7193483</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1615,7 +1615,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1652,10 +1652,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129319381</v>
+        <v>129319296</v>
       </c>
       <c r="B11" t="n">
-        <v>82873</v>
+        <v>79043</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1663,21 +1663,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540758</v>
+        <v>540970</v>
       </c>
       <c r="R11" t="n">
-        <v>7193475</v>
+        <v>7193365</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1759,32 +1759,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129319424</v>
+        <v>129319430</v>
       </c>
       <c r="B12" t="n">
-        <v>80147</v>
+        <v>80183</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1794,10 +1794,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540975</v>
+        <v>540971</v>
       </c>
       <c r="R12" t="n">
-        <v>7193139</v>
+        <v>7193066</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1829,7 +1829,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1866,10 +1866,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129319295</v>
+        <v>129319419</v>
       </c>
       <c r="B13" t="n">
-        <v>95932</v>
+        <v>80183</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1877,21 +1877,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2809</v>
+        <v>6463</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1901,10 +1901,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540972</v>
+        <v>540986</v>
       </c>
       <c r="R13" t="n">
-        <v>7193357</v>
+        <v>7193130</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1973,32 +1973,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129319361</v>
+        <v>129319313</v>
       </c>
       <c r="B14" t="n">
-        <v>91540</v>
+        <v>80184</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2008,10 +2008,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540726</v>
+        <v>540789</v>
       </c>
       <c r="R14" t="n">
-        <v>7193531</v>
+        <v>7193372</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2080,32 +2080,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129319419</v>
+        <v>129319352</v>
       </c>
       <c r="B15" t="n">
-        <v>80181</v>
+        <v>78056</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6463</v>
+        <v>228579</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540986</v>
+        <v>540715</v>
       </c>
       <c r="R15" t="n">
-        <v>7193130</v>
+        <v>7193537</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2187,10 +2187,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129319328</v>
+        <v>129319361</v>
       </c>
       <c r="B16" t="n">
-        <v>80146</v>
+        <v>91543</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2198,21 +2198,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2222,10 +2222,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540693</v>
+        <v>540726</v>
       </c>
       <c r="R16" t="n">
-        <v>7193540</v>
+        <v>7193531</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2294,10 +2294,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129319313</v>
+        <v>129319295</v>
       </c>
       <c r="B17" t="n">
-        <v>80182</v>
+        <v>95936</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2305,21 +2305,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6464</v>
+        <v>2809</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2329,10 +2329,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540789</v>
+        <v>540972</v>
       </c>
       <c r="R17" t="n">
-        <v>7193372</v>
+        <v>7193357</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2401,32 +2401,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129319430</v>
+        <v>129319424</v>
       </c>
       <c r="B18" t="n">
-        <v>80181</v>
+        <v>80149</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2436,10 +2436,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540971</v>
+        <v>540975</v>
       </c>
       <c r="R18" t="n">
-        <v>7193066</v>
+        <v>7193139</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2508,10 +2508,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129319296</v>
+        <v>129319381</v>
       </c>
       <c r="B19" t="n">
-        <v>79041</v>
+        <v>82877</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,21 +2519,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2543,10 +2543,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540970</v>
+        <v>540758</v>
       </c>
       <c r="R19" t="n">
-        <v>7193365</v>
+        <v>7193475</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2618,7 +2618,7 @@
         <v>129319324</v>
       </c>
       <c r="B20" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2722,10 +2722,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129319438</v>
+        <v>129319328</v>
       </c>
       <c r="B21" t="n">
-        <v>57887</v>
+        <v>80148</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2733,43 +2733,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540982</v>
+        <v>540693</v>
       </c>
       <c r="R21" t="n">
-        <v>7193110</v>
+        <v>7193540</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2801,7 +2792,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2811,7 +2802,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2838,10 +2829,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129319352</v>
+        <v>129319438</v>
       </c>
       <c r="B22" t="n">
-        <v>78054</v>
+        <v>57887</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2849,34 +2840,43 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228579</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540715</v>
+        <v>540982</v>
       </c>
       <c r="R22" t="n">
-        <v>7193537</v>
+        <v>7193110</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2945,10 +2945,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129319316</v>
+        <v>129319340</v>
       </c>
       <c r="B23" t="n">
-        <v>80147</v>
+        <v>91543</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2956,21 +2956,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2980,10 +2980,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540763</v>
+        <v>540666</v>
       </c>
       <c r="R23" t="n">
-        <v>7193372</v>
+        <v>7193537</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3015,7 +3015,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3055,7 +3055,7 @@
         <v>129319281</v>
       </c>
       <c r="B24" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3159,10 +3159,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129319291</v>
+        <v>129319316</v>
       </c>
       <c r="B25" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3194,10 +3194,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540996</v>
+        <v>540763</v>
       </c>
       <c r="R25" t="n">
-        <v>7193327</v>
+        <v>7193372</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3229,7 +3229,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3239,7 +3239,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3266,10 +3266,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129319340</v>
+        <v>129319291</v>
       </c>
       <c r="B26" t="n">
-        <v>91540</v>
+        <v>80149</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3277,21 +3277,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3301,10 +3301,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540666</v>
+        <v>540996</v>
       </c>
       <c r="R26" t="n">
-        <v>7193537</v>
+        <v>7193327</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3373,10 +3373,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129319349</v>
+        <v>129319390</v>
       </c>
       <c r="B27" t="n">
-        <v>91560</v>
+        <v>79043</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3384,19 +3384,23 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3404,10 +3408,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>540670</v>
+        <v>540818</v>
       </c>
       <c r="R27" t="n">
-        <v>7193521</v>
+        <v>7193358</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3439,7 +3443,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3449,7 +3453,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3476,10 +3480,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129319390</v>
+        <v>129319383</v>
       </c>
       <c r="B28" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3511,10 +3515,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>540818</v>
+        <v>540764</v>
       </c>
       <c r="R28" t="n">
-        <v>7193358</v>
+        <v>7193475</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3546,7 +3550,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3556,7 +3560,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3583,10 +3587,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129319383</v>
+        <v>129319349</v>
       </c>
       <c r="B29" t="n">
-        <v>79041</v>
+        <v>91563</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3594,23 +3598,19 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3618,10 +3618,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>540764</v>
+        <v>540670</v>
       </c>
       <c r="R29" t="n">
-        <v>7193475</v>
+        <v>7193521</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3653,7 +3653,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3693,7 +3693,7 @@
         <v>129319354</v>
       </c>
       <c r="B30" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3797,32 +3797,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129319377</v>
+        <v>129319422</v>
       </c>
       <c r="B31" t="n">
-        <v>80147</v>
+        <v>80183</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>540745</v>
+        <v>540980</v>
       </c>
       <c r="R31" t="n">
-        <v>7193494</v>
+        <v>7193139</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3867,7 +3867,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3907,7 +3907,7 @@
         <v>129319374</v>
       </c>
       <c r="B32" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4011,10 +4011,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129319337</v>
+        <v>129319377</v>
       </c>
       <c r="B33" t="n">
-        <v>80146</v>
+        <v>80149</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4022,21 +4022,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4046,10 +4046,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>540676</v>
+        <v>540745</v>
       </c>
       <c r="R33" t="n">
-        <v>7193539</v>
+        <v>7193494</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4081,7 +4081,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4118,27 +4118,27 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129319422</v>
+        <v>129319396</v>
       </c>
       <c r="B34" t="n">
-        <v>80181</v>
+        <v>79043</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4153,10 +4153,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>540980</v>
+        <v>540928</v>
       </c>
       <c r="R34" t="n">
-        <v>7193139</v>
+        <v>7193263</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4225,10 +4225,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129319396</v>
+        <v>129319427</v>
       </c>
       <c r="B35" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4260,10 +4260,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>540928</v>
+        <v>540969</v>
       </c>
       <c r="R35" t="n">
-        <v>7193263</v>
+        <v>7193117</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4295,7 +4295,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4305,7 +4305,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4332,10 +4332,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129319427</v>
+        <v>129319282</v>
       </c>
       <c r="B36" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4367,10 +4367,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>540969</v>
+        <v>540901</v>
       </c>
       <c r="R36" t="n">
-        <v>7193117</v>
+        <v>7193084</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4402,7 +4402,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4439,10 +4439,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129319282</v>
+        <v>129319337</v>
       </c>
       <c r="B37" t="n">
-        <v>79041</v>
+        <v>80148</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4450,21 +4450,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4474,10 +4474,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>540901</v>
+        <v>540676</v>
       </c>
       <c r="R37" t="n">
-        <v>7193084</v>
+        <v>7193539</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4549,7 +4549,7 @@
         <v>129319405</v>
       </c>
       <c r="B38" t="n">
-        <v>83007</v>
+        <v>83011</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>129319404</v>
       </c>
       <c r="B39" t="n">
-        <v>78054</v>
+        <v>78056</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4760,32 +4760,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129319278</v>
+        <v>129319395</v>
       </c>
       <c r="B40" t="n">
-        <v>80147</v>
+        <v>82996</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>540864</v>
+        <v>540878</v>
       </c>
       <c r="R40" t="n">
-        <v>7193066</v>
+        <v>7193291</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4840,7 +4840,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4867,10 +4867,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129319294</v>
+        <v>129319278</v>
       </c>
       <c r="B41" t="n">
-        <v>83012</v>
+        <v>80149</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4878,21 +4878,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1467</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>540974</v>
+        <v>540864</v>
       </c>
       <c r="R41" t="n">
-        <v>7193351</v>
+        <v>7193066</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4947,7 +4947,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4977,7 +4977,7 @@
         <v>129319365</v>
       </c>
       <c r="B42" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5081,10 +5081,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129319348</v>
+        <v>129319294</v>
       </c>
       <c r="B43" t="n">
-        <v>80146</v>
+        <v>83016</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5092,21 +5092,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>1467</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5116,10 +5116,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540653</v>
+        <v>540974</v>
       </c>
       <c r="R43" t="n">
-        <v>7193521</v>
+        <v>7193351</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5188,32 +5188,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129319401</v>
+        <v>129319303</v>
       </c>
       <c r="B44" t="n">
-        <v>80175</v>
+        <v>79043</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540942</v>
+        <v>540934</v>
       </c>
       <c r="R44" t="n">
-        <v>7193229</v>
+        <v>7193385</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5295,10 +5295,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129319403</v>
+        <v>129319288</v>
       </c>
       <c r="B45" t="n">
-        <v>80146</v>
+        <v>79043</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5306,21 +5306,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5330,10 +5330,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>540930</v>
+        <v>540915</v>
       </c>
       <c r="R45" t="n">
-        <v>7193219</v>
+        <v>7193185</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5365,7 +5365,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5375,7 +5375,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5402,32 +5402,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129319320</v>
+        <v>129319403</v>
       </c>
       <c r="B46" t="n">
-        <v>80181</v>
+        <v>80148</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5437,10 +5437,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>540719</v>
+        <v>540930</v>
       </c>
       <c r="R46" t="n">
-        <v>7193463</v>
+        <v>7193219</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5472,7 +5472,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5509,32 +5509,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129319395</v>
+        <v>129319348</v>
       </c>
       <c r="B47" t="n">
-        <v>82992</v>
+        <v>80148</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>306</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5544,10 +5544,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>540878</v>
+        <v>540653</v>
       </c>
       <c r="R47" t="n">
-        <v>7193291</v>
+        <v>7193521</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5579,7 +5579,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5616,32 +5616,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129319303</v>
+        <v>129319401</v>
       </c>
       <c r="B48" t="n">
-        <v>79041</v>
+        <v>80177</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5651,10 +5651,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>540934</v>
+        <v>540942</v>
       </c>
       <c r="R48" t="n">
-        <v>7193385</v>
+        <v>7193229</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5686,7 +5686,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5723,27 +5723,27 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129319288</v>
+        <v>129319320</v>
       </c>
       <c r="B49" t="n">
-        <v>79041</v>
+        <v>80183</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>540915</v>
+        <v>540719</v>
       </c>
       <c r="R49" t="n">
-        <v>7193185</v>
+        <v>7193463</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5830,32 +5830,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129319280</v>
+        <v>129319366</v>
       </c>
       <c r="B50" t="n">
-        <v>95932</v>
+        <v>80148</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2809</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5865,10 +5865,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>540900</v>
+        <v>540738</v>
       </c>
       <c r="R50" t="n">
-        <v>7193073</v>
+        <v>7193503</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5900,7 +5900,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5910,7 +5910,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5937,10 +5937,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129319335</v>
+        <v>129319356</v>
       </c>
       <c r="B51" t="n">
-        <v>80147</v>
+        <v>80148</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5948,21 +5948,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5972,10 +5972,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>540655</v>
+        <v>540726</v>
       </c>
       <c r="R51" t="n">
-        <v>7193534</v>
+        <v>7193540</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6044,32 +6044,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129319366</v>
+        <v>129319280</v>
       </c>
       <c r="B52" t="n">
-        <v>80146</v>
+        <v>95936</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>2809</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6079,10 +6079,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>540738</v>
+        <v>540900</v>
       </c>
       <c r="R52" t="n">
-        <v>7193503</v>
+        <v>7193073</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6124,7 +6124,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6151,10 +6151,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129319356</v>
+        <v>129319335</v>
       </c>
       <c r="B53" t="n">
-        <v>80146</v>
+        <v>80149</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6162,21 +6162,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6186,10 +6186,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>540726</v>
+        <v>540655</v>
       </c>
       <c r="R53" t="n">
-        <v>7193540</v>
+        <v>7193534</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6221,7 +6221,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6261,7 +6261,7 @@
         <v>129319429</v>
       </c>
       <c r="B54" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         <v>129319417</v>
       </c>
       <c r="B55" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6472,10 +6472,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129319388</v>
+        <v>129319304</v>
       </c>
       <c r="B56" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6483,48 +6483,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>540828</v>
+        <v>540962</v>
       </c>
       <c r="R56" t="n">
-        <v>7193425</v>
+        <v>7193388</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6556,7 +6542,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6566,7 +6552,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6593,10 +6579,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129319304</v>
+        <v>129319388</v>
       </c>
       <c r="B57" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6604,34 +6590,48 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>540962</v>
+        <v>540828</v>
       </c>
       <c r="R57" t="n">
-        <v>7193388</v>
+        <v>7193425</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6673,7 +6673,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6700,10 +6700,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129319339</v>
+        <v>129319311</v>
       </c>
       <c r="B58" t="n">
-        <v>80147</v>
+        <v>91539</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6711,21 +6711,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6735,10 +6735,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>540669</v>
+        <v>540830</v>
       </c>
       <c r="R58" t="n">
-        <v>7193542</v>
+        <v>7193366</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6807,10 +6807,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129319353</v>
+        <v>129319372</v>
       </c>
       <c r="B59" t="n">
-        <v>82873</v>
+        <v>80148</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6818,21 +6818,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6842,10 +6842,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>540721</v>
+        <v>540736</v>
       </c>
       <c r="R59" t="n">
-        <v>7193542</v>
+        <v>7193500</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6877,7 +6877,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6914,32 +6914,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129319311</v>
+        <v>129319330</v>
       </c>
       <c r="B60" t="n">
-        <v>91536</v>
+        <v>82994</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1108</v>
+        <v>6439</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6949,10 +6949,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>540830</v>
+        <v>540683</v>
       </c>
       <c r="R60" t="n">
-        <v>7193366</v>
+        <v>7193545</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6984,7 +6984,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6994,7 +6994,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7021,10 +7021,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129319279</v>
+        <v>129319353</v>
       </c>
       <c r="B61" t="n">
-        <v>80147</v>
+        <v>82877</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7032,21 +7032,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7056,10 +7056,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>540872</v>
+        <v>540721</v>
       </c>
       <c r="R61" t="n">
-        <v>7193070</v>
+        <v>7193542</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7091,7 +7091,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7128,10 +7128,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129319372</v>
+        <v>129319279</v>
       </c>
       <c r="B62" t="n">
-        <v>80146</v>
+        <v>80149</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7139,21 +7139,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7163,10 +7163,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>540736</v>
+        <v>540872</v>
       </c>
       <c r="R62" t="n">
-        <v>7193500</v>
+        <v>7193070</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7208,7 +7208,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7235,32 +7235,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129319330</v>
+        <v>129319339</v>
       </c>
       <c r="B63" t="n">
-        <v>82990</v>
+        <v>80149</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6439</v>
+        <v>2081</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7270,10 +7270,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>540683</v>
+        <v>540669</v>
       </c>
       <c r="R63" t="n">
-        <v>7193545</v>
+        <v>7193542</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7305,7 +7305,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7345,7 +7345,7 @@
         <v>129319292</v>
       </c>
       <c r="B64" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7452,7 +7452,7 @@
         <v>129319392</v>
       </c>
       <c r="B65" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7672,45 +7672,54 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129319421</v>
+        <v>129319293</v>
       </c>
       <c r="B67" t="n">
-        <v>80175</v>
+        <v>57887</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>540981</v>
+        <v>540980</v>
       </c>
       <c r="R67" t="n">
-        <v>7193140</v>
+        <v>7193345</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7742,7 +7751,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7752,7 +7761,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7779,10 +7788,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129319334</v>
+        <v>129319400</v>
       </c>
       <c r="B68" t="n">
-        <v>80146</v>
+        <v>79043</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7790,21 +7799,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7814,10 +7823,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>540674</v>
+        <v>540943</v>
       </c>
       <c r="R68" t="n">
-        <v>7193550</v>
+        <v>7193233</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7849,7 +7858,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7859,7 +7868,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7886,32 +7895,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129319370</v>
+        <v>129319334</v>
       </c>
       <c r="B69" t="n">
-        <v>80175</v>
+        <v>80148</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7921,10 +7930,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>540737</v>
+        <v>540674</v>
       </c>
       <c r="R69" t="n">
-        <v>7193504</v>
+        <v>7193550</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7956,7 +7965,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7966,7 +7975,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7996,7 +8005,7 @@
         <v>129319397</v>
       </c>
       <c r="B70" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8100,32 +8109,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129319400</v>
+        <v>129319370</v>
       </c>
       <c r="B71" t="n">
-        <v>79041</v>
+        <v>80177</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8135,10 +8144,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>540943</v>
+        <v>540737</v>
       </c>
       <c r="R71" t="n">
-        <v>7193233</v>
+        <v>7193504</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8170,7 +8179,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8180,7 +8189,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8207,54 +8216,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129319293</v>
+        <v>129319421</v>
       </c>
       <c r="B72" t="n">
-        <v>57887</v>
+        <v>80177</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>540980</v>
+        <v>540981</v>
       </c>
       <c r="R72" t="n">
-        <v>7193345</v>
+        <v>7193140</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8286,7 +8286,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8323,54 +8323,41 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129319432</v>
+        <v>129319412</v>
       </c>
       <c r="B73" t="n">
-        <v>58360</v>
+        <v>91563</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>102125</v>
+        <v>5432</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>540978</v>
+        <v>540952</v>
       </c>
       <c r="R73" t="n">
-        <v>7193078</v>
+        <v>7193187</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8402,7 +8389,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8412,7 +8399,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8442,7 +8429,7 @@
         <v>129319367</v>
       </c>
       <c r="B74" t="n">
-        <v>80175</v>
+        <v>80177</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8546,10 +8533,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129319402</v>
+        <v>129319413</v>
       </c>
       <c r="B75" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8581,10 +8568,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>540936</v>
+        <v>540965</v>
       </c>
       <c r="R75" t="n">
-        <v>7193225</v>
+        <v>7193181</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8616,7 +8603,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8626,7 +8613,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8653,10 +8640,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129319413</v>
+        <v>129319402</v>
       </c>
       <c r="B76" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8688,10 +8675,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>540965</v>
+        <v>540936</v>
       </c>
       <c r="R76" t="n">
-        <v>7193181</v>
+        <v>7193225</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8723,7 +8710,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8733,7 +8720,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8760,41 +8747,54 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129319412</v>
+        <v>129319432</v>
       </c>
       <c r="B77" t="n">
-        <v>91560</v>
+        <v>58360</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5432</v>
+        <v>102125</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
+          <t>Pinicola enucleator</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>540952</v>
+        <v>540978</v>
       </c>
       <c r="R77" t="n">
-        <v>7193187</v>
+        <v>7193078</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8826,7 +8826,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8836,7 +8836,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8866,7 +8866,7 @@
         <v>129319371</v>
       </c>
       <c r="B78" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9082,10 +9082,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129319336</v>
+        <v>129319382</v>
       </c>
       <c r="B80" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9117,10 +9117,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>540668</v>
+        <v>540761</v>
       </c>
       <c r="R80" t="n">
-        <v>7193543</v>
+        <v>7193473</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9152,7 +9152,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9162,7 +9162,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9189,10 +9189,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129319382</v>
+        <v>129319408</v>
       </c>
       <c r="B81" t="n">
-        <v>79041</v>
+        <v>80148</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9200,21 +9200,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9224,10 +9224,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>540761</v>
+        <v>540939</v>
       </c>
       <c r="R81" t="n">
-        <v>7193473</v>
+        <v>7193177</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9259,7 +9259,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9296,10 +9296,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129319394</v>
+        <v>129319336</v>
       </c>
       <c r="B82" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9331,10 +9331,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>540877</v>
+        <v>540668</v>
       </c>
       <c r="R82" t="n">
-        <v>7193291</v>
+        <v>7193543</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9366,7 +9366,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9376,7 +9376,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9403,32 +9403,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129319338</v>
+        <v>129319431</v>
       </c>
       <c r="B83" t="n">
-        <v>80147</v>
+        <v>80177</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9438,10 +9438,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>540676</v>
+        <v>540979</v>
       </c>
       <c r="R83" t="n">
-        <v>7193539</v>
+        <v>7193075</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9473,7 +9473,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9483,7 +9483,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9510,10 +9510,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129319408</v>
+        <v>129319338</v>
       </c>
       <c r="B84" t="n">
-        <v>80146</v>
+        <v>80149</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9521,21 +9521,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9545,10 +9545,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>540939</v>
+        <v>540676</v>
       </c>
       <c r="R84" t="n">
-        <v>7193177</v>
+        <v>7193539</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9580,7 +9580,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9590,7 +9590,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9617,32 +9617,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129319431</v>
+        <v>129319394</v>
       </c>
       <c r="B85" t="n">
-        <v>80175</v>
+        <v>79043</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9652,10 +9652,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>540979</v>
+        <v>540877</v>
       </c>
       <c r="R85" t="n">
-        <v>7193075</v>
+        <v>7193291</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9687,7 +9687,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9697,7 +9697,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9724,32 +9724,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129319375</v>
+        <v>129319389</v>
       </c>
       <c r="B86" t="n">
-        <v>80147</v>
+        <v>95936</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2081</v>
+        <v>2809</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9759,10 +9759,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>540730</v>
+        <v>540818</v>
       </c>
       <c r="R86" t="n">
-        <v>7193493</v>
+        <v>7193358</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9794,7 +9794,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9804,7 +9804,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9834,7 +9834,7 @@
         <v>129319333</v>
       </c>
       <c r="B87" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9941,7 +9941,7 @@
         <v>129319376</v>
       </c>
       <c r="B88" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10045,10 +10045,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129319433</v>
+        <v>129319375</v>
       </c>
       <c r="B89" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10080,10 +10080,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>540979</v>
+        <v>540730</v>
       </c>
       <c r="R89" t="n">
-        <v>7193075</v>
+        <v>7193493</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -10115,7 +10115,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10125,7 +10125,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10152,10 +10152,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129319357</v>
+        <v>129319433</v>
       </c>
       <c r="B90" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10187,10 +10187,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>540726</v>
+        <v>540979</v>
       </c>
       <c r="R90" t="n">
-        <v>7193539</v>
+        <v>7193075</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -10222,7 +10222,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10232,7 +10232,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10259,32 +10259,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129319389</v>
+        <v>129319357</v>
       </c>
       <c r="B91" t="n">
-        <v>95932</v>
+        <v>80149</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2809</v>
+        <v>2081</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10294,10 +10294,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>540818</v>
+        <v>540726</v>
       </c>
       <c r="R91" t="n">
-        <v>7193358</v>
+        <v>7193539</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -10329,7 +10329,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10339,7 +10339,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10366,10 +10366,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129319284</v>
+        <v>129319298</v>
       </c>
       <c r="B92" t="n">
-        <v>79041</v>
+        <v>91563</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10377,23 +10377,19 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -10401,10 +10397,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>540867</v>
+        <v>540964</v>
       </c>
       <c r="R92" t="n">
-        <v>7193169</v>
+        <v>7193371</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -10436,7 +10432,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10446,7 +10442,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10473,32 +10469,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129319393</v>
+        <v>129319299</v>
       </c>
       <c r="B93" t="n">
-        <v>82990</v>
+        <v>79043</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10508,10 +10504,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>540824</v>
+        <v>540964</v>
       </c>
       <c r="R93" t="n">
-        <v>7193288</v>
+        <v>7193371</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -10543,7 +10539,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10553,7 +10549,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10580,10 +10576,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129319299</v>
+        <v>129319344</v>
       </c>
       <c r="B94" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10615,10 +10611,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>540964</v>
+        <v>540650</v>
       </c>
       <c r="R94" t="n">
-        <v>7193371</v>
+        <v>7193540</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -10650,7 +10646,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10660,7 +10656,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10687,10 +10683,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129319344</v>
+        <v>129319409</v>
       </c>
       <c r="B95" t="n">
-        <v>79041</v>
+        <v>80148</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10698,21 +10694,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10722,10 +10718,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>540650</v>
+        <v>540942</v>
       </c>
       <c r="R95" t="n">
-        <v>7193540</v>
+        <v>7193182</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -10757,7 +10753,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10767,7 +10763,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10794,10 +10790,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129319298</v>
+        <v>129319284</v>
       </c>
       <c r="B96" t="n">
-        <v>91560</v>
+        <v>79043</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10805,19 +10801,23 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -10825,10 +10825,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>540964</v>
+        <v>540867</v>
       </c>
       <c r="R96" t="n">
-        <v>7193371</v>
+        <v>7193169</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -10860,7 +10860,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10870,7 +10870,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10897,32 +10897,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129319409</v>
+        <v>129319393</v>
       </c>
       <c r="B97" t="n">
-        <v>80146</v>
+        <v>82994</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6458</v>
+        <v>6439</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10932,10 +10932,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>540942</v>
+        <v>540824</v>
       </c>
       <c r="R97" t="n">
-        <v>7193182</v>
+        <v>7193288</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -10967,7 +10967,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10977,7 +10977,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11004,10 +11004,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129319359</v>
+        <v>129319445</v>
       </c>
       <c r="B98" t="n">
-        <v>80146</v>
+        <v>57724</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11015,34 +11015,43 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>540725</v>
+        <v>541052</v>
       </c>
       <c r="R98" t="n">
-        <v>7193537</v>
+        <v>7193255</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -11074,7 +11083,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11084,7 +11093,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11114,7 +11123,7 @@
         <v>129319399</v>
       </c>
       <c r="B99" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11221,7 +11230,7 @@
         <v>129319308</v>
       </c>
       <c r="B100" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11325,10 +11334,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129319362</v>
+        <v>129319359</v>
       </c>
       <c r="B101" t="n">
-        <v>79041</v>
+        <v>80148</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11336,21 +11345,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11360,10 +11369,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>540721</v>
+        <v>540725</v>
       </c>
       <c r="R101" t="n">
-        <v>7193527</v>
+        <v>7193537</v>
       </c>
       <c r="S101" t="n">
         <v>25</v>
@@ -11432,10 +11441,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129319306</v>
+        <v>129319286</v>
       </c>
       <c r="B102" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11467,10 +11476,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>540961</v>
+        <v>540891</v>
       </c>
       <c r="R102" t="n">
-        <v>7193398</v>
+        <v>7193174</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -11502,7 +11511,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11512,7 +11521,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11539,10 +11548,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129319286</v>
+        <v>129319362</v>
       </c>
       <c r="B103" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11574,10 +11583,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>540891</v>
+        <v>540721</v>
       </c>
       <c r="R103" t="n">
-        <v>7193174</v>
+        <v>7193527</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -11609,7 +11618,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11619,7 +11628,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11646,10 +11655,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129319445</v>
+        <v>129319306</v>
       </c>
       <c r="B104" t="n">
-        <v>57724</v>
+        <v>79043</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11657,43 +11666,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>541052</v>
+        <v>540961</v>
       </c>
       <c r="R104" t="n">
-        <v>7193255</v>
+        <v>7193398</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -11725,7 +11725,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11735,7 +11735,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11762,10 +11762,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129319368</v>
+        <v>129319360</v>
       </c>
       <c r="B105" t="n">
-        <v>80146</v>
+        <v>91539</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11773,21 +11773,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11797,10 +11797,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>540734</v>
+        <v>540725</v>
       </c>
       <c r="R105" t="n">
-        <v>7193503</v>
+        <v>7193532</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -11832,7 +11832,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11842,7 +11842,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11872,7 +11872,7 @@
         <v>129319418</v>
       </c>
       <c r="B106" t="n">
-        <v>80182</v>
+        <v>80184</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11976,10 +11976,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129319391</v>
+        <v>129319355</v>
       </c>
       <c r="B107" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12011,10 +12011,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>540818</v>
+        <v>540726</v>
       </c>
       <c r="R107" t="n">
-        <v>7193333</v>
+        <v>7193541</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -12046,7 +12046,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12056,7 +12056,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12083,10 +12083,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129319355</v>
+        <v>129319369</v>
       </c>
       <c r="B108" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12118,10 +12118,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>540726</v>
+        <v>540734</v>
       </c>
       <c r="R108" t="n">
-        <v>7193541</v>
+        <v>7193503</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -12153,7 +12153,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12163,7 +12163,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12190,10 +12190,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129319360</v>
+        <v>129319391</v>
       </c>
       <c r="B109" t="n">
-        <v>91536</v>
+        <v>80149</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12201,21 +12201,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12225,10 +12225,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>540725</v>
+        <v>540818</v>
       </c>
       <c r="R109" t="n">
-        <v>7193532</v>
+        <v>7193333</v>
       </c>
       <c r="S109" t="n">
         <v>25</v>
@@ -12260,7 +12260,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12270,7 +12270,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12297,10 +12297,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129319369</v>
+        <v>129319411</v>
       </c>
       <c r="B110" t="n">
-        <v>80147</v>
+        <v>79043</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12308,21 +12308,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12332,10 +12332,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>540734</v>
+        <v>540955</v>
       </c>
       <c r="R110" t="n">
-        <v>7193503</v>
+        <v>7193186</v>
       </c>
       <c r="S110" t="n">
         <v>25</v>
@@ -12367,7 +12367,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12377,7 +12377,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12404,10 +12404,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129319411</v>
+        <v>129319368</v>
       </c>
       <c r="B111" t="n">
-        <v>79041</v>
+        <v>80148</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12415,21 +12415,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12439,10 +12439,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>540955</v>
+        <v>540734</v>
       </c>
       <c r="R111" t="n">
-        <v>7193186</v>
+        <v>7193503</v>
       </c>
       <c r="S111" t="n">
         <v>25</v>
@@ -12474,7 +12474,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12484,7 +12484,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12514,7 +12514,7 @@
         <v>129319407</v>
       </c>
       <c r="B112" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12618,10 +12618,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129319309</v>
+        <v>129319341</v>
       </c>
       <c r="B113" t="n">
-        <v>79041</v>
+        <v>91539</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12629,21 +12629,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12653,10 +12653,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>540894</v>
+        <v>540670</v>
       </c>
       <c r="R113" t="n">
-        <v>7193411</v>
+        <v>7193533</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -12688,7 +12688,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12725,10 +12725,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129319332</v>
+        <v>129319426</v>
       </c>
       <c r="B114" t="n">
-        <v>57887</v>
+        <v>80149</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12736,43 +12736,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>540675</v>
+        <v>540979</v>
       </c>
       <c r="R114" t="n">
-        <v>7193538</v>
+        <v>7193115</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -12804,7 +12795,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12814,7 +12805,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12841,10 +12832,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129319341</v>
+        <v>129319305</v>
       </c>
       <c r="B115" t="n">
-        <v>91536</v>
+        <v>91563</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12852,23 +12843,19 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
@@ -12876,10 +12863,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>540670</v>
+        <v>540959</v>
       </c>
       <c r="R115" t="n">
-        <v>7193533</v>
+        <v>7193395</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -12911,7 +12898,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12921,7 +12908,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12948,10 +12935,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129319426</v>
+        <v>129319309</v>
       </c>
       <c r="B116" t="n">
-        <v>80147</v>
+        <v>79043</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12959,21 +12946,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12983,10 +12970,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>540979</v>
+        <v>540894</v>
       </c>
       <c r="R116" t="n">
-        <v>7193115</v>
+        <v>7193411</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -13018,7 +13005,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13028,7 +13015,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13058,7 +13045,7 @@
         <v>129319425</v>
       </c>
       <c r="B117" t="n">
-        <v>80181</v>
+        <v>80183</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13162,10 +13149,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129319305</v>
+        <v>129319332</v>
       </c>
       <c r="B118" t="n">
-        <v>91560</v>
+        <v>57887</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13173,30 +13160,43 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr"/>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>540959</v>
+        <v>540675</v>
       </c>
       <c r="R118" t="n">
-        <v>7193395</v>
+        <v>7193538</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -13228,7 +13228,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13238,7 +13238,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13265,54 +13265,45 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129319363</v>
+        <v>129319350</v>
       </c>
       <c r="B119" t="n">
-        <v>58360</v>
+        <v>80148</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>102125</v>
+        <v>6458</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>540731</v>
+        <v>540681</v>
       </c>
       <c r="R119" t="n">
-        <v>7193512</v>
+        <v>7193521</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -13344,7 +13335,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13354,7 +13345,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13381,10 +13372,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129319410</v>
+        <v>129319329</v>
       </c>
       <c r="B120" t="n">
-        <v>56908</v>
+        <v>88943</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13392,43 +13383,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>102612</v>
+        <v>510</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>540946</v>
+        <v>540692</v>
       </c>
       <c r="R120" t="n">
-        <v>7193171</v>
+        <v>7193539</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -13460,7 +13442,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13470,7 +13452,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13497,10 +13479,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129319329</v>
+        <v>129319277</v>
       </c>
       <c r="B121" t="n">
-        <v>88940</v>
+        <v>80149</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13508,21 +13490,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>510</v>
+        <v>2081</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13532,10 +13514,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>540692</v>
+        <v>540837</v>
       </c>
       <c r="R121" t="n">
-        <v>7193539</v>
+        <v>7193042</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -13567,7 +13549,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13577,7 +13559,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13607,7 +13589,7 @@
         <v>129319325</v>
       </c>
       <c r="B122" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13711,10 +13693,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129319277</v>
+        <v>129319319</v>
       </c>
       <c r="B123" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13746,10 +13728,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>540837</v>
+        <v>540719</v>
       </c>
       <c r="R123" t="n">
-        <v>7193042</v>
+        <v>7193463</v>
       </c>
       <c r="S123" t="n">
         <v>25</v>
@@ -13781,7 +13763,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13791,7 +13773,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13818,32 +13800,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129319319</v>
+        <v>129319416</v>
       </c>
       <c r="B124" t="n">
-        <v>80147</v>
+        <v>80184</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13853,10 +13835,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>540719</v>
+        <v>540970</v>
       </c>
       <c r="R124" t="n">
-        <v>7193463</v>
+        <v>7193154</v>
       </c>
       <c r="S124" t="n">
         <v>25</v>
@@ -13888,7 +13870,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13898,7 +13880,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13925,10 +13907,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129319416</v>
+        <v>129319321</v>
       </c>
       <c r="B125" t="n">
-        <v>80182</v>
+        <v>80177</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13936,21 +13918,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13960,10 +13942,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>540970</v>
+        <v>540719</v>
       </c>
       <c r="R125" t="n">
-        <v>7193154</v>
+        <v>7193463</v>
       </c>
       <c r="S125" t="n">
         <v>25</v>
@@ -13995,7 +13977,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14005,7 +13987,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14035,7 +14017,7 @@
         <v>129319373</v>
       </c>
       <c r="B126" t="n">
-        <v>80182</v>
+        <v>80184</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14139,45 +14121,54 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129319321</v>
+        <v>129319363</v>
       </c>
       <c r="B127" t="n">
-        <v>80175</v>
+        <v>58360</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6462</v>
+        <v>102125</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>540719</v>
+        <v>540731</v>
       </c>
       <c r="R127" t="n">
-        <v>7193463</v>
+        <v>7193512</v>
       </c>
       <c r="S127" t="n">
         <v>25</v>
@@ -14209,7 +14200,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14219,7 +14210,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14246,10 +14237,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129319350</v>
+        <v>129319410</v>
       </c>
       <c r="B128" t="n">
-        <v>80146</v>
+        <v>56908</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14257,34 +14248,43 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>540681</v>
+        <v>540946</v>
       </c>
       <c r="R128" t="n">
-        <v>7193521</v>
+        <v>7193171</v>
       </c>
       <c r="S128" t="n">
         <v>25</v>
@@ -14316,7 +14316,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14326,7 +14326,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14353,10 +14353,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129319326</v>
+        <v>129319434</v>
       </c>
       <c r="B129" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14388,10 +14388,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>540701</v>
+        <v>540979</v>
       </c>
       <c r="R129" t="n">
-        <v>7193533</v>
+        <v>7193075</v>
       </c>
       <c r="S129" t="n">
         <v>25</v>
@@ -14423,7 +14423,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14433,7 +14433,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14460,10 +14460,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129319434</v>
+        <v>129319326</v>
       </c>
       <c r="B130" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14495,10 +14495,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>540979</v>
+        <v>540701</v>
       </c>
       <c r="R130" t="n">
-        <v>7193075</v>
+        <v>7193533</v>
       </c>
       <c r="S130" t="n">
         <v>25</v>
@@ -14530,7 +14530,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14540,7 +14540,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14570,7 +14570,7 @@
         <v>129319379</v>
       </c>
       <c r="B131" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14674,32 +14674,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129319312</v>
+        <v>129319378</v>
       </c>
       <c r="B132" t="n">
-        <v>80147</v>
+        <v>82996</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>2081</v>
+        <v>306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14709,10 +14709,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>540789</v>
+        <v>540757</v>
       </c>
       <c r="R132" t="n">
-        <v>7193373</v>
+        <v>7193474</v>
       </c>
       <c r="S132" t="n">
         <v>25</v>
@@ -14744,7 +14744,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14754,7 +14754,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14781,32 +14781,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129319322</v>
+        <v>129319380</v>
       </c>
       <c r="B133" t="n">
-        <v>80147</v>
+        <v>92261</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>2081</v>
+        <v>3298</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14816,10 +14816,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>540719</v>
+        <v>540761</v>
       </c>
       <c r="R133" t="n">
-        <v>7193483</v>
+        <v>7193490</v>
       </c>
       <c r="S133" t="n">
         <v>25</v>
@@ -14851,7 +14851,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14861,7 +14861,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14888,32 +14888,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129319378</v>
+        <v>129319322</v>
       </c>
       <c r="B134" t="n">
-        <v>82992</v>
+        <v>80149</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>306</v>
+        <v>2081</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14923,10 +14923,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>540757</v>
+        <v>540719</v>
       </c>
       <c r="R134" t="n">
-        <v>7193474</v>
+        <v>7193483</v>
       </c>
       <c r="S134" t="n">
         <v>25</v>
@@ -14958,7 +14958,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14968,7 +14968,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14995,10 +14995,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129319343</v>
+        <v>129319312</v>
       </c>
       <c r="B135" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15006,39 +15006,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>540661</v>
+        <v>540789</v>
       </c>
       <c r="R135" t="n">
-        <v>7193538</v>
+        <v>7193373</v>
       </c>
       <c r="S135" t="n">
         <v>25</v>
@@ -15070,7 +15065,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15080,12 +15075,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>11:27</t>
-        </is>
-      </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>Färska och äldre spår på samma träd.</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15112,32 +15102,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129319380</v>
+        <v>129319310</v>
       </c>
       <c r="B136" t="n">
-        <v>92258</v>
+        <v>79043</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15147,10 +15137,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>540761</v>
+        <v>540830</v>
       </c>
       <c r="R136" t="n">
-        <v>7193490</v>
+        <v>7193366</v>
       </c>
       <c r="S136" t="n">
         <v>25</v>
@@ -15182,7 +15172,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15192,7 +15182,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15219,10 +15209,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129319310</v>
+        <v>129319343</v>
       </c>
       <c r="B137" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15230,34 +15220,39 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>540830</v>
+        <v>540661</v>
       </c>
       <c r="R137" t="n">
-        <v>7193366</v>
+        <v>7193538</v>
       </c>
       <c r="S137" t="n">
         <v>25</v>
@@ -15289,7 +15284,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15299,7 +15294,12 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>Färska och äldre spår på samma träd.</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15326,32 +15326,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129319315</v>
+        <v>129319387</v>
       </c>
       <c r="B138" t="n">
-        <v>82990</v>
+        <v>83003</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6439</v>
+        <v>308</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15361,10 +15361,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>540765</v>
+        <v>540772</v>
       </c>
       <c r="R138" t="n">
-        <v>7193370</v>
+        <v>7193446</v>
       </c>
       <c r="S138" t="n">
         <v>25</v>
@@ -15396,7 +15396,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15406,7 +15406,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15433,10 +15433,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129319327</v>
+        <v>129319406</v>
       </c>
       <c r="B139" t="n">
-        <v>79041</v>
+        <v>79122</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15444,21 +15444,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15468,10 +15468,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>540693</v>
+        <v>540938</v>
       </c>
       <c r="R139" t="n">
-        <v>7193540</v>
+        <v>7193168</v>
       </c>
       <c r="S139" t="n">
         <v>25</v>
@@ -15503,7 +15503,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15513,7 +15513,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15543,7 +15543,7 @@
         <v>129319287</v>
       </c>
       <c r="B140" t="n">
-        <v>92258</v>
+        <v>92261</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15647,10 +15647,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129319387</v>
+        <v>129319327</v>
       </c>
       <c r="B141" t="n">
-        <v>82999</v>
+        <v>79043</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15658,21 +15658,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15682,10 +15682,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>540772</v>
+        <v>540693</v>
       </c>
       <c r="R141" t="n">
-        <v>7193446</v>
+        <v>7193540</v>
       </c>
       <c r="S141" t="n">
         <v>25</v>
@@ -15717,7 +15717,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15727,7 +15727,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15754,32 +15754,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129319406</v>
+        <v>129319315</v>
       </c>
       <c r="B142" t="n">
-        <v>79120</v>
+        <v>82994</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>864</v>
+        <v>6439</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15789,10 +15789,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>540938</v>
+        <v>540765</v>
       </c>
       <c r="R142" t="n">
-        <v>7193168</v>
+        <v>7193370</v>
       </c>
       <c r="S142" t="n">
         <v>25</v>
@@ -15824,7 +15824,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15864,7 +15864,7 @@
         <v>129319428</v>
       </c>
       <c r="B143" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15971,7 +15971,7 @@
         <v>129319347</v>
       </c>
       <c r="B144" t="n">
-        <v>80182</v>
+        <v>80184</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>

--- a/artfynd/A 51086-2025 artfynd.xlsx
+++ b/artfynd/A 51086-2025 artfynd.xlsx
@@ -3797,32 +3797,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129319422</v>
+        <v>129319374</v>
       </c>
       <c r="B31" t="n">
-        <v>80183</v>
+        <v>80149</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>540980</v>
+        <v>540734</v>
       </c>
       <c r="R31" t="n">
-        <v>7193139</v>
+        <v>7193499</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3867,7 +3867,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3904,7 +3904,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129319374</v>
+        <v>129319377</v>
       </c>
       <c r="B32" t="n">
         <v>80149</v>
@@ -3939,10 +3939,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>540734</v>
+        <v>540745</v>
       </c>
       <c r="R32" t="n">
-        <v>7193499</v>
+        <v>7193494</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4011,10 +4011,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129319377</v>
+        <v>129319396</v>
       </c>
       <c r="B33" t="n">
-        <v>80149</v>
+        <v>79043</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4022,21 +4022,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4046,10 +4046,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>540745</v>
+        <v>540928</v>
       </c>
       <c r="R33" t="n">
-        <v>7193494</v>
+        <v>7193263</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4081,7 +4081,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4118,7 +4118,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129319396</v>
+        <v>129319427</v>
       </c>
       <c r="B34" t="n">
         <v>79043</v>
@@ -4153,10 +4153,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>540928</v>
+        <v>540969</v>
       </c>
       <c r="R34" t="n">
-        <v>7193263</v>
+        <v>7193117</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4225,7 +4225,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129319427</v>
+        <v>129319282</v>
       </c>
       <c r="B35" t="n">
         <v>79043</v>
@@ -4260,10 +4260,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>540969</v>
+        <v>540901</v>
       </c>
       <c r="R35" t="n">
-        <v>7193117</v>
+        <v>7193084</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4295,7 +4295,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4305,7 +4305,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4332,10 +4332,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129319282</v>
+        <v>129319337</v>
       </c>
       <c r="B36" t="n">
-        <v>79043</v>
+        <v>80148</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4343,21 +4343,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4367,10 +4367,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>540901</v>
+        <v>540676</v>
       </c>
       <c r="R36" t="n">
-        <v>7193084</v>
+        <v>7193539</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4402,7 +4402,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4439,10 +4439,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129319337</v>
+        <v>129319405</v>
       </c>
       <c r="B37" t="n">
-        <v>80148</v>
+        <v>83011</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4450,21 +4450,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4474,10 +4474,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>540676</v>
+        <v>540931</v>
       </c>
       <c r="R37" t="n">
-        <v>7193539</v>
+        <v>7193220</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4546,10 +4546,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129319405</v>
+        <v>129319404</v>
       </c>
       <c r="B38" t="n">
-        <v>83011</v>
+        <v>78056</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4557,21 +4557,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4653,32 +4653,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129319404</v>
+        <v>129319422</v>
       </c>
       <c r="B39" t="n">
-        <v>78056</v>
+        <v>80183</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228579</v>
+        <v>6463</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4688,10 +4688,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>540931</v>
+        <v>540980</v>
       </c>
       <c r="R39" t="n">
-        <v>7193220</v>
+        <v>7193139</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -6700,10 +6700,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129319311</v>
+        <v>129319353</v>
       </c>
       <c r="B58" t="n">
-        <v>91539</v>
+        <v>82877</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6711,21 +6711,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6735,10 +6735,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>540830</v>
+        <v>540721</v>
       </c>
       <c r="R58" t="n">
-        <v>7193366</v>
+        <v>7193542</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6807,10 +6807,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129319372</v>
+        <v>129319279</v>
       </c>
       <c r="B59" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6818,21 +6818,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6842,10 +6842,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>540736</v>
+        <v>540872</v>
       </c>
       <c r="R59" t="n">
-        <v>7193500</v>
+        <v>7193070</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6877,7 +6877,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6914,32 +6914,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129319330</v>
+        <v>129319339</v>
       </c>
       <c r="B60" t="n">
-        <v>82994</v>
+        <v>80149</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6439</v>
+        <v>2081</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6949,10 +6949,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>540683</v>
+        <v>540669</v>
       </c>
       <c r="R60" t="n">
-        <v>7193545</v>
+        <v>7193542</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6984,7 +6984,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6994,7 +6994,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7021,10 +7021,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129319353</v>
+        <v>129319292</v>
       </c>
       <c r="B61" t="n">
-        <v>82877</v>
+        <v>79043</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7032,21 +7032,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7056,10 +7056,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>540721</v>
+        <v>540996</v>
       </c>
       <c r="R61" t="n">
-        <v>7193542</v>
+        <v>7193327</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7091,7 +7091,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7128,10 +7128,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129319279</v>
+        <v>129319392</v>
       </c>
       <c r="B62" t="n">
-        <v>80149</v>
+        <v>79043</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7139,21 +7139,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7163,10 +7163,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>540872</v>
+        <v>540826</v>
       </c>
       <c r="R62" t="n">
-        <v>7193070</v>
+        <v>7193294</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7208,7 +7208,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7235,45 +7235,54 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129319339</v>
+        <v>129319423</v>
       </c>
       <c r="B63" t="n">
-        <v>80149</v>
+        <v>57831</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2081</v>
+        <v>103031</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>540669</v>
+        <v>540976</v>
       </c>
       <c r="R63" t="n">
-        <v>7193542</v>
+        <v>7193139</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7305,7 +7314,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7315,7 +7324,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7342,10 +7351,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129319292</v>
+        <v>129319311</v>
       </c>
       <c r="B64" t="n">
-        <v>79043</v>
+        <v>91539</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7353,21 +7362,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7377,10 +7386,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>540996</v>
+        <v>540830</v>
       </c>
       <c r="R64" t="n">
-        <v>7193327</v>
+        <v>7193366</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7412,7 +7421,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7422,7 +7431,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7449,10 +7458,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129319392</v>
+        <v>129319372</v>
       </c>
       <c r="B65" t="n">
-        <v>79043</v>
+        <v>80148</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7460,21 +7469,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7484,10 +7493,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>540826</v>
+        <v>540736</v>
       </c>
       <c r="R65" t="n">
-        <v>7193294</v>
+        <v>7193500</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7519,7 +7528,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7529,7 +7538,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7556,10 +7565,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129319423</v>
+        <v>129319330</v>
       </c>
       <c r="B66" t="n">
-        <v>57831</v>
+        <v>82994</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7567,43 +7576,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>103031</v>
+        <v>6439</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>540976</v>
+        <v>540683</v>
       </c>
       <c r="R66" t="n">
-        <v>7193139</v>
+        <v>7193545</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7635,7 +7635,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7645,7 +7645,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7672,10 +7672,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129319293</v>
+        <v>129319400</v>
       </c>
       <c r="B67" t="n">
-        <v>57887</v>
+        <v>79043</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7683,43 +7683,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>540980</v>
+        <v>540943</v>
       </c>
       <c r="R67" t="n">
-        <v>7193345</v>
+        <v>7193233</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7751,7 +7742,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7761,7 +7752,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7788,10 +7779,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129319400</v>
+        <v>129319334</v>
       </c>
       <c r="B68" t="n">
-        <v>79043</v>
+        <v>80148</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7799,21 +7790,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7823,10 +7814,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>540943</v>
+        <v>540674</v>
       </c>
       <c r="R68" t="n">
-        <v>7193233</v>
+        <v>7193550</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7858,7 +7849,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7868,7 +7859,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7895,10 +7886,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129319334</v>
+        <v>129319397</v>
       </c>
       <c r="B69" t="n">
-        <v>80148</v>
+        <v>79043</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7906,21 +7897,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7930,10 +7921,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>540674</v>
+        <v>540946</v>
       </c>
       <c r="R69" t="n">
-        <v>7193550</v>
+        <v>7193256</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7965,7 +7956,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7975,7 +7966,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8002,32 +7993,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129319397</v>
+        <v>129319370</v>
       </c>
       <c r="B70" t="n">
-        <v>79043</v>
+        <v>80177</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8037,10 +8028,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>540946</v>
+        <v>540737</v>
       </c>
       <c r="R70" t="n">
-        <v>7193256</v>
+        <v>7193504</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8072,7 +8063,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8082,7 +8073,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8109,7 +8100,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129319370</v>
+        <v>129319421</v>
       </c>
       <c r="B71" t="n">
         <v>80177</v>
@@ -8144,10 +8135,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>540737</v>
+        <v>540981</v>
       </c>
       <c r="R71" t="n">
-        <v>7193504</v>
+        <v>7193140</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8179,7 +8170,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8189,7 +8180,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8216,45 +8207,54 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129319421</v>
+        <v>129319293</v>
       </c>
       <c r="B72" t="n">
-        <v>80177</v>
+        <v>57887</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>540981</v>
+        <v>540980</v>
       </c>
       <c r="R72" t="n">
-        <v>7193140</v>
+        <v>7193345</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8286,7 +8286,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9082,10 +9082,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129319382</v>
+        <v>129319338</v>
       </c>
       <c r="B80" t="n">
-        <v>79043</v>
+        <v>80149</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9093,21 +9093,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9117,10 +9117,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>540761</v>
+        <v>540676</v>
       </c>
       <c r="R80" t="n">
-        <v>7193473</v>
+        <v>7193539</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9152,7 +9152,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9162,7 +9162,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9189,10 +9189,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129319408</v>
+        <v>129319394</v>
       </c>
       <c r="B81" t="n">
-        <v>80148</v>
+        <v>79043</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9200,21 +9200,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9224,10 +9224,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>540939</v>
+        <v>540877</v>
       </c>
       <c r="R81" t="n">
-        <v>7193177</v>
+        <v>7193291</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9259,7 +9259,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9296,7 +9296,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129319336</v>
+        <v>129319382</v>
       </c>
       <c r="B82" t="n">
         <v>79043</v>
@@ -9331,10 +9331,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>540668</v>
+        <v>540761</v>
       </c>
       <c r="R82" t="n">
-        <v>7193543</v>
+        <v>7193473</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9366,7 +9366,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9376,7 +9376,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9403,32 +9403,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129319431</v>
+        <v>129319408</v>
       </c>
       <c r="B83" t="n">
-        <v>80177</v>
+        <v>80148</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9438,10 +9438,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>540979</v>
+        <v>540939</v>
       </c>
       <c r="R83" t="n">
-        <v>7193075</v>
+        <v>7193177</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9473,7 +9473,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9483,7 +9483,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9510,10 +9510,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129319338</v>
+        <v>129319336</v>
       </c>
       <c r="B84" t="n">
-        <v>80149</v>
+        <v>79043</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9521,21 +9521,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9545,10 +9545,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>540676</v>
+        <v>540668</v>
       </c>
       <c r="R84" t="n">
-        <v>7193539</v>
+        <v>7193543</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9580,7 +9580,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9590,7 +9590,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9617,32 +9617,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129319394</v>
+        <v>129319431</v>
       </c>
       <c r="B85" t="n">
-        <v>79043</v>
+        <v>80177</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9652,10 +9652,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>540877</v>
+        <v>540979</v>
       </c>
       <c r="R85" t="n">
-        <v>7193291</v>
+        <v>7193075</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9687,7 +9687,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9697,7 +9697,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10366,10 +10366,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129319298</v>
+        <v>129319409</v>
       </c>
       <c r="B92" t="n">
-        <v>91563</v>
+        <v>80148</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10377,19 +10377,23 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -10397,10 +10401,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>540964</v>
+        <v>540942</v>
       </c>
       <c r="R92" t="n">
-        <v>7193371</v>
+        <v>7193182</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -10432,7 +10436,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10442,7 +10446,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10469,7 +10473,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129319299</v>
+        <v>129319284</v>
       </c>
       <c r="B93" t="n">
         <v>79043</v>
@@ -10504,10 +10508,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>540964</v>
+        <v>540867</v>
       </c>
       <c r="R93" t="n">
-        <v>7193371</v>
+        <v>7193169</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -10539,7 +10543,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10549,7 +10553,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10576,32 +10580,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129319344</v>
+        <v>129319393</v>
       </c>
       <c r="B94" t="n">
-        <v>79043</v>
+        <v>82994</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10611,10 +10615,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>540650</v>
+        <v>540824</v>
       </c>
       <c r="R94" t="n">
-        <v>7193540</v>
+        <v>7193288</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -10646,7 +10650,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10656,7 +10660,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10683,10 +10687,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129319409</v>
+        <v>129319298</v>
       </c>
       <c r="B95" t="n">
-        <v>80148</v>
+        <v>91563</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10694,23 +10698,19 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -10718,10 +10718,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>540942</v>
+        <v>540964</v>
       </c>
       <c r="R95" t="n">
-        <v>7193182</v>
+        <v>7193371</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -10753,7 +10753,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10763,7 +10763,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10790,7 +10790,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129319284</v>
+        <v>129319299</v>
       </c>
       <c r="B96" t="n">
         <v>79043</v>
@@ -10825,10 +10825,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>540867</v>
+        <v>540964</v>
       </c>
       <c r="R96" t="n">
-        <v>7193169</v>
+        <v>7193371</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -10860,7 +10860,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10870,7 +10870,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10897,32 +10897,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129319393</v>
+        <v>129319344</v>
       </c>
       <c r="B97" t="n">
-        <v>82994</v>
+        <v>79043</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10932,10 +10932,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>540824</v>
+        <v>540650</v>
       </c>
       <c r="R97" t="n">
-        <v>7193288</v>
+        <v>7193540</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -10967,7 +10967,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10977,7 +10977,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12832,30 +12832,34 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129319305</v>
+        <v>129319425</v>
       </c>
       <c r="B115" t="n">
-        <v>91563</v>
+        <v>80183</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr"/>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
@@ -12863,10 +12867,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>540959</v>
+        <v>540980</v>
       </c>
       <c r="R115" t="n">
-        <v>7193395</v>
+        <v>7193116</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -12898,7 +12902,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12908,7 +12912,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12935,10 +12939,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129319309</v>
+        <v>129319305</v>
       </c>
       <c r="B116" t="n">
-        <v>79043</v>
+        <v>91563</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12946,23 +12950,19 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
@@ -12970,10 +12970,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>540894</v>
+        <v>540959</v>
       </c>
       <c r="R116" t="n">
-        <v>7193411</v>
+        <v>7193395</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -13005,7 +13005,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13015,7 +13015,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13042,27 +13042,27 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129319425</v>
+        <v>129319309</v>
       </c>
       <c r="B117" t="n">
-        <v>80183</v>
+        <v>79043</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -13077,10 +13077,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>540980</v>
+        <v>540894</v>
       </c>
       <c r="R117" t="n">
-        <v>7193116</v>
+        <v>7193411</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -13112,7 +13112,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13122,7 +13122,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13265,10 +13265,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129319350</v>
+        <v>129319329</v>
       </c>
       <c r="B119" t="n">
-        <v>80148</v>
+        <v>88943</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13276,21 +13276,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13300,10 +13300,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>540681</v>
+        <v>540692</v>
       </c>
       <c r="R119" t="n">
-        <v>7193521</v>
+        <v>7193539</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -13335,7 +13335,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13345,7 +13345,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13372,10 +13372,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129319329</v>
+        <v>129319350</v>
       </c>
       <c r="B120" t="n">
-        <v>88943</v>
+        <v>80148</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13383,21 +13383,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13407,10 +13407,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>540692</v>
+        <v>540681</v>
       </c>
       <c r="R120" t="n">
-        <v>7193539</v>
+        <v>7193521</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -13442,7 +13442,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13452,7 +13452,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13800,45 +13800,54 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129319416</v>
+        <v>129319363</v>
       </c>
       <c r="B124" t="n">
-        <v>80184</v>
+        <v>58360</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6464</v>
+        <v>102125</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>540970</v>
+        <v>540731</v>
       </c>
       <c r="R124" t="n">
-        <v>7193154</v>
+        <v>7193512</v>
       </c>
       <c r="S124" t="n">
         <v>25</v>
@@ -13870,7 +13879,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13880,7 +13889,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13907,45 +13916,54 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129319321</v>
+        <v>129319410</v>
       </c>
       <c r="B125" t="n">
-        <v>80177</v>
+        <v>56908</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6462</v>
+        <v>102612</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>540719</v>
+        <v>540946</v>
       </c>
       <c r="R125" t="n">
-        <v>7193463</v>
+        <v>7193171</v>
       </c>
       <c r="S125" t="n">
         <v>25</v>
@@ -13977,7 +13995,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13987,7 +14005,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14014,7 +14032,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129319373</v>
+        <v>129319416</v>
       </c>
       <c r="B126" t="n">
         <v>80184</v>
@@ -14049,10 +14067,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>540734</v>
+        <v>540970</v>
       </c>
       <c r="R126" t="n">
-        <v>7193499</v>
+        <v>7193154</v>
       </c>
       <c r="S126" t="n">
         <v>25</v>
@@ -14084,7 +14102,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14094,7 +14112,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14121,54 +14139,45 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129319363</v>
+        <v>129319321</v>
       </c>
       <c r="B127" t="n">
-        <v>58360</v>
+        <v>80177</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>102125</v>
+        <v>6462</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>540731</v>
+        <v>540719</v>
       </c>
       <c r="R127" t="n">
-        <v>7193512</v>
+        <v>7193463</v>
       </c>
       <c r="S127" t="n">
         <v>25</v>
@@ -14200,7 +14209,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14210,7 +14219,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14237,54 +14246,45 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129319410</v>
+        <v>129319373</v>
       </c>
       <c r="B128" t="n">
-        <v>56908</v>
+        <v>80184</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>102612</v>
+        <v>6464</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>540946</v>
+        <v>540734</v>
       </c>
       <c r="R128" t="n">
-        <v>7193171</v>
+        <v>7193499</v>
       </c>
       <c r="S128" t="n">
         <v>25</v>
@@ -14316,7 +14316,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14326,7 +14326,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15326,32 +15326,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129319387</v>
+        <v>129319287</v>
       </c>
       <c r="B138" t="n">
-        <v>83003</v>
+        <v>92261</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>308</v>
+        <v>3298</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15361,10 +15361,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>540772</v>
+        <v>540913</v>
       </c>
       <c r="R138" t="n">
-        <v>7193446</v>
+        <v>7193185</v>
       </c>
       <c r="S138" t="n">
         <v>25</v>
@@ -15396,7 +15396,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15406,7 +15406,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15433,10 +15433,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129319406</v>
+        <v>129319327</v>
       </c>
       <c r="B139" t="n">
-        <v>79122</v>
+        <v>79043</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15444,21 +15444,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15468,10 +15468,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>540938</v>
+        <v>540693</v>
       </c>
       <c r="R139" t="n">
-        <v>7193168</v>
+        <v>7193540</v>
       </c>
       <c r="S139" t="n">
         <v>25</v>
@@ -15503,7 +15503,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15513,7 +15513,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15540,10 +15540,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129319287</v>
+        <v>129319315</v>
       </c>
       <c r="B140" t="n">
-        <v>92261</v>
+        <v>82994</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15551,21 +15551,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>3298</v>
+        <v>6439</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15575,10 +15575,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>540913</v>
+        <v>540765</v>
       </c>
       <c r="R140" t="n">
-        <v>7193185</v>
+        <v>7193370</v>
       </c>
       <c r="S140" t="n">
         <v>25</v>
@@ -15610,7 +15610,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15620,7 +15620,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15647,10 +15647,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129319327</v>
+        <v>129319428</v>
       </c>
       <c r="B141" t="n">
-        <v>79043</v>
+        <v>80148</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15658,21 +15658,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15682,10 +15682,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>540693</v>
+        <v>540971</v>
       </c>
       <c r="R141" t="n">
-        <v>7193540</v>
+        <v>7193081</v>
       </c>
       <c r="S141" t="n">
         <v>25</v>
@@ -15717,7 +15717,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15727,7 +15727,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15754,10 +15754,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129319315</v>
+        <v>129319347</v>
       </c>
       <c r="B142" t="n">
-        <v>82994</v>
+        <v>80184</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15765,21 +15765,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6439</v>
+        <v>6464</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15789,10 +15789,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>540765</v>
+        <v>540653</v>
       </c>
       <c r="R142" t="n">
-        <v>7193370</v>
+        <v>7193521</v>
       </c>
       <c r="S142" t="n">
         <v>25</v>
@@ -15824,7 +15824,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15861,10 +15861,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129319428</v>
+        <v>129319387</v>
       </c>
       <c r="B143" t="n">
-        <v>80148</v>
+        <v>83003</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15872,21 +15872,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15896,10 +15896,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>540971</v>
+        <v>540772</v>
       </c>
       <c r="R143" t="n">
-        <v>7193081</v>
+        <v>7193446</v>
       </c>
       <c r="S143" t="n">
         <v>25</v>
@@ -15931,7 +15931,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15941,7 +15941,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15968,32 +15968,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129319347</v>
+        <v>129319406</v>
       </c>
       <c r="B144" t="n">
-        <v>80184</v>
+        <v>79122</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6464</v>
+        <v>864</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -16003,10 +16003,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>540653</v>
+        <v>540938</v>
       </c>
       <c r="R144" t="n">
-        <v>7193521</v>
+        <v>7193168</v>
       </c>
       <c r="S144" t="n">
         <v>25</v>
@@ -16038,7 +16038,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16048,7 +16048,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD144" t="b">

--- a/artfynd/A 51086-2025 artfynd.xlsx
+++ b/artfynd/A 51086-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129319285</v>
+        <v>129319307</v>
       </c>
       <c r="B2" t="n">
-        <v>91539</v>
+        <v>91541</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540886</v>
+        <v>540962</v>
       </c>
       <c r="R2" t="n">
-        <v>7193172</v>
+        <v>7193400</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129319307</v>
+        <v>129319285</v>
       </c>
       <c r="B3" t="n">
-        <v>91539</v>
+        <v>91541</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540962</v>
+        <v>540886</v>
       </c>
       <c r="R3" t="n">
-        <v>7193400</v>
+        <v>7193172</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,32 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129319420</v>
+        <v>129319386</v>
       </c>
       <c r="B4" t="n">
-        <v>80148</v>
+        <v>95938</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>2809</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540982</v>
+        <v>540774</v>
       </c>
       <c r="R4" t="n">
-        <v>7193144</v>
+        <v>7193457</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,32 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129319384</v>
+        <v>129319323</v>
       </c>
       <c r="B5" t="n">
-        <v>79043</v>
+        <v>80185</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540775</v>
+        <v>540719</v>
       </c>
       <c r="R5" t="n">
-        <v>7193467</v>
+        <v>7193483</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129319302</v>
+        <v>129319420</v>
       </c>
       <c r="B6" t="n">
-        <v>79043</v>
+        <v>80149</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540960</v>
+        <v>540982</v>
       </c>
       <c r="R6" t="n">
-        <v>7193375</v>
+        <v>7193144</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1438,32 +1438,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129319386</v>
+        <v>129319384</v>
       </c>
       <c r="B9" t="n">
-        <v>95936</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1473,10 +1473,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540774</v>
+        <v>540775</v>
       </c>
       <c r="R9" t="n">
-        <v>7193457</v>
+        <v>7193467</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1508,7 +1508,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1545,32 +1545,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129319323</v>
+        <v>129319302</v>
       </c>
       <c r="B10" t="n">
-        <v>80184</v>
+        <v>79044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1580,10 +1580,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540719</v>
+        <v>540960</v>
       </c>
       <c r="R10" t="n">
-        <v>7193483</v>
+        <v>7193375</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1615,7 +1615,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1652,32 +1652,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129319296</v>
+        <v>129319295</v>
       </c>
       <c r="B11" t="n">
-        <v>79043</v>
+        <v>95938</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540970</v>
+        <v>540972</v>
       </c>
       <c r="R11" t="n">
-        <v>7193365</v>
+        <v>7193357</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1759,32 +1759,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129319430</v>
+        <v>129319361</v>
       </c>
       <c r="B12" t="n">
-        <v>80183</v>
+        <v>91545</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1794,10 +1794,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540971</v>
+        <v>540726</v>
       </c>
       <c r="R12" t="n">
-        <v>7193066</v>
+        <v>7193531</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1829,7 +1829,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1866,32 +1866,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129319419</v>
+        <v>129319424</v>
       </c>
       <c r="B13" t="n">
-        <v>80183</v>
+        <v>80150</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1901,10 +1901,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540986</v>
+        <v>540975</v>
       </c>
       <c r="R13" t="n">
-        <v>7193130</v>
+        <v>7193139</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1973,32 +1973,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129319313</v>
+        <v>129319381</v>
       </c>
       <c r="B14" t="n">
-        <v>80184</v>
+        <v>82878</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2008,10 +2008,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540789</v>
+        <v>540758</v>
       </c>
       <c r="R14" t="n">
-        <v>7193372</v>
+        <v>7193475</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2080,32 +2080,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129319352</v>
+        <v>129319419</v>
       </c>
       <c r="B15" t="n">
-        <v>78056</v>
+        <v>80184</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228579</v>
+        <v>6463</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540715</v>
+        <v>540986</v>
       </c>
       <c r="R15" t="n">
-        <v>7193537</v>
+        <v>7193130</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2187,10 +2187,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129319361</v>
+        <v>129319328</v>
       </c>
       <c r="B16" t="n">
-        <v>91543</v>
+        <v>80149</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2198,21 +2198,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2222,10 +2222,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540726</v>
+        <v>540693</v>
       </c>
       <c r="R16" t="n">
-        <v>7193531</v>
+        <v>7193540</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2294,10 +2294,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129319295</v>
+        <v>129319313</v>
       </c>
       <c r="B17" t="n">
-        <v>95936</v>
+        <v>80185</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2305,21 +2305,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2809</v>
+        <v>6464</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2329,10 +2329,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540972</v>
+        <v>540789</v>
       </c>
       <c r="R17" t="n">
-        <v>7193357</v>
+        <v>7193372</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2401,7 +2401,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129319424</v>
+        <v>129319324</v>
       </c>
       <c r="B18" t="n">
         <v>80149</v>
@@ -2412,21 +2412,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2436,10 +2436,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540975</v>
+        <v>540719</v>
       </c>
       <c r="R18" t="n">
-        <v>7193139</v>
+        <v>7193483</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2508,32 +2508,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129319381</v>
+        <v>129319430</v>
       </c>
       <c r="B19" t="n">
-        <v>82877</v>
+        <v>80184</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>6463</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2543,10 +2543,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540758</v>
+        <v>540971</v>
       </c>
       <c r="R19" t="n">
-        <v>7193475</v>
+        <v>7193066</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2615,10 +2615,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129319324</v>
+        <v>129319296</v>
       </c>
       <c r="B20" t="n">
-        <v>80148</v>
+        <v>79044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2626,21 +2626,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540719</v>
+        <v>540970</v>
       </c>
       <c r="R20" t="n">
-        <v>7193483</v>
+        <v>7193365</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2722,10 +2722,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129319328</v>
+        <v>129319352</v>
       </c>
       <c r="B21" t="n">
-        <v>80148</v>
+        <v>78057</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2733,21 +2733,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2757,10 +2757,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540693</v>
+        <v>540715</v>
       </c>
       <c r="R21" t="n">
-        <v>7193540</v>
+        <v>7193537</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2945,10 +2945,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129319340</v>
+        <v>129319349</v>
       </c>
       <c r="B23" t="n">
-        <v>91543</v>
+        <v>91565</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2956,23 +2956,19 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2980,10 +2976,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540666</v>
+        <v>540670</v>
       </c>
       <c r="R23" t="n">
-        <v>7193537</v>
+        <v>7193521</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3015,7 +3011,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3025,7 +3021,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3055,7 +3051,7 @@
         <v>129319281</v>
       </c>
       <c r="B24" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3162,7 +3158,7 @@
         <v>129319316</v>
       </c>
       <c r="B25" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3269,7 +3265,7 @@
         <v>129319291</v>
       </c>
       <c r="B26" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3373,10 +3369,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129319390</v>
+        <v>129319340</v>
       </c>
       <c r="B27" t="n">
-        <v>79043</v>
+        <v>91545</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3384,21 +3380,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3408,10 +3404,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>540818</v>
+        <v>540666</v>
       </c>
       <c r="R27" t="n">
-        <v>7193358</v>
+        <v>7193537</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3443,7 +3439,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3453,7 +3449,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3480,10 +3476,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129319383</v>
+        <v>129319390</v>
       </c>
       <c r="B28" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3515,10 +3511,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>540764</v>
+        <v>540818</v>
       </c>
       <c r="R28" t="n">
-        <v>7193475</v>
+        <v>7193358</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3550,7 +3546,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3560,7 +3556,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3587,10 +3583,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129319349</v>
+        <v>129319383</v>
       </c>
       <c r="B29" t="n">
-        <v>91563</v>
+        <v>79044</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3598,19 +3594,23 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3618,10 +3618,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>540670</v>
+        <v>540764</v>
       </c>
       <c r="R29" t="n">
-        <v>7193521</v>
+        <v>7193475</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3653,7 +3653,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3693,7 +3693,7 @@
         <v>129319354</v>
       </c>
       <c r="B30" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>129319374</v>
       </c>
       <c r="B31" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>129319377</v>
       </c>
       <c r="B32" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4011,10 +4011,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129319396</v>
+        <v>129319337</v>
       </c>
       <c r="B33" t="n">
-        <v>79043</v>
+        <v>80149</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4022,21 +4022,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4046,10 +4046,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>540928</v>
+        <v>540676</v>
       </c>
       <c r="R33" t="n">
-        <v>7193263</v>
+        <v>7193539</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4081,7 +4081,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4118,27 +4118,27 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129319427</v>
+        <v>129319422</v>
       </c>
       <c r="B34" t="n">
-        <v>79043</v>
+        <v>80184</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4153,10 +4153,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>540969</v>
+        <v>540980</v>
       </c>
       <c r="R34" t="n">
-        <v>7193117</v>
+        <v>7193139</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4225,10 +4225,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129319282</v>
+        <v>129319396</v>
       </c>
       <c r="B35" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4260,10 +4260,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>540901</v>
+        <v>540928</v>
       </c>
       <c r="R35" t="n">
-        <v>7193084</v>
+        <v>7193263</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4295,7 +4295,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4305,7 +4305,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4332,10 +4332,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129319337</v>
+        <v>129319427</v>
       </c>
       <c r="B36" t="n">
-        <v>80148</v>
+        <v>79044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4343,21 +4343,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4367,10 +4367,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>540676</v>
+        <v>540969</v>
       </c>
       <c r="R36" t="n">
-        <v>7193539</v>
+        <v>7193117</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4402,7 +4402,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4439,10 +4439,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129319405</v>
+        <v>129319282</v>
       </c>
       <c r="B37" t="n">
-        <v>83011</v>
+        <v>79044</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4450,21 +4450,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4474,10 +4474,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>540931</v>
+        <v>540901</v>
       </c>
       <c r="R37" t="n">
-        <v>7193220</v>
+        <v>7193084</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4546,10 +4546,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129319404</v>
+        <v>129319405</v>
       </c>
       <c r="B38" t="n">
-        <v>78056</v>
+        <v>83012</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4557,21 +4557,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4653,32 +4653,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129319422</v>
+        <v>129319404</v>
       </c>
       <c r="B39" t="n">
-        <v>80183</v>
+        <v>78057</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6463</v>
+        <v>228579</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4688,10 +4688,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>540980</v>
+        <v>540931</v>
       </c>
       <c r="R39" t="n">
-        <v>7193139</v>
+        <v>7193220</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4763,7 +4763,7 @@
         <v>129319395</v>
       </c>
       <c r="B40" t="n">
-        <v>82996</v>
+        <v>82997</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129319278</v>
+        <v>129319348</v>
       </c>
       <c r="B41" t="n">
         <v>80149</v>
@@ -4878,21 +4878,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>540864</v>
+        <v>540653</v>
       </c>
       <c r="R41" t="n">
-        <v>7193066</v>
+        <v>7193521</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4947,7 +4947,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4974,32 +4974,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129319365</v>
+        <v>129319401</v>
       </c>
       <c r="B42" t="n">
-        <v>80149</v>
+        <v>80178</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>540738</v>
+        <v>540942</v>
       </c>
       <c r="R42" t="n">
-        <v>7193503</v>
+        <v>7193229</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5081,10 +5081,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129319294</v>
+        <v>129319403</v>
       </c>
       <c r="B43" t="n">
-        <v>83016</v>
+        <v>80149</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5092,21 +5092,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1467</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5116,10 +5116,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540974</v>
+        <v>540930</v>
       </c>
       <c r="R43" t="n">
-        <v>7193351</v>
+        <v>7193219</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5188,27 +5188,27 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129319303</v>
+        <v>129319320</v>
       </c>
       <c r="B44" t="n">
-        <v>79043</v>
+        <v>80184</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540934</v>
+        <v>540719</v>
       </c>
       <c r="R44" t="n">
-        <v>7193385</v>
+        <v>7193463</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5295,10 +5295,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129319288</v>
+        <v>129319303</v>
       </c>
       <c r="B45" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5330,10 +5330,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>540915</v>
+        <v>540934</v>
       </c>
       <c r="R45" t="n">
-        <v>7193185</v>
+        <v>7193385</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5365,7 +5365,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5375,7 +5375,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5402,10 +5402,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129319403</v>
+        <v>129319288</v>
       </c>
       <c r="B46" t="n">
-        <v>80148</v>
+        <v>79044</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5413,21 +5413,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5437,10 +5437,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>540930</v>
+        <v>540915</v>
       </c>
       <c r="R46" t="n">
-        <v>7193219</v>
+        <v>7193185</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5472,7 +5472,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5509,10 +5509,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129319348</v>
+        <v>129319278</v>
       </c>
       <c r="B47" t="n">
-        <v>80148</v>
+        <v>80150</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5520,21 +5520,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5544,10 +5544,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>540653</v>
+        <v>540864</v>
       </c>
       <c r="R47" t="n">
-        <v>7193521</v>
+        <v>7193066</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5579,7 +5579,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5616,32 +5616,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129319401</v>
+        <v>129319365</v>
       </c>
       <c r="B48" t="n">
-        <v>80177</v>
+        <v>80150</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5651,10 +5651,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>540942</v>
+        <v>540738</v>
       </c>
       <c r="R48" t="n">
-        <v>7193229</v>
+        <v>7193503</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5686,7 +5686,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5723,32 +5723,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129319320</v>
+        <v>129319294</v>
       </c>
       <c r="B49" t="n">
-        <v>80183</v>
+        <v>83017</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6463</v>
+        <v>1467</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>540719</v>
+        <v>540974</v>
       </c>
       <c r="R49" t="n">
-        <v>7193463</v>
+        <v>7193351</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5833,7 +5833,7 @@
         <v>129319366</v>
       </c>
       <c r="B50" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
         <v>129319356</v>
       </c>
       <c r="B51" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
         <v>129319280</v>
       </c>
       <c r="B52" t="n">
-        <v>95936</v>
+        <v>95938</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6154,7 +6154,7 @@
         <v>129319335</v>
       </c>
       <c r="B53" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6261,7 +6261,7 @@
         <v>129319429</v>
       </c>
       <c r="B54" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         <v>129319417</v>
       </c>
       <c r="B55" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6472,10 +6472,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129319304</v>
+        <v>129319388</v>
       </c>
       <c r="B56" t="n">
-        <v>79043</v>
+        <v>57727</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6483,34 +6483,48 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>540962</v>
+        <v>540828</v>
       </c>
       <c r="R56" t="n">
-        <v>7193388</v>
+        <v>7193425</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6542,7 +6556,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6552,7 +6566,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6579,10 +6593,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129319388</v>
+        <v>129319304</v>
       </c>
       <c r="B57" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6590,48 +6604,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>540828</v>
+        <v>540962</v>
       </c>
       <c r="R57" t="n">
-        <v>7193425</v>
+        <v>7193388</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6673,7 +6673,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6703,7 +6703,7 @@
         <v>129319353</v>
       </c>
       <c r="B58" t="n">
-        <v>82877</v>
+        <v>82878</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         <v>129319279</v>
       </c>
       <c r="B59" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>129319339</v>
       </c>
       <c r="B60" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7021,10 +7021,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129319292</v>
+        <v>129319311</v>
       </c>
       <c r="B61" t="n">
-        <v>79043</v>
+        <v>91541</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7032,21 +7032,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7056,10 +7056,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>540996</v>
+        <v>540830</v>
       </c>
       <c r="R61" t="n">
-        <v>7193327</v>
+        <v>7193366</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7091,7 +7091,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7128,10 +7128,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129319392</v>
+        <v>129319372</v>
       </c>
       <c r="B62" t="n">
-        <v>79043</v>
+        <v>80149</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7139,21 +7139,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7163,10 +7163,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>540826</v>
+        <v>540736</v>
       </c>
       <c r="R62" t="n">
-        <v>7193294</v>
+        <v>7193500</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7208,7 +7208,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7235,10 +7235,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129319423</v>
+        <v>129319330</v>
       </c>
       <c r="B63" t="n">
-        <v>57831</v>
+        <v>82995</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7246,43 +7246,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103031</v>
+        <v>6439</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>540976</v>
+        <v>540683</v>
       </c>
       <c r="R63" t="n">
-        <v>7193139</v>
+        <v>7193545</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7314,7 +7305,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7324,7 +7315,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7351,10 +7342,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129319311</v>
+        <v>129319292</v>
       </c>
       <c r="B64" t="n">
-        <v>91539</v>
+        <v>79044</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7362,21 +7353,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7386,10 +7377,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>540830</v>
+        <v>540996</v>
       </c>
       <c r="R64" t="n">
-        <v>7193366</v>
+        <v>7193327</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7421,7 +7412,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7431,7 +7422,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7458,10 +7449,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129319372</v>
+        <v>129319392</v>
       </c>
       <c r="B65" t="n">
-        <v>80148</v>
+        <v>79044</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7469,21 +7460,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7493,10 +7484,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>540736</v>
+        <v>540826</v>
       </c>
       <c r="R65" t="n">
-        <v>7193500</v>
+        <v>7193294</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7528,7 +7519,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7538,7 +7529,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7565,10 +7556,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129319330</v>
+        <v>129319423</v>
       </c>
       <c r="B66" t="n">
-        <v>82994</v>
+        <v>57831</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7576,34 +7567,43 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6439</v>
+        <v>103031</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>540683</v>
+        <v>540976</v>
       </c>
       <c r="R66" t="n">
-        <v>7193545</v>
+        <v>7193139</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7635,7 +7635,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7645,7 +7645,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7672,32 +7672,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129319400</v>
+        <v>129319421</v>
       </c>
       <c r="B67" t="n">
-        <v>79043</v>
+        <v>80178</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7707,10 +7707,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>540943</v>
+        <v>540981</v>
       </c>
       <c r="R67" t="n">
-        <v>7193233</v>
+        <v>7193140</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7742,7 +7742,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7752,7 +7752,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7782,7 +7782,7 @@
         <v>129319334</v>
       </c>
       <c r="B68" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7886,32 +7886,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129319397</v>
+        <v>129319370</v>
       </c>
       <c r="B69" t="n">
-        <v>79043</v>
+        <v>80178</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7921,10 +7921,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>540946</v>
+        <v>540737</v>
       </c>
       <c r="R69" t="n">
-        <v>7193256</v>
+        <v>7193504</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7956,7 +7956,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7966,7 +7966,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7993,45 +7993,54 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129319370</v>
+        <v>129319293</v>
       </c>
       <c r="B70" t="n">
-        <v>80177</v>
+        <v>57887</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>540737</v>
+        <v>540980</v>
       </c>
       <c r="R70" t="n">
-        <v>7193504</v>
+        <v>7193345</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8063,7 +8072,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8073,7 +8082,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8100,32 +8109,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129319421</v>
+        <v>129319397</v>
       </c>
       <c r="B71" t="n">
-        <v>80177</v>
+        <v>79044</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8135,10 +8144,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>540981</v>
+        <v>540946</v>
       </c>
       <c r="R71" t="n">
-        <v>7193140</v>
+        <v>7193256</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8170,7 +8179,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8180,7 +8189,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8207,10 +8216,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129319293</v>
+        <v>129319400</v>
       </c>
       <c r="B72" t="n">
-        <v>57887</v>
+        <v>79044</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8218,43 +8227,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>540980</v>
+        <v>540943</v>
       </c>
       <c r="R72" t="n">
-        <v>7193345</v>
+        <v>7193233</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8286,7 +8286,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8323,10 +8323,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129319412</v>
+        <v>129319402</v>
       </c>
       <c r="B73" t="n">
-        <v>91563</v>
+        <v>79044</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8334,19 +8334,23 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -8354,10 +8358,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>540952</v>
+        <v>540936</v>
       </c>
       <c r="R73" t="n">
-        <v>7193187</v>
+        <v>7193225</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8389,7 +8393,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8399,7 +8403,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8426,32 +8430,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129319367</v>
+        <v>129319413</v>
       </c>
       <c r="B74" t="n">
-        <v>80177</v>
+        <v>79044</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8461,10 +8465,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>540734</v>
+        <v>540965</v>
       </c>
       <c r="R74" t="n">
-        <v>7193503</v>
+        <v>7193181</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8496,7 +8500,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8506,7 +8510,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8533,10 +8537,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129319413</v>
+        <v>129319412</v>
       </c>
       <c r="B75" t="n">
-        <v>79043</v>
+        <v>91565</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8544,23 +8548,19 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -8568,10 +8568,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>540965</v>
+        <v>540952</v>
       </c>
       <c r="R75" t="n">
-        <v>7193181</v>
+        <v>7193187</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8603,7 +8603,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8613,7 +8613,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8640,32 +8640,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129319402</v>
+        <v>129319367</v>
       </c>
       <c r="B76" t="n">
-        <v>79043</v>
+        <v>80178</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8675,10 +8675,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>540936</v>
+        <v>540734</v>
       </c>
       <c r="R76" t="n">
-        <v>7193225</v>
+        <v>7193503</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8710,7 +8710,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8720,7 +8720,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8866,7 +8866,7 @@
         <v>129319371</v>
       </c>
       <c r="B78" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9085,7 +9085,7 @@
         <v>129319338</v>
       </c>
       <c r="B80" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9189,10 +9189,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129319394</v>
+        <v>129319408</v>
       </c>
       <c r="B81" t="n">
-        <v>79043</v>
+        <v>80149</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9200,21 +9200,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9224,10 +9224,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>540877</v>
+        <v>540939</v>
       </c>
       <c r="R81" t="n">
-        <v>7193291</v>
+        <v>7193177</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9259,7 +9259,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9296,32 +9296,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129319382</v>
+        <v>129319431</v>
       </c>
       <c r="B82" t="n">
-        <v>79043</v>
+        <v>80178</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9331,10 +9331,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>540761</v>
+        <v>540979</v>
       </c>
       <c r="R82" t="n">
-        <v>7193473</v>
+        <v>7193075</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9366,7 +9366,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9376,7 +9376,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9403,10 +9403,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129319408</v>
+        <v>129319336</v>
       </c>
       <c r="B83" t="n">
-        <v>80148</v>
+        <v>79044</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9414,21 +9414,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9438,10 +9438,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>540939</v>
+        <v>540668</v>
       </c>
       <c r="R83" t="n">
-        <v>7193177</v>
+        <v>7193543</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9473,7 +9473,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9483,7 +9483,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9510,10 +9510,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129319336</v>
+        <v>129319382</v>
       </c>
       <c r="B84" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9545,10 +9545,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>540668</v>
+        <v>540761</v>
       </c>
       <c r="R84" t="n">
-        <v>7193543</v>
+        <v>7193473</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9580,7 +9580,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9590,7 +9590,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9617,32 +9617,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129319431</v>
+        <v>129319394</v>
       </c>
       <c r="B85" t="n">
-        <v>80177</v>
+        <v>79044</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9652,10 +9652,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>540979</v>
+        <v>540877</v>
       </c>
       <c r="R85" t="n">
-        <v>7193075</v>
+        <v>7193291</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9687,7 +9687,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9697,7 +9697,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9727,7 +9727,7 @@
         <v>129319389</v>
       </c>
       <c r="B86" t="n">
-        <v>95936</v>
+        <v>95938</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
         <v>129319333</v>
       </c>
       <c r="B87" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9941,7 +9941,7 @@
         <v>129319376</v>
       </c>
       <c r="B88" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10048,7 +10048,7 @@
         <v>129319375</v>
       </c>
       <c r="B89" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10155,7 +10155,7 @@
         <v>129319433</v>
       </c>
       <c r="B90" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10262,7 +10262,7 @@
         <v>129319357</v>
       </c>
       <c r="B91" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10366,10 +10366,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129319409</v>
+        <v>129319284</v>
       </c>
       <c r="B92" t="n">
-        <v>80148</v>
+        <v>79044</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10377,21 +10377,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10401,10 +10401,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>540942</v>
+        <v>540867</v>
       </c>
       <c r="R92" t="n">
-        <v>7193182</v>
+        <v>7193169</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -10436,7 +10436,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10446,7 +10446,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10473,32 +10473,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129319284</v>
+        <v>129319393</v>
       </c>
       <c r="B93" t="n">
-        <v>79043</v>
+        <v>82995</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10508,10 +10508,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>540867</v>
+        <v>540824</v>
       </c>
       <c r="R93" t="n">
-        <v>7193169</v>
+        <v>7193288</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -10543,7 +10543,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10553,7 +10553,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10580,32 +10580,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129319393</v>
+        <v>129319299</v>
       </c>
       <c r="B94" t="n">
-        <v>82994</v>
+        <v>79044</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10615,10 +10615,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>540824</v>
+        <v>540964</v>
       </c>
       <c r="R94" t="n">
-        <v>7193288</v>
+        <v>7193371</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -10650,7 +10650,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10660,7 +10660,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10687,10 +10687,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129319298</v>
+        <v>129319344</v>
       </c>
       <c r="B95" t="n">
-        <v>91563</v>
+        <v>79044</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10698,19 +10698,23 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -10718,10 +10722,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>540964</v>
+        <v>540650</v>
       </c>
       <c r="R95" t="n">
-        <v>7193371</v>
+        <v>7193540</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -10753,7 +10757,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10763,7 +10767,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10790,10 +10794,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129319299</v>
+        <v>129319298</v>
       </c>
       <c r="B96" t="n">
-        <v>79043</v>
+        <v>91565</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10801,23 +10805,19 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -10897,10 +10897,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129319344</v>
+        <v>129319409</v>
       </c>
       <c r="B97" t="n">
-        <v>79043</v>
+        <v>80149</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10908,21 +10908,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10932,10 +10932,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>540650</v>
+        <v>540942</v>
       </c>
       <c r="R97" t="n">
-        <v>7193540</v>
+        <v>7193182</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -10967,7 +10967,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10977,7 +10977,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11004,10 +11004,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129319445</v>
+        <v>129319359</v>
       </c>
       <c r="B98" t="n">
-        <v>57724</v>
+        <v>80149</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11015,43 +11015,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>541052</v>
+        <v>540725</v>
       </c>
       <c r="R98" t="n">
-        <v>7193255</v>
+        <v>7193537</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -11083,7 +11074,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11093,7 +11084,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11123,7 +11114,7 @@
         <v>129319399</v>
       </c>
       <c r="B99" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11230,7 +11221,7 @@
         <v>129319308</v>
       </c>
       <c r="B100" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11334,10 +11325,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129319359</v>
+        <v>129319362</v>
       </c>
       <c r="B101" t="n">
-        <v>80148</v>
+        <v>79044</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11345,21 +11336,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11369,10 +11360,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>540725</v>
+        <v>540721</v>
       </c>
       <c r="R101" t="n">
-        <v>7193537</v>
+        <v>7193527</v>
       </c>
       <c r="S101" t="n">
         <v>25</v>
@@ -11441,10 +11432,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129319286</v>
+        <v>129319306</v>
       </c>
       <c r="B102" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11476,10 +11467,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>540891</v>
+        <v>540961</v>
       </c>
       <c r="R102" t="n">
-        <v>7193174</v>
+        <v>7193398</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -11511,7 +11502,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11521,7 +11512,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11548,10 +11539,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129319362</v>
+        <v>129319286</v>
       </c>
       <c r="B103" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11583,10 +11574,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>540721</v>
+        <v>540891</v>
       </c>
       <c r="R103" t="n">
-        <v>7193527</v>
+        <v>7193174</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -11618,7 +11609,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11628,7 +11619,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11655,10 +11646,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129319306</v>
+        <v>129319445</v>
       </c>
       <c r="B104" t="n">
-        <v>79043</v>
+        <v>57724</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11666,34 +11657,43 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>540961</v>
+        <v>541052</v>
       </c>
       <c r="R104" t="n">
-        <v>7193398</v>
+        <v>7193255</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -11725,7 +11725,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11735,7 +11735,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11762,10 +11762,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129319360</v>
+        <v>129319355</v>
       </c>
       <c r="B105" t="n">
-        <v>91539</v>
+        <v>80150</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11773,21 +11773,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11797,10 +11797,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>540725</v>
+        <v>540726</v>
       </c>
       <c r="R105" t="n">
-        <v>7193532</v>
+        <v>7193541</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -11832,7 +11832,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11842,7 +11842,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11869,32 +11869,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129319418</v>
+        <v>129319360</v>
       </c>
       <c r="B106" t="n">
-        <v>80184</v>
+        <v>91541</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6464</v>
+        <v>1108</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11904,10 +11904,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>540986</v>
+        <v>540725</v>
       </c>
       <c r="R106" t="n">
-        <v>7193130</v>
+        <v>7193532</v>
       </c>
       <c r="S106" t="n">
         <v>25</v>
@@ -11939,7 +11939,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11949,7 +11949,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11976,10 +11976,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129319355</v>
+        <v>129319369</v>
       </c>
       <c r="B107" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12011,10 +12011,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>540726</v>
+        <v>540734</v>
       </c>
       <c r="R107" t="n">
-        <v>7193541</v>
+        <v>7193503</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -12046,7 +12046,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12056,7 +12056,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12083,10 +12083,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129319369</v>
+        <v>129319391</v>
       </c>
       <c r="B108" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12118,10 +12118,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>540734</v>
+        <v>540818</v>
       </c>
       <c r="R108" t="n">
-        <v>7193503</v>
+        <v>7193333</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -12153,7 +12153,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12163,7 +12163,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12190,7 +12190,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129319391</v>
+        <v>129319368</v>
       </c>
       <c r="B109" t="n">
         <v>80149</v>
@@ -12201,21 +12201,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12225,10 +12225,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>540818</v>
+        <v>540734</v>
       </c>
       <c r="R109" t="n">
-        <v>7193333</v>
+        <v>7193503</v>
       </c>
       <c r="S109" t="n">
         <v>25</v>
@@ -12260,7 +12260,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12270,7 +12270,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12297,32 +12297,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129319411</v>
+        <v>129319418</v>
       </c>
       <c r="B110" t="n">
-        <v>79043</v>
+        <v>80185</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12332,10 +12332,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>540955</v>
+        <v>540986</v>
       </c>
       <c r="R110" t="n">
-        <v>7193186</v>
+        <v>7193130</v>
       </c>
       <c r="S110" t="n">
         <v>25</v>
@@ -12367,7 +12367,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12377,7 +12377,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12404,10 +12404,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129319368</v>
+        <v>129319411</v>
       </c>
       <c r="B111" t="n">
-        <v>80148</v>
+        <v>79044</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12415,21 +12415,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12439,10 +12439,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>540734</v>
+        <v>540955</v>
       </c>
       <c r="R111" t="n">
-        <v>7193503</v>
+        <v>7193186</v>
       </c>
       <c r="S111" t="n">
         <v>25</v>
@@ -12474,7 +12474,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12484,7 +12484,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12514,7 +12514,7 @@
         <v>129319407</v>
       </c>
       <c r="B112" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12618,10 +12618,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129319341</v>
+        <v>129319305</v>
       </c>
       <c r="B113" t="n">
-        <v>91539</v>
+        <v>91565</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12629,23 +12629,19 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
@@ -12653,10 +12649,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>540670</v>
+        <v>540959</v>
       </c>
       <c r="R113" t="n">
-        <v>7193533</v>
+        <v>7193395</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -12688,7 +12684,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12698,7 +12694,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12725,32 +12721,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129319426</v>
+        <v>129319425</v>
       </c>
       <c r="B114" t="n">
-        <v>80149</v>
+        <v>80184</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12760,10 +12756,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>540979</v>
+        <v>540980</v>
       </c>
       <c r="R114" t="n">
-        <v>7193115</v>
+        <v>7193116</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -12832,27 +12828,27 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129319425</v>
+        <v>129319309</v>
       </c>
       <c r="B115" t="n">
-        <v>80183</v>
+        <v>79044</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -12867,10 +12863,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>540980</v>
+        <v>540894</v>
       </c>
       <c r="R115" t="n">
-        <v>7193116</v>
+        <v>7193411</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -12902,7 +12898,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12912,7 +12908,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12939,10 +12935,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129319305</v>
+        <v>129319332</v>
       </c>
       <c r="B116" t="n">
-        <v>91563</v>
+        <v>57887</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12950,30 +12946,43 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr"/>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>540959</v>
+        <v>540675</v>
       </c>
       <c r="R116" t="n">
-        <v>7193395</v>
+        <v>7193538</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -13005,7 +13014,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13015,7 +13024,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13042,10 +13051,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129319309</v>
+        <v>129319426</v>
       </c>
       <c r="B117" t="n">
-        <v>79043</v>
+        <v>80150</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13053,21 +13062,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13077,10 +13086,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>540894</v>
+        <v>540979</v>
       </c>
       <c r="R117" t="n">
-        <v>7193411</v>
+        <v>7193115</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -13112,7 +13121,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13122,7 +13131,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13149,10 +13158,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129319332</v>
+        <v>129319341</v>
       </c>
       <c r="B118" t="n">
-        <v>57887</v>
+        <v>91541</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13160,43 +13169,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>540675</v>
+        <v>540670</v>
       </c>
       <c r="R118" t="n">
-        <v>7193538</v>
+        <v>7193533</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -13228,7 +13228,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13238,7 +13238,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13268,7 +13268,7 @@
         <v>129319329</v>
       </c>
       <c r="B119" t="n">
-        <v>88943</v>
+        <v>88945</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13372,32 +13372,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129319350</v>
+        <v>129319416</v>
       </c>
       <c r="B120" t="n">
-        <v>80148</v>
+        <v>80185</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13407,10 +13407,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>540681</v>
+        <v>540970</v>
       </c>
       <c r="R120" t="n">
-        <v>7193521</v>
+        <v>7193154</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -13442,7 +13442,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13452,7 +13452,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13479,32 +13479,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129319277</v>
+        <v>129319373</v>
       </c>
       <c r="B121" t="n">
-        <v>80149</v>
+        <v>80185</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13514,10 +13514,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>540837</v>
+        <v>540734</v>
       </c>
       <c r="R121" t="n">
-        <v>7193042</v>
+        <v>7193499</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -13549,7 +13549,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13559,7 +13559,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13586,32 +13586,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129319325</v>
+        <v>129319321</v>
       </c>
       <c r="B122" t="n">
-        <v>80149</v>
+        <v>80178</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13621,10 +13621,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>540714</v>
+        <v>540719</v>
       </c>
       <c r="R122" t="n">
-        <v>7193488</v>
+        <v>7193463</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -13656,7 +13656,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13666,7 +13666,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13693,7 +13693,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129319319</v>
+        <v>129319350</v>
       </c>
       <c r="B123" t="n">
         <v>80149</v>
@@ -13704,21 +13704,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13728,10 +13728,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>540719</v>
+        <v>540681</v>
       </c>
       <c r="R123" t="n">
-        <v>7193463</v>
+        <v>7193521</v>
       </c>
       <c r="S123" t="n">
         <v>25</v>
@@ -13763,7 +13763,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13773,7 +13773,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14032,32 +14032,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129319416</v>
+        <v>129319277</v>
       </c>
       <c r="B126" t="n">
-        <v>80184</v>
+        <v>80150</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14067,10 +14067,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>540970</v>
+        <v>540837</v>
       </c>
       <c r="R126" t="n">
-        <v>7193154</v>
+        <v>7193042</v>
       </c>
       <c r="S126" t="n">
         <v>25</v>
@@ -14102,7 +14102,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14112,7 +14112,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14139,32 +14139,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129319321</v>
+        <v>129319325</v>
       </c>
       <c r="B127" t="n">
-        <v>80177</v>
+        <v>80150</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14174,10 +14174,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>540719</v>
+        <v>540714</v>
       </c>
       <c r="R127" t="n">
-        <v>7193463</v>
+        <v>7193488</v>
       </c>
       <c r="S127" t="n">
         <v>25</v>
@@ -14209,7 +14209,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14219,7 +14219,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14246,32 +14246,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129319373</v>
+        <v>129319319</v>
       </c>
       <c r="B128" t="n">
-        <v>80184</v>
+        <v>80150</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14281,10 +14281,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>540734</v>
+        <v>540719</v>
       </c>
       <c r="R128" t="n">
-        <v>7193499</v>
+        <v>7193463</v>
       </c>
       <c r="S128" t="n">
         <v>25</v>
@@ -14316,7 +14316,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14326,7 +14326,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14353,10 +14353,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129319434</v>
+        <v>129319379</v>
       </c>
       <c r="B129" t="n">
-        <v>80148</v>
+        <v>79044</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14364,21 +14364,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14388,10 +14388,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>540979</v>
+        <v>540761</v>
       </c>
       <c r="R129" t="n">
-        <v>7193075</v>
+        <v>7193485</v>
       </c>
       <c r="S129" t="n">
         <v>25</v>
@@ -14423,7 +14423,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14433,7 +14433,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14463,7 +14463,7 @@
         <v>129319326</v>
       </c>
       <c r="B130" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14567,10 +14567,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129319379</v>
+        <v>129319434</v>
       </c>
       <c r="B131" t="n">
-        <v>79043</v>
+        <v>80149</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14578,21 +14578,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14602,10 +14602,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>540761</v>
+        <v>540979</v>
       </c>
       <c r="R131" t="n">
-        <v>7193485</v>
+        <v>7193075</v>
       </c>
       <c r="S131" t="n">
         <v>25</v>
@@ -14637,7 +14637,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14647,7 +14647,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14674,10 +14674,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129319378</v>
+        <v>129319380</v>
       </c>
       <c r="B132" t="n">
-        <v>82996</v>
+        <v>92263</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14685,21 +14685,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>306</v>
+        <v>3298</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14709,10 +14709,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>540757</v>
+        <v>540761</v>
       </c>
       <c r="R132" t="n">
-        <v>7193474</v>
+        <v>7193490</v>
       </c>
       <c r="S132" t="n">
         <v>25</v>
@@ -14744,7 +14744,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14754,7 +14754,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14781,10 +14781,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129319380</v>
+        <v>129319378</v>
       </c>
       <c r="B133" t="n">
-        <v>92261</v>
+        <v>82997</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14792,21 +14792,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>3298</v>
+        <v>306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14816,10 +14816,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>540761</v>
+        <v>540757</v>
       </c>
       <c r="R133" t="n">
-        <v>7193490</v>
+        <v>7193474</v>
       </c>
       <c r="S133" t="n">
         <v>25</v>
@@ -14851,7 +14851,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14861,7 +14861,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14891,7 +14891,7 @@
         <v>129319322</v>
       </c>
       <c r="B134" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14998,7 +14998,7 @@
         <v>129319312</v>
       </c>
       <c r="B135" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15102,10 +15102,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129319310</v>
+        <v>129319343</v>
       </c>
       <c r="B136" t="n">
-        <v>79043</v>
+        <v>57727</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15113,34 +15113,39 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>540830</v>
+        <v>540661</v>
       </c>
       <c r="R136" t="n">
-        <v>7193366</v>
+        <v>7193538</v>
       </c>
       <c r="S136" t="n">
         <v>25</v>
@@ -15172,7 +15177,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15182,7 +15187,12 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Färska och äldre spår på samma träd.</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15209,10 +15219,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129319343</v>
+        <v>129319310</v>
       </c>
       <c r="B137" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15220,39 +15230,34 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P137" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>540661</v>
+        <v>540830</v>
       </c>
       <c r="R137" t="n">
-        <v>7193538</v>
+        <v>7193366</v>
       </c>
       <c r="S137" t="n">
         <v>25</v>
@@ -15284,7 +15289,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15294,12 +15299,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>11:27</t>
-        </is>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>Färska och äldre spår på samma träd.</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15326,32 +15326,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129319287</v>
+        <v>129319387</v>
       </c>
       <c r="B138" t="n">
-        <v>92261</v>
+        <v>83004</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>3298</v>
+        <v>308</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15361,10 +15361,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>540913</v>
+        <v>540772</v>
       </c>
       <c r="R138" t="n">
-        <v>7193185</v>
+        <v>7193446</v>
       </c>
       <c r="S138" t="n">
         <v>25</v>
@@ -15396,7 +15396,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15406,7 +15406,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15433,32 +15433,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129319327</v>
+        <v>129319315</v>
       </c>
       <c r="B139" t="n">
-        <v>79043</v>
+        <v>82995</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15468,10 +15468,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>540693</v>
+        <v>540765</v>
       </c>
       <c r="R139" t="n">
-        <v>7193540</v>
+        <v>7193370</v>
       </c>
       <c r="S139" t="n">
         <v>25</v>
@@ -15503,7 +15503,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15513,7 +15513,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15540,32 +15540,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129319315</v>
+        <v>129319327</v>
       </c>
       <c r="B140" t="n">
-        <v>82994</v>
+        <v>79044</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15575,10 +15575,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>540765</v>
+        <v>540693</v>
       </c>
       <c r="R140" t="n">
-        <v>7193370</v>
+        <v>7193540</v>
       </c>
       <c r="S140" t="n">
         <v>25</v>
@@ -15610,7 +15610,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15620,7 +15620,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15647,32 +15647,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129319428</v>
+        <v>129319287</v>
       </c>
       <c r="B141" t="n">
-        <v>80148</v>
+        <v>92263</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6458</v>
+        <v>3298</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15682,10 +15682,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>540971</v>
+        <v>540913</v>
       </c>
       <c r="R141" t="n">
-        <v>7193081</v>
+        <v>7193185</v>
       </c>
       <c r="S141" t="n">
         <v>25</v>
@@ -15717,7 +15717,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15727,7 +15727,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15754,32 +15754,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129319347</v>
+        <v>129319406</v>
       </c>
       <c r="B142" t="n">
-        <v>80184</v>
+        <v>79123</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6464</v>
+        <v>864</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15789,10 +15789,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>540653</v>
+        <v>540938</v>
       </c>
       <c r="R142" t="n">
-        <v>7193521</v>
+        <v>7193168</v>
       </c>
       <c r="S142" t="n">
         <v>25</v>
@@ -15824,7 +15824,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15861,10 +15861,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129319387</v>
+        <v>129319428</v>
       </c>
       <c r="B143" t="n">
-        <v>83003</v>
+        <v>80149</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15872,21 +15872,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15896,10 +15896,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>540772</v>
+        <v>540971</v>
       </c>
       <c r="R143" t="n">
-        <v>7193446</v>
+        <v>7193081</v>
       </c>
       <c r="S143" t="n">
         <v>25</v>
@@ -15931,7 +15931,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15941,7 +15941,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15968,32 +15968,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129319406</v>
+        <v>129319347</v>
       </c>
       <c r="B144" t="n">
-        <v>79122</v>
+        <v>80185</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>864</v>
+        <v>6464</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -16003,10 +16003,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>540938</v>
+        <v>540653</v>
       </c>
       <c r="R144" t="n">
-        <v>7193168</v>
+        <v>7193521</v>
       </c>
       <c r="S144" t="n">
         <v>25</v>
@@ -16038,7 +16038,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16048,7 +16048,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD144" t="b">

--- a/artfynd/A 51086-2025 artfynd.xlsx
+++ b/artfynd/A 51086-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129319307</v>
+        <v>129319386</v>
       </c>
       <c r="B2" t="n">
-        <v>91541</v>
+        <v>95942</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>2809</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540962</v>
+        <v>540774</v>
       </c>
       <c r="R2" t="n">
-        <v>7193400</v>
+        <v>7193457</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129319285</v>
+        <v>129319307</v>
       </c>
       <c r="B3" t="n">
-        <v>91541</v>
+        <v>91545</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540886</v>
+        <v>540962</v>
       </c>
       <c r="R3" t="n">
-        <v>7193172</v>
+        <v>7193400</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,32 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129319386</v>
+        <v>129319285</v>
       </c>
       <c r="B4" t="n">
-        <v>95938</v>
+        <v>91545</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2809</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540774</v>
+        <v>540886</v>
       </c>
       <c r="R4" t="n">
-        <v>7193457</v>
+        <v>7193172</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129319300</v>
+        <v>129319384</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,39 +1221,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540961</v>
+        <v>540775</v>
       </c>
       <c r="R7" t="n">
-        <v>7193376</v>
+        <v>7193467</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1285,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1295,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1322,54 +1317,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129319414</v>
+        <v>129319302</v>
       </c>
       <c r="B8" t="n">
-        <v>58360</v>
+        <v>79044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102125</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540963</v>
+        <v>540960</v>
       </c>
       <c r="R8" t="n">
-        <v>7193203</v>
+        <v>7193375</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1401,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1411,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1438,45 +1424,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129319384</v>
+        <v>129319414</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>58360</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>102125</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540775</v>
+        <v>540963</v>
       </c>
       <c r="R9" t="n">
-        <v>7193467</v>
+        <v>7193203</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1508,7 +1503,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1518,7 +1513,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1545,10 +1540,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129319302</v>
+        <v>129319300</v>
       </c>
       <c r="B10" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1556,34 +1551,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540960</v>
+        <v>540961</v>
       </c>
       <c r="R10" t="n">
-        <v>7193375</v>
+        <v>7193376</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1615,7 +1615,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1652,32 +1652,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129319295</v>
+        <v>129319296</v>
       </c>
       <c r="B11" t="n">
-        <v>95938</v>
+        <v>79044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540972</v>
+        <v>540970</v>
       </c>
       <c r="R11" t="n">
-        <v>7193357</v>
+        <v>7193365</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1759,10 +1759,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129319361</v>
+        <v>129319352</v>
       </c>
       <c r="B12" t="n">
-        <v>91545</v>
+        <v>78057</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1770,21 +1770,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1794,10 +1794,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540726</v>
+        <v>540715</v>
       </c>
       <c r="R12" t="n">
-        <v>7193531</v>
+        <v>7193537</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1829,7 +1829,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1866,32 +1866,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129319424</v>
+        <v>129319295</v>
       </c>
       <c r="B13" t="n">
-        <v>80150</v>
+        <v>95942</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>2809</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1901,10 +1901,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540975</v>
+        <v>540972</v>
       </c>
       <c r="R13" t="n">
-        <v>7193139</v>
+        <v>7193357</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1973,10 +1973,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129319381</v>
+        <v>129319361</v>
       </c>
       <c r="B14" t="n">
-        <v>82878</v>
+        <v>91549</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1984,21 +1984,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2008,10 +2008,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540758</v>
+        <v>540726</v>
       </c>
       <c r="R14" t="n">
-        <v>7193475</v>
+        <v>7193531</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2080,32 +2080,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129319419</v>
+        <v>129319424</v>
       </c>
       <c r="B15" t="n">
-        <v>80184</v>
+        <v>80150</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540986</v>
+        <v>540975</v>
       </c>
       <c r="R15" t="n">
-        <v>7193130</v>
+        <v>7193139</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2187,10 +2187,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129319328</v>
+        <v>129319381</v>
       </c>
       <c r="B16" t="n">
-        <v>80149</v>
+        <v>82878</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2198,21 +2198,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2222,10 +2222,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540693</v>
+        <v>540758</v>
       </c>
       <c r="R16" t="n">
-        <v>7193540</v>
+        <v>7193475</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2294,10 +2294,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129319313</v>
+        <v>129319419</v>
       </c>
       <c r="B17" t="n">
-        <v>80185</v>
+        <v>80184</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2305,21 +2305,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2329,10 +2329,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540789</v>
+        <v>540986</v>
       </c>
       <c r="R17" t="n">
-        <v>7193372</v>
+        <v>7193130</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2401,7 +2401,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129319324</v>
+        <v>129319328</v>
       </c>
       <c r="B18" t="n">
         <v>80149</v>
@@ -2436,10 +2436,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540719</v>
+        <v>540693</v>
       </c>
       <c r="R18" t="n">
-        <v>7193483</v>
+        <v>7193540</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2508,32 +2508,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129319430</v>
+        <v>129319324</v>
       </c>
       <c r="B19" t="n">
-        <v>80184</v>
+        <v>80149</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2543,10 +2543,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540971</v>
+        <v>540719</v>
       </c>
       <c r="R19" t="n">
-        <v>7193066</v>
+        <v>7193483</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2615,27 +2615,27 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129319296</v>
+        <v>129319430</v>
       </c>
       <c r="B20" t="n">
-        <v>79044</v>
+        <v>80184</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540970</v>
+        <v>540971</v>
       </c>
       <c r="R20" t="n">
-        <v>7193365</v>
+        <v>7193066</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2722,32 +2722,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129319352</v>
+        <v>129319313</v>
       </c>
       <c r="B21" t="n">
-        <v>78057</v>
+        <v>80185</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228579</v>
+        <v>6464</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2757,10 +2757,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540715</v>
+        <v>540789</v>
       </c>
       <c r="R21" t="n">
-        <v>7193537</v>
+        <v>7193372</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2948,7 +2948,7 @@
         <v>129319349</v>
       </c>
       <c r="B23" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3048,10 +3048,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129319281</v>
+        <v>129319390</v>
       </c>
       <c r="B24" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3059,21 +3059,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540902</v>
+        <v>540818</v>
       </c>
       <c r="R24" t="n">
-        <v>7193083</v>
+        <v>7193358</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3118,7 +3118,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3155,10 +3155,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129319316</v>
+        <v>129319383</v>
       </c>
       <c r="B25" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3166,21 +3166,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3190,10 +3190,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540763</v>
+        <v>540764</v>
       </c>
       <c r="R25" t="n">
-        <v>7193372</v>
+        <v>7193475</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3262,10 +3262,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129319291</v>
+        <v>129319354</v>
       </c>
       <c r="B26" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3273,21 +3273,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540996</v>
+        <v>540722</v>
       </c>
       <c r="R26" t="n">
-        <v>7193327</v>
+        <v>7193542</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3369,10 +3369,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129319340</v>
+        <v>129319281</v>
       </c>
       <c r="B27" t="n">
-        <v>91545</v>
+        <v>80150</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3380,21 +3380,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3404,10 +3404,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>540666</v>
+        <v>540902</v>
       </c>
       <c r="R27" t="n">
-        <v>7193537</v>
+        <v>7193083</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3439,7 +3439,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3476,10 +3476,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129319390</v>
+        <v>129319316</v>
       </c>
       <c r="B28" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3487,21 +3487,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>540818</v>
+        <v>540763</v>
       </c>
       <c r="R28" t="n">
-        <v>7193358</v>
+        <v>7193372</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3583,10 +3583,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129319383</v>
+        <v>129319291</v>
       </c>
       <c r="B29" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3594,21 +3594,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3618,10 +3618,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>540764</v>
+        <v>540996</v>
       </c>
       <c r="R29" t="n">
-        <v>7193475</v>
+        <v>7193327</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3653,7 +3653,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3690,10 +3690,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129319354</v>
+        <v>129319340</v>
       </c>
       <c r="B30" t="n">
-        <v>79044</v>
+        <v>91549</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3701,21 +3701,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3725,10 +3725,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>540722</v>
+        <v>540666</v>
       </c>
       <c r="R30" t="n">
-        <v>7193542</v>
+        <v>7193537</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3760,7 +3760,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3797,10 +3797,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129319374</v>
+        <v>129319404</v>
       </c>
       <c r="B31" t="n">
-        <v>80150</v>
+        <v>78057</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3808,21 +3808,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>228579</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>540734</v>
+        <v>540931</v>
       </c>
       <c r="R31" t="n">
-        <v>7193499</v>
+        <v>7193220</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3867,7 +3867,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3904,7 +3904,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129319377</v>
+        <v>129319374</v>
       </c>
       <c r="B32" t="n">
         <v>80150</v>
@@ -3939,10 +3939,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>540745</v>
+        <v>540734</v>
       </c>
       <c r="R32" t="n">
-        <v>7193494</v>
+        <v>7193499</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4011,10 +4011,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129319337</v>
+        <v>129319377</v>
       </c>
       <c r="B33" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4022,21 +4022,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4046,10 +4046,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>540676</v>
+        <v>540745</v>
       </c>
       <c r="R33" t="n">
-        <v>7193539</v>
+        <v>7193494</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4081,7 +4081,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4118,32 +4118,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129319422</v>
+        <v>129319337</v>
       </c>
       <c r="B34" t="n">
-        <v>80184</v>
+        <v>80149</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4153,10 +4153,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>540980</v>
+        <v>540676</v>
       </c>
       <c r="R34" t="n">
-        <v>7193139</v>
+        <v>7193539</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4225,27 +4225,27 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129319396</v>
+        <v>129319422</v>
       </c>
       <c r="B35" t="n">
-        <v>79044</v>
+        <v>80184</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4260,10 +4260,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>540928</v>
+        <v>540980</v>
       </c>
       <c r="R35" t="n">
-        <v>7193263</v>
+        <v>7193139</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4295,7 +4295,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4305,7 +4305,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4332,10 +4332,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129319427</v>
+        <v>129319405</v>
       </c>
       <c r="B36" t="n">
-        <v>79044</v>
+        <v>83012</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4343,21 +4343,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4367,10 +4367,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>540969</v>
+        <v>540931</v>
       </c>
       <c r="R36" t="n">
-        <v>7193117</v>
+        <v>7193220</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4402,7 +4402,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4439,7 +4439,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129319282</v>
+        <v>129319396</v>
       </c>
       <c r="B37" t="n">
         <v>79044</v>
@@ -4474,10 +4474,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>540901</v>
+        <v>540928</v>
       </c>
       <c r="R37" t="n">
-        <v>7193084</v>
+        <v>7193263</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4546,10 +4546,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129319405</v>
+        <v>129319427</v>
       </c>
       <c r="B38" t="n">
-        <v>83012</v>
+        <v>79044</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4557,21 +4557,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>540931</v>
+        <v>540969</v>
       </c>
       <c r="R38" t="n">
-        <v>7193220</v>
+        <v>7193117</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4653,10 +4653,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129319404</v>
+        <v>129319282</v>
       </c>
       <c r="B39" t="n">
-        <v>78057</v>
+        <v>79044</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4664,21 +4664,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4688,10 +4688,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>540931</v>
+        <v>540901</v>
       </c>
       <c r="R39" t="n">
-        <v>7193220</v>
+        <v>7193084</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4867,10 +4867,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129319348</v>
+        <v>129319278</v>
       </c>
       <c r="B41" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4878,21 +4878,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>540653</v>
+        <v>540864</v>
       </c>
       <c r="R41" t="n">
-        <v>7193521</v>
+        <v>7193066</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4947,7 +4947,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4974,32 +4974,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129319401</v>
+        <v>129319365</v>
       </c>
       <c r="B42" t="n">
-        <v>80178</v>
+        <v>80150</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>540942</v>
+        <v>540738</v>
       </c>
       <c r="R42" t="n">
-        <v>7193229</v>
+        <v>7193503</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5081,10 +5081,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129319403</v>
+        <v>129319294</v>
       </c>
       <c r="B43" t="n">
-        <v>80149</v>
+        <v>83017</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5092,21 +5092,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>1467</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5116,10 +5116,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540930</v>
+        <v>540974</v>
       </c>
       <c r="R43" t="n">
-        <v>7193219</v>
+        <v>7193351</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5188,32 +5188,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129319320</v>
+        <v>129319348</v>
       </c>
       <c r="B44" t="n">
-        <v>80184</v>
+        <v>80149</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540719</v>
+        <v>540653</v>
       </c>
       <c r="R44" t="n">
-        <v>7193463</v>
+        <v>7193521</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5295,32 +5295,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129319303</v>
+        <v>129319401</v>
       </c>
       <c r="B45" t="n">
-        <v>79044</v>
+        <v>80178</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5330,10 +5330,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>540934</v>
+        <v>540942</v>
       </c>
       <c r="R45" t="n">
-        <v>7193385</v>
+        <v>7193229</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5365,7 +5365,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5375,7 +5375,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5402,10 +5402,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129319288</v>
+        <v>129319403</v>
       </c>
       <c r="B46" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5413,21 +5413,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5437,10 +5437,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>540915</v>
+        <v>540930</v>
       </c>
       <c r="R46" t="n">
-        <v>7193185</v>
+        <v>7193219</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5472,7 +5472,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5509,32 +5509,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129319278</v>
+        <v>129319320</v>
       </c>
       <c r="B47" t="n">
-        <v>80150</v>
+        <v>80184</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5544,10 +5544,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>540864</v>
+        <v>540719</v>
       </c>
       <c r="R47" t="n">
-        <v>7193066</v>
+        <v>7193463</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5579,7 +5579,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5616,10 +5616,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129319365</v>
+        <v>129319303</v>
       </c>
       <c r="B48" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5627,21 +5627,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5651,10 +5651,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>540738</v>
+        <v>540934</v>
       </c>
       <c r="R48" t="n">
-        <v>7193503</v>
+        <v>7193385</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5686,7 +5686,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5723,10 +5723,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129319294</v>
+        <v>129319288</v>
       </c>
       <c r="B49" t="n">
-        <v>83017</v>
+        <v>79044</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5734,21 +5734,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>540974</v>
+        <v>540915</v>
       </c>
       <c r="R49" t="n">
-        <v>7193351</v>
+        <v>7193185</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5830,10 +5830,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129319366</v>
+        <v>129319335</v>
       </c>
       <c r="B50" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5841,21 +5841,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5865,10 +5865,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>540738</v>
+        <v>540655</v>
       </c>
       <c r="R50" t="n">
-        <v>7193503</v>
+        <v>7193534</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5900,7 +5900,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5910,7 +5910,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5937,32 +5937,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129319356</v>
+        <v>129319280</v>
       </c>
       <c r="B51" t="n">
-        <v>80149</v>
+        <v>95942</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>2809</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5972,10 +5972,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>540726</v>
+        <v>540900</v>
       </c>
       <c r="R51" t="n">
-        <v>7193540</v>
+        <v>7193073</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6044,32 +6044,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129319280</v>
+        <v>129319366</v>
       </c>
       <c r="B52" t="n">
-        <v>95938</v>
+        <v>80149</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2809</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6079,10 +6079,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>540900</v>
+        <v>540738</v>
       </c>
       <c r="R52" t="n">
-        <v>7193073</v>
+        <v>7193503</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6124,7 +6124,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6151,10 +6151,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129319335</v>
+        <v>129319356</v>
       </c>
       <c r="B53" t="n">
-        <v>80150</v>
+        <v>80149</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6162,21 +6162,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6186,10 +6186,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>540655</v>
+        <v>540726</v>
       </c>
       <c r="R53" t="n">
-        <v>7193534</v>
+        <v>7193540</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6221,7 +6221,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6258,10 +6258,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129319429</v>
+        <v>129319304</v>
       </c>
       <c r="B54" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6269,21 +6269,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6293,10 +6293,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>540972</v>
+        <v>540962</v>
       </c>
       <c r="R54" t="n">
-        <v>7193067</v>
+        <v>7193388</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6328,7 +6328,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6338,7 +6338,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6365,7 +6365,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129319417</v>
+        <v>129319429</v>
       </c>
       <c r="B55" t="n">
         <v>80150</v>
@@ -6400,10 +6400,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>540989</v>
+        <v>540972</v>
       </c>
       <c r="R55" t="n">
-        <v>7193132</v>
+        <v>7193067</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6435,7 +6435,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6445,7 +6445,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6472,10 +6472,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129319388</v>
+        <v>129319417</v>
       </c>
       <c r="B56" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6483,48 +6483,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>540828</v>
+        <v>540989</v>
       </c>
       <c r="R56" t="n">
-        <v>7193425</v>
+        <v>7193132</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6556,7 +6542,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6566,7 +6552,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6593,10 +6579,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129319304</v>
+        <v>129319388</v>
       </c>
       <c r="B57" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6604,34 +6590,48 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>540962</v>
+        <v>540828</v>
       </c>
       <c r="R57" t="n">
-        <v>7193388</v>
+        <v>7193425</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6673,7 +6673,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6700,10 +6700,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129319353</v>
+        <v>129319292</v>
       </c>
       <c r="B58" t="n">
-        <v>82878</v>
+        <v>79044</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6711,21 +6711,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6735,10 +6735,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>540721</v>
+        <v>540996</v>
       </c>
       <c r="R58" t="n">
-        <v>7193542</v>
+        <v>7193327</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6807,10 +6807,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129319279</v>
+        <v>129319392</v>
       </c>
       <c r="B59" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6818,21 +6818,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6842,10 +6842,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>540872</v>
+        <v>540826</v>
       </c>
       <c r="R59" t="n">
-        <v>7193070</v>
+        <v>7193294</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6877,7 +6877,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6914,10 +6914,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129319339</v>
+        <v>129319353</v>
       </c>
       <c r="B60" t="n">
-        <v>80150</v>
+        <v>82878</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6925,21 +6925,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6949,7 +6949,7 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>540669</v>
+        <v>540721</v>
       </c>
       <c r="R60" t="n">
         <v>7193542</v>
@@ -6984,7 +6984,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6994,7 +6994,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7021,10 +7021,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129319311</v>
+        <v>129319279</v>
       </c>
       <c r="B61" t="n">
-        <v>91541</v>
+        <v>80150</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7032,21 +7032,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7056,10 +7056,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>540830</v>
+        <v>540872</v>
       </c>
       <c r="R61" t="n">
-        <v>7193366</v>
+        <v>7193070</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7091,7 +7091,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7128,10 +7128,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129319372</v>
+        <v>129319339</v>
       </c>
       <c r="B62" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7139,21 +7139,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7163,10 +7163,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>540736</v>
+        <v>540669</v>
       </c>
       <c r="R62" t="n">
-        <v>7193500</v>
+        <v>7193542</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7208,7 +7208,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7235,32 +7235,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129319330</v>
+        <v>129319311</v>
       </c>
       <c r="B63" t="n">
-        <v>82995</v>
+        <v>91545</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6439</v>
+        <v>1108</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7270,10 +7270,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>540683</v>
+        <v>540830</v>
       </c>
       <c r="R63" t="n">
-        <v>7193545</v>
+        <v>7193366</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7305,7 +7305,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7342,32 +7342,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129319292</v>
+        <v>129319330</v>
       </c>
       <c r="B64" t="n">
-        <v>79044</v>
+        <v>82995</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7377,10 +7377,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>540996</v>
+        <v>540683</v>
       </c>
       <c r="R64" t="n">
-        <v>7193327</v>
+        <v>7193545</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7449,10 +7449,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129319392</v>
+        <v>129319372</v>
       </c>
       <c r="B65" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7460,21 +7460,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7484,10 +7484,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>540826</v>
+        <v>540736</v>
       </c>
       <c r="R65" t="n">
-        <v>7193294</v>
+        <v>7193500</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7519,7 +7519,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7529,7 +7529,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7672,32 +7672,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129319421</v>
+        <v>129319334</v>
       </c>
       <c r="B67" t="n">
-        <v>80178</v>
+        <v>80149</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7707,10 +7707,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>540981</v>
+        <v>540674</v>
       </c>
       <c r="R67" t="n">
-        <v>7193140</v>
+        <v>7193550</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7742,7 +7742,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7752,7 +7752,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7779,32 +7779,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129319334</v>
+        <v>129319370</v>
       </c>
       <c r="B68" t="n">
-        <v>80149</v>
+        <v>80178</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7814,10 +7814,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>540674</v>
+        <v>540737</v>
       </c>
       <c r="R68" t="n">
-        <v>7193550</v>
+        <v>7193504</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7849,7 +7849,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7859,7 +7859,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7886,32 +7886,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129319370</v>
+        <v>129319397</v>
       </c>
       <c r="B69" t="n">
-        <v>80178</v>
+        <v>79044</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7921,10 +7921,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>540737</v>
+        <v>540946</v>
       </c>
       <c r="R69" t="n">
-        <v>7193504</v>
+        <v>7193256</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7956,7 +7956,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7966,7 +7966,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7993,10 +7993,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129319293</v>
+        <v>129319400</v>
       </c>
       <c r="B70" t="n">
-        <v>57887</v>
+        <v>79044</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8004,43 +8004,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>540980</v>
+        <v>540943</v>
       </c>
       <c r="R70" t="n">
-        <v>7193345</v>
+        <v>7193233</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8072,7 +8063,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8082,7 +8073,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8109,10 +8100,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129319397</v>
+        <v>129319293</v>
       </c>
       <c r="B71" t="n">
-        <v>79044</v>
+        <v>57887</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8120,34 +8111,43 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>540946</v>
+        <v>540980</v>
       </c>
       <c r="R71" t="n">
-        <v>7193256</v>
+        <v>7193345</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8179,7 +8179,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8189,7 +8189,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8216,32 +8216,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129319400</v>
+        <v>129319421</v>
       </c>
       <c r="B72" t="n">
-        <v>79044</v>
+        <v>80178</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8251,10 +8251,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>540943</v>
+        <v>540981</v>
       </c>
       <c r="R72" t="n">
-        <v>7193233</v>
+        <v>7193140</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8286,7 +8286,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8323,10 +8323,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129319402</v>
+        <v>129319412</v>
       </c>
       <c r="B73" t="n">
-        <v>79044</v>
+        <v>91569</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8334,23 +8334,19 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -8358,10 +8354,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>540936</v>
+        <v>540952</v>
       </c>
       <c r="R73" t="n">
-        <v>7193225</v>
+        <v>7193187</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8393,7 +8389,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8403,7 +8399,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8430,32 +8426,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129319413</v>
+        <v>129319367</v>
       </c>
       <c r="B74" t="n">
-        <v>79044</v>
+        <v>80178</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8465,10 +8461,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>540965</v>
+        <v>540734</v>
       </c>
       <c r="R74" t="n">
-        <v>7193181</v>
+        <v>7193503</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8500,7 +8496,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8510,7 +8506,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8537,10 +8533,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129319412</v>
+        <v>129319402</v>
       </c>
       <c r="B75" t="n">
-        <v>91565</v>
+        <v>79044</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8548,19 +8544,23 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -8568,10 +8568,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>540952</v>
+        <v>540936</v>
       </c>
       <c r="R75" t="n">
-        <v>7193187</v>
+        <v>7193225</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8603,7 +8603,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8613,7 +8613,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8640,32 +8640,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129319367</v>
+        <v>129319413</v>
       </c>
       <c r="B76" t="n">
-        <v>80178</v>
+        <v>79044</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8675,10 +8675,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>540734</v>
+        <v>540965</v>
       </c>
       <c r="R76" t="n">
-        <v>7193503</v>
+        <v>7193181</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8710,7 +8710,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8720,7 +8720,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9724,34 +9724,30 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129319389</v>
+        <v>129319298</v>
       </c>
       <c r="B86" t="n">
-        <v>95938</v>
+        <v>91569</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2809</v>
+        <v>5432</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -9759,10 +9755,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>540818</v>
+        <v>540964</v>
       </c>
       <c r="R86" t="n">
-        <v>7193358</v>
+        <v>7193371</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9794,7 +9790,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9804,7 +9800,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9831,32 +9827,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129319333</v>
+        <v>129319389</v>
       </c>
       <c r="B87" t="n">
-        <v>80150</v>
+        <v>95942</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2081</v>
+        <v>2809</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9866,10 +9862,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>540674</v>
+        <v>540818</v>
       </c>
       <c r="R87" t="n">
-        <v>7193551</v>
+        <v>7193358</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -9901,7 +9897,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9911,7 +9907,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9938,7 +9934,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129319376</v>
+        <v>129319333</v>
       </c>
       <c r="B88" t="n">
         <v>80150</v>
@@ -9973,10 +9969,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>540738</v>
+        <v>540674</v>
       </c>
       <c r="R88" t="n">
-        <v>7193476</v>
+        <v>7193551</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -10008,7 +10004,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10018,7 +10014,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10045,7 +10041,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129319375</v>
+        <v>129319376</v>
       </c>
       <c r="B89" t="n">
         <v>80150</v>
@@ -10080,10 +10076,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>540730</v>
+        <v>540738</v>
       </c>
       <c r="R89" t="n">
-        <v>7193493</v>
+        <v>7193476</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -10115,7 +10111,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10125,7 +10121,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10152,7 +10148,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129319433</v>
+        <v>129319375</v>
       </c>
       <c r="B90" t="n">
         <v>80150</v>
@@ -10187,10 +10183,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>540979</v>
+        <v>540730</v>
       </c>
       <c r="R90" t="n">
-        <v>7193075</v>
+        <v>7193493</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -10222,7 +10218,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10232,7 +10228,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10259,7 +10255,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129319357</v>
+        <v>129319433</v>
       </c>
       <c r="B91" t="n">
         <v>80150</v>
@@ -10294,10 +10290,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>540726</v>
+        <v>540979</v>
       </c>
       <c r="R91" t="n">
-        <v>7193539</v>
+        <v>7193075</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -10329,7 +10325,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10339,7 +10335,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10366,10 +10362,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129319284</v>
+        <v>129319357</v>
       </c>
       <c r="B92" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10377,21 +10373,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10401,10 +10397,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>540867</v>
+        <v>540726</v>
       </c>
       <c r="R92" t="n">
-        <v>7193169</v>
+        <v>7193539</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -10436,7 +10432,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10446,7 +10442,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10473,32 +10469,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129319393</v>
+        <v>129319409</v>
       </c>
       <c r="B93" t="n">
-        <v>82995</v>
+        <v>80149</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6439</v>
+        <v>6458</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10508,10 +10504,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>540824</v>
+        <v>540942</v>
       </c>
       <c r="R93" t="n">
-        <v>7193288</v>
+        <v>7193182</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -10543,7 +10539,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10553,7 +10549,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10580,32 +10576,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129319299</v>
+        <v>129319393</v>
       </c>
       <c r="B94" t="n">
-        <v>79044</v>
+        <v>82995</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10615,10 +10611,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>540964</v>
+        <v>540824</v>
       </c>
       <c r="R94" t="n">
-        <v>7193371</v>
+        <v>7193288</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -10650,7 +10646,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10660,7 +10656,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10687,7 +10683,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129319344</v>
+        <v>129319284</v>
       </c>
       <c r="B95" t="n">
         <v>79044</v>
@@ -10722,10 +10718,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>540650</v>
+        <v>540867</v>
       </c>
       <c r="R95" t="n">
-        <v>7193540</v>
+        <v>7193169</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -10757,7 +10753,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10767,7 +10763,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10794,10 +10790,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129319298</v>
+        <v>129319299</v>
       </c>
       <c r="B96" t="n">
-        <v>91565</v>
+        <v>79044</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10805,19 +10801,23 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -10897,10 +10897,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129319409</v>
+        <v>129319344</v>
       </c>
       <c r="B97" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10908,21 +10908,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10932,10 +10932,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>540942</v>
+        <v>540650</v>
       </c>
       <c r="R97" t="n">
-        <v>7193182</v>
+        <v>7193540</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -10967,7 +10967,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10977,7 +10977,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11004,10 +11004,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129319359</v>
+        <v>129319445</v>
       </c>
       <c r="B98" t="n">
-        <v>80149</v>
+        <v>57724</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11015,34 +11015,43 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>540725</v>
+        <v>541052</v>
       </c>
       <c r="R98" t="n">
-        <v>7193537</v>
+        <v>7193255</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -11074,7 +11083,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11084,7 +11093,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11111,10 +11120,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129319399</v>
+        <v>129319359</v>
       </c>
       <c r="B99" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11122,21 +11131,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11146,10 +11155,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>540945</v>
+        <v>540725</v>
       </c>
       <c r="R99" t="n">
-        <v>7193248</v>
+        <v>7193537</v>
       </c>
       <c r="S99" t="n">
         <v>25</v>
@@ -11181,7 +11190,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11191,7 +11200,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11218,7 +11227,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129319308</v>
+        <v>129319399</v>
       </c>
       <c r="B100" t="n">
         <v>79044</v>
@@ -11253,10 +11262,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>540907</v>
+        <v>540945</v>
       </c>
       <c r="R100" t="n">
-        <v>7193409</v>
+        <v>7193248</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -11288,7 +11297,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11298,7 +11307,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11325,7 +11334,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129319362</v>
+        <v>129319308</v>
       </c>
       <c r="B101" t="n">
         <v>79044</v>
@@ -11360,10 +11369,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>540721</v>
+        <v>540907</v>
       </c>
       <c r="R101" t="n">
-        <v>7193527</v>
+        <v>7193409</v>
       </c>
       <c r="S101" t="n">
         <v>25</v>
@@ -11395,7 +11404,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11405,7 +11414,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11432,7 +11441,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129319306</v>
+        <v>129319362</v>
       </c>
       <c r="B102" t="n">
         <v>79044</v>
@@ -11467,10 +11476,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>540961</v>
+        <v>540721</v>
       </c>
       <c r="R102" t="n">
-        <v>7193398</v>
+        <v>7193527</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -11502,7 +11511,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11512,7 +11521,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11539,7 +11548,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129319286</v>
+        <v>129319306</v>
       </c>
       <c r="B103" t="n">
         <v>79044</v>
@@ -11574,10 +11583,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>540891</v>
+        <v>540961</v>
       </c>
       <c r="R103" t="n">
-        <v>7193174</v>
+        <v>7193398</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -11609,7 +11618,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11619,7 +11628,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11646,10 +11655,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129319445</v>
+        <v>129319286</v>
       </c>
       <c r="B104" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11657,43 +11666,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>541052</v>
+        <v>540891</v>
       </c>
       <c r="R104" t="n">
-        <v>7193255</v>
+        <v>7193174</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -11725,7 +11725,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11735,7 +11735,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11872,7 +11872,7 @@
         <v>129319360</v>
       </c>
       <c r="B106" t="n">
-        <v>91541</v>
+        <v>91545</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12618,10 +12618,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129319305</v>
+        <v>129319309</v>
       </c>
       <c r="B113" t="n">
-        <v>91565</v>
+        <v>79044</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12629,19 +12629,23 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
@@ -12649,10 +12653,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>540959</v>
+        <v>540894</v>
       </c>
       <c r="R113" t="n">
-        <v>7193395</v>
+        <v>7193411</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -12684,7 +12688,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12694,7 +12698,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12721,32 +12725,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129319425</v>
+        <v>129319426</v>
       </c>
       <c r="B114" t="n">
-        <v>80184</v>
+        <v>80150</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12756,10 +12760,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>540980</v>
+        <v>540979</v>
       </c>
       <c r="R114" t="n">
-        <v>7193116</v>
+        <v>7193115</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -12828,10 +12832,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129319309</v>
+        <v>129319341</v>
       </c>
       <c r="B115" t="n">
-        <v>79044</v>
+        <v>91545</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12839,21 +12843,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12863,10 +12867,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>540894</v>
+        <v>540670</v>
       </c>
       <c r="R115" t="n">
-        <v>7193411</v>
+        <v>7193533</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -12898,7 +12902,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12908,7 +12912,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12935,10 +12939,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129319332</v>
+        <v>129319305</v>
       </c>
       <c r="B116" t="n">
-        <v>57887</v>
+        <v>91569</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12946,43 +12950,30 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>540675</v>
+        <v>540959</v>
       </c>
       <c r="R116" t="n">
-        <v>7193538</v>
+        <v>7193395</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -13014,7 +13005,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13024,7 +13015,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13051,32 +13042,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129319426</v>
+        <v>129319425</v>
       </c>
       <c r="B117" t="n">
-        <v>80150</v>
+        <v>80184</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13086,10 +13077,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>540979</v>
+        <v>540980</v>
       </c>
       <c r="R117" t="n">
-        <v>7193115</v>
+        <v>7193116</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -13158,10 +13149,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129319341</v>
+        <v>129319332</v>
       </c>
       <c r="B118" t="n">
-        <v>91541</v>
+        <v>57887</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13169,34 +13160,43 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>540670</v>
+        <v>540675</v>
       </c>
       <c r="R118" t="n">
-        <v>7193533</v>
+        <v>7193538</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -13228,7 +13228,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13238,7 +13238,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13268,7 +13268,7 @@
         <v>129319329</v>
       </c>
       <c r="B119" t="n">
-        <v>88945</v>
+        <v>88949</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13372,32 +13372,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129319416</v>
+        <v>129319325</v>
       </c>
       <c r="B120" t="n">
-        <v>80185</v>
+        <v>80150</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13407,10 +13407,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>540970</v>
+        <v>540714</v>
       </c>
       <c r="R120" t="n">
-        <v>7193154</v>
+        <v>7193488</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -13442,7 +13442,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13452,7 +13452,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13479,32 +13479,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129319373</v>
+        <v>129319319</v>
       </c>
       <c r="B121" t="n">
-        <v>80185</v>
+        <v>80150</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13514,10 +13514,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>540734</v>
+        <v>540719</v>
       </c>
       <c r="R121" t="n">
-        <v>7193499</v>
+        <v>7193463</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -13549,7 +13549,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13559,7 +13559,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13586,10 +13586,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129319321</v>
+        <v>129319416</v>
       </c>
       <c r="B122" t="n">
-        <v>80178</v>
+        <v>80185</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13597,21 +13597,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13621,10 +13621,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>540719</v>
+        <v>540970</v>
       </c>
       <c r="R122" t="n">
-        <v>7193463</v>
+        <v>7193154</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -13656,7 +13656,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13666,7 +13666,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13693,45 +13693,54 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129319350</v>
+        <v>129319363</v>
       </c>
       <c r="B123" t="n">
-        <v>80149</v>
+        <v>58360</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6458</v>
+        <v>102125</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>540681</v>
+        <v>540731</v>
       </c>
       <c r="R123" t="n">
-        <v>7193521</v>
+        <v>7193512</v>
       </c>
       <c r="S123" t="n">
         <v>25</v>
@@ -13763,7 +13772,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13773,7 +13782,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13800,27 +13809,27 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129319363</v>
+        <v>129319410</v>
       </c>
       <c r="B124" t="n">
-        <v>58360</v>
+        <v>56908</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>102125</v>
+        <v>102612</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -13830,12 +13839,12 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
@@ -13844,10 +13853,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>540731</v>
+        <v>540946</v>
       </c>
       <c r="R124" t="n">
-        <v>7193512</v>
+        <v>7193171</v>
       </c>
       <c r="S124" t="n">
         <v>25</v>
@@ -13879,7 +13888,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13889,7 +13898,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13916,54 +13925,45 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129319410</v>
+        <v>129319373</v>
       </c>
       <c r="B125" t="n">
-        <v>56908</v>
+        <v>80185</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>102612</v>
+        <v>6464</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>540946</v>
+        <v>540734</v>
       </c>
       <c r="R125" t="n">
-        <v>7193171</v>
+        <v>7193499</v>
       </c>
       <c r="S125" t="n">
         <v>25</v>
@@ -13995,7 +13995,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14005,7 +14005,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14032,32 +14032,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129319277</v>
+        <v>129319321</v>
       </c>
       <c r="B126" t="n">
-        <v>80150</v>
+        <v>80178</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14067,10 +14067,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>540837</v>
+        <v>540719</v>
       </c>
       <c r="R126" t="n">
-        <v>7193042</v>
+        <v>7193463</v>
       </c>
       <c r="S126" t="n">
         <v>25</v>
@@ -14102,7 +14102,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14112,7 +14112,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14139,10 +14139,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129319325</v>
+        <v>129319350</v>
       </c>
       <c r="B127" t="n">
-        <v>80150</v>
+        <v>80149</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14150,21 +14150,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14174,10 +14174,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>540714</v>
+        <v>540681</v>
       </c>
       <c r="R127" t="n">
-        <v>7193488</v>
+        <v>7193521</v>
       </c>
       <c r="S127" t="n">
         <v>25</v>
@@ -14209,7 +14209,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14219,7 +14219,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14246,7 +14246,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129319319</v>
+        <v>129319277</v>
       </c>
       <c r="B128" t="n">
         <v>80150</v>
@@ -14281,10 +14281,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>540719</v>
+        <v>540837</v>
       </c>
       <c r="R128" t="n">
-        <v>7193463</v>
+        <v>7193042</v>
       </c>
       <c r="S128" t="n">
         <v>25</v>
@@ -14316,7 +14316,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14326,7 +14326,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14353,10 +14353,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129319379</v>
+        <v>129319326</v>
       </c>
       <c r="B129" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14364,21 +14364,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14388,10 +14388,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>540761</v>
+        <v>540701</v>
       </c>
       <c r="R129" t="n">
-        <v>7193485</v>
+        <v>7193533</v>
       </c>
       <c r="S129" t="n">
         <v>25</v>
@@ -14423,7 +14423,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14433,7 +14433,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14460,7 +14460,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129319326</v>
+        <v>129319434</v>
       </c>
       <c r="B130" t="n">
         <v>80149</v>
@@ -14495,10 +14495,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>540701</v>
+        <v>540979</v>
       </c>
       <c r="R130" t="n">
-        <v>7193533</v>
+        <v>7193075</v>
       </c>
       <c r="S130" t="n">
         <v>25</v>
@@ -14530,7 +14530,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14540,7 +14540,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14567,10 +14567,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129319434</v>
+        <v>129319379</v>
       </c>
       <c r="B131" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14578,21 +14578,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14602,10 +14602,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>540979</v>
+        <v>540761</v>
       </c>
       <c r="R131" t="n">
-        <v>7193075</v>
+        <v>7193485</v>
       </c>
       <c r="S131" t="n">
         <v>25</v>
@@ -14637,7 +14637,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14647,7 +14647,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14674,32 +14674,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129319380</v>
+        <v>129319322</v>
       </c>
       <c r="B132" t="n">
-        <v>92263</v>
+        <v>80150</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>3298</v>
+        <v>2081</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14709,10 +14709,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>540761</v>
+        <v>540719</v>
       </c>
       <c r="R132" t="n">
-        <v>7193490</v>
+        <v>7193483</v>
       </c>
       <c r="S132" t="n">
         <v>25</v>
@@ -14744,7 +14744,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14754,7 +14754,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14781,32 +14781,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129319378</v>
+        <v>129319312</v>
       </c>
       <c r="B133" t="n">
-        <v>82997</v>
+        <v>80150</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>306</v>
+        <v>2081</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14816,10 +14816,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>540757</v>
+        <v>540789</v>
       </c>
       <c r="R133" t="n">
-        <v>7193474</v>
+        <v>7193373</v>
       </c>
       <c r="S133" t="n">
         <v>25</v>
@@ -14851,7 +14851,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14861,7 +14861,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14888,10 +14888,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129319322</v>
+        <v>129319343</v>
       </c>
       <c r="B134" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14899,34 +14899,39 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>540719</v>
+        <v>540661</v>
       </c>
       <c r="R134" t="n">
-        <v>7193483</v>
+        <v>7193538</v>
       </c>
       <c r="S134" t="n">
         <v>25</v>
@@ -14958,7 +14963,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14968,7 +14973,12 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>Färska och äldre spår på samma träd.</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14995,32 +15005,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129319312</v>
+        <v>129319378</v>
       </c>
       <c r="B135" t="n">
-        <v>80150</v>
+        <v>82997</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>2081</v>
+        <v>306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15030,10 +15040,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>540789</v>
+        <v>540757</v>
       </c>
       <c r="R135" t="n">
-        <v>7193373</v>
+        <v>7193474</v>
       </c>
       <c r="S135" t="n">
         <v>25</v>
@@ -15065,7 +15075,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15075,7 +15085,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15102,50 +15112,45 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129319343</v>
+        <v>129319380</v>
       </c>
       <c r="B136" t="n">
-        <v>57727</v>
+        <v>92267</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>540661</v>
+        <v>540761</v>
       </c>
       <c r="R136" t="n">
-        <v>7193538</v>
+        <v>7193490</v>
       </c>
       <c r="S136" t="n">
         <v>25</v>
@@ -15177,7 +15182,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15187,12 +15192,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>11:27</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>Färska och äldre spår på samma träd.</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15433,32 +15433,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129319315</v>
+        <v>129319406</v>
       </c>
       <c r="B139" t="n">
-        <v>82995</v>
+        <v>79123</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6439</v>
+        <v>864</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15468,10 +15468,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>540765</v>
+        <v>540938</v>
       </c>
       <c r="R139" t="n">
-        <v>7193370</v>
+        <v>7193168</v>
       </c>
       <c r="S139" t="n">
         <v>25</v>
@@ -15503,7 +15503,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15513,7 +15513,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15540,10 +15540,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129319327</v>
+        <v>129319428</v>
       </c>
       <c r="B140" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15551,21 +15551,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15575,10 +15575,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>540693</v>
+        <v>540971</v>
       </c>
       <c r="R140" t="n">
-        <v>7193540</v>
+        <v>7193081</v>
       </c>
       <c r="S140" t="n">
         <v>25</v>
@@ -15610,7 +15610,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15620,7 +15620,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15647,10 +15647,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129319287</v>
+        <v>129319315</v>
       </c>
       <c r="B141" t="n">
-        <v>92263</v>
+        <v>82995</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15658,21 +15658,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>3298</v>
+        <v>6439</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15682,10 +15682,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>540913</v>
+        <v>540765</v>
       </c>
       <c r="R141" t="n">
-        <v>7193185</v>
+        <v>7193370</v>
       </c>
       <c r="S141" t="n">
         <v>25</v>
@@ -15717,7 +15717,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15727,7 +15727,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15754,10 +15754,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129319406</v>
+        <v>129319327</v>
       </c>
       <c r="B142" t="n">
-        <v>79123</v>
+        <v>79044</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15765,21 +15765,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15789,10 +15789,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>540938</v>
+        <v>540693</v>
       </c>
       <c r="R142" t="n">
-        <v>7193168</v>
+        <v>7193540</v>
       </c>
       <c r="S142" t="n">
         <v>25</v>
@@ -15824,7 +15824,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15861,32 +15861,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129319428</v>
+        <v>129319287</v>
       </c>
       <c r="B143" t="n">
-        <v>80149</v>
+        <v>92267</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6458</v>
+        <v>3298</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15896,10 +15896,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>540971</v>
+        <v>540913</v>
       </c>
       <c r="R143" t="n">
-        <v>7193081</v>
+        <v>7193185</v>
       </c>
       <c r="S143" t="n">
         <v>25</v>
@@ -15931,7 +15931,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15941,7 +15941,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD143" t="b">

--- a/artfynd/A 51086-2025 artfynd.xlsx
+++ b/artfynd/A 51086-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129319386</v>
+        <v>129319285</v>
       </c>
       <c r="B2" t="n">
-        <v>95942</v>
+        <v>91546</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2809</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540774</v>
+        <v>540886</v>
       </c>
       <c r="R2" t="n">
-        <v>7193457</v>
+        <v>7193172</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,7 +785,7 @@
         <v>129319307</v>
       </c>
       <c r="B3" t="n">
-        <v>91545</v>
+        <v>91546</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,45 +889,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129319285</v>
+        <v>129319414</v>
       </c>
       <c r="B4" t="n">
-        <v>91545</v>
+        <v>58360</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>102125</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540886</v>
+        <v>540963</v>
       </c>
       <c r="R4" t="n">
-        <v>7193172</v>
+        <v>7193203</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -959,7 +968,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +978,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,45 +1005,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129319323</v>
+        <v>129319300</v>
       </c>
       <c r="B5" t="n">
-        <v>80185</v>
+        <v>57727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540719</v>
+        <v>540961</v>
       </c>
       <c r="R5" t="n">
-        <v>7193483</v>
+        <v>7193376</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1066,7 +1080,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1090,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129319420</v>
+        <v>129319384</v>
       </c>
       <c r="B6" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,21 +1128,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540982</v>
+        <v>540775</v>
       </c>
       <c r="R6" t="n">
-        <v>7193144</v>
+        <v>7193467</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1173,7 +1187,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1197,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1224,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129319384</v>
+        <v>129319302</v>
       </c>
       <c r="B7" t="n">
         <v>79044</v>
@@ -1245,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540775</v>
+        <v>540960</v>
       </c>
       <c r="R7" t="n">
-        <v>7193467</v>
+        <v>7193375</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1280,7 +1294,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1304,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,32 +1331,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129319302</v>
+        <v>129319323</v>
       </c>
       <c r="B8" t="n">
-        <v>79044</v>
+        <v>80185</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1366,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540960</v>
+        <v>540719</v>
       </c>
       <c r="R8" t="n">
-        <v>7193375</v>
+        <v>7193483</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1387,7 +1401,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1411,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,54 +1438,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129319414</v>
+        <v>129319420</v>
       </c>
       <c r="B9" t="n">
-        <v>58360</v>
+        <v>80149</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102125</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540963</v>
+        <v>540982</v>
       </c>
       <c r="R9" t="n">
-        <v>7193203</v>
+        <v>7193144</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1503,7 +1508,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1513,7 +1518,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1540,50 +1545,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129319300</v>
+        <v>129319386</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>95950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>2809</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540961</v>
+        <v>540774</v>
       </c>
       <c r="R10" t="n">
-        <v>7193376</v>
+        <v>7193457</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1615,7 +1615,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1652,10 +1652,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129319296</v>
+        <v>129319381</v>
       </c>
       <c r="B11" t="n">
-        <v>79044</v>
+        <v>82878</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1663,21 +1663,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540970</v>
+        <v>540758</v>
       </c>
       <c r="R11" t="n">
-        <v>7193365</v>
+        <v>7193475</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1759,10 +1759,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129319352</v>
+        <v>129319424</v>
       </c>
       <c r="B12" t="n">
-        <v>78057</v>
+        <v>80150</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1770,21 +1770,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228579</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1794,10 +1794,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540715</v>
+        <v>540975</v>
       </c>
       <c r="R12" t="n">
-        <v>7193537</v>
+        <v>7193139</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1829,7 +1829,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1866,32 +1866,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129319295</v>
+        <v>129319361</v>
       </c>
       <c r="B13" t="n">
-        <v>95942</v>
+        <v>91550</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2809</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1901,10 +1901,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540972</v>
+        <v>540726</v>
       </c>
       <c r="R13" t="n">
-        <v>7193357</v>
+        <v>7193531</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1973,32 +1973,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129319361</v>
+        <v>129319295</v>
       </c>
       <c r="B14" t="n">
-        <v>91549</v>
+        <v>95950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>2809</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2008,10 +2008,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540726</v>
+        <v>540972</v>
       </c>
       <c r="R14" t="n">
-        <v>7193531</v>
+        <v>7193357</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2080,10 +2080,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129319424</v>
+        <v>129319328</v>
       </c>
       <c r="B15" t="n">
-        <v>80150</v>
+        <v>80149</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2091,21 +2091,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540975</v>
+        <v>540693</v>
       </c>
       <c r="R15" t="n">
-        <v>7193139</v>
+        <v>7193540</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2187,10 +2187,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129319381</v>
+        <v>129319296</v>
       </c>
       <c r="B16" t="n">
-        <v>82878</v>
+        <v>79044</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2198,21 +2198,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2222,10 +2222,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540758</v>
+        <v>540970</v>
       </c>
       <c r="R16" t="n">
-        <v>7193475</v>
+        <v>7193365</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2294,45 +2294,54 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129319419</v>
+        <v>129319438</v>
       </c>
       <c r="B17" t="n">
-        <v>80184</v>
+        <v>57887</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6463</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540986</v>
+        <v>540982</v>
       </c>
       <c r="R17" t="n">
-        <v>7193130</v>
+        <v>7193110</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2364,7 +2373,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2374,7 +2383,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2401,10 +2410,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129319328</v>
+        <v>129319352</v>
       </c>
       <c r="B18" t="n">
-        <v>80149</v>
+        <v>78057</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2412,21 +2421,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2436,10 +2445,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540693</v>
+        <v>540715</v>
       </c>
       <c r="R18" t="n">
-        <v>7193540</v>
+        <v>7193537</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2471,7 +2480,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2481,7 +2490,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2508,32 +2517,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129319324</v>
+        <v>129319419</v>
       </c>
       <c r="B19" t="n">
-        <v>80149</v>
+        <v>80184</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2543,10 +2552,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540719</v>
+        <v>540986</v>
       </c>
       <c r="R19" t="n">
-        <v>7193483</v>
+        <v>7193130</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2578,7 +2587,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2588,7 +2597,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2615,10 +2624,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129319430</v>
+        <v>129319313</v>
       </c>
       <c r="B20" t="n">
-        <v>80184</v>
+        <v>80185</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2626,21 +2635,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2650,10 +2659,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540971</v>
+        <v>540789</v>
       </c>
       <c r="R20" t="n">
-        <v>7193066</v>
+        <v>7193372</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2685,7 +2694,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2695,7 +2704,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2722,32 +2731,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129319313</v>
+        <v>129319324</v>
       </c>
       <c r="B21" t="n">
-        <v>80185</v>
+        <v>80149</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2757,10 +2766,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540789</v>
+        <v>540719</v>
       </c>
       <c r="R21" t="n">
-        <v>7193372</v>
+        <v>7193483</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2792,7 +2801,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2802,7 +2811,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2829,54 +2838,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129319438</v>
+        <v>129319430</v>
       </c>
       <c r="B22" t="n">
-        <v>57887</v>
+        <v>80184</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>6463</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540982</v>
+        <v>540971</v>
       </c>
       <c r="R22" t="n">
-        <v>7193110</v>
+        <v>7193066</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2945,10 +2945,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129319349</v>
+        <v>129319316</v>
       </c>
       <c r="B23" t="n">
-        <v>91569</v>
+        <v>80150</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2956,19 +2956,23 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2976,10 +2980,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540670</v>
+        <v>540763</v>
       </c>
       <c r="R23" t="n">
-        <v>7193521</v>
+        <v>7193372</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3011,7 +3015,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3021,7 +3025,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3048,10 +3052,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129319390</v>
+        <v>129319281</v>
       </c>
       <c r="B24" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3059,21 +3063,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3083,10 +3087,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540818</v>
+        <v>540902</v>
       </c>
       <c r="R24" t="n">
-        <v>7193358</v>
+        <v>7193083</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3118,7 +3122,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3128,7 +3132,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3155,10 +3159,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129319383</v>
+        <v>129319291</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3166,21 +3170,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3190,10 +3194,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540764</v>
+        <v>540996</v>
       </c>
       <c r="R25" t="n">
-        <v>7193475</v>
+        <v>7193327</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3225,7 +3229,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3235,7 +3239,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3262,10 +3266,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129319354</v>
+        <v>129319340</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>91550</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3273,21 +3277,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3297,10 +3301,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540722</v>
+        <v>540666</v>
       </c>
       <c r="R26" t="n">
-        <v>7193542</v>
+        <v>7193537</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3332,7 +3336,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3342,7 +3346,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3369,10 +3373,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129319281</v>
+        <v>129319349</v>
       </c>
       <c r="B27" t="n">
-        <v>80150</v>
+        <v>91570</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3380,23 +3384,19 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3404,10 +3404,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>540902</v>
+        <v>540670</v>
       </c>
       <c r="R27" t="n">
-        <v>7193083</v>
+        <v>7193521</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3439,7 +3439,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3476,10 +3476,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129319316</v>
+        <v>129319390</v>
       </c>
       <c r="B28" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3487,21 +3487,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>540763</v>
+        <v>540818</v>
       </c>
       <c r="R28" t="n">
-        <v>7193372</v>
+        <v>7193358</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3583,10 +3583,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129319291</v>
+        <v>129319383</v>
       </c>
       <c r="B29" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3594,21 +3594,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3618,10 +3618,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>540996</v>
+        <v>540764</v>
       </c>
       <c r="R29" t="n">
-        <v>7193327</v>
+        <v>7193475</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3653,7 +3653,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3690,10 +3690,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129319340</v>
+        <v>129319354</v>
       </c>
       <c r="B30" t="n">
-        <v>91549</v>
+        <v>79044</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3701,21 +3701,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3725,10 +3725,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>540666</v>
+        <v>540722</v>
       </c>
       <c r="R30" t="n">
-        <v>7193537</v>
+        <v>7193542</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3760,7 +3760,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3797,10 +3797,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129319404</v>
+        <v>129319377</v>
       </c>
       <c r="B31" t="n">
-        <v>78057</v>
+        <v>80150</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3808,21 +3808,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228579</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>540931</v>
+        <v>540745</v>
       </c>
       <c r="R31" t="n">
-        <v>7193220</v>
+        <v>7193494</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3867,7 +3867,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4011,10 +4011,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129319377</v>
+        <v>129319337</v>
       </c>
       <c r="B33" t="n">
-        <v>80150</v>
+        <v>80149</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4022,21 +4022,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4046,10 +4046,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>540745</v>
+        <v>540676</v>
       </c>
       <c r="R33" t="n">
-        <v>7193494</v>
+        <v>7193539</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4081,7 +4081,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4118,32 +4118,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129319337</v>
+        <v>129319422</v>
       </c>
       <c r="B34" t="n">
-        <v>80149</v>
+        <v>80184</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4153,10 +4153,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>540676</v>
+        <v>540980</v>
       </c>
       <c r="R34" t="n">
-        <v>7193539</v>
+        <v>7193139</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4225,32 +4225,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129319422</v>
+        <v>129319404</v>
       </c>
       <c r="B35" t="n">
-        <v>80184</v>
+        <v>78057</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6463</v>
+        <v>228579</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4260,10 +4260,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>540980</v>
+        <v>540931</v>
       </c>
       <c r="R35" t="n">
-        <v>7193139</v>
+        <v>7193220</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4295,7 +4295,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4305,7 +4305,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4332,10 +4332,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129319405</v>
+        <v>129319396</v>
       </c>
       <c r="B36" t="n">
-        <v>83012</v>
+        <v>79044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4343,21 +4343,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4367,10 +4367,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>540931</v>
+        <v>540928</v>
       </c>
       <c r="R36" t="n">
-        <v>7193220</v>
+        <v>7193263</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4402,7 +4402,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4439,7 +4439,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129319396</v>
+        <v>129319427</v>
       </c>
       <c r="B37" t="n">
         <v>79044</v>
@@ -4474,10 +4474,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>540928</v>
+        <v>540969</v>
       </c>
       <c r="R37" t="n">
-        <v>7193263</v>
+        <v>7193117</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4546,7 +4546,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129319427</v>
+        <v>129319282</v>
       </c>
       <c r="B38" t="n">
         <v>79044</v>
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>540969</v>
+        <v>540901</v>
       </c>
       <c r="R38" t="n">
-        <v>7193117</v>
+        <v>7193084</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4653,10 +4653,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129319282</v>
+        <v>129319405</v>
       </c>
       <c r="B39" t="n">
-        <v>79044</v>
+        <v>83012</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4664,21 +4664,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4688,10 +4688,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>540901</v>
+        <v>540931</v>
       </c>
       <c r="R39" t="n">
-        <v>7193084</v>
+        <v>7193220</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4760,32 +4760,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129319395</v>
+        <v>129319303</v>
       </c>
       <c r="B40" t="n">
-        <v>82997</v>
+        <v>79044</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>306</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>540878</v>
+        <v>540934</v>
       </c>
       <c r="R40" t="n">
-        <v>7193291</v>
+        <v>7193385</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4840,7 +4840,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4867,10 +4867,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129319278</v>
+        <v>129319348</v>
       </c>
       <c r="B41" t="n">
-        <v>80150</v>
+        <v>80149</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4878,21 +4878,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>540864</v>
+        <v>540653</v>
       </c>
       <c r="R41" t="n">
-        <v>7193066</v>
+        <v>7193521</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4947,7 +4947,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4974,10 +4974,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129319365</v>
+        <v>129319288</v>
       </c>
       <c r="B42" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4985,21 +4985,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>540738</v>
+        <v>540915</v>
       </c>
       <c r="R42" t="n">
-        <v>7193503</v>
+        <v>7193185</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5081,32 +5081,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129319294</v>
+        <v>129319395</v>
       </c>
       <c r="B43" t="n">
-        <v>83017</v>
+        <v>82997</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1467</v>
+        <v>306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5116,10 +5116,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540974</v>
+        <v>540878</v>
       </c>
       <c r="R43" t="n">
-        <v>7193351</v>
+        <v>7193291</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5188,10 +5188,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129319348</v>
+        <v>129319278</v>
       </c>
       <c r="B44" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5199,21 +5199,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540653</v>
+        <v>540864</v>
       </c>
       <c r="R44" t="n">
-        <v>7193521</v>
+        <v>7193066</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5295,32 +5295,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129319401</v>
+        <v>129319294</v>
       </c>
       <c r="B45" t="n">
-        <v>80178</v>
+        <v>83017</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6462</v>
+        <v>1467</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5330,10 +5330,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>540942</v>
+        <v>540974</v>
       </c>
       <c r="R45" t="n">
-        <v>7193229</v>
+        <v>7193351</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5365,7 +5365,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5375,7 +5375,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5402,10 +5402,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129319403</v>
+        <v>129319365</v>
       </c>
       <c r="B46" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5413,21 +5413,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5437,10 +5437,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>540930</v>
+        <v>540738</v>
       </c>
       <c r="R46" t="n">
-        <v>7193219</v>
+        <v>7193503</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5472,7 +5472,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5509,10 +5509,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129319320</v>
+        <v>129319401</v>
       </c>
       <c r="B47" t="n">
-        <v>80184</v>
+        <v>80178</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5520,21 +5520,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5544,10 +5544,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>540719</v>
+        <v>540942</v>
       </c>
       <c r="R47" t="n">
-        <v>7193463</v>
+        <v>7193229</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5579,7 +5579,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5616,10 +5616,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129319303</v>
+        <v>129319403</v>
       </c>
       <c r="B48" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5627,21 +5627,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5651,10 +5651,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>540934</v>
+        <v>540930</v>
       </c>
       <c r="R48" t="n">
-        <v>7193385</v>
+        <v>7193219</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5686,7 +5686,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5723,27 +5723,27 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129319288</v>
+        <v>129319320</v>
       </c>
       <c r="B49" t="n">
-        <v>79044</v>
+        <v>80184</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>540915</v>
+        <v>540719</v>
       </c>
       <c r="R49" t="n">
-        <v>7193185</v>
+        <v>7193463</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5830,10 +5830,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129319335</v>
+        <v>129319366</v>
       </c>
       <c r="B50" t="n">
-        <v>80150</v>
+        <v>80149</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5841,21 +5841,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5865,10 +5865,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>540655</v>
+        <v>540738</v>
       </c>
       <c r="R50" t="n">
-        <v>7193534</v>
+        <v>7193503</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5900,7 +5900,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5910,7 +5910,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5937,32 +5937,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129319280</v>
+        <v>129319356</v>
       </c>
       <c r="B51" t="n">
-        <v>95942</v>
+        <v>80149</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2809</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5972,10 +5972,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>540900</v>
+        <v>540726</v>
       </c>
       <c r="R51" t="n">
-        <v>7193073</v>
+        <v>7193540</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6044,32 +6044,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129319366</v>
+        <v>129319280</v>
       </c>
       <c r="B52" t="n">
-        <v>80149</v>
+        <v>95950</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>2809</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6079,10 +6079,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>540738</v>
+        <v>540900</v>
       </c>
       <c r="R52" t="n">
-        <v>7193503</v>
+        <v>7193073</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6124,7 +6124,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6151,10 +6151,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129319356</v>
+        <v>129319335</v>
       </c>
       <c r="B53" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6162,21 +6162,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6186,10 +6186,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>540726</v>
+        <v>540655</v>
       </c>
       <c r="R53" t="n">
-        <v>7193540</v>
+        <v>7193534</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6221,7 +6221,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6258,10 +6258,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129319304</v>
+        <v>129319429</v>
       </c>
       <c r="B54" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6269,21 +6269,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6293,10 +6293,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>540962</v>
+        <v>540972</v>
       </c>
       <c r="R54" t="n">
-        <v>7193388</v>
+        <v>7193067</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6328,7 +6328,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6338,7 +6338,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6365,7 +6365,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129319429</v>
+        <v>129319417</v>
       </c>
       <c r="B55" t="n">
         <v>80150</v>
@@ -6400,10 +6400,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>540972</v>
+        <v>540989</v>
       </c>
       <c r="R55" t="n">
-        <v>7193067</v>
+        <v>7193132</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6435,7 +6435,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6445,7 +6445,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6472,10 +6472,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129319417</v>
+        <v>129319304</v>
       </c>
       <c r="B56" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6483,21 +6483,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6507,10 +6507,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>540989</v>
+        <v>540962</v>
       </c>
       <c r="R56" t="n">
-        <v>7193132</v>
+        <v>7193388</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6542,7 +6542,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6552,7 +6552,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6700,10 +6700,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129319292</v>
+        <v>129319339</v>
       </c>
       <c r="B58" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6711,21 +6711,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6735,10 +6735,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>540996</v>
+        <v>540669</v>
       </c>
       <c r="R58" t="n">
-        <v>7193327</v>
+        <v>7193542</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6807,10 +6807,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129319392</v>
+        <v>129319353</v>
       </c>
       <c r="B59" t="n">
-        <v>79044</v>
+        <v>82878</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6818,21 +6818,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6842,10 +6842,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>540826</v>
+        <v>540721</v>
       </c>
       <c r="R59" t="n">
-        <v>7193294</v>
+        <v>7193542</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6877,7 +6877,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6914,10 +6914,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129319353</v>
+        <v>129319311</v>
       </c>
       <c r="B60" t="n">
-        <v>82878</v>
+        <v>91546</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6925,21 +6925,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6949,10 +6949,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>540721</v>
+        <v>540830</v>
       </c>
       <c r="R60" t="n">
-        <v>7193542</v>
+        <v>7193366</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6984,7 +6984,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6994,7 +6994,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7128,10 +7128,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129319339</v>
+        <v>129319372</v>
       </c>
       <c r="B62" t="n">
-        <v>80150</v>
+        <v>80149</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7139,21 +7139,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7163,10 +7163,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>540669</v>
+        <v>540736</v>
       </c>
       <c r="R62" t="n">
-        <v>7193542</v>
+        <v>7193500</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7208,7 +7208,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7235,32 +7235,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129319311</v>
+        <v>129319330</v>
       </c>
       <c r="B63" t="n">
-        <v>91545</v>
+        <v>82995</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1108</v>
+        <v>6439</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7270,10 +7270,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>540830</v>
+        <v>540683</v>
       </c>
       <c r="R63" t="n">
-        <v>7193366</v>
+        <v>7193545</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7305,7 +7305,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7342,32 +7342,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129319330</v>
+        <v>129319292</v>
       </c>
       <c r="B64" t="n">
-        <v>82995</v>
+        <v>79044</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7377,10 +7377,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>540683</v>
+        <v>540996</v>
       </c>
       <c r="R64" t="n">
-        <v>7193545</v>
+        <v>7193327</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7449,10 +7449,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129319372</v>
+        <v>129319392</v>
       </c>
       <c r="B65" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7460,21 +7460,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7484,10 +7484,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>540736</v>
+        <v>540826</v>
       </c>
       <c r="R65" t="n">
-        <v>7193500</v>
+        <v>7193294</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7519,7 +7519,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7529,7 +7529,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7672,32 +7672,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129319334</v>
+        <v>129319421</v>
       </c>
       <c r="B67" t="n">
-        <v>80149</v>
+        <v>80178</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7707,10 +7707,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>540674</v>
+        <v>540981</v>
       </c>
       <c r="R67" t="n">
-        <v>7193550</v>
+        <v>7193140</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7742,7 +7742,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7752,7 +7752,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7779,32 +7779,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129319370</v>
+        <v>129319334</v>
       </c>
       <c r="B68" t="n">
-        <v>80178</v>
+        <v>80149</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7814,10 +7814,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>540737</v>
+        <v>540674</v>
       </c>
       <c r="R68" t="n">
-        <v>7193504</v>
+        <v>7193550</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7849,7 +7849,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7859,7 +7859,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7886,32 +7886,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129319397</v>
+        <v>129319370</v>
       </c>
       <c r="B69" t="n">
-        <v>79044</v>
+        <v>80178</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7921,10 +7921,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>540946</v>
+        <v>540737</v>
       </c>
       <c r="R69" t="n">
-        <v>7193256</v>
+        <v>7193504</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7956,7 +7956,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7966,7 +7966,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7993,7 +7993,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129319400</v>
+        <v>129319397</v>
       </c>
       <c r="B70" t="n">
         <v>79044</v>
@@ -8028,10 +8028,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>540943</v>
+        <v>540946</v>
       </c>
       <c r="R70" t="n">
-        <v>7193233</v>
+        <v>7193256</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8063,7 +8063,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8100,10 +8100,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129319293</v>
+        <v>129319400</v>
       </c>
       <c r="B71" t="n">
-        <v>57887</v>
+        <v>79044</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8111,43 +8111,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>540980</v>
+        <v>540943</v>
       </c>
       <c r="R71" t="n">
-        <v>7193345</v>
+        <v>7193233</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8179,7 +8170,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8189,7 +8180,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8216,45 +8207,54 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129319421</v>
+        <v>129319293</v>
       </c>
       <c r="B72" t="n">
-        <v>80178</v>
+        <v>57887</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>540981</v>
+        <v>540980</v>
       </c>
       <c r="R72" t="n">
-        <v>7193140</v>
+        <v>7193345</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8286,7 +8286,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8326,7 +8326,7 @@
         <v>129319412</v>
       </c>
       <c r="B73" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9082,10 +9082,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129319338</v>
+        <v>129319408</v>
       </c>
       <c r="B80" t="n">
-        <v>80150</v>
+        <v>80149</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9093,21 +9093,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9117,10 +9117,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>540676</v>
+        <v>540939</v>
       </c>
       <c r="R80" t="n">
-        <v>7193539</v>
+        <v>7193177</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9152,7 +9152,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9162,7 +9162,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9189,32 +9189,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129319408</v>
+        <v>129319431</v>
       </c>
       <c r="B81" t="n">
-        <v>80149</v>
+        <v>80178</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9224,10 +9224,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>540939</v>
+        <v>540979</v>
       </c>
       <c r="R81" t="n">
-        <v>7193177</v>
+        <v>7193075</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9259,7 +9259,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9296,32 +9296,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129319431</v>
+        <v>129319338</v>
       </c>
       <c r="B82" t="n">
-        <v>80178</v>
+        <v>80150</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9331,10 +9331,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>540979</v>
+        <v>540676</v>
       </c>
       <c r="R82" t="n">
-        <v>7193075</v>
+        <v>7193539</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9366,7 +9366,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9376,7 +9376,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9724,10 +9724,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129319298</v>
+        <v>129319409</v>
       </c>
       <c r="B86" t="n">
-        <v>91569</v>
+        <v>80149</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9735,19 +9735,23 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -9755,10 +9759,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>540964</v>
+        <v>540942</v>
       </c>
       <c r="R86" t="n">
-        <v>7193371</v>
+        <v>7193182</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9790,7 +9794,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9800,7 +9804,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9827,34 +9831,30 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129319389</v>
+        <v>129319298</v>
       </c>
       <c r="B87" t="n">
-        <v>95942</v>
+        <v>91570</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2809</v>
+        <v>5432</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -9862,10 +9862,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>540818</v>
+        <v>540964</v>
       </c>
       <c r="R87" t="n">
-        <v>7193358</v>
+        <v>7193371</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -9897,7 +9897,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9934,7 +9934,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129319333</v>
+        <v>129319375</v>
       </c>
       <c r="B88" t="n">
         <v>80150</v>
@@ -9969,10 +9969,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>540674</v>
+        <v>540730</v>
       </c>
       <c r="R88" t="n">
-        <v>7193551</v>
+        <v>7193493</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -10004,7 +10004,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10014,7 +10014,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10041,7 +10041,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129319376</v>
+        <v>129319333</v>
       </c>
       <c r="B89" t="n">
         <v>80150</v>
@@ -10076,10 +10076,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>540738</v>
+        <v>540674</v>
       </c>
       <c r="R89" t="n">
-        <v>7193476</v>
+        <v>7193551</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -10111,7 +10111,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10121,7 +10121,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10148,7 +10148,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129319375</v>
+        <v>129319376</v>
       </c>
       <c r="B90" t="n">
         <v>80150</v>
@@ -10183,10 +10183,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>540730</v>
+        <v>540738</v>
       </c>
       <c r="R90" t="n">
-        <v>7193493</v>
+        <v>7193476</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -10218,7 +10218,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10469,32 +10469,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129319409</v>
+        <v>129319389</v>
       </c>
       <c r="B93" t="n">
-        <v>80149</v>
+        <v>95950</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6458</v>
+        <v>2809</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10504,10 +10504,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>540942</v>
+        <v>540818</v>
       </c>
       <c r="R93" t="n">
-        <v>7193182</v>
+        <v>7193358</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -10539,7 +10539,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10549,7 +10549,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10576,32 +10576,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129319393</v>
+        <v>129319284</v>
       </c>
       <c r="B94" t="n">
-        <v>82995</v>
+        <v>79044</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10611,10 +10611,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>540824</v>
+        <v>540867</v>
       </c>
       <c r="R94" t="n">
-        <v>7193288</v>
+        <v>7193169</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10656,7 +10656,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10683,32 +10683,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129319284</v>
+        <v>129319393</v>
       </c>
       <c r="B95" t="n">
-        <v>79044</v>
+        <v>82995</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10718,10 +10718,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>540867</v>
+        <v>540824</v>
       </c>
       <c r="R95" t="n">
-        <v>7193169</v>
+        <v>7193288</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -10753,7 +10753,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10763,7 +10763,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11004,10 +11004,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129319445</v>
+        <v>129319359</v>
       </c>
       <c r="B98" t="n">
-        <v>57724</v>
+        <v>80149</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11015,43 +11015,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>541052</v>
+        <v>540725</v>
       </c>
       <c r="R98" t="n">
-        <v>7193255</v>
+        <v>7193537</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -11083,7 +11074,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11093,7 +11084,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11120,10 +11111,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129319359</v>
+        <v>129319399</v>
       </c>
       <c r="B99" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11131,21 +11122,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11155,10 +11146,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>540725</v>
+        <v>540945</v>
       </c>
       <c r="R99" t="n">
-        <v>7193537</v>
+        <v>7193248</v>
       </c>
       <c r="S99" t="n">
         <v>25</v>
@@ -11190,7 +11181,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11200,7 +11191,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11227,7 +11218,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129319399</v>
+        <v>129319308</v>
       </c>
       <c r="B100" t="n">
         <v>79044</v>
@@ -11262,10 +11253,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>540945</v>
+        <v>540907</v>
       </c>
       <c r="R100" t="n">
-        <v>7193248</v>
+        <v>7193409</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -11297,7 +11288,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11307,7 +11298,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11334,7 +11325,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129319308</v>
+        <v>129319362</v>
       </c>
       <c r="B101" t="n">
         <v>79044</v>
@@ -11369,10 +11360,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>540907</v>
+        <v>540721</v>
       </c>
       <c r="R101" t="n">
-        <v>7193409</v>
+        <v>7193527</v>
       </c>
       <c r="S101" t="n">
         <v>25</v>
@@ -11404,7 +11395,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11414,7 +11405,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11441,7 +11432,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129319362</v>
+        <v>129319306</v>
       </c>
       <c r="B102" t="n">
         <v>79044</v>
@@ -11476,10 +11467,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>540721</v>
+        <v>540961</v>
       </c>
       <c r="R102" t="n">
-        <v>7193527</v>
+        <v>7193398</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -11511,7 +11502,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11521,7 +11512,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11548,7 +11539,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129319306</v>
+        <v>129319286</v>
       </c>
       <c r="B103" t="n">
         <v>79044</v>
@@ -11583,10 +11574,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>540961</v>
+        <v>540891</v>
       </c>
       <c r="R103" t="n">
-        <v>7193398</v>
+        <v>7193174</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -11618,7 +11609,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11628,7 +11619,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11655,10 +11646,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129319286</v>
+        <v>129319445</v>
       </c>
       <c r="B104" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11666,34 +11657,43 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>540891</v>
+        <v>541052</v>
       </c>
       <c r="R104" t="n">
-        <v>7193174</v>
+        <v>7193255</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -11725,7 +11725,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11735,7 +11735,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11762,7 +11762,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129319355</v>
+        <v>129319391</v>
       </c>
       <c r="B105" t="n">
         <v>80150</v>
@@ -11797,10 +11797,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>540726</v>
+        <v>540818</v>
       </c>
       <c r="R105" t="n">
-        <v>7193541</v>
+        <v>7193333</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -11832,7 +11832,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11842,7 +11842,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11869,10 +11869,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129319360</v>
+        <v>129319355</v>
       </c>
       <c r="B106" t="n">
-        <v>91545</v>
+        <v>80150</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11880,21 +11880,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11904,10 +11904,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>540725</v>
+        <v>540726</v>
       </c>
       <c r="R106" t="n">
-        <v>7193532</v>
+        <v>7193541</v>
       </c>
       <c r="S106" t="n">
         <v>25</v>
@@ -11939,7 +11939,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11949,7 +11949,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11976,10 +11976,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129319369</v>
+        <v>129319360</v>
       </c>
       <c r="B107" t="n">
-        <v>80150</v>
+        <v>91546</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11987,21 +11987,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12011,10 +12011,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>540734</v>
+        <v>540725</v>
       </c>
       <c r="R107" t="n">
-        <v>7193503</v>
+        <v>7193532</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -12046,7 +12046,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12056,7 +12056,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12083,7 +12083,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129319391</v>
+        <v>129319369</v>
       </c>
       <c r="B108" t="n">
         <v>80150</v>
@@ -12118,10 +12118,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>540818</v>
+        <v>540734</v>
       </c>
       <c r="R108" t="n">
-        <v>7193333</v>
+        <v>7193503</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -12153,7 +12153,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12163,7 +12163,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12618,27 +12618,27 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129319309</v>
+        <v>129319425</v>
       </c>
       <c r="B113" t="n">
-        <v>79044</v>
+        <v>80184</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -12653,10 +12653,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>540894</v>
+        <v>540980</v>
       </c>
       <c r="R113" t="n">
-        <v>7193411</v>
+        <v>7193116</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -12688,7 +12688,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12725,10 +12725,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129319426</v>
+        <v>129319305</v>
       </c>
       <c r="B114" t="n">
-        <v>80150</v>
+        <v>91570</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12736,23 +12736,19 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
@@ -12760,10 +12756,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>540979</v>
+        <v>540959</v>
       </c>
       <c r="R114" t="n">
-        <v>7193115</v>
+        <v>7193395</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -12795,7 +12791,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12805,7 +12801,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12835,7 +12831,7 @@
         <v>129319341</v>
       </c>
       <c r="B115" t="n">
-        <v>91545</v>
+        <v>91546</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12939,10 +12935,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129319305</v>
+        <v>129319426</v>
       </c>
       <c r="B116" t="n">
-        <v>91569</v>
+        <v>80150</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12950,19 +12946,23 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr"/>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
@@ -12970,10 +12970,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>540959</v>
+        <v>540979</v>
       </c>
       <c r="R116" t="n">
-        <v>7193395</v>
+        <v>7193115</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -13005,7 +13005,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13015,7 +13015,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13042,27 +13042,27 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129319425</v>
+        <v>129319309</v>
       </c>
       <c r="B117" t="n">
-        <v>80184</v>
+        <v>79044</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -13077,10 +13077,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>540980</v>
+        <v>540894</v>
       </c>
       <c r="R117" t="n">
-        <v>7193116</v>
+        <v>7193411</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -13112,7 +13112,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13122,7 +13122,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13268,7 +13268,7 @@
         <v>129319329</v>
       </c>
       <c r="B119" t="n">
-        <v>88949</v>
+        <v>88950</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13479,7 +13479,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129319319</v>
+        <v>129319277</v>
       </c>
       <c r="B121" t="n">
         <v>80150</v>
@@ -13514,10 +13514,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>540719</v>
+        <v>540837</v>
       </c>
       <c r="R121" t="n">
-        <v>7193463</v>
+        <v>7193042</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -13549,7 +13549,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13559,7 +13559,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13586,32 +13586,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129319416</v>
+        <v>129319319</v>
       </c>
       <c r="B122" t="n">
-        <v>80185</v>
+        <v>80150</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13621,10 +13621,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>540970</v>
+        <v>540719</v>
       </c>
       <c r="R122" t="n">
-        <v>7193154</v>
+        <v>7193463</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -13656,7 +13656,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13666,7 +13666,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13693,54 +13693,45 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129319363</v>
+        <v>129319416</v>
       </c>
       <c r="B123" t="n">
-        <v>58360</v>
+        <v>80185</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>102125</v>
+        <v>6464</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>540731</v>
+        <v>540970</v>
       </c>
       <c r="R123" t="n">
-        <v>7193512</v>
+        <v>7193154</v>
       </c>
       <c r="S123" t="n">
         <v>25</v>
@@ -13772,7 +13763,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13782,7 +13773,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13809,54 +13800,45 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129319410</v>
+        <v>129319373</v>
       </c>
       <c r="B124" t="n">
-        <v>56908</v>
+        <v>80185</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>102612</v>
+        <v>6464</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>540946</v>
+        <v>540734</v>
       </c>
       <c r="R124" t="n">
-        <v>7193171</v>
+        <v>7193499</v>
       </c>
       <c r="S124" t="n">
         <v>25</v>
@@ -13888,7 +13870,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13898,7 +13880,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13925,10 +13907,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129319373</v>
+        <v>129319321</v>
       </c>
       <c r="B125" t="n">
-        <v>80185</v>
+        <v>80178</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13936,21 +13918,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13960,10 +13942,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>540734</v>
+        <v>540719</v>
       </c>
       <c r="R125" t="n">
-        <v>7193499</v>
+        <v>7193463</v>
       </c>
       <c r="S125" t="n">
         <v>25</v>
@@ -13995,7 +13977,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14005,7 +13987,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14032,32 +14014,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129319321</v>
+        <v>129319350</v>
       </c>
       <c r="B126" t="n">
-        <v>80178</v>
+        <v>80149</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14067,10 +14049,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>540719</v>
+        <v>540681</v>
       </c>
       <c r="R126" t="n">
-        <v>7193463</v>
+        <v>7193521</v>
       </c>
       <c r="S126" t="n">
         <v>25</v>
@@ -14102,7 +14084,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14112,7 +14094,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14139,45 +14121,54 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129319350</v>
+        <v>129319363</v>
       </c>
       <c r="B127" t="n">
-        <v>80149</v>
+        <v>58360</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6458</v>
+        <v>102125</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>540681</v>
+        <v>540731</v>
       </c>
       <c r="R127" t="n">
-        <v>7193521</v>
+        <v>7193512</v>
       </c>
       <c r="S127" t="n">
         <v>25</v>
@@ -14209,7 +14200,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14219,7 +14210,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14246,10 +14237,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129319277</v>
+        <v>129319410</v>
       </c>
       <c r="B128" t="n">
-        <v>80150</v>
+        <v>56908</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14257,34 +14248,43 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>2081</v>
+        <v>102612</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>540837</v>
+        <v>540946</v>
       </c>
       <c r="R128" t="n">
-        <v>7193042</v>
+        <v>7193171</v>
       </c>
       <c r="S128" t="n">
         <v>25</v>
@@ -14316,7 +14316,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14326,7 +14326,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14353,10 +14353,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129319326</v>
+        <v>129319379</v>
       </c>
       <c r="B129" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14364,21 +14364,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14388,10 +14388,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>540701</v>
+        <v>540761</v>
       </c>
       <c r="R129" t="n">
-        <v>7193533</v>
+        <v>7193485</v>
       </c>
       <c r="S129" t="n">
         <v>25</v>
@@ -14423,7 +14423,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14433,7 +14433,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14460,7 +14460,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129319434</v>
+        <v>129319326</v>
       </c>
       <c r="B130" t="n">
         <v>80149</v>
@@ -14495,10 +14495,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>540979</v>
+        <v>540701</v>
       </c>
       <c r="R130" t="n">
-        <v>7193075</v>
+        <v>7193533</v>
       </c>
       <c r="S130" t="n">
         <v>25</v>
@@ -14530,7 +14530,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14540,7 +14540,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14567,10 +14567,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129319379</v>
+        <v>129319434</v>
       </c>
       <c r="B131" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14578,21 +14578,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14602,10 +14602,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>540761</v>
+        <v>540979</v>
       </c>
       <c r="R131" t="n">
-        <v>7193485</v>
+        <v>7193075</v>
       </c>
       <c r="S131" t="n">
         <v>25</v>
@@ -14637,7 +14637,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14647,7 +14647,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14674,10 +14674,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129319322</v>
+        <v>129319310</v>
       </c>
       <c r="B132" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14685,21 +14685,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14709,10 +14709,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>540719</v>
+        <v>540830</v>
       </c>
       <c r="R132" t="n">
-        <v>7193483</v>
+        <v>7193366</v>
       </c>
       <c r="S132" t="n">
         <v>25</v>
@@ -14744,7 +14744,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14754,7 +14754,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14781,32 +14781,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129319312</v>
+        <v>129319380</v>
       </c>
       <c r="B133" t="n">
-        <v>80150</v>
+        <v>92268</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>2081</v>
+        <v>3298</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14816,10 +14816,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>540789</v>
+        <v>540761</v>
       </c>
       <c r="R133" t="n">
-        <v>7193373</v>
+        <v>7193490</v>
       </c>
       <c r="S133" t="n">
         <v>25</v>
@@ -14851,7 +14851,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14861,7 +14861,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15112,32 +15112,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129319380</v>
+        <v>129319312</v>
       </c>
       <c r="B136" t="n">
-        <v>92267</v>
+        <v>80150</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>3298</v>
+        <v>2081</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15147,10 +15147,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>540761</v>
+        <v>540789</v>
       </c>
       <c r="R136" t="n">
-        <v>7193490</v>
+        <v>7193373</v>
       </c>
       <c r="S136" t="n">
         <v>25</v>
@@ -15182,7 +15182,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15192,7 +15192,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15219,10 +15219,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129319310</v>
+        <v>129319322</v>
       </c>
       <c r="B137" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15230,21 +15230,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15254,10 +15254,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>540830</v>
+        <v>540719</v>
       </c>
       <c r="R137" t="n">
-        <v>7193366</v>
+        <v>7193483</v>
       </c>
       <c r="S137" t="n">
         <v>25</v>
@@ -15289,7 +15289,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15299,7 +15299,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15326,10 +15326,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129319387</v>
+        <v>129319428</v>
       </c>
       <c r="B138" t="n">
-        <v>83004</v>
+        <v>80149</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15337,21 +15337,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15361,10 +15361,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>540772</v>
+        <v>540971</v>
       </c>
       <c r="R138" t="n">
-        <v>7193446</v>
+        <v>7193081</v>
       </c>
       <c r="S138" t="n">
         <v>25</v>
@@ -15396,7 +15396,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15406,7 +15406,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15433,32 +15433,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129319406</v>
+        <v>129319347</v>
       </c>
       <c r="B139" t="n">
-        <v>79123</v>
+        <v>80185</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>864</v>
+        <v>6464</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15468,10 +15468,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>540938</v>
+        <v>540653</v>
       </c>
       <c r="R139" t="n">
-        <v>7193168</v>
+        <v>7193521</v>
       </c>
       <c r="S139" t="n">
         <v>25</v>
@@ -15503,7 +15503,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15513,7 +15513,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15540,10 +15540,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129319428</v>
+        <v>129319387</v>
       </c>
       <c r="B140" t="n">
-        <v>80149</v>
+        <v>83004</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15551,21 +15551,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15575,10 +15575,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>540971</v>
+        <v>540772</v>
       </c>
       <c r="R140" t="n">
-        <v>7193081</v>
+        <v>7193446</v>
       </c>
       <c r="S140" t="n">
         <v>25</v>
@@ -15610,7 +15610,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15620,7 +15620,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15647,32 +15647,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129319315</v>
+        <v>129319406</v>
       </c>
       <c r="B141" t="n">
-        <v>82995</v>
+        <v>79123</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6439</v>
+        <v>864</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15682,10 +15682,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>540765</v>
+        <v>540938</v>
       </c>
       <c r="R141" t="n">
-        <v>7193370</v>
+        <v>7193168</v>
       </c>
       <c r="S141" t="n">
         <v>25</v>
@@ -15717,7 +15717,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15727,7 +15727,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15754,32 +15754,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129319327</v>
+        <v>129319315</v>
       </c>
       <c r="B142" t="n">
-        <v>79044</v>
+        <v>82995</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15789,10 +15789,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>540693</v>
+        <v>540765</v>
       </c>
       <c r="R142" t="n">
-        <v>7193540</v>
+        <v>7193370</v>
       </c>
       <c r="S142" t="n">
         <v>25</v>
@@ -15824,7 +15824,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15861,32 +15861,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129319287</v>
+        <v>129319327</v>
       </c>
       <c r="B143" t="n">
-        <v>92267</v>
+        <v>79044</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15896,10 +15896,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>540913</v>
+        <v>540693</v>
       </c>
       <c r="R143" t="n">
-        <v>7193185</v>
+        <v>7193540</v>
       </c>
       <c r="S143" t="n">
         <v>25</v>
@@ -15931,7 +15931,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15941,7 +15941,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15968,10 +15968,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129319347</v>
+        <v>129319287</v>
       </c>
       <c r="B144" t="n">
-        <v>80185</v>
+        <v>92268</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15979,21 +15979,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6464</v>
+        <v>3298</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -16003,10 +16003,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>540653</v>
+        <v>540913</v>
       </c>
       <c r="R144" t="n">
-        <v>7193521</v>
+        <v>7193185</v>
       </c>
       <c r="S144" t="n">
         <v>25</v>
@@ -16038,7 +16038,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16048,7 +16048,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD144" t="b">

--- a/artfynd/A 51086-2025 artfynd.xlsx
+++ b/artfynd/A 51086-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129319285</v>
+        <v>129319307</v>
       </c>
       <c r="B2" t="n">
         <v>91546</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540886</v>
+        <v>540962</v>
       </c>
       <c r="R2" t="n">
-        <v>7193172</v>
+        <v>7193400</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129319307</v>
+        <v>129319285</v>
       </c>
       <c r="B3" t="n">
         <v>91546</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540962</v>
+        <v>540886</v>
       </c>
       <c r="R3" t="n">
-        <v>7193400</v>
+        <v>7193172</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,54 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129319414</v>
+        <v>129319386</v>
       </c>
       <c r="B4" t="n">
-        <v>58360</v>
+        <v>95950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102125</v>
+        <v>2809</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540963</v>
+        <v>540774</v>
       </c>
       <c r="R4" t="n">
-        <v>7193203</v>
+        <v>7193457</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -968,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -978,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129319300</v>
+        <v>129319384</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,39 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540961</v>
+        <v>540775</v>
       </c>
       <c r="R5" t="n">
-        <v>7193376</v>
+        <v>7193467</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1080,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1090,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129319384</v>
+        <v>129319302</v>
       </c>
       <c r="B6" t="n">
         <v>79044</v>
@@ -1152,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540775</v>
+        <v>540960</v>
       </c>
       <c r="R6" t="n">
-        <v>7193467</v>
+        <v>7193375</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1187,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1197,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1224,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129319302</v>
+        <v>129319300</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1235,34 +1221,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540960</v>
+        <v>540961</v>
       </c>
       <c r="R7" t="n">
-        <v>7193375</v>
+        <v>7193376</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1294,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1304,7 +1295,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1545,45 +1536,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129319386</v>
+        <v>129319414</v>
       </c>
       <c r="B10" t="n">
-        <v>95950</v>
+        <v>58360</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2809</v>
+        <v>102125</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540774</v>
+        <v>540963</v>
       </c>
       <c r="R10" t="n">
-        <v>7193457</v>
+        <v>7193203</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1615,7 +1615,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1652,10 +1652,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129319381</v>
+        <v>129319361</v>
       </c>
       <c r="B11" t="n">
-        <v>82878</v>
+        <v>91550</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1663,21 +1663,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540758</v>
+        <v>540726</v>
       </c>
       <c r="R11" t="n">
-        <v>7193475</v>
+        <v>7193531</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1866,10 +1866,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129319361</v>
+        <v>129319381</v>
       </c>
       <c r="B13" t="n">
-        <v>91550</v>
+        <v>82878</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1877,21 +1877,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1901,10 +1901,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540726</v>
+        <v>540758</v>
       </c>
       <c r="R13" t="n">
-        <v>7193531</v>
+        <v>7193475</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2080,10 +2080,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129319328</v>
+        <v>129319296</v>
       </c>
       <c r="B15" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2091,21 +2091,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540693</v>
+        <v>540970</v>
       </c>
       <c r="R15" t="n">
-        <v>7193540</v>
+        <v>7193365</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2187,27 +2187,27 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129319296</v>
+        <v>129319419</v>
       </c>
       <c r="B16" t="n">
-        <v>79044</v>
+        <v>80184</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2222,10 +2222,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540970</v>
+        <v>540986</v>
       </c>
       <c r="R16" t="n">
-        <v>7193365</v>
+        <v>7193130</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2294,10 +2294,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129319438</v>
+        <v>129319328</v>
       </c>
       <c r="B17" t="n">
-        <v>57887</v>
+        <v>80149</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2305,43 +2305,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540982</v>
+        <v>540693</v>
       </c>
       <c r="R17" t="n">
-        <v>7193110</v>
+        <v>7193540</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2373,7 +2364,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2383,7 +2374,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2410,32 +2401,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129319352</v>
+        <v>129319313</v>
       </c>
       <c r="B18" t="n">
-        <v>78057</v>
+        <v>80185</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228579</v>
+        <v>6464</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2445,10 +2436,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540715</v>
+        <v>540789</v>
       </c>
       <c r="R18" t="n">
-        <v>7193537</v>
+        <v>7193372</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2480,7 +2471,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2490,7 +2481,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2517,32 +2508,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129319419</v>
+        <v>129319324</v>
       </c>
       <c r="B19" t="n">
-        <v>80184</v>
+        <v>80149</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2552,10 +2543,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540986</v>
+        <v>540719</v>
       </c>
       <c r="R19" t="n">
-        <v>7193130</v>
+        <v>7193483</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2587,7 +2578,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2597,7 +2588,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2624,10 +2615,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129319313</v>
+        <v>129319430</v>
       </c>
       <c r="B20" t="n">
-        <v>80185</v>
+        <v>80184</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2635,21 +2626,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2659,10 +2650,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540789</v>
+        <v>540971</v>
       </c>
       <c r="R20" t="n">
-        <v>7193372</v>
+        <v>7193066</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2694,7 +2685,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2704,7 +2695,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2731,10 +2722,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129319324</v>
+        <v>129319438</v>
       </c>
       <c r="B21" t="n">
-        <v>80149</v>
+        <v>57887</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2742,34 +2733,43 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540719</v>
+        <v>540982</v>
       </c>
       <c r="R21" t="n">
-        <v>7193483</v>
+        <v>7193110</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2838,32 +2838,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129319430</v>
+        <v>129319352</v>
       </c>
       <c r="B22" t="n">
-        <v>80184</v>
+        <v>78057</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6463</v>
+        <v>228579</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540971</v>
+        <v>540715</v>
       </c>
       <c r="R22" t="n">
-        <v>7193066</v>
+        <v>7193537</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2945,7 +2945,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129319316</v>
+        <v>129319281</v>
       </c>
       <c r="B23" t="n">
         <v>80150</v>
@@ -2980,10 +2980,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540763</v>
+        <v>540902</v>
       </c>
       <c r="R23" t="n">
-        <v>7193372</v>
+        <v>7193083</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3015,7 +3015,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3052,7 +3052,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129319281</v>
+        <v>129319316</v>
       </c>
       <c r="B24" t="n">
         <v>80150</v>
@@ -3087,10 +3087,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540902</v>
+        <v>540763</v>
       </c>
       <c r="R24" t="n">
-        <v>7193083</v>
+        <v>7193372</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3373,10 +3373,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129319349</v>
+        <v>129319383</v>
       </c>
       <c r="B27" t="n">
-        <v>91570</v>
+        <v>79044</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3384,19 +3384,23 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3404,10 +3408,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>540670</v>
+        <v>540764</v>
       </c>
       <c r="R27" t="n">
-        <v>7193521</v>
+        <v>7193475</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3439,7 +3443,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3449,7 +3453,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3583,7 +3587,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129319383</v>
+        <v>129319354</v>
       </c>
       <c r="B29" t="n">
         <v>79044</v>
@@ -3618,10 +3622,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>540764</v>
+        <v>540722</v>
       </c>
       <c r="R29" t="n">
-        <v>7193475</v>
+        <v>7193542</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3653,7 +3657,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3663,7 +3667,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3690,10 +3694,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129319354</v>
+        <v>129319349</v>
       </c>
       <c r="B30" t="n">
-        <v>79044</v>
+        <v>91570</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3701,23 +3705,19 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3725,10 +3725,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>540722</v>
+        <v>540670</v>
       </c>
       <c r="R30" t="n">
-        <v>7193542</v>
+        <v>7193521</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3760,7 +3760,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4011,10 +4011,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129319337</v>
+        <v>129319405</v>
       </c>
       <c r="B33" t="n">
-        <v>80149</v>
+        <v>83012</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4022,21 +4022,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4046,10 +4046,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>540676</v>
+        <v>540931</v>
       </c>
       <c r="R33" t="n">
-        <v>7193539</v>
+        <v>7193220</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4081,7 +4081,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4118,27 +4118,27 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129319422</v>
+        <v>129319427</v>
       </c>
       <c r="B34" t="n">
-        <v>80184</v>
+        <v>79044</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4153,10 +4153,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>540980</v>
+        <v>540969</v>
       </c>
       <c r="R34" t="n">
-        <v>7193139</v>
+        <v>7193117</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4225,10 +4225,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129319404</v>
+        <v>129319396</v>
       </c>
       <c r="B35" t="n">
-        <v>78057</v>
+        <v>79044</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4236,21 +4236,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4260,10 +4260,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>540931</v>
+        <v>540928</v>
       </c>
       <c r="R35" t="n">
-        <v>7193220</v>
+        <v>7193263</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4295,7 +4295,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4305,7 +4305,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4332,7 +4332,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129319396</v>
+        <v>129319282</v>
       </c>
       <c r="B36" t="n">
         <v>79044</v>
@@ -4367,10 +4367,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>540928</v>
+        <v>540901</v>
       </c>
       <c r="R36" t="n">
-        <v>7193263</v>
+        <v>7193084</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4402,7 +4402,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4439,10 +4439,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129319427</v>
+        <v>129319337</v>
       </c>
       <c r="B37" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4450,21 +4450,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4474,10 +4474,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>540969</v>
+        <v>540676</v>
       </c>
       <c r="R37" t="n">
-        <v>7193117</v>
+        <v>7193539</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4546,27 +4546,27 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129319282</v>
+        <v>129319422</v>
       </c>
       <c r="B38" t="n">
-        <v>79044</v>
+        <v>80184</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>540901</v>
+        <v>540980</v>
       </c>
       <c r="R38" t="n">
-        <v>7193084</v>
+        <v>7193139</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4653,10 +4653,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129319405</v>
+        <v>129319404</v>
       </c>
       <c r="B39" t="n">
-        <v>83012</v>
+        <v>78057</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4664,21 +4664,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4760,32 +4760,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129319303</v>
+        <v>129319395</v>
       </c>
       <c r="B40" t="n">
-        <v>79044</v>
+        <v>82997</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>540934</v>
+        <v>540878</v>
       </c>
       <c r="R40" t="n">
-        <v>7193385</v>
+        <v>7193291</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4840,7 +4840,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4867,10 +4867,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129319348</v>
+        <v>129319303</v>
       </c>
       <c r="B41" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4878,21 +4878,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>540653</v>
+        <v>540934</v>
       </c>
       <c r="R41" t="n">
-        <v>7193521</v>
+        <v>7193385</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4947,7 +4947,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5081,32 +5081,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129319395</v>
+        <v>129319278</v>
       </c>
       <c r="B43" t="n">
-        <v>82997</v>
+        <v>80150</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>306</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5116,10 +5116,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540878</v>
+        <v>540864</v>
       </c>
       <c r="R43" t="n">
-        <v>7193291</v>
+        <v>7193066</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5188,7 +5188,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129319278</v>
+        <v>129319365</v>
       </c>
       <c r="B44" t="n">
         <v>80150</v>
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540864</v>
+        <v>540738</v>
       </c>
       <c r="R44" t="n">
-        <v>7193066</v>
+        <v>7193503</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5402,10 +5402,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129319365</v>
+        <v>129319348</v>
       </c>
       <c r="B46" t="n">
-        <v>80150</v>
+        <v>80149</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5413,21 +5413,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5437,10 +5437,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>540738</v>
+        <v>540653</v>
       </c>
       <c r="R46" t="n">
-        <v>7193503</v>
+        <v>7193521</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5472,7 +5472,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6044,32 +6044,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129319280</v>
+        <v>129319335</v>
       </c>
       <c r="B52" t="n">
-        <v>95950</v>
+        <v>80150</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2809</v>
+        <v>2081</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6079,10 +6079,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>540900</v>
+        <v>540655</v>
       </c>
       <c r="R52" t="n">
-        <v>7193073</v>
+        <v>7193534</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6124,7 +6124,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6151,32 +6151,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129319335</v>
+        <v>129319280</v>
       </c>
       <c r="B53" t="n">
-        <v>80150</v>
+        <v>95950</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2081</v>
+        <v>2809</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6186,10 +6186,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>540655</v>
+        <v>540900</v>
       </c>
       <c r="R53" t="n">
-        <v>7193534</v>
+        <v>7193073</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6221,7 +6221,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6472,10 +6472,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129319304</v>
+        <v>129319388</v>
       </c>
       <c r="B56" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6483,34 +6483,48 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>540962</v>
+        <v>540828</v>
       </c>
       <c r="R56" t="n">
-        <v>7193388</v>
+        <v>7193425</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6542,7 +6556,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6552,7 +6566,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6579,10 +6593,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129319388</v>
+        <v>129319304</v>
       </c>
       <c r="B57" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6590,48 +6604,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>540828</v>
+        <v>540962</v>
       </c>
       <c r="R57" t="n">
-        <v>7193425</v>
+        <v>7193388</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6673,7 +6673,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6700,10 +6700,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129319339</v>
+        <v>129319292</v>
       </c>
       <c r="B58" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6711,21 +6711,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6735,10 +6735,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>540669</v>
+        <v>540996</v>
       </c>
       <c r="R58" t="n">
-        <v>7193542</v>
+        <v>7193327</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6807,10 +6807,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129319353</v>
+        <v>129319392</v>
       </c>
       <c r="B59" t="n">
-        <v>82878</v>
+        <v>79044</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6818,21 +6818,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6842,10 +6842,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>540721</v>
+        <v>540826</v>
       </c>
       <c r="R59" t="n">
-        <v>7193542</v>
+        <v>7193294</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6877,7 +6877,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6914,10 +6914,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129319311</v>
+        <v>129319353</v>
       </c>
       <c r="B60" t="n">
-        <v>91546</v>
+        <v>82878</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6925,21 +6925,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6949,10 +6949,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>540830</v>
+        <v>540721</v>
       </c>
       <c r="R60" t="n">
-        <v>7193366</v>
+        <v>7193542</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6984,7 +6984,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6994,7 +6994,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7128,10 +7128,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129319372</v>
+        <v>129319339</v>
       </c>
       <c r="B62" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7139,21 +7139,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7163,10 +7163,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>540736</v>
+        <v>540669</v>
       </c>
       <c r="R62" t="n">
-        <v>7193500</v>
+        <v>7193542</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7208,7 +7208,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7235,32 +7235,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129319330</v>
+        <v>129319311</v>
       </c>
       <c r="B63" t="n">
-        <v>82995</v>
+        <v>91546</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6439</v>
+        <v>1108</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7270,10 +7270,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>540683</v>
+        <v>540830</v>
       </c>
       <c r="R63" t="n">
-        <v>7193545</v>
+        <v>7193366</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7305,7 +7305,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7342,45 +7342,54 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129319292</v>
+        <v>129319423</v>
       </c>
       <c r="B64" t="n">
-        <v>79044</v>
+        <v>57831</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>540996</v>
+        <v>540976</v>
       </c>
       <c r="R64" t="n">
-        <v>7193327</v>
+        <v>7193139</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7412,7 +7421,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7422,7 +7431,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7449,32 +7458,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129319392</v>
+        <v>129319330</v>
       </c>
       <c r="B65" t="n">
-        <v>79044</v>
+        <v>82995</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7484,10 +7493,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>540826</v>
+        <v>540683</v>
       </c>
       <c r="R65" t="n">
-        <v>7193294</v>
+        <v>7193545</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7519,7 +7528,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7529,7 +7538,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7556,54 +7565,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129319423</v>
+        <v>129319372</v>
       </c>
       <c r="B66" t="n">
-        <v>57831</v>
+        <v>80149</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>103031</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>540976</v>
+        <v>540736</v>
       </c>
       <c r="R66" t="n">
-        <v>7193139</v>
+        <v>7193500</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7635,7 +7635,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7645,7 +7645,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7672,45 +7672,54 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129319421</v>
+        <v>129319293</v>
       </c>
       <c r="B67" t="n">
-        <v>80178</v>
+        <v>57887</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>540981</v>
+        <v>540980</v>
       </c>
       <c r="R67" t="n">
-        <v>7193140</v>
+        <v>7193345</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7742,7 +7751,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7752,7 +7761,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7779,10 +7788,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129319334</v>
+        <v>129319400</v>
       </c>
       <c r="B68" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7790,21 +7799,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7814,10 +7823,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>540674</v>
+        <v>540943</v>
       </c>
       <c r="R68" t="n">
-        <v>7193550</v>
+        <v>7193233</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7849,7 +7858,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7859,7 +7868,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7886,32 +7895,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129319370</v>
+        <v>129319397</v>
       </c>
       <c r="B69" t="n">
-        <v>80178</v>
+        <v>79044</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7921,10 +7930,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>540737</v>
+        <v>540946</v>
       </c>
       <c r="R69" t="n">
-        <v>7193504</v>
+        <v>7193256</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7956,7 +7965,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7966,7 +7975,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7993,32 +8002,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129319397</v>
+        <v>129319421</v>
       </c>
       <c r="B70" t="n">
-        <v>79044</v>
+        <v>80178</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8028,10 +8037,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>540946</v>
+        <v>540981</v>
       </c>
       <c r="R70" t="n">
-        <v>7193256</v>
+        <v>7193140</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8063,7 +8072,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8073,7 +8082,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8100,10 +8109,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129319400</v>
+        <v>129319334</v>
       </c>
       <c r="B71" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8111,21 +8120,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8135,10 +8144,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>540943</v>
+        <v>540674</v>
       </c>
       <c r="R71" t="n">
-        <v>7193233</v>
+        <v>7193550</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8170,7 +8179,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8180,7 +8189,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8207,54 +8216,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129319293</v>
+        <v>129319370</v>
       </c>
       <c r="B72" t="n">
-        <v>57887</v>
+        <v>80178</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>540980</v>
+        <v>540737</v>
       </c>
       <c r="R72" t="n">
-        <v>7193345</v>
+        <v>7193504</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8286,7 +8286,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8323,10 +8323,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129319412</v>
+        <v>129319413</v>
       </c>
       <c r="B73" t="n">
-        <v>91570</v>
+        <v>79044</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8334,19 +8334,23 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -8354,10 +8358,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>540952</v>
+        <v>540965</v>
       </c>
       <c r="R73" t="n">
-        <v>7193187</v>
+        <v>7193181</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8389,7 +8393,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8399,7 +8403,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8426,32 +8430,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129319367</v>
+        <v>129319402</v>
       </c>
       <c r="B74" t="n">
-        <v>80178</v>
+        <v>79044</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8461,10 +8465,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>540734</v>
+        <v>540936</v>
       </c>
       <c r="R74" t="n">
-        <v>7193503</v>
+        <v>7193225</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8496,7 +8500,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8506,7 +8510,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8533,32 +8537,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129319402</v>
+        <v>129319367</v>
       </c>
       <c r="B75" t="n">
-        <v>79044</v>
+        <v>80178</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8568,10 +8572,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>540936</v>
+        <v>540734</v>
       </c>
       <c r="R75" t="n">
-        <v>7193225</v>
+        <v>7193503</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8603,7 +8607,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8613,7 +8617,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8640,10 +8644,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129319413</v>
+        <v>129319412</v>
       </c>
       <c r="B76" t="n">
-        <v>79044</v>
+        <v>91570</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8651,23 +8655,19 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -8675,10 +8675,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>540965</v>
+        <v>540952</v>
       </c>
       <c r="R76" t="n">
-        <v>7193181</v>
+        <v>7193187</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8710,7 +8710,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8720,7 +8720,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9082,10 +9082,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129319408</v>
+        <v>129319338</v>
       </c>
       <c r="B80" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9093,21 +9093,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9117,10 +9117,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>540939</v>
+        <v>540676</v>
       </c>
       <c r="R80" t="n">
-        <v>7193177</v>
+        <v>7193539</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9152,7 +9152,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9162,7 +9162,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9189,32 +9189,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129319431</v>
+        <v>129319382</v>
       </c>
       <c r="B81" t="n">
-        <v>80178</v>
+        <v>79044</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9224,10 +9224,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>540979</v>
+        <v>540761</v>
       </c>
       <c r="R81" t="n">
-        <v>7193075</v>
+        <v>7193473</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9259,7 +9259,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9296,10 +9296,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129319338</v>
+        <v>129319336</v>
       </c>
       <c r="B82" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9307,21 +9307,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9331,10 +9331,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>540676</v>
+        <v>540668</v>
       </c>
       <c r="R82" t="n">
-        <v>7193539</v>
+        <v>7193543</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9366,7 +9366,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9376,7 +9376,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9403,7 +9403,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129319336</v>
+        <v>129319394</v>
       </c>
       <c r="B83" t="n">
         <v>79044</v>
@@ -9438,10 +9438,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>540668</v>
+        <v>540877</v>
       </c>
       <c r="R83" t="n">
-        <v>7193543</v>
+        <v>7193291</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9473,7 +9473,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9483,7 +9483,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9510,10 +9510,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129319382</v>
+        <v>129319408</v>
       </c>
       <c r="B84" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9521,21 +9521,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9545,10 +9545,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>540761</v>
+        <v>540939</v>
       </c>
       <c r="R84" t="n">
-        <v>7193473</v>
+        <v>7193177</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9580,7 +9580,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9590,7 +9590,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9617,32 +9617,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129319394</v>
+        <v>129319431</v>
       </c>
       <c r="B85" t="n">
-        <v>79044</v>
+        <v>80178</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9652,10 +9652,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>540877</v>
+        <v>540979</v>
       </c>
       <c r="R85" t="n">
-        <v>7193291</v>
+        <v>7193075</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9687,7 +9687,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9697,7 +9697,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9724,10 +9724,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129319409</v>
+        <v>129319333</v>
       </c>
       <c r="B86" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9735,21 +9735,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9759,10 +9759,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>540942</v>
+        <v>540674</v>
       </c>
       <c r="R86" t="n">
-        <v>7193182</v>
+        <v>7193551</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9794,7 +9794,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9804,7 +9804,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9831,10 +9831,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129319298</v>
+        <v>129319376</v>
       </c>
       <c r="B87" t="n">
-        <v>91570</v>
+        <v>80150</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9842,19 +9842,23 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr"/>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -9862,10 +9866,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>540964</v>
+        <v>540738</v>
       </c>
       <c r="R87" t="n">
-        <v>7193371</v>
+        <v>7193476</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -9897,7 +9901,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9907,7 +9911,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10041,7 +10045,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129319333</v>
+        <v>129319433</v>
       </c>
       <c r="B89" t="n">
         <v>80150</v>
@@ -10076,10 +10080,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>540674</v>
+        <v>540979</v>
       </c>
       <c r="R89" t="n">
-        <v>7193551</v>
+        <v>7193075</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -10111,7 +10115,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10121,7 +10125,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10148,7 +10152,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129319376</v>
+        <v>129319357</v>
       </c>
       <c r="B90" t="n">
         <v>80150</v>
@@ -10183,10 +10187,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>540738</v>
+        <v>540726</v>
       </c>
       <c r="R90" t="n">
-        <v>7193476</v>
+        <v>7193539</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -10218,7 +10222,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10228,7 +10232,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10255,32 +10259,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129319433</v>
+        <v>129319389</v>
       </c>
       <c r="B91" t="n">
-        <v>80150</v>
+        <v>95950</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2081</v>
+        <v>2809</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10290,10 +10294,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>540979</v>
+        <v>540818</v>
       </c>
       <c r="R91" t="n">
-        <v>7193075</v>
+        <v>7193358</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -10325,7 +10329,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10335,7 +10339,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10362,10 +10366,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129319357</v>
+        <v>129319299</v>
       </c>
       <c r="B92" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10373,21 +10377,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10397,10 +10401,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>540726</v>
+        <v>540964</v>
       </c>
       <c r="R92" t="n">
-        <v>7193539</v>
+        <v>7193371</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -10432,7 +10436,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10442,7 +10446,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10469,32 +10473,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129319389</v>
+        <v>129319409</v>
       </c>
       <c r="B93" t="n">
-        <v>95950</v>
+        <v>80149</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2809</v>
+        <v>6458</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10504,10 +10508,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>540818</v>
+        <v>540942</v>
       </c>
       <c r="R93" t="n">
-        <v>7193358</v>
+        <v>7193182</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -10539,7 +10543,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10549,7 +10553,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10576,10 +10580,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129319284</v>
+        <v>129319298</v>
       </c>
       <c r="B94" t="n">
-        <v>79044</v>
+        <v>91570</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10587,23 +10591,19 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -10611,10 +10611,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>540867</v>
+        <v>540964</v>
       </c>
       <c r="R94" t="n">
-        <v>7193169</v>
+        <v>7193371</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10656,7 +10656,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10683,32 +10683,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129319393</v>
+        <v>129319284</v>
       </c>
       <c r="B95" t="n">
-        <v>82995</v>
+        <v>79044</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10718,10 +10718,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>540824</v>
+        <v>540867</v>
       </c>
       <c r="R95" t="n">
-        <v>7193288</v>
+        <v>7193169</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -10753,7 +10753,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10763,7 +10763,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10790,32 +10790,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129319299</v>
+        <v>129319393</v>
       </c>
       <c r="B96" t="n">
-        <v>79044</v>
+        <v>82995</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10825,10 +10825,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>540964</v>
+        <v>540824</v>
       </c>
       <c r="R96" t="n">
-        <v>7193371</v>
+        <v>7193288</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -10860,7 +10860,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10870,7 +10870,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11004,10 +11004,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129319359</v>
+        <v>129319399</v>
       </c>
       <c r="B98" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11015,21 +11015,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11039,10 +11039,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>540725</v>
+        <v>540945</v>
       </c>
       <c r="R98" t="n">
-        <v>7193537</v>
+        <v>7193248</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -11074,7 +11074,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11084,7 +11084,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11111,7 +11111,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129319399</v>
+        <v>129319308</v>
       </c>
       <c r="B99" t="n">
         <v>79044</v>
@@ -11146,10 +11146,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>540945</v>
+        <v>540907</v>
       </c>
       <c r="R99" t="n">
-        <v>7193248</v>
+        <v>7193409</v>
       </c>
       <c r="S99" t="n">
         <v>25</v>
@@ -11181,7 +11181,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11191,7 +11191,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11218,7 +11218,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129319308</v>
+        <v>129319286</v>
       </c>
       <c r="B100" t="n">
         <v>79044</v>
@@ -11253,10 +11253,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>540907</v>
+        <v>540891</v>
       </c>
       <c r="R100" t="n">
-        <v>7193409</v>
+        <v>7193174</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -11288,7 +11288,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11298,7 +11298,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11539,10 +11539,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129319286</v>
+        <v>129319359</v>
       </c>
       <c r="B103" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11550,21 +11550,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11574,10 +11574,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>540891</v>
+        <v>540725</v>
       </c>
       <c r="R103" t="n">
-        <v>7193174</v>
+        <v>7193537</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -11609,7 +11609,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11619,7 +11619,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11762,7 +11762,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129319391</v>
+        <v>129319355</v>
       </c>
       <c r="B105" t="n">
         <v>80150</v>
@@ -11797,10 +11797,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>540818</v>
+        <v>540726</v>
       </c>
       <c r="R105" t="n">
-        <v>7193333</v>
+        <v>7193541</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -11832,7 +11832,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11842,7 +11842,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11869,10 +11869,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129319355</v>
+        <v>129319360</v>
       </c>
       <c r="B106" t="n">
-        <v>80150</v>
+        <v>91546</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11880,21 +11880,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11904,10 +11904,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>540726</v>
+        <v>540725</v>
       </c>
       <c r="R106" t="n">
-        <v>7193541</v>
+        <v>7193532</v>
       </c>
       <c r="S106" t="n">
         <v>25</v>
@@ -11939,7 +11939,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11949,7 +11949,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11976,10 +11976,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129319360</v>
+        <v>129319369</v>
       </c>
       <c r="B107" t="n">
-        <v>91546</v>
+        <v>80150</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11987,21 +11987,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12011,10 +12011,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>540725</v>
+        <v>540734</v>
       </c>
       <c r="R107" t="n">
-        <v>7193532</v>
+        <v>7193503</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -12046,7 +12046,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12056,7 +12056,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12083,7 +12083,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129319369</v>
+        <v>129319391</v>
       </c>
       <c r="B108" t="n">
         <v>80150</v>
@@ -12118,10 +12118,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>540734</v>
+        <v>540818</v>
       </c>
       <c r="R108" t="n">
-        <v>7193503</v>
+        <v>7193333</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -12153,7 +12153,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12163,7 +12163,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12190,10 +12190,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129319368</v>
+        <v>129319411</v>
       </c>
       <c r="B109" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12201,21 +12201,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12225,10 +12225,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>540734</v>
+        <v>540955</v>
       </c>
       <c r="R109" t="n">
-        <v>7193503</v>
+        <v>7193186</v>
       </c>
       <c r="S109" t="n">
         <v>25</v>
@@ -12260,7 +12260,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12270,7 +12270,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12297,32 +12297,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129319418</v>
+        <v>129319407</v>
       </c>
       <c r="B110" t="n">
-        <v>80185</v>
+        <v>79044</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12332,10 +12332,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>540986</v>
+        <v>540924</v>
       </c>
       <c r="R110" t="n">
-        <v>7193130</v>
+        <v>7193211</v>
       </c>
       <c r="S110" t="n">
         <v>25</v>
@@ -12367,7 +12367,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12377,7 +12377,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12404,10 +12404,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129319411</v>
+        <v>129319368</v>
       </c>
       <c r="B111" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12415,21 +12415,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12439,10 +12439,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>540955</v>
+        <v>540734</v>
       </c>
       <c r="R111" t="n">
-        <v>7193186</v>
+        <v>7193503</v>
       </c>
       <c r="S111" t="n">
         <v>25</v>
@@ -12474,7 +12474,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12484,7 +12484,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12511,32 +12511,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129319407</v>
+        <v>129319418</v>
       </c>
       <c r="B112" t="n">
-        <v>79044</v>
+        <v>80185</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12546,10 +12546,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>540924</v>
+        <v>540986</v>
       </c>
       <c r="R112" t="n">
-        <v>7193211</v>
+        <v>7193130</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>
@@ -12581,7 +12581,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12591,7 +12591,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12618,27 +12618,27 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129319425</v>
+        <v>129319309</v>
       </c>
       <c r="B113" t="n">
-        <v>80184</v>
+        <v>79044</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -12653,10 +12653,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>540980</v>
+        <v>540894</v>
       </c>
       <c r="R113" t="n">
-        <v>7193116</v>
+        <v>7193411</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -12688,7 +12688,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12725,30 +12725,34 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129319305</v>
+        <v>129319425</v>
       </c>
       <c r="B114" t="n">
-        <v>91570</v>
+        <v>80184</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr"/>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
@@ -12756,10 +12760,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>540959</v>
+        <v>540980</v>
       </c>
       <c r="R114" t="n">
-        <v>7193395</v>
+        <v>7193116</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -12791,7 +12795,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12801,7 +12805,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12828,10 +12832,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129319341</v>
+        <v>129319426</v>
       </c>
       <c r="B115" t="n">
-        <v>91546</v>
+        <v>80150</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12839,21 +12843,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12863,10 +12867,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>540670</v>
+        <v>540979</v>
       </c>
       <c r="R115" t="n">
-        <v>7193533</v>
+        <v>7193115</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -12898,7 +12902,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12908,7 +12912,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12935,10 +12939,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129319426</v>
+        <v>129319341</v>
       </c>
       <c r="B116" t="n">
-        <v>80150</v>
+        <v>91546</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12946,21 +12950,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12970,10 +12974,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>540979</v>
+        <v>540670</v>
       </c>
       <c r="R116" t="n">
-        <v>7193115</v>
+        <v>7193533</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -13005,7 +13009,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13015,7 +13019,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13042,10 +13046,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129319309</v>
+        <v>129319305</v>
       </c>
       <c r="B117" t="n">
-        <v>79044</v>
+        <v>91570</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13053,23 +13057,19 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
@@ -13077,10 +13077,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>540894</v>
+        <v>540959</v>
       </c>
       <c r="R117" t="n">
-        <v>7193411</v>
+        <v>7193395</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -13112,7 +13112,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13122,7 +13122,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13372,32 +13372,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129319325</v>
+        <v>129319416</v>
       </c>
       <c r="B120" t="n">
-        <v>80150</v>
+        <v>80185</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13407,10 +13407,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>540714</v>
+        <v>540970</v>
       </c>
       <c r="R120" t="n">
-        <v>7193488</v>
+        <v>7193154</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -13442,7 +13442,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13452,7 +13452,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13479,32 +13479,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129319277</v>
+        <v>129319373</v>
       </c>
       <c r="B121" t="n">
-        <v>80150</v>
+        <v>80185</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13514,10 +13514,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>540837</v>
+        <v>540734</v>
       </c>
       <c r="R121" t="n">
-        <v>7193042</v>
+        <v>7193499</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -13549,7 +13549,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13559,7 +13559,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13586,7 +13586,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129319319</v>
+        <v>129319277</v>
       </c>
       <c r="B122" t="n">
         <v>80150</v>
@@ -13621,10 +13621,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>540719</v>
+        <v>540837</v>
       </c>
       <c r="R122" t="n">
-        <v>7193463</v>
+        <v>7193042</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -13656,7 +13656,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13666,7 +13666,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13693,32 +13693,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129319416</v>
+        <v>129319325</v>
       </c>
       <c r="B123" t="n">
-        <v>80185</v>
+        <v>80150</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13728,10 +13728,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>540970</v>
+        <v>540714</v>
       </c>
       <c r="R123" t="n">
-        <v>7193154</v>
+        <v>7193488</v>
       </c>
       <c r="S123" t="n">
         <v>25</v>
@@ -13763,7 +13763,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13773,7 +13773,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13800,32 +13800,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129319373</v>
+        <v>129319319</v>
       </c>
       <c r="B124" t="n">
-        <v>80185</v>
+        <v>80150</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13835,10 +13835,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>540734</v>
+        <v>540719</v>
       </c>
       <c r="R124" t="n">
-        <v>7193499</v>
+        <v>7193463</v>
       </c>
       <c r="S124" t="n">
         <v>25</v>
@@ -13870,7 +13870,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13880,7 +13880,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14781,32 +14781,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129319380</v>
+        <v>129319322</v>
       </c>
       <c r="B133" t="n">
-        <v>92268</v>
+        <v>80150</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>3298</v>
+        <v>2081</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14816,10 +14816,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>540761</v>
+        <v>540719</v>
       </c>
       <c r="R133" t="n">
-        <v>7193490</v>
+        <v>7193483</v>
       </c>
       <c r="S133" t="n">
         <v>25</v>
@@ -14851,7 +14851,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14861,7 +14861,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14888,10 +14888,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129319343</v>
+        <v>129319312</v>
       </c>
       <c r="B134" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14899,39 +14899,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>540661</v>
+        <v>540789</v>
       </c>
       <c r="R134" t="n">
-        <v>7193538</v>
+        <v>7193373</v>
       </c>
       <c r="S134" t="n">
         <v>25</v>
@@ -14963,7 +14958,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14973,12 +14968,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>11:27</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>Färska och äldre spår på samma träd.</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15005,10 +14995,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129319378</v>
+        <v>129319380</v>
       </c>
       <c r="B135" t="n">
-        <v>82997</v>
+        <v>92268</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15016,21 +15006,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>306</v>
+        <v>3298</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15040,10 +15030,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>540757</v>
+        <v>540761</v>
       </c>
       <c r="R135" t="n">
-        <v>7193474</v>
+        <v>7193490</v>
       </c>
       <c r="S135" t="n">
         <v>25</v>
@@ -15075,7 +15065,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15085,7 +15075,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15112,32 +15102,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129319312</v>
+        <v>129319378</v>
       </c>
       <c r="B136" t="n">
-        <v>80150</v>
+        <v>82997</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>2081</v>
+        <v>306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15147,10 +15137,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>540789</v>
+        <v>540757</v>
       </c>
       <c r="R136" t="n">
-        <v>7193373</v>
+        <v>7193474</v>
       </c>
       <c r="S136" t="n">
         <v>25</v>
@@ -15182,7 +15172,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15192,7 +15182,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15219,10 +15209,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129319322</v>
+        <v>129319343</v>
       </c>
       <c r="B137" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15230,34 +15220,39 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>540719</v>
+        <v>540661</v>
       </c>
       <c r="R137" t="n">
-        <v>7193483</v>
+        <v>7193538</v>
       </c>
       <c r="S137" t="n">
         <v>25</v>
@@ -15289,7 +15284,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15299,7 +15294,12 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>Färska och äldre spår på samma träd.</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15326,10 +15326,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129319428</v>
+        <v>129319387</v>
       </c>
       <c r="B138" t="n">
-        <v>80149</v>
+        <v>83004</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15337,21 +15337,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15361,10 +15361,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>540971</v>
+        <v>540772</v>
       </c>
       <c r="R138" t="n">
-        <v>7193081</v>
+        <v>7193446</v>
       </c>
       <c r="S138" t="n">
         <v>25</v>
@@ -15396,7 +15396,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15406,7 +15406,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15433,10 +15433,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129319347</v>
+        <v>129319287</v>
       </c>
       <c r="B139" t="n">
-        <v>80185</v>
+        <v>92268</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15444,21 +15444,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6464</v>
+        <v>3298</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15468,10 +15468,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>540653</v>
+        <v>540913</v>
       </c>
       <c r="R139" t="n">
-        <v>7193521</v>
+        <v>7193185</v>
       </c>
       <c r="S139" t="n">
         <v>25</v>
@@ -15503,7 +15503,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15513,7 +15513,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15540,10 +15540,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129319387</v>
+        <v>129319428</v>
       </c>
       <c r="B140" t="n">
-        <v>83004</v>
+        <v>80149</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15551,21 +15551,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15575,10 +15575,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>540772</v>
+        <v>540971</v>
       </c>
       <c r="R140" t="n">
-        <v>7193446</v>
+        <v>7193081</v>
       </c>
       <c r="S140" t="n">
         <v>25</v>
@@ -15610,7 +15610,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15620,7 +15620,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15647,32 +15647,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129319406</v>
+        <v>129319347</v>
       </c>
       <c r="B141" t="n">
-        <v>79123</v>
+        <v>80185</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>864</v>
+        <v>6464</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15682,10 +15682,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>540938</v>
+        <v>540653</v>
       </c>
       <c r="R141" t="n">
-        <v>7193168</v>
+        <v>7193521</v>
       </c>
       <c r="S141" t="n">
         <v>25</v>
@@ -15717,7 +15717,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15727,7 +15727,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15754,32 +15754,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129319315</v>
+        <v>129319406</v>
       </c>
       <c r="B142" t="n">
-        <v>82995</v>
+        <v>79123</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6439</v>
+        <v>864</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15789,10 +15789,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>540765</v>
+        <v>540938</v>
       </c>
       <c r="R142" t="n">
-        <v>7193370</v>
+        <v>7193168</v>
       </c>
       <c r="S142" t="n">
         <v>25</v>
@@ -15824,7 +15824,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15968,10 +15968,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129319287</v>
+        <v>129319315</v>
       </c>
       <c r="B144" t="n">
-        <v>92268</v>
+        <v>82995</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15979,21 +15979,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>3298</v>
+        <v>6439</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -16003,10 +16003,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>540913</v>
+        <v>540765</v>
       </c>
       <c r="R144" t="n">
-        <v>7193185</v>
+        <v>7193370</v>
       </c>
       <c r="S144" t="n">
         <v>25</v>
@@ -16038,7 +16038,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16048,7 +16048,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD144" t="b">

--- a/artfynd/A 51086-2025 artfynd.xlsx
+++ b/artfynd/A 51086-2025 artfynd.xlsx
@@ -1652,10 +1652,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129319361</v>
+        <v>129319296</v>
       </c>
       <c r="B11" t="n">
-        <v>91550</v>
+        <v>79044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1663,21 +1663,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540726</v>
+        <v>540970</v>
       </c>
       <c r="R11" t="n">
-        <v>7193531</v>
+        <v>7193365</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1759,32 +1759,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129319424</v>
+        <v>129319419</v>
       </c>
       <c r="B12" t="n">
-        <v>80150</v>
+        <v>80184</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1794,10 +1794,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540975</v>
+        <v>540986</v>
       </c>
       <c r="R12" t="n">
-        <v>7193139</v>
+        <v>7193130</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1829,7 +1829,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1866,10 +1866,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129319381</v>
+        <v>129319328</v>
       </c>
       <c r="B13" t="n">
-        <v>82878</v>
+        <v>80149</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1877,21 +1877,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1901,10 +1901,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540758</v>
+        <v>540693</v>
       </c>
       <c r="R13" t="n">
-        <v>7193475</v>
+        <v>7193540</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1973,10 +1973,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129319295</v>
+        <v>129319313</v>
       </c>
       <c r="B14" t="n">
-        <v>95950</v>
+        <v>80185</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1984,21 +1984,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2809</v>
+        <v>6464</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2008,10 +2008,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540972</v>
+        <v>540789</v>
       </c>
       <c r="R14" t="n">
-        <v>7193357</v>
+        <v>7193372</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2080,10 +2080,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129319296</v>
+        <v>129319324</v>
       </c>
       <c r="B15" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2091,21 +2091,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540970</v>
+        <v>540719</v>
       </c>
       <c r="R15" t="n">
-        <v>7193365</v>
+        <v>7193483</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2187,7 +2187,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129319419</v>
+        <v>129319430</v>
       </c>
       <c r="B16" t="n">
         <v>80184</v>
@@ -2222,10 +2222,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540986</v>
+        <v>540971</v>
       </c>
       <c r="R16" t="n">
-        <v>7193130</v>
+        <v>7193066</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2294,10 +2294,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129319328</v>
+        <v>129319361</v>
       </c>
       <c r="B17" t="n">
-        <v>80149</v>
+        <v>91550</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2305,21 +2305,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2329,10 +2329,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540693</v>
+        <v>540726</v>
       </c>
       <c r="R17" t="n">
-        <v>7193540</v>
+        <v>7193531</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2401,32 +2401,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129319313</v>
+        <v>129319424</v>
       </c>
       <c r="B18" t="n">
-        <v>80185</v>
+        <v>80150</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2436,10 +2436,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540789</v>
+        <v>540975</v>
       </c>
       <c r="R18" t="n">
-        <v>7193372</v>
+        <v>7193139</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2508,10 +2508,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129319324</v>
+        <v>129319381</v>
       </c>
       <c r="B19" t="n">
-        <v>80149</v>
+        <v>82878</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,21 +2519,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2543,10 +2543,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540719</v>
+        <v>540758</v>
       </c>
       <c r="R19" t="n">
-        <v>7193483</v>
+        <v>7193475</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2615,10 +2615,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129319430</v>
+        <v>129319295</v>
       </c>
       <c r="B20" t="n">
-        <v>80184</v>
+        <v>95950</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2626,21 +2626,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6463</v>
+        <v>2809</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540971</v>
+        <v>540972</v>
       </c>
       <c r="R20" t="n">
-        <v>7193066</v>
+        <v>7193357</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2945,10 +2945,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129319281</v>
+        <v>129319383</v>
       </c>
       <c r="B23" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2956,21 +2956,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2980,10 +2980,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540902</v>
+        <v>540764</v>
       </c>
       <c r="R23" t="n">
-        <v>7193083</v>
+        <v>7193475</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3015,7 +3015,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3052,10 +3052,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129319316</v>
+        <v>129319390</v>
       </c>
       <c r="B24" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3063,21 +3063,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3087,10 +3087,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540763</v>
+        <v>540818</v>
       </c>
       <c r="R24" t="n">
-        <v>7193372</v>
+        <v>7193358</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3159,10 +3159,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129319291</v>
+        <v>129319354</v>
       </c>
       <c r="B25" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3170,21 +3170,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3194,10 +3194,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540996</v>
+        <v>540722</v>
       </c>
       <c r="R25" t="n">
-        <v>7193327</v>
+        <v>7193542</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3229,7 +3229,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3239,7 +3239,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3266,10 +3266,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129319340</v>
+        <v>129319349</v>
       </c>
       <c r="B26" t="n">
-        <v>91550</v>
+        <v>91570</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3277,23 +3277,19 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3301,10 +3297,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540666</v>
+        <v>540670</v>
       </c>
       <c r="R26" t="n">
-        <v>7193537</v>
+        <v>7193521</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3336,7 +3332,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3346,7 +3342,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3373,10 +3369,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129319383</v>
+        <v>129319281</v>
       </c>
       <c r="B27" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3384,21 +3380,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3408,10 +3404,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>540764</v>
+        <v>540902</v>
       </c>
       <c r="R27" t="n">
-        <v>7193475</v>
+        <v>7193083</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3443,7 +3439,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3453,7 +3449,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3480,10 +3476,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129319390</v>
+        <v>129319316</v>
       </c>
       <c r="B28" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3491,21 +3487,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3515,10 +3511,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>540818</v>
+        <v>540763</v>
       </c>
       <c r="R28" t="n">
-        <v>7193358</v>
+        <v>7193372</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3550,7 +3546,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3560,7 +3556,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3587,10 +3583,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129319354</v>
+        <v>129319291</v>
       </c>
       <c r="B29" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3598,21 +3594,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3622,10 +3618,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>540722</v>
+        <v>540996</v>
       </c>
       <c r="R29" t="n">
-        <v>7193542</v>
+        <v>7193327</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3657,7 +3653,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3667,7 +3663,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3694,10 +3690,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129319349</v>
+        <v>129319340</v>
       </c>
       <c r="B30" t="n">
-        <v>91570</v>
+        <v>91550</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3705,19 +3701,23 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3725,10 +3725,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>540670</v>
+        <v>540666</v>
       </c>
       <c r="R30" t="n">
-        <v>7193521</v>
+        <v>7193537</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3760,7 +3760,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3797,10 +3797,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129319377</v>
+        <v>129319404</v>
       </c>
       <c r="B31" t="n">
-        <v>80150</v>
+        <v>78057</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3808,21 +3808,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>228579</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>540745</v>
+        <v>540931</v>
       </c>
       <c r="R31" t="n">
-        <v>7193494</v>
+        <v>7193220</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3867,7 +3867,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3904,10 +3904,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129319374</v>
+        <v>129319405</v>
       </c>
       <c r="B32" t="n">
-        <v>80150</v>
+        <v>83012</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3915,21 +3915,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3939,10 +3939,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>540734</v>
+        <v>540931</v>
       </c>
       <c r="R32" t="n">
-        <v>7193499</v>
+        <v>7193220</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4011,10 +4011,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129319405</v>
+        <v>129319427</v>
       </c>
       <c r="B33" t="n">
-        <v>83012</v>
+        <v>79044</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4022,21 +4022,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4046,10 +4046,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>540931</v>
+        <v>540969</v>
       </c>
       <c r="R33" t="n">
-        <v>7193220</v>
+        <v>7193117</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4081,7 +4081,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4118,7 +4118,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129319427</v>
+        <v>129319396</v>
       </c>
       <c r="B34" t="n">
         <v>79044</v>
@@ -4153,10 +4153,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>540969</v>
+        <v>540928</v>
       </c>
       <c r="R34" t="n">
-        <v>7193117</v>
+        <v>7193263</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4225,7 +4225,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129319396</v>
+        <v>129319282</v>
       </c>
       <c r="B35" t="n">
         <v>79044</v>
@@ -4260,10 +4260,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>540928</v>
+        <v>540901</v>
       </c>
       <c r="R35" t="n">
-        <v>7193263</v>
+        <v>7193084</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4295,7 +4295,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4305,7 +4305,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4332,10 +4332,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129319282</v>
+        <v>129319337</v>
       </c>
       <c r="B36" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4343,21 +4343,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4367,10 +4367,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>540901</v>
+        <v>540676</v>
       </c>
       <c r="R36" t="n">
-        <v>7193084</v>
+        <v>7193539</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4402,7 +4402,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4439,32 +4439,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129319337</v>
+        <v>129319422</v>
       </c>
       <c r="B37" t="n">
-        <v>80149</v>
+        <v>80184</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4474,10 +4474,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>540676</v>
+        <v>540980</v>
       </c>
       <c r="R37" t="n">
-        <v>7193539</v>
+        <v>7193139</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4546,32 +4546,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129319422</v>
+        <v>129319374</v>
       </c>
       <c r="B38" t="n">
-        <v>80184</v>
+        <v>80150</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>540980</v>
+        <v>540734</v>
       </c>
       <c r="R38" t="n">
-        <v>7193139</v>
+        <v>7193499</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4653,10 +4653,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129319404</v>
+        <v>129319377</v>
       </c>
       <c r="B39" t="n">
-        <v>78057</v>
+        <v>80150</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4664,21 +4664,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228579</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4688,10 +4688,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>540931</v>
+        <v>540745</v>
       </c>
       <c r="R39" t="n">
-        <v>7193220</v>
+        <v>7193494</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4760,32 +4760,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129319395</v>
+        <v>129319278</v>
       </c>
       <c r="B40" t="n">
-        <v>82997</v>
+        <v>80150</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>306</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>540878</v>
+        <v>540864</v>
       </c>
       <c r="R40" t="n">
-        <v>7193291</v>
+        <v>7193066</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4840,7 +4840,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4867,10 +4867,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129319303</v>
+        <v>129319365</v>
       </c>
       <c r="B41" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4878,21 +4878,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>540934</v>
+        <v>540738</v>
       </c>
       <c r="R41" t="n">
-        <v>7193385</v>
+        <v>7193503</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4947,7 +4947,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4974,10 +4974,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129319288</v>
+        <v>129319294</v>
       </c>
       <c r="B42" t="n">
-        <v>79044</v>
+        <v>83017</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4985,21 +4985,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>540915</v>
+        <v>540974</v>
       </c>
       <c r="R42" t="n">
-        <v>7193185</v>
+        <v>7193351</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5081,10 +5081,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129319278</v>
+        <v>129319348</v>
       </c>
       <c r="B43" t="n">
-        <v>80150</v>
+        <v>80149</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5092,21 +5092,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5116,10 +5116,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540864</v>
+        <v>540653</v>
       </c>
       <c r="R43" t="n">
-        <v>7193066</v>
+        <v>7193521</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5188,32 +5188,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129319365</v>
+        <v>129319401</v>
       </c>
       <c r="B44" t="n">
-        <v>80150</v>
+        <v>80178</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540738</v>
+        <v>540942</v>
       </c>
       <c r="R44" t="n">
-        <v>7193503</v>
+        <v>7193229</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5295,10 +5295,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129319294</v>
+        <v>129319403</v>
       </c>
       <c r="B45" t="n">
-        <v>83017</v>
+        <v>80149</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5306,21 +5306,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1467</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5330,10 +5330,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>540974</v>
+        <v>540930</v>
       </c>
       <c r="R45" t="n">
-        <v>7193351</v>
+        <v>7193219</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5365,7 +5365,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5375,7 +5375,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5402,32 +5402,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129319348</v>
+        <v>129319320</v>
       </c>
       <c r="B46" t="n">
-        <v>80149</v>
+        <v>80184</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5437,10 +5437,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>540653</v>
+        <v>540719</v>
       </c>
       <c r="R46" t="n">
-        <v>7193521</v>
+        <v>7193463</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5472,7 +5472,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5509,10 +5509,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129319401</v>
+        <v>129319395</v>
       </c>
       <c r="B47" t="n">
-        <v>80178</v>
+        <v>82997</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5520,21 +5520,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6462</v>
+        <v>306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5544,10 +5544,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>540942</v>
+        <v>540878</v>
       </c>
       <c r="R47" t="n">
-        <v>7193229</v>
+        <v>7193291</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5579,7 +5579,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5616,10 +5616,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129319403</v>
+        <v>129319303</v>
       </c>
       <c r="B48" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5627,21 +5627,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5651,10 +5651,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>540930</v>
+        <v>540934</v>
       </c>
       <c r="R48" t="n">
-        <v>7193219</v>
+        <v>7193385</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5686,7 +5686,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5723,27 +5723,27 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129319320</v>
+        <v>129319288</v>
       </c>
       <c r="B49" t="n">
-        <v>80184</v>
+        <v>79044</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>540719</v>
+        <v>540915</v>
       </c>
       <c r="R49" t="n">
-        <v>7193463</v>
+        <v>7193185</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6258,10 +6258,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129319429</v>
+        <v>129319388</v>
       </c>
       <c r="B54" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6269,34 +6269,48 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>540972</v>
+        <v>540828</v>
       </c>
       <c r="R54" t="n">
-        <v>7193067</v>
+        <v>7193425</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6328,7 +6342,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6338,7 +6352,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6365,7 +6379,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129319417</v>
+        <v>129319429</v>
       </c>
       <c r="B55" t="n">
         <v>80150</v>
@@ -6400,10 +6414,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>540989</v>
+        <v>540972</v>
       </c>
       <c r="R55" t="n">
-        <v>7193132</v>
+        <v>7193067</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6435,7 +6449,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6445,7 +6459,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6472,10 +6486,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129319388</v>
+        <v>129319417</v>
       </c>
       <c r="B56" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6483,48 +6497,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>540828</v>
+        <v>540989</v>
       </c>
       <c r="R56" t="n">
-        <v>7193425</v>
+        <v>7193132</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6556,7 +6556,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6700,10 +6700,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129319292</v>
+        <v>129319353</v>
       </c>
       <c r="B58" t="n">
-        <v>79044</v>
+        <v>82878</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6711,21 +6711,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6735,10 +6735,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>540996</v>
+        <v>540721</v>
       </c>
       <c r="R58" t="n">
-        <v>7193327</v>
+        <v>7193542</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6807,10 +6807,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129319392</v>
+        <v>129319279</v>
       </c>
       <c r="B59" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6818,21 +6818,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6842,10 +6842,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>540826</v>
+        <v>540872</v>
       </c>
       <c r="R59" t="n">
-        <v>7193294</v>
+        <v>7193070</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6877,7 +6877,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6914,10 +6914,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129319353</v>
+        <v>129319292</v>
       </c>
       <c r="B60" t="n">
-        <v>82878</v>
+        <v>79044</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6925,21 +6925,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6949,10 +6949,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>540721</v>
+        <v>540996</v>
       </c>
       <c r="R60" t="n">
-        <v>7193542</v>
+        <v>7193327</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6984,7 +6984,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6994,7 +6994,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7021,32 +7021,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129319279</v>
+        <v>129319330</v>
       </c>
       <c r="B61" t="n">
-        <v>80150</v>
+        <v>82995</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2081</v>
+        <v>6439</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7056,10 +7056,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>540872</v>
+        <v>540683</v>
       </c>
       <c r="R61" t="n">
-        <v>7193070</v>
+        <v>7193545</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7091,7 +7091,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7128,10 +7128,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129319339</v>
+        <v>129319392</v>
       </c>
       <c r="B62" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7139,21 +7139,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7163,10 +7163,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>540669</v>
+        <v>540826</v>
       </c>
       <c r="R62" t="n">
-        <v>7193542</v>
+        <v>7193294</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7208,7 +7208,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7235,45 +7235,54 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129319311</v>
+        <v>129319423</v>
       </c>
       <c r="B63" t="n">
-        <v>91546</v>
+        <v>57831</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1108</v>
+        <v>103031</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>540830</v>
+        <v>540976</v>
       </c>
       <c r="R63" t="n">
-        <v>7193366</v>
+        <v>7193139</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7305,7 +7314,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7315,7 +7324,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7342,54 +7351,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129319423</v>
+        <v>129319339</v>
       </c>
       <c r="B64" t="n">
-        <v>57831</v>
+        <v>80150</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103031</v>
+        <v>2081</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>540976</v>
+        <v>540669</v>
       </c>
       <c r="R64" t="n">
-        <v>7193139</v>
+        <v>7193542</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7431,7 +7431,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7458,32 +7458,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129319330</v>
+        <v>129319311</v>
       </c>
       <c r="B65" t="n">
-        <v>82995</v>
+        <v>91546</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6439</v>
+        <v>1108</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7493,10 +7493,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>540683</v>
+        <v>540830</v>
       </c>
       <c r="R65" t="n">
-        <v>7193545</v>
+        <v>7193366</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7528,7 +7528,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7672,10 +7672,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129319293</v>
+        <v>129319400</v>
       </c>
       <c r="B67" t="n">
-        <v>57887</v>
+        <v>79044</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7683,43 +7683,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>540980</v>
+        <v>540943</v>
       </c>
       <c r="R67" t="n">
-        <v>7193345</v>
+        <v>7193233</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7751,7 +7742,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7761,7 +7752,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7788,7 +7779,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129319400</v>
+        <v>129319397</v>
       </c>
       <c r="B68" t="n">
         <v>79044</v>
@@ -7823,10 +7814,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>540943</v>
+        <v>540946</v>
       </c>
       <c r="R68" t="n">
-        <v>7193233</v>
+        <v>7193256</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7858,7 +7849,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7868,7 +7859,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7895,32 +7886,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129319397</v>
+        <v>129319421</v>
       </c>
       <c r="B69" t="n">
-        <v>79044</v>
+        <v>80178</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7930,10 +7921,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>540946</v>
+        <v>540981</v>
       </c>
       <c r="R69" t="n">
-        <v>7193256</v>
+        <v>7193140</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7965,7 +7956,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7975,7 +7966,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8002,32 +7993,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129319421</v>
+        <v>129319334</v>
       </c>
       <c r="B70" t="n">
-        <v>80178</v>
+        <v>80149</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8037,10 +8028,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>540981</v>
+        <v>540674</v>
       </c>
       <c r="R70" t="n">
-        <v>7193140</v>
+        <v>7193550</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8072,7 +8063,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8082,7 +8073,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8109,32 +8100,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129319334</v>
+        <v>129319370</v>
       </c>
       <c r="B71" t="n">
-        <v>80149</v>
+        <v>80178</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8144,10 +8135,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>540674</v>
+        <v>540737</v>
       </c>
       <c r="R71" t="n">
-        <v>7193550</v>
+        <v>7193504</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8179,7 +8170,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8189,7 +8180,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8216,45 +8207,54 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129319370</v>
+        <v>129319293</v>
       </c>
       <c r="B72" t="n">
-        <v>80178</v>
+        <v>57887</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>540737</v>
+        <v>540980</v>
       </c>
       <c r="R72" t="n">
-        <v>7193504</v>
+        <v>7193345</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8286,7 +8286,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8863,10 +8863,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129319371</v>
+        <v>129319342</v>
       </c>
       <c r="B78" t="n">
-        <v>80149</v>
+        <v>57724</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8874,34 +8874,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>540737</v>
+        <v>540667</v>
       </c>
       <c r="R78" t="n">
-        <v>7193504</v>
+        <v>7193539</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8933,7 +8938,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8943,7 +8948,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8970,10 +8975,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129319342</v>
+        <v>129319371</v>
       </c>
       <c r="B79" t="n">
-        <v>57724</v>
+        <v>80149</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8981,39 +8986,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>540667</v>
+        <v>540737</v>
       </c>
       <c r="R79" t="n">
-        <v>7193539</v>
+        <v>7193504</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9045,7 +9045,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9724,10 +9724,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129319333</v>
+        <v>129319299</v>
       </c>
       <c r="B86" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9735,21 +9735,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9759,10 +9759,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>540674</v>
+        <v>540964</v>
       </c>
       <c r="R86" t="n">
-        <v>7193551</v>
+        <v>7193371</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9794,7 +9794,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9804,7 +9804,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9831,10 +9831,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129319376</v>
+        <v>129319284</v>
       </c>
       <c r="B87" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9842,21 +9842,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9866,10 +9866,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>540738</v>
+        <v>540867</v>
       </c>
       <c r="R87" t="n">
-        <v>7193476</v>
+        <v>7193169</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -9901,7 +9901,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9911,7 +9911,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9938,32 +9938,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129319375</v>
+        <v>129319393</v>
       </c>
       <c r="B88" t="n">
-        <v>80150</v>
+        <v>82995</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2081</v>
+        <v>6439</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9973,10 +9973,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>540730</v>
+        <v>540824</v>
       </c>
       <c r="R88" t="n">
-        <v>7193493</v>
+        <v>7193288</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -10008,7 +10008,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10018,7 +10018,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10045,10 +10045,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129319433</v>
+        <v>129319344</v>
       </c>
       <c r="B89" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10056,21 +10056,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10080,10 +10080,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>540979</v>
+        <v>540650</v>
       </c>
       <c r="R89" t="n">
-        <v>7193075</v>
+        <v>7193540</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -10115,7 +10115,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10125,7 +10125,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10152,10 +10152,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129319357</v>
+        <v>129319298</v>
       </c>
       <c r="B90" t="n">
-        <v>80150</v>
+        <v>91570</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10163,23 +10163,19 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
@@ -10187,10 +10183,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>540726</v>
+        <v>540964</v>
       </c>
       <c r="R90" t="n">
-        <v>7193539</v>
+        <v>7193371</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -10222,7 +10218,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10232,7 +10228,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10259,32 +10255,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129319389</v>
+        <v>129319333</v>
       </c>
       <c r="B91" t="n">
-        <v>95950</v>
+        <v>80150</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2809</v>
+        <v>2081</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10294,10 +10290,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>540818</v>
+        <v>540674</v>
       </c>
       <c r="R91" t="n">
-        <v>7193358</v>
+        <v>7193551</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -10329,7 +10325,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10339,7 +10335,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10366,10 +10362,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129319299</v>
+        <v>129319376</v>
       </c>
       <c r="B92" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10377,21 +10373,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10401,10 +10397,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>540964</v>
+        <v>540738</v>
       </c>
       <c r="R92" t="n">
-        <v>7193371</v>
+        <v>7193476</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -10436,7 +10432,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10446,7 +10442,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10473,10 +10469,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129319409</v>
+        <v>129319375</v>
       </c>
       <c r="B93" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10484,21 +10480,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10508,10 +10504,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>540942</v>
+        <v>540730</v>
       </c>
       <c r="R93" t="n">
-        <v>7193182</v>
+        <v>7193493</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -10543,7 +10539,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10553,7 +10549,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10580,10 +10576,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129319298</v>
+        <v>129319433</v>
       </c>
       <c r="B94" t="n">
-        <v>91570</v>
+        <v>80150</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10591,19 +10587,23 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr"/>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -10611,10 +10611,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>540964</v>
+        <v>540979</v>
       </c>
       <c r="R94" t="n">
-        <v>7193371</v>
+        <v>7193075</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10656,7 +10656,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10683,10 +10683,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129319284</v>
+        <v>129319357</v>
       </c>
       <c r="B95" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10694,21 +10694,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10718,10 +10718,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>540867</v>
+        <v>540726</v>
       </c>
       <c r="R95" t="n">
-        <v>7193169</v>
+        <v>7193539</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -10753,7 +10753,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10763,7 +10763,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10790,10 +10790,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129319393</v>
+        <v>129319389</v>
       </c>
       <c r="B96" t="n">
-        <v>82995</v>
+        <v>95950</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10801,21 +10801,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6439</v>
+        <v>2809</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10825,10 +10825,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>540824</v>
+        <v>540818</v>
       </c>
       <c r="R96" t="n">
-        <v>7193288</v>
+        <v>7193358</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -10860,7 +10860,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10870,7 +10870,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10897,10 +10897,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129319344</v>
+        <v>129319409</v>
       </c>
       <c r="B97" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10908,21 +10908,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10932,10 +10932,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>540650</v>
+        <v>540942</v>
       </c>
       <c r="R97" t="n">
-        <v>7193540</v>
+        <v>7193182</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -10967,7 +10967,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10977,7 +10977,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12618,10 +12618,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129319309</v>
+        <v>129319332</v>
       </c>
       <c r="B113" t="n">
-        <v>79044</v>
+        <v>57887</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12629,34 +12629,43 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>540894</v>
+        <v>540675</v>
       </c>
       <c r="R113" t="n">
-        <v>7193411</v>
+        <v>7193538</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -12688,7 +12697,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12698,7 +12707,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12725,32 +12734,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129319425</v>
+        <v>129319426</v>
       </c>
       <c r="B114" t="n">
-        <v>80184</v>
+        <v>80150</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12760,10 +12769,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>540980</v>
+        <v>540979</v>
       </c>
       <c r="R114" t="n">
-        <v>7193116</v>
+        <v>7193115</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -12832,10 +12841,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129319426</v>
+        <v>129319341</v>
       </c>
       <c r="B115" t="n">
-        <v>80150</v>
+        <v>91546</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12843,21 +12852,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12867,10 +12876,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>540979</v>
+        <v>540670</v>
       </c>
       <c r="R115" t="n">
-        <v>7193115</v>
+        <v>7193533</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -12902,7 +12911,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12912,7 +12921,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12939,10 +12948,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129319341</v>
+        <v>129319309</v>
       </c>
       <c r="B116" t="n">
-        <v>91546</v>
+        <v>79044</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12950,21 +12959,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12974,10 +12983,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>540670</v>
+        <v>540894</v>
       </c>
       <c r="R116" t="n">
-        <v>7193533</v>
+        <v>7193411</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -13009,7 +13018,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13019,7 +13028,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13046,30 +13055,34 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129319305</v>
+        <v>129319425</v>
       </c>
       <c r="B117" t="n">
-        <v>91570</v>
+        <v>80184</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr"/>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
@@ -13077,10 +13090,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>540959</v>
+        <v>540980</v>
       </c>
       <c r="R117" t="n">
-        <v>7193395</v>
+        <v>7193116</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -13112,7 +13125,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13122,7 +13135,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13149,10 +13162,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129319332</v>
+        <v>129319305</v>
       </c>
       <c r="B118" t="n">
-        <v>57887</v>
+        <v>91570</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13160,43 +13173,30 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>540675</v>
+        <v>540959</v>
       </c>
       <c r="R118" t="n">
-        <v>7193538</v>
+        <v>7193395</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -13228,7 +13228,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13238,7 +13238,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -14674,32 +14674,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129319310</v>
+        <v>129319378</v>
       </c>
       <c r="B132" t="n">
-        <v>79044</v>
+        <v>82997</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14709,10 +14709,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>540830</v>
+        <v>540757</v>
       </c>
       <c r="R132" t="n">
-        <v>7193366</v>
+        <v>7193474</v>
       </c>
       <c r="S132" t="n">
         <v>25</v>
@@ -14744,7 +14744,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14754,7 +14754,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15102,32 +15102,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129319378</v>
+        <v>129319310</v>
       </c>
       <c r="B136" t="n">
-        <v>82997</v>
+        <v>79044</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>306</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15137,10 +15137,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>540757</v>
+        <v>540830</v>
       </c>
       <c r="R136" t="n">
-        <v>7193474</v>
+        <v>7193366</v>
       </c>
       <c r="S136" t="n">
         <v>25</v>
@@ -15172,7 +15172,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15182,7 +15182,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD136" t="b">

--- a/artfynd/A 51086-2025 artfynd.xlsx
+++ b/artfynd/A 51086-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129319307</v>
+        <v>129319384</v>
       </c>
       <c r="B2" t="n">
-        <v>91546</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540962</v>
+        <v>540775</v>
       </c>
       <c r="R2" t="n">
-        <v>7193400</v>
+        <v>7193467</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129319285</v>
+        <v>129319302</v>
       </c>
       <c r="B3" t="n">
-        <v>91546</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540886</v>
+        <v>540960</v>
       </c>
       <c r="R3" t="n">
-        <v>7193172</v>
+        <v>7193375</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,45 +889,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129319386</v>
+        <v>129319300</v>
       </c>
       <c r="B4" t="n">
-        <v>95950</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2809</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540774</v>
+        <v>540961</v>
       </c>
       <c r="R4" t="n">
-        <v>7193457</v>
+        <v>7193376</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -959,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,32 +1001,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129319384</v>
+        <v>129319323</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>80185</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540775</v>
+        <v>540719</v>
       </c>
       <c r="R5" t="n">
-        <v>7193467</v>
+        <v>7193483</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1066,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129319302</v>
+        <v>129319420</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540960</v>
+        <v>540982</v>
       </c>
       <c r="R6" t="n">
-        <v>7193375</v>
+        <v>7193144</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1173,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,27 +1215,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129319300</v>
+        <v>129319414</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>58360</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>102125</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1238,10 +1243,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1250,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540961</v>
+        <v>540963</v>
       </c>
       <c r="R7" t="n">
-        <v>7193376</v>
+        <v>7193203</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1285,7 +1294,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1295,7 +1304,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1322,32 +1331,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129319323</v>
+        <v>129319307</v>
       </c>
       <c r="B8" t="n">
-        <v>80185</v>
+        <v>91549</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6464</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1357,10 +1366,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540719</v>
+        <v>540962</v>
       </c>
       <c r="R8" t="n">
-        <v>7193483</v>
+        <v>7193400</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1392,7 +1401,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1402,7 +1411,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1429,32 +1438,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129319420</v>
+        <v>129319386</v>
       </c>
       <c r="B9" t="n">
-        <v>80149</v>
+        <v>95953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>2809</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1473,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540982</v>
+        <v>540774</v>
       </c>
       <c r="R9" t="n">
-        <v>7193144</v>
+        <v>7193457</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1499,7 +1508,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1509,7 +1518,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,54 +1545,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129319414</v>
+        <v>129319285</v>
       </c>
       <c r="B10" t="n">
-        <v>58360</v>
+        <v>91549</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102125</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540963</v>
+        <v>540886</v>
       </c>
       <c r="R10" t="n">
-        <v>7193203</v>
+        <v>7193172</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1615,7 +1615,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2294,10 +2294,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129319361</v>
+        <v>129319381</v>
       </c>
       <c r="B17" t="n">
-        <v>91550</v>
+        <v>82878</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2305,21 +2305,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2329,10 +2329,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540726</v>
+        <v>540758</v>
       </c>
       <c r="R17" t="n">
-        <v>7193531</v>
+        <v>7193475</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2508,32 +2508,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129319381</v>
+        <v>129319295</v>
       </c>
       <c r="B19" t="n">
-        <v>82878</v>
+        <v>95953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>2809</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2543,10 +2543,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540758</v>
+        <v>540972</v>
       </c>
       <c r="R19" t="n">
-        <v>7193475</v>
+        <v>7193357</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2615,32 +2615,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129319295</v>
+        <v>129319361</v>
       </c>
       <c r="B20" t="n">
-        <v>95950</v>
+        <v>91553</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2809</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540972</v>
+        <v>540726</v>
       </c>
       <c r="R20" t="n">
-        <v>7193357</v>
+        <v>7193531</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2945,7 +2945,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129319383</v>
+        <v>129319390</v>
       </c>
       <c r="B23" t="n">
         <v>79044</v>
@@ -2980,10 +2980,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540764</v>
+        <v>540818</v>
       </c>
       <c r="R23" t="n">
-        <v>7193475</v>
+        <v>7193358</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3015,7 +3015,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3052,7 +3052,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129319390</v>
+        <v>129319383</v>
       </c>
       <c r="B24" t="n">
         <v>79044</v>
@@ -3087,10 +3087,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540818</v>
+        <v>540764</v>
       </c>
       <c r="R24" t="n">
-        <v>7193358</v>
+        <v>7193475</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3266,10 +3266,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129319349</v>
+        <v>129319316</v>
       </c>
       <c r="B26" t="n">
-        <v>91570</v>
+        <v>80150</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3277,19 +3277,23 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3297,10 +3301,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540670</v>
+        <v>540763</v>
       </c>
       <c r="R26" t="n">
-        <v>7193521</v>
+        <v>7193372</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3332,7 +3336,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3342,7 +3346,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3476,7 +3480,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129319316</v>
+        <v>129319291</v>
       </c>
       <c r="B28" t="n">
         <v>80150</v>
@@ -3511,10 +3515,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>540763</v>
+        <v>540996</v>
       </c>
       <c r="R28" t="n">
-        <v>7193372</v>
+        <v>7193327</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3546,7 +3550,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3556,7 +3560,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3583,10 +3587,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129319291</v>
+        <v>129319340</v>
       </c>
       <c r="B29" t="n">
-        <v>80150</v>
+        <v>91553</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3594,21 +3598,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3618,10 +3622,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>540996</v>
+        <v>540666</v>
       </c>
       <c r="R29" t="n">
-        <v>7193327</v>
+        <v>7193537</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3653,7 +3657,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3663,7 +3667,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3690,10 +3694,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129319340</v>
+        <v>129319349</v>
       </c>
       <c r="B30" t="n">
-        <v>91550</v>
+        <v>91573</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3701,23 +3705,19 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3725,10 +3725,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>540666</v>
+        <v>540670</v>
       </c>
       <c r="R30" t="n">
-        <v>7193537</v>
+        <v>7193521</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3760,7 +3760,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3797,10 +3797,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129319404</v>
+        <v>129319337</v>
       </c>
       <c r="B31" t="n">
-        <v>78057</v>
+        <v>80149</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3808,21 +3808,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>540931</v>
+        <v>540676</v>
       </c>
       <c r="R31" t="n">
-        <v>7193220</v>
+        <v>7193539</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3867,7 +3867,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3904,10 +3904,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129319405</v>
+        <v>129319396</v>
       </c>
       <c r="B32" t="n">
-        <v>83012</v>
+        <v>79044</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3915,21 +3915,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3939,10 +3939,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>540931</v>
+        <v>540928</v>
       </c>
       <c r="R32" t="n">
-        <v>7193220</v>
+        <v>7193263</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4118,7 +4118,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129319396</v>
+        <v>129319282</v>
       </c>
       <c r="B34" t="n">
         <v>79044</v>
@@ -4153,10 +4153,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>540928</v>
+        <v>540901</v>
       </c>
       <c r="R34" t="n">
-        <v>7193263</v>
+        <v>7193084</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4225,10 +4225,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129319282</v>
+        <v>129319405</v>
       </c>
       <c r="B35" t="n">
-        <v>79044</v>
+        <v>83012</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4236,21 +4236,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4260,10 +4260,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>540901</v>
+        <v>540931</v>
       </c>
       <c r="R35" t="n">
-        <v>7193084</v>
+        <v>7193220</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4295,7 +4295,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4305,7 +4305,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4332,10 +4332,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129319337</v>
+        <v>129319377</v>
       </c>
       <c r="B36" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4343,21 +4343,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4367,10 +4367,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>540676</v>
+        <v>540745</v>
       </c>
       <c r="R36" t="n">
-        <v>7193539</v>
+        <v>7193494</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4402,7 +4402,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4439,32 +4439,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129319422</v>
+        <v>129319374</v>
       </c>
       <c r="B37" t="n">
-        <v>80184</v>
+        <v>80150</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4474,10 +4474,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>540980</v>
+        <v>540734</v>
       </c>
       <c r="R37" t="n">
-        <v>7193139</v>
+        <v>7193499</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4546,10 +4546,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129319374</v>
+        <v>129319404</v>
       </c>
       <c r="B38" t="n">
-        <v>80150</v>
+        <v>78057</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4557,21 +4557,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>228579</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>540734</v>
+        <v>540931</v>
       </c>
       <c r="R38" t="n">
-        <v>7193499</v>
+        <v>7193220</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4653,32 +4653,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129319377</v>
+        <v>129319422</v>
       </c>
       <c r="B39" t="n">
-        <v>80150</v>
+        <v>80184</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4688,10 +4688,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>540745</v>
+        <v>540980</v>
       </c>
       <c r="R39" t="n">
-        <v>7193494</v>
+        <v>7193139</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4760,10 +4760,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129319278</v>
+        <v>129319348</v>
       </c>
       <c r="B40" t="n">
-        <v>80150</v>
+        <v>80149</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4771,21 +4771,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>540864</v>
+        <v>540653</v>
       </c>
       <c r="R40" t="n">
-        <v>7193066</v>
+        <v>7193521</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4840,7 +4840,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4867,32 +4867,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129319365</v>
+        <v>129319401</v>
       </c>
       <c r="B41" t="n">
-        <v>80150</v>
+        <v>80178</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>540738</v>
+        <v>540942</v>
       </c>
       <c r="R41" t="n">
-        <v>7193503</v>
+        <v>7193229</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4947,7 +4947,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4974,10 +4974,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129319294</v>
+        <v>129319403</v>
       </c>
       <c r="B42" t="n">
-        <v>83017</v>
+        <v>80149</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4985,21 +4985,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1467</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5009,10 +5009,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>540974</v>
+        <v>540930</v>
       </c>
       <c r="R42" t="n">
-        <v>7193351</v>
+        <v>7193219</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5081,32 +5081,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129319348</v>
+        <v>129319320</v>
       </c>
       <c r="B43" t="n">
-        <v>80149</v>
+        <v>80184</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5116,10 +5116,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540653</v>
+        <v>540719</v>
       </c>
       <c r="R43" t="n">
-        <v>7193521</v>
+        <v>7193463</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5188,10 +5188,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129319401</v>
+        <v>129319395</v>
       </c>
       <c r="B44" t="n">
-        <v>80178</v>
+        <v>82997</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5199,21 +5199,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6462</v>
+        <v>306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540942</v>
+        <v>540878</v>
       </c>
       <c r="R44" t="n">
-        <v>7193229</v>
+        <v>7193291</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5295,10 +5295,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129319403</v>
+        <v>129319303</v>
       </c>
       <c r="B45" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5306,21 +5306,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5330,10 +5330,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>540930</v>
+        <v>540934</v>
       </c>
       <c r="R45" t="n">
-        <v>7193219</v>
+        <v>7193385</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5365,7 +5365,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5375,7 +5375,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5402,27 +5402,27 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129319320</v>
+        <v>129319288</v>
       </c>
       <c r="B46" t="n">
-        <v>80184</v>
+        <v>79044</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5437,10 +5437,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>540719</v>
+        <v>540915</v>
       </c>
       <c r="R46" t="n">
-        <v>7193463</v>
+        <v>7193185</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5472,7 +5472,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5509,32 +5509,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129319395</v>
+        <v>129319278</v>
       </c>
       <c r="B47" t="n">
-        <v>82997</v>
+        <v>80150</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>306</v>
+        <v>2081</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5544,10 +5544,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>540878</v>
+        <v>540864</v>
       </c>
       <c r="R47" t="n">
-        <v>7193291</v>
+        <v>7193066</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5579,7 +5579,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5616,10 +5616,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129319303</v>
+        <v>129319294</v>
       </c>
       <c r="B48" t="n">
-        <v>79044</v>
+        <v>83017</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5627,21 +5627,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5651,10 +5651,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>540934</v>
+        <v>540974</v>
       </c>
       <c r="R48" t="n">
-        <v>7193385</v>
+        <v>7193351</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5686,7 +5686,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5723,10 +5723,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129319288</v>
+        <v>129319365</v>
       </c>
       <c r="B49" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5734,21 +5734,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>540915</v>
+        <v>540738</v>
       </c>
       <c r="R49" t="n">
-        <v>7193185</v>
+        <v>7193503</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5830,32 +5830,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129319366</v>
+        <v>129319280</v>
       </c>
       <c r="B50" t="n">
-        <v>80149</v>
+        <v>95953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>2809</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5865,10 +5865,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>540738</v>
+        <v>540900</v>
       </c>
       <c r="R50" t="n">
-        <v>7193503</v>
+        <v>7193073</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5900,7 +5900,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5910,7 +5910,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5937,10 +5937,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129319356</v>
+        <v>129319335</v>
       </c>
       <c r="B51" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5948,21 +5948,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5972,10 +5972,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>540726</v>
+        <v>540655</v>
       </c>
       <c r="R51" t="n">
-        <v>7193540</v>
+        <v>7193534</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6044,10 +6044,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129319335</v>
+        <v>129319366</v>
       </c>
       <c r="B52" t="n">
-        <v>80150</v>
+        <v>80149</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6055,21 +6055,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6079,10 +6079,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>540655</v>
+        <v>540738</v>
       </c>
       <c r="R52" t="n">
-        <v>7193534</v>
+        <v>7193503</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6124,7 +6124,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6151,32 +6151,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129319280</v>
+        <v>129319356</v>
       </c>
       <c r="B53" t="n">
-        <v>95950</v>
+        <v>80149</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2809</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6186,10 +6186,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>540900</v>
+        <v>540726</v>
       </c>
       <c r="R53" t="n">
-        <v>7193073</v>
+        <v>7193540</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6221,7 +6221,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6258,10 +6258,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129319388</v>
+        <v>129319304</v>
       </c>
       <c r="B54" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6269,48 +6269,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>540828</v>
+        <v>540962</v>
       </c>
       <c r="R54" t="n">
-        <v>7193425</v>
+        <v>7193388</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6342,7 +6328,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6352,7 +6338,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6593,10 +6579,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129319304</v>
+        <v>129319388</v>
       </c>
       <c r="B57" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6604,34 +6590,48 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>540962</v>
+        <v>540828</v>
       </c>
       <c r="R57" t="n">
-        <v>7193388</v>
+        <v>7193425</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6673,7 +6673,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6700,10 +6700,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129319353</v>
+        <v>129319311</v>
       </c>
       <c r="B58" t="n">
-        <v>82878</v>
+        <v>91549</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6711,21 +6711,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6735,10 +6735,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>540721</v>
+        <v>540830</v>
       </c>
       <c r="R58" t="n">
-        <v>7193542</v>
+        <v>7193366</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6807,32 +6807,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129319279</v>
+        <v>129319330</v>
       </c>
       <c r="B59" t="n">
-        <v>80150</v>
+        <v>82995</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2081</v>
+        <v>6439</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6842,10 +6842,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>540872</v>
+        <v>540683</v>
       </c>
       <c r="R59" t="n">
-        <v>7193070</v>
+        <v>7193545</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6877,7 +6877,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7021,32 +7021,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129319330</v>
+        <v>129319392</v>
       </c>
       <c r="B61" t="n">
-        <v>82995</v>
+        <v>79044</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7056,10 +7056,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>540683</v>
+        <v>540826</v>
       </c>
       <c r="R61" t="n">
-        <v>7193545</v>
+        <v>7193294</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7091,7 +7091,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7128,10 +7128,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129319392</v>
+        <v>129319339</v>
       </c>
       <c r="B62" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7139,21 +7139,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7163,10 +7163,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>540826</v>
+        <v>540669</v>
       </c>
       <c r="R62" t="n">
-        <v>7193294</v>
+        <v>7193542</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7208,7 +7208,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7235,54 +7235,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129319423</v>
+        <v>129319353</v>
       </c>
       <c r="B63" t="n">
-        <v>57831</v>
+        <v>82878</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103031</v>
+        <v>1312</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>540976</v>
+        <v>540721</v>
       </c>
       <c r="R63" t="n">
-        <v>7193139</v>
+        <v>7193542</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7314,7 +7305,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7324,7 +7315,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7351,7 +7342,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129319339</v>
+        <v>129319279</v>
       </c>
       <c r="B64" t="n">
         <v>80150</v>
@@ -7386,10 +7377,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>540669</v>
+        <v>540872</v>
       </c>
       <c r="R64" t="n">
-        <v>7193542</v>
+        <v>7193070</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7421,7 +7412,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7431,7 +7422,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7458,45 +7449,54 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129319311</v>
+        <v>129319423</v>
       </c>
       <c r="B65" t="n">
-        <v>91546</v>
+        <v>57831</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1108</v>
+        <v>103031</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>540830</v>
+        <v>540976</v>
       </c>
       <c r="R65" t="n">
-        <v>7193366</v>
+        <v>7193139</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7528,7 +7528,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7672,7 +7672,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129319400</v>
+        <v>129319397</v>
       </c>
       <c r="B67" t="n">
         <v>79044</v>
@@ -7707,10 +7707,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>540943</v>
+        <v>540946</v>
       </c>
       <c r="R67" t="n">
-        <v>7193233</v>
+        <v>7193256</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7742,7 +7742,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7752,7 +7752,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7779,10 +7779,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129319397</v>
+        <v>129319334</v>
       </c>
       <c r="B68" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7790,21 +7790,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7814,10 +7814,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>540946</v>
+        <v>540674</v>
       </c>
       <c r="R68" t="n">
-        <v>7193256</v>
+        <v>7193550</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7849,7 +7849,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7859,7 +7859,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7886,32 +7886,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129319421</v>
+        <v>129319400</v>
       </c>
       <c r="B69" t="n">
-        <v>80178</v>
+        <v>79044</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7921,10 +7921,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>540981</v>
+        <v>540943</v>
       </c>
       <c r="R69" t="n">
-        <v>7193140</v>
+        <v>7193233</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7956,7 +7956,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7966,7 +7966,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7993,10 +7993,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129319334</v>
+        <v>129319293</v>
       </c>
       <c r="B70" t="n">
-        <v>80149</v>
+        <v>57887</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8004,34 +8004,43 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>540674</v>
+        <v>540980</v>
       </c>
       <c r="R70" t="n">
-        <v>7193550</v>
+        <v>7193345</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8063,7 +8072,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8073,7 +8082,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8100,7 +8109,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129319370</v>
+        <v>129319421</v>
       </c>
       <c r="B71" t="n">
         <v>80178</v>
@@ -8135,10 +8144,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>540737</v>
+        <v>540981</v>
       </c>
       <c r="R71" t="n">
-        <v>7193504</v>
+        <v>7193140</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8170,7 +8179,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8180,7 +8189,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8207,54 +8216,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129319293</v>
+        <v>129319370</v>
       </c>
       <c r="B72" t="n">
-        <v>57887</v>
+        <v>80178</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>540980</v>
+        <v>540737</v>
       </c>
       <c r="R72" t="n">
-        <v>7193345</v>
+        <v>7193504</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8286,7 +8286,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8323,7 +8323,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129319413</v>
+        <v>129319402</v>
       </c>
       <c r="B73" t="n">
         <v>79044</v>
@@ -8358,10 +8358,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>540965</v>
+        <v>540936</v>
       </c>
       <c r="R73" t="n">
-        <v>7193181</v>
+        <v>7193225</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8393,7 +8393,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8403,7 +8403,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8430,7 +8430,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129319402</v>
+        <v>129319413</v>
       </c>
       <c r="B74" t="n">
         <v>79044</v>
@@ -8465,10 +8465,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>540936</v>
+        <v>540965</v>
       </c>
       <c r="R74" t="n">
-        <v>7193225</v>
+        <v>7193181</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8500,7 +8500,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8510,7 +8510,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8537,34 +8537,30 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129319367</v>
+        <v>129319412</v>
       </c>
       <c r="B75" t="n">
-        <v>80178</v>
+        <v>91573</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -8572,10 +8568,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>540734</v>
+        <v>540952</v>
       </c>
       <c r="R75" t="n">
-        <v>7193503</v>
+        <v>7193187</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8607,7 +8603,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8617,7 +8613,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8644,30 +8640,34 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129319412</v>
+        <v>129319367</v>
       </c>
       <c r="B76" t="n">
-        <v>91570</v>
+        <v>80178</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr"/>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -8675,10 +8675,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>540952</v>
+        <v>540734</v>
       </c>
       <c r="R76" t="n">
-        <v>7193187</v>
+        <v>7193503</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8710,7 +8710,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8720,7 +8720,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9082,10 +9082,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129319338</v>
+        <v>129319336</v>
       </c>
       <c r="B80" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9093,21 +9093,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9117,10 +9117,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>540676</v>
+        <v>540668</v>
       </c>
       <c r="R80" t="n">
-        <v>7193539</v>
+        <v>7193543</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9152,7 +9152,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9162,7 +9162,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9296,7 +9296,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129319336</v>
+        <v>129319394</v>
       </c>
       <c r="B82" t="n">
         <v>79044</v>
@@ -9331,10 +9331,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>540668</v>
+        <v>540877</v>
       </c>
       <c r="R82" t="n">
-        <v>7193543</v>
+        <v>7193291</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9366,7 +9366,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9376,7 +9376,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9403,10 +9403,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129319394</v>
+        <v>129319338</v>
       </c>
       <c r="B83" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9414,21 +9414,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9438,10 +9438,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>540877</v>
+        <v>540676</v>
       </c>
       <c r="R83" t="n">
-        <v>7193291</v>
+        <v>7193539</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9473,7 +9473,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9483,7 +9483,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9724,10 +9724,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129319299</v>
+        <v>129319298</v>
       </c>
       <c r="B86" t="n">
-        <v>79044</v>
+        <v>91573</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9735,23 +9735,19 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -10045,7 +10041,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129319344</v>
+        <v>129319299</v>
       </c>
       <c r="B89" t="n">
         <v>79044</v>
@@ -10080,10 +10076,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>540650</v>
+        <v>540964</v>
       </c>
       <c r="R89" t="n">
-        <v>7193540</v>
+        <v>7193371</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -10115,7 +10111,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10125,7 +10121,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10152,10 +10148,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129319298</v>
+        <v>129319344</v>
       </c>
       <c r="B90" t="n">
-        <v>91570</v>
+        <v>79044</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10163,19 +10159,23 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
@@ -10183,10 +10183,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>540964</v>
+        <v>540650</v>
       </c>
       <c r="R90" t="n">
-        <v>7193371</v>
+        <v>7193540</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -10218,7 +10218,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10255,7 +10255,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129319333</v>
+        <v>129319375</v>
       </c>
       <c r="B91" t="n">
         <v>80150</v>
@@ -10290,10 +10290,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>540674</v>
+        <v>540730</v>
       </c>
       <c r="R91" t="n">
-        <v>7193551</v>
+        <v>7193493</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -10325,7 +10325,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10335,7 +10335,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10362,7 +10362,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129319376</v>
+        <v>129319333</v>
       </c>
       <c r="B92" t="n">
         <v>80150</v>
@@ -10397,10 +10397,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>540738</v>
+        <v>540674</v>
       </c>
       <c r="R92" t="n">
-        <v>7193476</v>
+        <v>7193551</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -10432,7 +10432,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10442,7 +10442,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10469,7 +10469,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129319375</v>
+        <v>129319376</v>
       </c>
       <c r="B93" t="n">
         <v>80150</v>
@@ -10504,10 +10504,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>540730</v>
+        <v>540738</v>
       </c>
       <c r="R93" t="n">
-        <v>7193493</v>
+        <v>7193476</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -10539,7 +10539,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10549,7 +10549,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10793,7 +10793,7 @@
         <v>129319389</v>
       </c>
       <c r="B96" t="n">
-        <v>95950</v>
+        <v>95953</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11218,7 +11218,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129319286</v>
+        <v>129319362</v>
       </c>
       <c r="B100" t="n">
         <v>79044</v>
@@ -11253,10 +11253,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>540891</v>
+        <v>540721</v>
       </c>
       <c r="R100" t="n">
-        <v>7193174</v>
+        <v>7193527</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -11288,7 +11288,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11298,7 +11298,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11325,7 +11325,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129319362</v>
+        <v>129319306</v>
       </c>
       <c r="B101" t="n">
         <v>79044</v>
@@ -11360,10 +11360,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>540721</v>
+        <v>540961</v>
       </c>
       <c r="R101" t="n">
-        <v>7193527</v>
+        <v>7193398</v>
       </c>
       <c r="S101" t="n">
         <v>25</v>
@@ -11395,7 +11395,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11405,7 +11405,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11432,7 +11432,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129319306</v>
+        <v>129319286</v>
       </c>
       <c r="B102" t="n">
         <v>79044</v>
@@ -11467,10 +11467,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>540961</v>
+        <v>540891</v>
       </c>
       <c r="R102" t="n">
-        <v>7193398</v>
+        <v>7193174</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -11502,7 +11502,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11512,7 +11512,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11539,10 +11539,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129319359</v>
+        <v>129319445</v>
       </c>
       <c r="B103" t="n">
-        <v>80149</v>
+        <v>57724</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11550,34 +11550,43 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>540725</v>
+        <v>541052</v>
       </c>
       <c r="R103" t="n">
-        <v>7193537</v>
+        <v>7193255</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -11609,7 +11618,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11619,7 +11628,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11646,10 +11655,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129319445</v>
+        <v>129319359</v>
       </c>
       <c r="B104" t="n">
-        <v>57724</v>
+        <v>80149</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11657,43 +11666,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Valklinten, Ås lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>541052</v>
+        <v>540725</v>
       </c>
       <c r="R104" t="n">
-        <v>7193255</v>
+        <v>7193537</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -11725,7 +11725,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11735,7 +11735,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11762,10 +11762,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129319355</v>
+        <v>129319411</v>
       </c>
       <c r="B105" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11773,21 +11773,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11797,10 +11797,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>540726</v>
+        <v>540955</v>
       </c>
       <c r="R105" t="n">
-        <v>7193541</v>
+        <v>7193186</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -11832,7 +11832,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11842,7 +11842,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11869,10 +11869,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129319360</v>
+        <v>129319407</v>
       </c>
       <c r="B106" t="n">
-        <v>91546</v>
+        <v>79044</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11880,21 +11880,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11904,10 +11904,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>540725</v>
+        <v>540924</v>
       </c>
       <c r="R106" t="n">
-        <v>7193532</v>
+        <v>7193211</v>
       </c>
       <c r="S106" t="n">
         <v>25</v>
@@ -11939,7 +11939,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11949,7 +11949,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11976,7 +11976,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129319369</v>
+        <v>129319391</v>
       </c>
       <c r="B107" t="n">
         <v>80150</v>
@@ -12011,10 +12011,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>540734</v>
+        <v>540818</v>
       </c>
       <c r="R107" t="n">
-        <v>7193503</v>
+        <v>7193333</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -12046,7 +12046,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12056,7 +12056,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12083,7 +12083,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129319391</v>
+        <v>129319355</v>
       </c>
       <c r="B108" t="n">
         <v>80150</v>
@@ -12118,10 +12118,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>540818</v>
+        <v>540726</v>
       </c>
       <c r="R108" t="n">
-        <v>7193333</v>
+        <v>7193541</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -12153,7 +12153,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12163,7 +12163,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12190,10 +12190,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129319411</v>
+        <v>129319369</v>
       </c>
       <c r="B109" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12201,21 +12201,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12225,10 +12225,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>540955</v>
+        <v>540734</v>
       </c>
       <c r="R109" t="n">
-        <v>7193186</v>
+        <v>7193503</v>
       </c>
       <c r="S109" t="n">
         <v>25</v>
@@ -12260,7 +12260,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12270,7 +12270,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12297,10 +12297,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129319407</v>
+        <v>129319360</v>
       </c>
       <c r="B110" t="n">
-        <v>79044</v>
+        <v>91549</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12308,21 +12308,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12332,10 +12332,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>540924</v>
+        <v>540725</v>
       </c>
       <c r="R110" t="n">
-        <v>7193211</v>
+        <v>7193532</v>
       </c>
       <c r="S110" t="n">
         <v>25</v>
@@ -12367,7 +12367,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12377,7 +12377,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>10:33</t>
+          